--- a/outputs/forecast_zhvi_by_tract.xlsx
+++ b/outputs/forecast_zhvi_by_tract.xlsx
@@ -412,7 +412,7 @@
         <v>2026</v>
       </c>
       <c r="D4">
-        <v>303864.5921946415</v>
+        <v>278415.3311344833</v>
       </c>
     </row>
     <row r="5">
@@ -425,7 +425,7 @@
         <v>2027</v>
       </c>
       <c r="D5">
-        <v>331734.3832042146</v>
+        <v>303871.8456027544</v>
       </c>
     </row>
     <row r="6">
@@ -438,7 +438,7 @@
         <v>2028</v>
       </c>
       <c r="D6">
-        <v>362163.2416684655</v>
+        <v>331735.2722038388</v>
       </c>
     </row>
     <row r="7">
@@ -477,7 +477,7 @@
         <v>2026</v>
       </c>
       <c r="D9">
-        <v>393824.3812634929</v>
+        <v>366563.4106603409</v>
       </c>
     </row>
     <row r="10">
@@ -490,7 +490,7 @@
         <v>2027</v>
       </c>
       <c r="D10">
-        <v>423122.512403396</v>
+        <v>393824.6579744138</v>
       </c>
     </row>
     <row r="11">
@@ -503,7 +503,7 @@
         <v>2028</v>
       </c>
       <c r="D11">
-        <v>454600.2777665221</v>
+        <v>423122.5223383044</v>
       </c>
     </row>
     <row r="12">
@@ -542,7 +542,7 @@
         <v>2026</v>
       </c>
       <c r="D14">
-        <v>393824.3812634929</v>
+        <v>366563.4106603409</v>
       </c>
     </row>
     <row r="15">
@@ -555,7 +555,7 @@
         <v>2027</v>
       </c>
       <c r="D15">
-        <v>423122.512403396</v>
+        <v>393824.6579744138</v>
       </c>
     </row>
     <row r="16">
@@ -568,7 +568,7 @@
         <v>2028</v>
       </c>
       <c r="D16">
-        <v>454600.2777665221</v>
+        <v>423122.5223383044</v>
       </c>
     </row>
     <row r="17">
@@ -607,7 +607,7 @@
         <v>2026</v>
       </c>
       <c r="D19">
-        <v>393824.3812634929</v>
+        <v>366563.4106603409</v>
       </c>
     </row>
     <row r="20">
@@ -620,7 +620,7 @@
         <v>2027</v>
       </c>
       <c r="D20">
-        <v>423122.512403396</v>
+        <v>393824.6579744138</v>
       </c>
     </row>
     <row r="21">
@@ -633,7 +633,7 @@
         <v>2028</v>
       </c>
       <c r="D21">
-        <v>454600.2777665221</v>
+        <v>423122.5223383044</v>
       </c>
     </row>
     <row r="22">
@@ -672,7 +672,7 @@
         <v>2026</v>
       </c>
       <c r="D24">
-        <v>393824.3812634929</v>
+        <v>366563.4106603409</v>
       </c>
     </row>
     <row r="25">
@@ -685,7 +685,7 @@
         <v>2027</v>
       </c>
       <c r="D25">
-        <v>423122.512403396</v>
+        <v>393824.6579744138</v>
       </c>
     </row>
     <row r="26">
@@ -698,7 +698,7 @@
         <v>2028</v>
       </c>
       <c r="D26">
-        <v>454600.2777665221</v>
+        <v>423122.5223383044</v>
       </c>
     </row>
     <row r="27">
@@ -737,7 +737,7 @@
         <v>2026</v>
       </c>
       <c r="D29">
-        <v>393824.3812634929</v>
+        <v>366563.4106603409</v>
       </c>
     </row>
     <row r="30">
@@ -750,7 +750,7 @@
         <v>2027</v>
       </c>
       <c r="D30">
-        <v>423122.512403396</v>
+        <v>393824.6579744138</v>
       </c>
     </row>
     <row r="31">
@@ -763,7 +763,7 @@
         <v>2028</v>
       </c>
       <c r="D31">
-        <v>454600.2777665221</v>
+        <v>423122.5223383044</v>
       </c>
     </row>
     <row r="32">
@@ -802,7 +802,7 @@
         <v>2026</v>
       </c>
       <c r="D34">
-        <v>377215.8042992281</v>
+        <v>348851.8338514452</v>
       </c>
     </row>
     <row r="35">
@@ -815,7 +815,7 @@
         <v>2027</v>
       </c>
       <c r="D35">
-        <v>408147.9651275449</v>
+        <v>377251.1855309155</v>
       </c>
     </row>
     <row r="36">
@@ -828,7 +828,7 @@
         <v>2028</v>
       </c>
       <c r="D36">
-        <v>441648.9056093694</v>
+        <v>408157.9169207505</v>
       </c>
     </row>
     <row r="37">
@@ -867,7 +867,7 @@
         <v>2026</v>
       </c>
       <c r="D39">
-        <v>377215.8042992281</v>
+        <v>348851.8338514452</v>
       </c>
     </row>
     <row r="40">
@@ -880,7 +880,7 @@
         <v>2027</v>
       </c>
       <c r="D40">
-        <v>408147.9651275449</v>
+        <v>377251.1855309155</v>
       </c>
     </row>
     <row r="41">
@@ -893,7 +893,7 @@
         <v>2028</v>
       </c>
       <c r="D41">
-        <v>441648.9056093694</v>
+        <v>408157.9169207505</v>
       </c>
     </row>
     <row r="42">
@@ -932,7 +932,7 @@
         <v>2026</v>
       </c>
       <c r="D44">
-        <v>324660.0782210762</v>
+        <v>300512.6650659974</v>
       </c>
     </row>
     <row r="45">
@@ -945,7 +945,7 @@
         <v>2027</v>
       </c>
       <c r="D45">
-        <v>351013.7532750868</v>
+        <v>324689.5169400455</v>
       </c>
     </row>
     <row r="46">
@@ -958,7 +958,7 @@
         <v>2028</v>
       </c>
       <c r="D46">
-        <v>379525.9046725636</v>
+        <v>351019.6930269767</v>
       </c>
     </row>
     <row r="47">
@@ -997,7 +997,7 @@
         <v>2026</v>
       </c>
       <c r="D49">
-        <v>377215.8042992281</v>
+        <v>348851.8338514452</v>
       </c>
     </row>
     <row r="50">
@@ -1010,7 +1010,7 @@
         <v>2027</v>
       </c>
       <c r="D50">
-        <v>408147.9651275449</v>
+        <v>377251.1855309155</v>
       </c>
     </row>
     <row r="51">
@@ -1023,7 +1023,7 @@
         <v>2028</v>
       </c>
       <c r="D51">
-        <v>441648.9056093694</v>
+        <v>408157.9169207505</v>
       </c>
     </row>
     <row r="52">
@@ -1062,7 +1062,7 @@
         <v>2026</v>
       </c>
       <c r="D54">
-        <v>272173.5507725673</v>
+        <v>247645.1172390108</v>
       </c>
     </row>
     <row r="55">
@@ -1075,7 +1075,7 @@
         <v>2027</v>
       </c>
       <c r="D55">
-        <v>299131.4631912823</v>
+        <v>272173.5507439406</v>
       </c>
     </row>
     <row r="56">
@@ -1088,7 +1088,7 @@
         <v>2028</v>
       </c>
       <c r="D56">
-        <v>328759.4698934448</v>
+        <v>299131.463191336</v>
       </c>
     </row>
     <row r="57">
@@ -1127,7 +1127,7 @@
         <v>2026</v>
       </c>
       <c r="D59">
-        <v>353458.7754253999</v>
+        <v>325778.963420152</v>
       </c>
     </row>
     <row r="60">
@@ -1140,7 +1140,7 @@
         <v>2027</v>
       </c>
       <c r="D60">
-        <v>383514.3190203005</v>
+        <v>353459.6597509771</v>
       </c>
     </row>
     <row r="61">
@@ -1153,7 +1153,7 @@
         <v>2028</v>
       </c>
       <c r="D61">
-        <v>416125.7082008488</v>
+        <v>383514.3627823247</v>
       </c>
     </row>
     <row r="62">
@@ -1192,7 +1192,7 @@
         <v>2026</v>
       </c>
       <c r="D64">
-        <v>271919.6816277375</v>
+        <v>247295.1784669193</v>
       </c>
     </row>
     <row r="65">
@@ -1205,7 +1205,7 @@
         <v>2027</v>
       </c>
       <c r="D65">
-        <v>298996.3825409782</v>
+        <v>271919.6805486455</v>
       </c>
     </row>
     <row r="66">
@@ -1218,7 +1218,7 @@
         <v>2028</v>
       </c>
       <c r="D66">
-        <v>328769.2757049291</v>
+        <v>298996.3825477516</v>
       </c>
     </row>
     <row r="67">
@@ -1257,7 +1257,7 @@
         <v>2026</v>
       </c>
       <c r="D69">
-        <v>271818.1037353462</v>
+        <v>247301.3626374819</v>
       </c>
     </row>
     <row r="70">
@@ -1270,7 +1270,7 @@
         <v>2027</v>
       </c>
       <c r="D70">
-        <v>298765.3918417389</v>
+        <v>271818.1036801805</v>
       </c>
     </row>
     <row r="71">
@@ -1283,7 +1283,7 @@
         <v>2028</v>
       </c>
       <c r="D71">
-        <v>328384.1588762314</v>
+        <v>298765.3918418684</v>
       </c>
     </row>
     <row r="72">
@@ -1322,7 +1322,7 @@
         <v>2026</v>
       </c>
       <c r="D74">
-        <v>470254.5105612233</v>
+        <v>441289.8530637257</v>
       </c>
     </row>
     <row r="75">
@@ -1335,7 +1335,7 @@
         <v>2027</v>
       </c>
       <c r="D75">
-        <v>501695.6362554573</v>
+        <v>470331.9281969927</v>
       </c>
     </row>
     <row r="76">
@@ -1348,7 +1348,7 @@
         <v>2028</v>
       </c>
       <c r="D76">
-        <v>535305.487942569</v>
+        <v>501716.4373780646</v>
       </c>
     </row>
     <row r="77">
@@ -1387,7 +1387,7 @@
         <v>2026</v>
       </c>
       <c r="D79">
-        <v>472095.5726504429</v>
+        <v>443088.9510598898</v>
       </c>
     </row>
     <row r="80">
@@ -1400,7 +1400,7 @@
         <v>2027</v>
       </c>
       <c r="D80">
-        <v>503581.1991800835</v>
+        <v>472173.8158483912</v>
       </c>
     </row>
     <row r="81">
@@ -1413,7 +1413,7 @@
         <v>2028</v>
       </c>
       <c r="D81">
-        <v>537234.2348224048</v>
+        <v>503602.3002011494</v>
       </c>
     </row>
     <row r="82">
@@ -1452,7 +1452,7 @@
         <v>2026</v>
       </c>
       <c r="D84">
-        <v>338674.3064026155</v>
+        <v>311824.0560333859</v>
       </c>
     </row>
     <row r="85">
@@ -1465,7 +1465,7 @@
         <v>2027</v>
       </c>
       <c r="D85">
-        <v>367965.2193650494</v>
+        <v>338684.8879635837</v>
       </c>
     </row>
     <row r="86">
@@ -1478,7 +1478,7 @@
         <v>2028</v>
       </c>
       <c r="D86">
-        <v>399793.9878487976</v>
+        <v>367966.6224599352</v>
       </c>
     </row>
     <row r="87">
@@ -1517,7 +1517,7 @@
         <v>2026</v>
       </c>
       <c r="D89">
-        <v>338674.3064026155</v>
+        <v>311824.0560333859</v>
       </c>
     </row>
     <row r="90">
@@ -1530,7 +1530,7 @@
         <v>2027</v>
       </c>
       <c r="D90">
-        <v>367965.2193650494</v>
+        <v>338684.8879635837</v>
       </c>
     </row>
     <row r="91">
@@ -1543,7 +1543,7 @@
         <v>2028</v>
       </c>
       <c r="D91">
-        <v>399793.9878487976</v>
+        <v>367966.6224599352</v>
       </c>
     </row>
     <row r="92">
@@ -1582,7 +1582,7 @@
         <v>2026</v>
       </c>
       <c r="D94">
-        <v>313232.7355075887</v>
+        <v>287523.0002731558</v>
       </c>
     </row>
     <row r="95">
@@ -1595,7 +1595,7 @@
         <v>2027</v>
       </c>
       <c r="D95">
-        <v>341531.4991818194</v>
+        <v>313264.8006110343</v>
       </c>
     </row>
     <row r="96">
@@ -1608,7 +1608,7 @@
         <v>2028</v>
       </c>
       <c r="D96">
-        <v>372408.4615176573</v>
+        <v>341538.0930719335</v>
       </c>
     </row>
     <row r="97">
@@ -1647,7 +1647,7 @@
         <v>2026</v>
       </c>
       <c r="D99">
-        <v>313232.7355075887</v>
+        <v>287523.0002731558</v>
       </c>
     </row>
     <row r="100">
@@ -1660,7 +1660,7 @@
         <v>2027</v>
       </c>
       <c r="D100">
-        <v>341531.4991818194</v>
+        <v>313264.8006110343</v>
       </c>
     </row>
     <row r="101">
@@ -1673,7 +1673,7 @@
         <v>2028</v>
       </c>
       <c r="D101">
-        <v>372408.4615176573</v>
+        <v>341538.0930719335</v>
       </c>
     </row>
     <row r="102">
@@ -1712,7 +1712,7 @@
         <v>2026</v>
       </c>
       <c r="D104">
-        <v>338674.3064026155</v>
+        <v>311824.0560333859</v>
       </c>
     </row>
     <row r="105">
@@ -1725,7 +1725,7 @@
         <v>2027</v>
       </c>
       <c r="D105">
-        <v>367965.2193650494</v>
+        <v>338684.8879635837</v>
       </c>
     </row>
     <row r="106">
@@ -1738,7 +1738,7 @@
         <v>2028</v>
       </c>
       <c r="D106">
-        <v>399793.9878487976</v>
+        <v>367966.6224599352</v>
       </c>
     </row>
     <row r="107">
@@ -1777,7 +1777,7 @@
         <v>2026</v>
       </c>
       <c r="D109">
-        <v>313232.7354296903</v>
+        <v>287523.0002169756</v>
       </c>
     </row>
     <row r="110">
@@ -1790,7 +1790,7 @@
         <v>2027</v>
       </c>
       <c r="D110">
-        <v>341531.4990846733</v>
+        <v>313264.8005339944</v>
       </c>
     </row>
     <row r="111">
@@ -1803,7 +1803,7 @@
         <v>2028</v>
       </c>
       <c r="D111">
-        <v>372408.4613992129</v>
+        <v>341538.0929750294</v>
       </c>
     </row>
     <row r="112">
@@ -1842,7 +1842,7 @@
         <v>2026</v>
       </c>
       <c r="D114">
-        <v>338674.3064026155</v>
+        <v>311824.0560333859</v>
       </c>
     </row>
     <row r="115">
@@ -1855,7 +1855,7 @@
         <v>2027</v>
       </c>
       <c r="D115">
-        <v>367965.2193650494</v>
+        <v>338684.8879635837</v>
       </c>
     </row>
     <row r="116">
@@ -1868,7 +1868,7 @@
         <v>2028</v>
       </c>
       <c r="D116">
-        <v>399793.9878487976</v>
+        <v>367966.6224599352</v>
       </c>
     </row>
     <row r="117">
@@ -1907,7 +1907,7 @@
         <v>2026</v>
       </c>
       <c r="D119">
-        <v>338674.3064026155</v>
+        <v>311824.0560333859</v>
       </c>
     </row>
     <row r="120">
@@ -1920,7 +1920,7 @@
         <v>2027</v>
       </c>
       <c r="D120">
-        <v>367965.2193650494</v>
+        <v>338684.8879635837</v>
       </c>
     </row>
     <row r="121">
@@ -1933,7 +1933,7 @@
         <v>2028</v>
       </c>
       <c r="D121">
-        <v>399793.9878487976</v>
+        <v>367966.6224599352</v>
       </c>
     </row>
     <row r="122">
@@ -1972,7 +1972,7 @@
         <v>2026</v>
       </c>
       <c r="D124">
-        <v>303864.5921946415</v>
+        <v>278415.3311344833</v>
       </c>
     </row>
     <row r="125">
@@ -1985,7 +1985,7 @@
         <v>2027</v>
       </c>
       <c r="D125">
-        <v>331734.3832042146</v>
+        <v>303871.8456027544</v>
       </c>
     </row>
     <row r="126">
@@ -1998,7 +1998,7 @@
         <v>2028</v>
       </c>
       <c r="D126">
-        <v>362163.2416684655</v>
+        <v>331735.2722038388</v>
       </c>
     </row>
     <row r="127">
@@ -2037,7 +2037,7 @@
         <v>2026</v>
       </c>
       <c r="D129">
-        <v>362142.5349108929</v>
+        <v>335874.3882508578</v>
       </c>
     </row>
     <row r="130">
@@ -2050,7 +2050,7 @@
         <v>2027</v>
       </c>
       <c r="D130">
-        <v>390757.342895754</v>
+        <v>362175.3469870159</v>
       </c>
     </row>
     <row r="131">
@@ -2063,7 +2063,7 @@
         <v>2028</v>
       </c>
       <c r="D131">
-        <v>421654.952243703</v>
+        <v>390764.0752071551</v>
       </c>
     </row>
     <row r="132">
@@ -2102,7 +2102,7 @@
         <v>2026</v>
       </c>
       <c r="D134">
-        <v>308744.3864057814</v>
+        <v>283650.8450274403</v>
       </c>
     </row>
     <row r="135">
@@ -2115,7 +2115,7 @@
         <v>2027</v>
       </c>
       <c r="D135">
-        <v>336190.1241662781</v>
+        <v>308755.9034308086</v>
       </c>
     </row>
     <row r="136">
@@ -2128,7 +2128,7 @@
         <v>2028</v>
       </c>
       <c r="D136">
-        <v>366081.0691920608</v>
+        <v>336191.7854160077</v>
       </c>
     </row>
     <row r="137">
@@ -2167,7 +2167,7 @@
         <v>2026</v>
       </c>
       <c r="D139">
-        <v>310349.9174415245</v>
+        <v>284694.0353213935</v>
       </c>
     </row>
     <row r="140">
@@ -2180,7 +2180,7 @@
         <v>2027</v>
       </c>
       <c r="D140">
-        <v>338431.4025530138</v>
+        <v>310359.1548938031</v>
       </c>
     </row>
     <row r="141">
@@ -2193,7 +2193,7 @@
         <v>2028</v>
       </c>
       <c r="D141">
-        <v>369057.7751885076</v>
+        <v>338432.6197592693</v>
       </c>
     </row>
     <row r="142">
@@ -2232,7 +2232,7 @@
         <v>2026</v>
       </c>
       <c r="D144">
-        <v>270914.2664060779</v>
+        <v>246709.7220193894</v>
       </c>
     </row>
     <row r="145">
@@ -2245,7 +2245,7 @@
         <v>2027</v>
       </c>
       <c r="D145">
-        <v>297567.1114660384</v>
+        <v>270919.6639445653</v>
       </c>
     </row>
     <row r="146">
@@ -2258,7 +2258,7 @@
         <v>2028</v>
       </c>
       <c r="D146">
-        <v>326844.1672825909</v>
+        <v>297567.7409946572</v>
       </c>
     </row>
     <row r="147">
@@ -2297,7 +2297,7 @@
         <v>2026</v>
       </c>
       <c r="D149">
-        <v>270914.2664060779</v>
+        <v>246709.7220193894</v>
       </c>
     </row>
     <row r="150">
@@ -2310,7 +2310,7 @@
         <v>2027</v>
       </c>
       <c r="D150">
-        <v>297567.1114660384</v>
+        <v>270919.6639445653</v>
       </c>
     </row>
     <row r="151">
@@ -2323,7 +2323,7 @@
         <v>2028</v>
       </c>
       <c r="D151">
-        <v>326844.1672825909</v>
+        <v>297567.7409946572</v>
       </c>
     </row>
     <row r="152">
@@ -2362,7 +2362,7 @@
         <v>2026</v>
       </c>
       <c r="D154">
-        <v>472095.5726504429</v>
+        <v>443088.9510598898</v>
       </c>
     </row>
     <row r="155">
@@ -2375,7 +2375,7 @@
         <v>2027</v>
       </c>
       <c r="D155">
-        <v>503581.1991800835</v>
+        <v>472173.8158483912</v>
       </c>
     </row>
     <row r="156">
@@ -2388,7 +2388,7 @@
         <v>2028</v>
       </c>
       <c r="D156">
-        <v>537234.2348224048</v>
+        <v>503602.3002011494</v>
       </c>
     </row>
     <row r="157">
@@ -2427,7 +2427,7 @@
         <v>2026</v>
       </c>
       <c r="D159">
-        <v>472010.6034654264</v>
+        <v>443005.9267907981</v>
       </c>
     </row>
     <row r="160">
@@ -2440,7 +2440,7 @@
         <v>2027</v>
       </c>
       <c r="D160">
-        <v>503494.167148654</v>
+        <v>472088.8086770794</v>
       </c>
     </row>
     <row r="161">
@@ -2453,7 +2453,7 @@
         <v>2028</v>
       </c>
       <c r="D161">
-        <v>537145.1990130919</v>
+        <v>503515.254349565</v>
       </c>
     </row>
     <row r="162">
@@ -2492,7 +2492,7 @@
         <v>2026</v>
       </c>
       <c r="D164">
-        <v>303864.5921946415</v>
+        <v>278415.3311344833</v>
       </c>
     </row>
     <row r="165">
@@ -2505,7 +2505,7 @@
         <v>2027</v>
       </c>
       <c r="D165">
-        <v>331734.3832042146</v>
+        <v>303871.8456027544</v>
       </c>
     </row>
     <row r="166">
@@ -2518,7 +2518,7 @@
         <v>2028</v>
       </c>
       <c r="D166">
-        <v>362163.2416684655</v>
+        <v>331735.2722038388</v>
       </c>
     </row>
     <row r="167">
@@ -2557,7 +2557,7 @@
         <v>2026</v>
       </c>
       <c r="D169">
-        <v>355140.5944977046</v>
+        <v>329005.8925436896</v>
       </c>
     </row>
     <row r="170">
@@ -2570,7 +2570,7 @@
         <v>2027</v>
       </c>
       <c r="D170">
-        <v>383621.1741467959</v>
+        <v>355170.1661664348</v>
       </c>
     </row>
     <row r="171">
@@ -2583,7 +2583,7 @@
         <v>2028</v>
       </c>
       <c r="D171">
-        <v>414404.7485573029</v>
+        <v>383627.0335805306</v>
       </c>
     </row>
     <row r="172">
@@ -2622,7 +2622,7 @@
         <v>2026</v>
       </c>
       <c r="D174">
-        <v>304937.9751242995</v>
+        <v>279569.8940553228</v>
       </c>
     </row>
     <row r="175">
@@ -2635,7 +2635,7 @@
         <v>2027</v>
       </c>
       <c r="D175">
-        <v>332710.2786442924</v>
+        <v>304946.0914226463</v>
       </c>
     </row>
     <row r="176">
@@ -2648,7 +2648,7 @@
         <v>2028</v>
       </c>
       <c r="D176">
-        <v>363015.338902299</v>
+        <v>332711.3134436555</v>
       </c>
     </row>
     <row r="177">
@@ -2687,7 +2687,7 @@
         <v>2026</v>
       </c>
       <c r="D179">
-        <v>270914.2664060779</v>
+        <v>246709.7220193894</v>
       </c>
     </row>
     <row r="180">
@@ -2700,7 +2700,7 @@
         <v>2027</v>
       </c>
       <c r="D180">
-        <v>297567.1114660384</v>
+        <v>270919.6639445653</v>
       </c>
     </row>
     <row r="181">
@@ -2713,7 +2713,7 @@
         <v>2028</v>
       </c>
       <c r="D181">
-        <v>326844.1672825909</v>
+        <v>297567.7409946572</v>
       </c>
     </row>
     <row r="182">
@@ -2752,7 +2752,7 @@
         <v>2026</v>
       </c>
       <c r="D184">
-        <v>270914.2664060779</v>
+        <v>246709.7220193894</v>
       </c>
     </row>
     <row r="185">
@@ -2765,7 +2765,7 @@
         <v>2027</v>
       </c>
       <c r="D185">
-        <v>297567.1114660384</v>
+        <v>270919.6639445653</v>
       </c>
     </row>
     <row r="186">
@@ -2778,7 +2778,7 @@
         <v>2028</v>
       </c>
       <c r="D186">
-        <v>326844.1672825909</v>
+        <v>297567.7409946572</v>
       </c>
     </row>
     <row r="187">
@@ -2817,7 +2817,7 @@
         <v>2026</v>
       </c>
       <c r="D189">
-        <v>309827.7317955933</v>
+        <v>284025.0312810856</v>
       </c>
     </row>
     <row r="190">
@@ -2830,7 +2830,7 @@
         <v>2027</v>
       </c>
       <c r="D190">
-        <v>338042.8908072146</v>
+        <v>309832.3625674977</v>
       </c>
     </row>
     <row r="191">
@@ -2843,7 +2843,7 @@
         <v>2028</v>
       </c>
       <c r="D191">
-        <v>368829.0966873575</v>
+        <v>338043.3704513524</v>
       </c>
     </row>
     <row r="192">
@@ -2882,7 +2882,7 @@
         <v>2026</v>
       </c>
       <c r="D194">
-        <v>270914.2664062006</v>
+        <v>246709.7220194933</v>
       </c>
     </row>
     <row r="195">
@@ -2895,7 +2895,7 @@
         <v>2027</v>
       </c>
       <c r="D195">
-        <v>297567.1114661727</v>
+        <v>270919.6639446866</v>
       </c>
     </row>
     <row r="196">
@@ -2908,7 +2908,7 @@
         <v>2028</v>
       </c>
       <c r="D196">
-        <v>326844.167282736</v>
+        <v>297567.7409947909</v>
       </c>
     </row>
     <row r="197">
@@ -2947,7 +2947,7 @@
         <v>2026</v>
       </c>
       <c r="D199">
-        <v>270914.2664060779</v>
+        <v>246709.7220193894</v>
       </c>
     </row>
     <row r="200">
@@ -2960,7 +2960,7 @@
         <v>2027</v>
       </c>
       <c r="D200">
-        <v>297567.1114660384</v>
+        <v>270919.6639445653</v>
       </c>
     </row>
     <row r="201">
@@ -2973,7 +2973,7 @@
         <v>2028</v>
       </c>
       <c r="D201">
-        <v>326844.1672825909</v>
+        <v>297567.7409946572</v>
       </c>
     </row>
     <row r="202">
@@ -3012,7 +3012,7 @@
         <v>2026</v>
       </c>
       <c r="D204">
-        <v>318160.109935311</v>
+        <v>291996.3805548427</v>
       </c>
     </row>
     <row r="205">
@@ -3025,7 +3025,7 @@
         <v>2027</v>
       </c>
       <c r="D205">
-        <v>346735.6933542024</v>
+        <v>318164.6123266579</v>
       </c>
     </row>
     <row r="206">
@@ -3038,7 +3038,7 @@
         <v>2028</v>
       </c>
       <c r="D206">
-        <v>377879.2867774619</v>
+        <v>346736.1493950812</v>
       </c>
     </row>
     <row r="207">
@@ -3077,7 +3077,7 @@
         <v>2026</v>
       </c>
       <c r="D209">
-        <v>270914.2664060779</v>
+        <v>246709.7220193894</v>
       </c>
     </row>
     <row r="210">
@@ -3090,7 +3090,7 @@
         <v>2027</v>
       </c>
       <c r="D210">
-        <v>297567.1114660384</v>
+        <v>270919.6639445653</v>
       </c>
     </row>
     <row r="211">
@@ -3103,7 +3103,7 @@
         <v>2028</v>
       </c>
       <c r="D211">
-        <v>326844.1672825909</v>
+        <v>297567.7409946572</v>
       </c>
     </row>
     <row r="212">
@@ -3142,7 +3142,7 @@
         <v>2026</v>
       </c>
       <c r="D214">
-        <v>350351.4762329028</v>
+        <v>327132.7170364123</v>
       </c>
     </row>
     <row r="215">
@@ -3155,7 +3155,7 @@
         <v>2027</v>
       </c>
       <c r="D215">
-        <v>375653.6576701892</v>
+        <v>350407.8967404912</v>
       </c>
     </row>
     <row r="216">
@@ -3168,7 +3168,7 @@
         <v>2028</v>
       </c>
       <c r="D216">
-        <v>402829.4499118177</v>
+        <v>375668.0515174768</v>
       </c>
     </row>
     <row r="217">
@@ -3207,7 +3207,7 @@
         <v>2026</v>
       </c>
       <c r="D219">
-        <v>350351.4762329028</v>
+        <v>327132.7170364123</v>
       </c>
     </row>
     <row r="220">
@@ -3220,7 +3220,7 @@
         <v>2027</v>
       </c>
       <c r="D220">
-        <v>375653.6576701892</v>
+        <v>350407.8967404912</v>
       </c>
     </row>
     <row r="221">
@@ -3233,7 +3233,7 @@
         <v>2028</v>
       </c>
       <c r="D221">
-        <v>402829.4499118177</v>
+        <v>375668.0515174768</v>
       </c>
     </row>
     <row r="222">
@@ -3272,7 +3272,7 @@
         <v>2026</v>
       </c>
       <c r="D224">
-        <v>350351.4762329028</v>
+        <v>327132.7170364123</v>
       </c>
     </row>
     <row r="225">
@@ -3285,7 +3285,7 @@
         <v>2027</v>
       </c>
       <c r="D225">
-        <v>375653.6576701892</v>
+        <v>350407.8967404912</v>
       </c>
     </row>
     <row r="226">
@@ -3298,7 +3298,7 @@
         <v>2028</v>
       </c>
       <c r="D226">
-        <v>402829.4499118177</v>
+        <v>375668.0515174768</v>
       </c>
     </row>
     <row r="227">
@@ -3337,7 +3337,7 @@
         <v>2026</v>
       </c>
       <c r="D229">
-        <v>350351.4762329028</v>
+        <v>327132.7170364123</v>
       </c>
     </row>
     <row r="230">
@@ -3350,7 +3350,7 @@
         <v>2027</v>
       </c>
       <c r="D230">
-        <v>375653.6576701892</v>
+        <v>350407.8967404912</v>
       </c>
     </row>
     <row r="231">
@@ -3363,7 +3363,7 @@
         <v>2028</v>
       </c>
       <c r="D231">
-        <v>402829.4499118177</v>
+        <v>375668.0515174768</v>
       </c>
     </row>
     <row r="232">
@@ -3402,7 +3402,7 @@
         <v>2026</v>
       </c>
       <c r="D234">
-        <v>350351.4762329028</v>
+        <v>327132.7170364123</v>
       </c>
     </row>
     <row r="235">
@@ -3415,7 +3415,7 @@
         <v>2027</v>
       </c>
       <c r="D235">
-        <v>375653.6576701892</v>
+        <v>350407.8967404912</v>
       </c>
     </row>
     <row r="236">
@@ -3428,7 +3428,7 @@
         <v>2028</v>
       </c>
       <c r="D236">
-        <v>402829.4499118177</v>
+        <v>375668.0515174768</v>
       </c>
     </row>
     <row r="237">
@@ -3467,7 +3467,7 @@
         <v>2026</v>
       </c>
       <c r="D239">
-        <v>395392.0065353211</v>
+        <v>369718.944202198</v>
       </c>
     </row>
     <row r="240">
@@ -3480,7 +3480,7 @@
         <v>2027</v>
       </c>
       <c r="D240">
-        <v>422929.9474505896</v>
+        <v>395397.6225311106</v>
       </c>
     </row>
     <row r="241">
@@ -3493,7 +3493,7 @@
         <v>2028</v>
       </c>
       <c r="D241">
-        <v>452387.6337425828</v>
+        <v>422930.5100226681</v>
       </c>
     </row>
     <row r="242">
@@ -3532,7 +3532,7 @@
         <v>2026</v>
       </c>
       <c r="D244">
-        <v>377215.8042992281</v>
+        <v>348851.8338514452</v>
       </c>
     </row>
     <row r="245">
@@ -3545,7 +3545,7 @@
         <v>2027</v>
       </c>
       <c r="D245">
-        <v>408147.9651275449</v>
+        <v>377251.1855309155</v>
       </c>
     </row>
     <row r="246">
@@ -3558,7 +3558,7 @@
         <v>2028</v>
       </c>
       <c r="D246">
-        <v>441648.9056093694</v>
+        <v>408157.9169207505</v>
       </c>
     </row>
     <row r="247">
@@ -3597,7 +3597,7 @@
         <v>2026</v>
       </c>
       <c r="D249">
-        <v>395392.0065353211</v>
+        <v>369718.944202198</v>
       </c>
     </row>
     <row r="250">
@@ -3610,7 +3610,7 @@
         <v>2027</v>
       </c>
       <c r="D250">
-        <v>422929.9474505896</v>
+        <v>395397.6225311106</v>
       </c>
     </row>
     <row r="251">
@@ -3623,7 +3623,7 @@
         <v>2028</v>
       </c>
       <c r="D251">
-        <v>452387.6337425828</v>
+        <v>422930.5100226681</v>
       </c>
     </row>
     <row r="252">
@@ -3662,7 +3662,7 @@
         <v>2026</v>
       </c>
       <c r="D254">
-        <v>395392.0065353211</v>
+        <v>369718.944202198</v>
       </c>
     </row>
     <row r="255">
@@ -3675,7 +3675,7 @@
         <v>2027</v>
       </c>
       <c r="D255">
-        <v>422929.9474505896</v>
+        <v>395397.6225311106</v>
       </c>
     </row>
     <row r="256">
@@ -3688,7 +3688,7 @@
         <v>2028</v>
       </c>
       <c r="D256">
-        <v>452387.6337425828</v>
+        <v>422930.5100226681</v>
       </c>
     </row>
     <row r="257">
@@ -3727,7 +3727,7 @@
         <v>2026</v>
       </c>
       <c r="D259">
-        <v>395392.0065353211</v>
+        <v>369718.944202198</v>
       </c>
     </row>
     <row r="260">
@@ -3740,7 +3740,7 @@
         <v>2027</v>
       </c>
       <c r="D260">
-        <v>422929.9474505896</v>
+        <v>395397.6225311106</v>
       </c>
     </row>
     <row r="261">
@@ -3753,7 +3753,7 @@
         <v>2028</v>
       </c>
       <c r="D261">
-        <v>452387.6337425828</v>
+        <v>422930.5100226681</v>
       </c>
     </row>
     <row r="262">
@@ -3792,7 +3792,7 @@
         <v>2026</v>
       </c>
       <c r="D264">
-        <v>395392.0065353211</v>
+        <v>369718.944202198</v>
       </c>
     </row>
     <row r="265">
@@ -3805,7 +3805,7 @@
         <v>2027</v>
       </c>
       <c r="D265">
-        <v>422929.9474505896</v>
+        <v>395397.6225311106</v>
       </c>
     </row>
     <row r="266">
@@ -3818,7 +3818,7 @@
         <v>2028</v>
       </c>
       <c r="D266">
-        <v>452387.6337425828</v>
+        <v>422930.5100226681</v>
       </c>
     </row>
     <row r="267">
@@ -3857,7 +3857,7 @@
         <v>2026</v>
       </c>
       <c r="D269">
-        <v>395392.0065353211</v>
+        <v>369718.944202198</v>
       </c>
     </row>
     <row r="270">
@@ -3870,7 +3870,7 @@
         <v>2027</v>
       </c>
       <c r="D270">
-        <v>422929.9474505896</v>
+        <v>395397.6225311106</v>
       </c>
     </row>
     <row r="271">
@@ -3883,7 +3883,7 @@
         <v>2028</v>
       </c>
       <c r="D271">
-        <v>452387.6337425828</v>
+        <v>422930.5100226681</v>
       </c>
     </row>
     <row r="272">
@@ -3922,7 +3922,7 @@
         <v>2026</v>
       </c>
       <c r="D274">
-        <v>395392.0065353211</v>
+        <v>369718.944202198</v>
       </c>
     </row>
     <row r="275">
@@ -3935,7 +3935,7 @@
         <v>2027</v>
       </c>
       <c r="D275">
-        <v>422929.9474505896</v>
+        <v>395397.6225311106</v>
       </c>
     </row>
     <row r="276">
@@ -3948,7 +3948,7 @@
         <v>2028</v>
       </c>
       <c r="D276">
-        <v>452387.6337425828</v>
+        <v>422930.5100226681</v>
       </c>
     </row>
     <row r="277">
@@ -3987,7 +3987,7 @@
         <v>2026</v>
       </c>
       <c r="D279">
-        <v>395357.6997577403</v>
+        <v>369686.5061424968</v>
       </c>
     </row>
     <row r="280">
@@ -4000,7 +4000,7 @@
         <v>2027</v>
       </c>
       <c r="D280">
-        <v>422893.8578786106</v>
+        <v>395363.3338714255</v>
       </c>
     </row>
     <row r="281">
@@ -4013,7 +4013,7 @@
         <v>2028</v>
       </c>
       <c r="D281">
-        <v>452349.6874307297</v>
+        <v>422894.422934767</v>
       </c>
     </row>
     <row r="282">
@@ -4052,7 +4052,7 @@
         <v>2026</v>
       </c>
       <c r="D284">
-        <v>354175.7036716905</v>
+        <v>330762.1690683965</v>
       </c>
     </row>
     <row r="285">
@@ -4065,7 +4065,7 @@
         <v>2027</v>
       </c>
       <c r="D285">
-        <v>379651.3392268324</v>
+        <v>354226.6553395889</v>
       </c>
     </row>
     <row r="286">
@@ -4078,7 +4078,7 @@
         <v>2028</v>
       </c>
       <c r="D286">
-        <v>406999.2019679822</v>
+        <v>379663.7092741048</v>
       </c>
     </row>
     <row r="287">
@@ -4117,7 +4117,7 @@
         <v>2026</v>
       </c>
       <c r="D289">
-        <v>350351.4762329028</v>
+        <v>327132.7170364123</v>
       </c>
     </row>
     <row r="290">
@@ -4130,7 +4130,7 @@
         <v>2027</v>
       </c>
       <c r="D290">
-        <v>375653.6576701892</v>
+        <v>350407.8967404912</v>
       </c>
     </row>
     <row r="291">
@@ -4143,7 +4143,7 @@
         <v>2028</v>
       </c>
       <c r="D291">
-        <v>402829.4499118177</v>
+        <v>375668.0515174768</v>
       </c>
     </row>
     <row r="292">
@@ -4182,7 +4182,7 @@
         <v>2026</v>
       </c>
       <c r="D294">
-        <v>350351.4762329028</v>
+        <v>327132.7170364123</v>
       </c>
     </row>
     <row r="295">
@@ -4195,7 +4195,7 @@
         <v>2027</v>
       </c>
       <c r="D295">
-        <v>375653.6576701892</v>
+        <v>350407.8967404912</v>
       </c>
     </row>
     <row r="296">
@@ -4208,7 +4208,7 @@
         <v>2028</v>
       </c>
       <c r="D296">
-        <v>402829.4499118177</v>
+        <v>375668.0515174768</v>
       </c>
     </row>
     <row r="297">
@@ -4247,7 +4247,7 @@
         <v>2026</v>
       </c>
       <c r="D299">
-        <v>350226.5664179342</v>
+        <v>327004.8447748426</v>
       </c>
     </row>
     <row r="300">
@@ -4260,7 +4260,7 @@
         <v>2027</v>
       </c>
       <c r="D300">
-        <v>375532.1940414257</v>
+        <v>350282.8883136607</v>
       </c>
     </row>
     <row r="301">
@@ -4273,7 +4273,7 @@
         <v>2028</v>
       </c>
       <c r="D301">
-        <v>402712.474269491</v>
+        <v>375546.5538727458</v>
       </c>
     </row>
     <row r="302">
@@ -4312,7 +4312,7 @@
         <v>2026</v>
       </c>
       <c r="D304">
-        <v>324901.6406089331</v>
+        <v>298513.7471730451</v>
       </c>
     </row>
     <row r="305">
@@ -4325,7 +4325,7 @@
         <v>2027</v>
       </c>
       <c r="D305">
-        <v>353693.2588895752</v>
+        <v>324906.4416619404</v>
       </c>
     </row>
     <row r="306">
@@ -4338,7 +4338,7 @@
         <v>2028</v>
       </c>
       <c r="D306">
-        <v>385037.8966492331</v>
+        <v>353693.7517208442</v>
       </c>
     </row>
     <row r="307">
@@ -4377,7 +4377,7 @@
         <v>2026</v>
       </c>
       <c r="D309">
-        <v>324693.716265775</v>
+        <v>298242.6301645385</v>
       </c>
     </row>
     <row r="310">
@@ -4390,7 +4390,7 @@
         <v>2027</v>
       </c>
       <c r="D310">
-        <v>353557.6568893177</v>
+        <v>324698.1276041339</v>
       </c>
     </row>
     <row r="311">
@@ -4403,7 +4403,7 @@
         <v>2028</v>
       </c>
       <c r="D311">
-        <v>384988.9189846051</v>
+        <v>353558.0963090294</v>
       </c>
     </row>
     <row r="312">
@@ -4442,7 +4442,7 @@
         <v>2026</v>
       </c>
       <c r="D314">
-        <v>316854.7391454254</v>
+        <v>290685.0903413373</v>
       </c>
     </row>
     <row r="315">
@@ -4455,7 +4455,7 @@
         <v>2027</v>
       </c>
       <c r="D315">
-        <v>345484.591653891</v>
+        <v>316862.7496772689</v>
       </c>
     </row>
     <row r="316">
@@ -4468,7 +4468,7 @@
         <v>2028</v>
       </c>
       <c r="D316">
-        <v>376704.5325163704</v>
+        <v>345485.5693262916</v>
       </c>
     </row>
     <row r="317">
@@ -4507,7 +4507,7 @@
         <v>2026</v>
       </c>
       <c r="D319">
-        <v>371166.9275757635</v>
+        <v>345879.8487804518</v>
       </c>
     </row>
     <row r="320">
@@ -4520,7 +4520,7 @@
         <v>2027</v>
       </c>
       <c r="D320">
-        <v>398436.8627135377</v>
+        <v>371177.87183998</v>
       </c>
     </row>
     <row r="321">
@@ -4533,7 +4533,7 @@
         <v>2028</v>
       </c>
       <c r="D321">
-        <v>427714.8358837236</v>
+        <v>398438.2581154539</v>
       </c>
     </row>
     <row r="322">
@@ -4572,7 +4572,7 @@
         <v>2026</v>
       </c>
       <c r="D324">
-        <v>395392.0065353211</v>
+        <v>369718.944202198</v>
       </c>
     </row>
     <row r="325">
@@ -4585,7 +4585,7 @@
         <v>2027</v>
       </c>
       <c r="D325">
-        <v>422929.9474505896</v>
+        <v>395397.6225311106</v>
       </c>
     </row>
     <row r="326">
@@ -4598,7 +4598,7 @@
         <v>2028</v>
       </c>
       <c r="D326">
-        <v>452387.6337425828</v>
+        <v>422930.5100226681</v>
       </c>
     </row>
     <row r="327">
@@ -4637,7 +4637,7 @@
         <v>2026</v>
       </c>
       <c r="D329">
-        <v>395392.0065353211</v>
+        <v>369718.944202198</v>
       </c>
     </row>
     <row r="330">
@@ -4650,7 +4650,7 @@
         <v>2027</v>
       </c>
       <c r="D330">
-        <v>422929.9474505896</v>
+        <v>395397.6225311106</v>
       </c>
     </row>
     <row r="331">
@@ -4663,7 +4663,7 @@
         <v>2028</v>
       </c>
       <c r="D331">
-        <v>452387.6337425828</v>
+        <v>422930.5100226681</v>
       </c>
     </row>
     <row r="332">
@@ -4702,7 +4702,7 @@
         <v>2026</v>
       </c>
       <c r="D334">
-        <v>342274.8895230365</v>
+        <v>314182.3661402086</v>
       </c>
     </row>
     <row r="335">
@@ -4715,7 +4715,7 @@
         <v>2027</v>
       </c>
       <c r="D335">
-        <v>372896.7445487161</v>
+        <v>342274.0646266888</v>
       </c>
     </row>
     <row r="336">
@@ -4728,7 +4728,7 @@
         <v>2028</v>
       </c>
       <c r="D336">
-        <v>406258.3356405181</v>
+        <v>372896.78464394</v>
       </c>
     </row>
     <row r="337">
@@ -4767,7 +4767,7 @@
         <v>2026</v>
       </c>
       <c r="D339">
-        <v>383849.8401997011</v>
+        <v>356434.2727005602</v>
       </c>
     </row>
     <row r="340">
@@ -4780,7 +4780,7 @@
         <v>2027</v>
       </c>
       <c r="D340">
-        <v>413377.9275966179</v>
+        <v>383849.9073768063</v>
       </c>
     </row>
     <row r="341">
@@ -4793,7 +4793,7 @@
         <v>2028</v>
       </c>
       <c r="D341">
-        <v>445177.5015386613</v>
+        <v>413377.9290497213</v>
       </c>
     </row>
     <row r="342">
@@ -4832,7 +4832,7 @@
         <v>2026</v>
       </c>
       <c r="D344">
-        <v>335522.0135228338</v>
+        <v>310639.3549958317</v>
       </c>
     </row>
     <row r="345">
@@ -4845,7 +4845,7 @@
         <v>2027</v>
       </c>
       <c r="D345">
-        <v>362658.4730572659</v>
+        <v>335548.3313939571</v>
       </c>
     </row>
     <row r="346">
@@ -4858,7 +4858,7 @@
         <v>2028</v>
       </c>
       <c r="D346">
-        <v>392004.6410216906</v>
+        <v>362663.0855896368</v>
       </c>
     </row>
     <row r="347">
@@ -4897,7 +4897,7 @@
         <v>2026</v>
       </c>
       <c r="D349">
-        <v>238176.0223991052</v>
+        <v>215358.36881839</v>
       </c>
     </row>
     <row r="350">
@@ -4910,7 +4910,7 @@
         <v>2027</v>
       </c>
       <c r="D350">
-        <v>265064.5861475251</v>
+        <v>238444.6433551398</v>
       </c>
     </row>
     <row r="351">
@@ -4923,7 +4923,7 @@
         <v>2028</v>
       </c>
       <c r="D351">
-        <v>295379.9934113523</v>
+        <v>265181.7348536342</v>
       </c>
     </row>
     <row r="352">
@@ -4962,7 +4962,7 @@
         <v>2026</v>
       </c>
       <c r="D354">
-        <v>237681.0746062641</v>
+        <v>214929.9535655357</v>
       </c>
     </row>
     <row r="355">
@@ -4975,7 +4975,7 @@
         <v>2027</v>
       </c>
       <c r="D355">
-        <v>264504.836089653</v>
+        <v>237952.1502398725</v>
       </c>
     </row>
     <row r="356">
@@ -4988,7 +4988,7 @@
         <v>2028</v>
       </c>
       <c r="D356">
-        <v>294752.7282224735</v>
+        <v>264623.6675692835</v>
       </c>
     </row>
     <row r="357">
@@ -5027,7 +5027,7 @@
         <v>2026</v>
       </c>
       <c r="D359">
-        <v>343007.5912081982</v>
+        <v>309862.565275585</v>
       </c>
     </row>
     <row r="360">
@@ -5040,7 +5040,7 @@
         <v>2027</v>
       </c>
       <c r="D360">
-        <v>379698.505974901</v>
+        <v>343007.5937036644</v>
       </c>
     </row>
     <row r="361">
@@ -5053,7 +5053,7 @@
         <v>2028</v>
       </c>
       <c r="D361">
-        <v>420314.1829911045</v>
+        <v>379698.5059914481</v>
       </c>
     </row>
     <row r="362">
@@ -5092,7 +5092,7 @@
         <v>2026</v>
       </c>
       <c r="D364">
-        <v>343007.5912081982</v>
+        <v>309862.565275585</v>
       </c>
     </row>
     <row r="365">
@@ -5105,7 +5105,7 @@
         <v>2027</v>
       </c>
       <c r="D365">
-        <v>379698.505974901</v>
+        <v>343007.5937036644</v>
       </c>
     </row>
     <row r="366">
@@ -5118,7 +5118,7 @@
         <v>2028</v>
       </c>
       <c r="D366">
-        <v>420314.1829911045</v>
+        <v>379698.5059914481</v>
       </c>
     </row>
     <row r="367">
@@ -5157,7 +5157,7 @@
         <v>2026</v>
       </c>
       <c r="D369">
-        <v>343007.5912081982</v>
+        <v>309862.565275585</v>
       </c>
     </row>
     <row r="370">
@@ -5170,7 +5170,7 @@
         <v>2027</v>
       </c>
       <c r="D370">
-        <v>379698.505974901</v>
+        <v>343007.5937036644</v>
       </c>
     </row>
     <row r="371">
@@ -5183,7 +5183,7 @@
         <v>2028</v>
       </c>
       <c r="D371">
-        <v>420314.1829911045</v>
+        <v>379698.5059914481</v>
       </c>
     </row>
     <row r="372">
@@ -5222,7 +5222,7 @@
         <v>2026</v>
       </c>
       <c r="D374">
-        <v>343007.5912081982</v>
+        <v>309862.565275585</v>
       </c>
     </row>
     <row r="375">
@@ -5235,7 +5235,7 @@
         <v>2027</v>
       </c>
       <c r="D375">
-        <v>379698.505974901</v>
+        <v>343007.5937036644</v>
       </c>
     </row>
     <row r="376">
@@ -5248,7 +5248,7 @@
         <v>2028</v>
       </c>
       <c r="D376">
-        <v>420314.1829911045</v>
+        <v>379698.5059914481</v>
       </c>
     </row>
     <row r="377">
@@ -5287,7 +5287,7 @@
         <v>2026</v>
       </c>
       <c r="D379">
-        <v>343007.5912081982</v>
+        <v>309862.565275585</v>
       </c>
     </row>
     <row r="380">
@@ -5300,7 +5300,7 @@
         <v>2027</v>
       </c>
       <c r="D380">
-        <v>379698.505974901</v>
+        <v>343007.5937036644</v>
       </c>
     </row>
     <row r="381">
@@ -5313,7 +5313,7 @@
         <v>2028</v>
       </c>
       <c r="D381">
-        <v>420314.1829911045</v>
+        <v>379698.5059914481</v>
       </c>
     </row>
     <row r="382">
@@ -5352,7 +5352,7 @@
         <v>2026</v>
       </c>
       <c r="D384">
-        <v>331339.7204341433</v>
+        <v>298800.626722076</v>
       </c>
     </row>
     <row r="385">
@@ -5365,7 +5365,7 @@
         <v>2027</v>
       </c>
       <c r="D385">
-        <v>367424.9558627411</v>
+        <v>331339.6832978525</v>
       </c>
     </row>
     <row r="386">
@@ -5378,7 +5378,7 @@
         <v>2028</v>
       </c>
       <c r="D386">
-        <v>407440.1302803</v>
+        <v>367424.956470565</v>
       </c>
     </row>
     <row r="387">
@@ -5417,7 +5417,7 @@
         <v>2026</v>
       </c>
       <c r="D389">
-        <v>341914.8988819366</v>
+        <v>308843.6622148303</v>
       </c>
     </row>
     <row r="390">
@@ -5430,7 +5430,7 @@
         <v>2027</v>
       </c>
       <c r="D390">
-        <v>378527.5788535576</v>
+        <v>341914.8993277834</v>
       </c>
     </row>
     <row r="391">
@@ -5443,7 +5443,7 @@
         <v>2028</v>
       </c>
       <c r="D391">
-        <v>419060.790925358</v>
+        <v>378527.5788552238</v>
       </c>
     </row>
     <row r="392">
@@ -5482,7 +5482,7 @@
         <v>2026</v>
       </c>
       <c r="D394">
-        <v>206408.2563636045</v>
+        <v>185018.0899168191</v>
       </c>
     </row>
     <row r="395">
@@ -5495,7 +5495,7 @@
         <v>2027</v>
       </c>
       <c r="D395">
-        <v>230435.0672019241</v>
+        <v>206423.1748052656</v>
       </c>
     </row>
     <row r="396">
@@ -5508,7 +5508,7 @@
         <v>2028</v>
       </c>
       <c r="D396">
-        <v>257266.8659761057</v>
+        <v>230437.5046377698</v>
       </c>
     </row>
     <row r="397">
@@ -5547,7 +5547,7 @@
         <v>2026</v>
       </c>
       <c r="D399">
-        <v>393824.3812634929</v>
+        <v>366563.4106603409</v>
       </c>
     </row>
     <row r="400">
@@ -5560,7 +5560,7 @@
         <v>2027</v>
       </c>
       <c r="D400">
-        <v>423122.512403396</v>
+        <v>393824.6579744138</v>
       </c>
     </row>
     <row r="401">
@@ -5573,7 +5573,7 @@
         <v>2028</v>
       </c>
       <c r="D401">
-        <v>454600.2777665221</v>
+        <v>423122.5223383044</v>
       </c>
     </row>
     <row r="402">
@@ -5612,7 +5612,7 @@
         <v>2026</v>
       </c>
       <c r="D404">
-        <v>393824.3812634929</v>
+        <v>366563.4106603409</v>
       </c>
     </row>
     <row r="405">
@@ -5625,7 +5625,7 @@
         <v>2027</v>
       </c>
       <c r="D405">
-        <v>423122.512403396</v>
+        <v>393824.6579744138</v>
       </c>
     </row>
     <row r="406">
@@ -5638,7 +5638,7 @@
         <v>2028</v>
       </c>
       <c r="D406">
-        <v>454600.2777665221</v>
+        <v>423122.5223383044</v>
       </c>
     </row>
     <row r="407">
@@ -5677,7 +5677,7 @@
         <v>2026</v>
       </c>
       <c r="D409">
-        <v>393824.3812634929</v>
+        <v>366563.4106603409</v>
       </c>
     </row>
     <row r="410">
@@ -5690,7 +5690,7 @@
         <v>2027</v>
       </c>
       <c r="D410">
-        <v>423122.512403396</v>
+        <v>393824.6579744138</v>
       </c>
     </row>
     <row r="411">
@@ -5703,7 +5703,7 @@
         <v>2028</v>
       </c>
       <c r="D411">
-        <v>454600.2777665221</v>
+        <v>423122.5223383044</v>
       </c>
     </row>
     <row r="412">
@@ -5742,7 +5742,7 @@
         <v>2026</v>
       </c>
       <c r="D414">
-        <v>393824.3812634929</v>
+        <v>366563.4106603409</v>
       </c>
     </row>
     <row r="415">
@@ -5755,7 +5755,7 @@
         <v>2027</v>
       </c>
       <c r="D415">
-        <v>423122.512403396</v>
+        <v>393824.6579744138</v>
       </c>
     </row>
     <row r="416">
@@ -5768,7 +5768,7 @@
         <v>2028</v>
       </c>
       <c r="D416">
-        <v>454600.2777665221</v>
+        <v>423122.5223383044</v>
       </c>
     </row>
     <row r="417">
@@ -5807,7 +5807,7 @@
         <v>2026</v>
       </c>
       <c r="D419">
-        <v>393824.3812634929</v>
+        <v>366563.4106603409</v>
       </c>
     </row>
     <row r="420">
@@ -5820,7 +5820,7 @@
         <v>2027</v>
       </c>
       <c r="D420">
-        <v>423122.512403396</v>
+        <v>393824.6579744138</v>
       </c>
     </row>
     <row r="421">
@@ -5833,7 +5833,7 @@
         <v>2028</v>
       </c>
       <c r="D421">
-        <v>454600.2777665221</v>
+        <v>423122.5223383044</v>
       </c>
     </row>
     <row r="422">
@@ -5872,7 +5872,7 @@
         <v>2026</v>
       </c>
       <c r="D424">
-        <v>393824.3812634929</v>
+        <v>366563.4106603409</v>
       </c>
     </row>
     <row r="425">
@@ -5885,7 +5885,7 @@
         <v>2027</v>
       </c>
       <c r="D425">
-        <v>423122.512403396</v>
+        <v>393824.6579744138</v>
       </c>
     </row>
     <row r="426">
@@ -5898,7 +5898,7 @@
         <v>2028</v>
       </c>
       <c r="D426">
-        <v>454600.2777665221</v>
+        <v>423122.5223383044</v>
       </c>
     </row>
     <row r="427">
@@ -5937,7 +5937,7 @@
         <v>2026</v>
       </c>
       <c r="D429">
-        <v>273750.0517216091</v>
+        <v>247585.0779466876</v>
       </c>
     </row>
     <row r="430">
@@ -5950,7 +5950,7 @@
         <v>2027</v>
       </c>
       <c r="D430">
-        <v>302704.5669450988</v>
+        <v>273748.4038976505</v>
       </c>
     </row>
     <row r="431">
@@ -5963,7 +5963,7 @@
         <v>2028</v>
       </c>
       <c r="D431">
-        <v>334721.9669735088</v>
+        <v>302704.678078649</v>
       </c>
     </row>
     <row r="432">
@@ -6002,7 +6002,7 @@
         <v>2026</v>
       </c>
       <c r="D434">
-        <v>273750.0517216091</v>
+        <v>247585.0779466876</v>
       </c>
     </row>
     <row r="435">
@@ -6015,7 +6015,7 @@
         <v>2027</v>
       </c>
       <c r="D435">
-        <v>302704.5669450988</v>
+        <v>273748.4038976505</v>
       </c>
     </row>
     <row r="436">
@@ -6028,7 +6028,7 @@
         <v>2028</v>
       </c>
       <c r="D436">
-        <v>334721.9669735088</v>
+        <v>302704.678078649</v>
       </c>
     </row>
     <row r="437">
@@ -6067,7 +6067,7 @@
         <v>2026</v>
       </c>
       <c r="D439">
-        <v>273750.0517216091</v>
+        <v>247585.0779466876</v>
       </c>
     </row>
     <row r="440">
@@ -6080,7 +6080,7 @@
         <v>2027</v>
       </c>
       <c r="D440">
-        <v>302704.5669450988</v>
+        <v>273748.4038976505</v>
       </c>
     </row>
     <row r="441">
@@ -6093,7 +6093,7 @@
         <v>2028</v>
       </c>
       <c r="D441">
-        <v>334721.9669735088</v>
+        <v>302704.678078649</v>
       </c>
     </row>
     <row r="442">
@@ -6132,7 +6132,7 @@
         <v>2026</v>
       </c>
       <c r="D444">
-        <v>273750.0517216091</v>
+        <v>247585.0779466876</v>
       </c>
     </row>
     <row r="445">
@@ -6145,7 +6145,7 @@
         <v>2027</v>
       </c>
       <c r="D445">
-        <v>302704.5669450988</v>
+        <v>273748.4038976505</v>
       </c>
     </row>
     <row r="446">
@@ -6158,7 +6158,7 @@
         <v>2028</v>
       </c>
       <c r="D446">
-        <v>334721.9669735088</v>
+        <v>302704.678078649</v>
       </c>
     </row>
     <row r="447">
@@ -6197,7 +6197,7 @@
         <v>2026</v>
       </c>
       <c r="D449">
-        <v>390894.3923337234</v>
+        <v>364532.3706096096</v>
       </c>
     </row>
     <row r="450">
@@ -6210,7 +6210,7 @@
         <v>2027</v>
       </c>
       <c r="D450">
-        <v>419198.7568271771</v>
+        <v>390896.1680930458</v>
       </c>
     </row>
     <row r="451">
@@ -6223,7 +6223,7 @@
         <v>2028</v>
       </c>
       <c r="D451">
-        <v>449553.0050856035</v>
+        <v>419198.876912808</v>
       </c>
     </row>
     <row r="452">
@@ -6262,7 +6262,7 @@
         <v>2026</v>
       </c>
       <c r="D454">
-        <v>207251.949792317</v>
+        <v>185867.4558853358</v>
       </c>
     </row>
     <row r="455">
@@ -6275,7 +6275,7 @@
         <v>2027</v>
       </c>
       <c r="D455">
-        <v>231261.2307858785</v>
+        <v>207266.9811141192</v>
       </c>
     </row>
     <row r="456">
@@ -6288,7 +6288,7 @@
         <v>2028</v>
       </c>
       <c r="D456">
-        <v>258060.1340902369</v>
+        <v>231263.6941920996</v>
       </c>
     </row>
     <row r="457">
@@ -6327,7 +6327,7 @@
         <v>2026</v>
       </c>
       <c r="D459">
-        <v>207251.949792317</v>
+        <v>185867.4558853358</v>
       </c>
     </row>
     <row r="460">
@@ -6340,7 +6340,7 @@
         <v>2027</v>
       </c>
       <c r="D460">
-        <v>231261.2307858785</v>
+        <v>207266.9811141192</v>
       </c>
     </row>
     <row r="461">
@@ -6353,7 +6353,7 @@
         <v>2028</v>
       </c>
       <c r="D461">
-        <v>258060.1340902369</v>
+        <v>231263.6941920996</v>
       </c>
     </row>
     <row r="462">
@@ -6392,7 +6392,7 @@
         <v>2026</v>
       </c>
       <c r="D464">
-        <v>207251.949792317</v>
+        <v>185867.4558853358</v>
       </c>
     </row>
     <row r="465">
@@ -6405,7 +6405,7 @@
         <v>2027</v>
       </c>
       <c r="D465">
-        <v>231261.2307858785</v>
+        <v>207266.9811141192</v>
       </c>
     </row>
     <row r="466">
@@ -6418,7 +6418,7 @@
         <v>2028</v>
       </c>
       <c r="D466">
-        <v>258060.1340902369</v>
+        <v>231263.6941920996</v>
       </c>
     </row>
     <row r="467">
@@ -6457,7 +6457,7 @@
         <v>2026</v>
       </c>
       <c r="D469">
-        <v>263966.0428220129</v>
+        <v>238406.7957066435</v>
       </c>
     </row>
     <row r="470">
@@ -6470,7 +6470,7 @@
         <v>2027</v>
       </c>
       <c r="D470">
-        <v>292278.0585794365</v>
+        <v>263965.4763094994</v>
       </c>
     </row>
     <row r="471">
@@ -6483,7 +6483,7 @@
         <v>2028</v>
       </c>
       <c r="D471">
-        <v>323626.8060807794</v>
+        <v>292278.0857513974</v>
       </c>
     </row>
     <row r="472">
@@ -6522,7 +6522,7 @@
         <v>2026</v>
       </c>
       <c r="D474">
-        <v>273750.0517216091</v>
+        <v>247585.0779466876</v>
       </c>
     </row>
     <row r="475">
@@ -6535,7 +6535,7 @@
         <v>2027</v>
       </c>
       <c r="D475">
-        <v>302704.5669450988</v>
+        <v>273748.4038976505</v>
       </c>
     </row>
     <row r="476">
@@ -6548,7 +6548,7 @@
         <v>2028</v>
       </c>
       <c r="D476">
-        <v>334721.9669735088</v>
+        <v>302704.678078649</v>
       </c>
     </row>
     <row r="477">
@@ -6587,7 +6587,7 @@
         <v>2026</v>
       </c>
       <c r="D479">
-        <v>273261.4887401669</v>
+        <v>247126.4464581462</v>
       </c>
     </row>
     <row r="480">
@@ -6600,7 +6600,7 @@
         <v>2027</v>
       </c>
       <c r="D480">
-        <v>302184.2619738968</v>
+        <v>273259.9076267802</v>
       </c>
     </row>
     <row r="481">
@@ -6613,7 +6613,7 @@
         <v>2028</v>
       </c>
       <c r="D481">
-        <v>334168.6529662397</v>
+        <v>302184.367224369</v>
       </c>
     </row>
     <row r="482">
@@ -6652,7 +6652,7 @@
         <v>2026</v>
       </c>
       <c r="D484">
-        <v>207251.949792317</v>
+        <v>185867.4558853358</v>
       </c>
     </row>
     <row r="485">
@@ -6665,7 +6665,7 @@
         <v>2027</v>
       </c>
       <c r="D485">
-        <v>231261.2307858785</v>
+        <v>207266.9811141192</v>
       </c>
     </row>
     <row r="486">
@@ -6678,7 +6678,7 @@
         <v>2028</v>
       </c>
       <c r="D486">
-        <v>258060.1340902369</v>
+        <v>231263.6941920996</v>
       </c>
     </row>
     <row r="487">
@@ -6717,7 +6717,7 @@
         <v>2026</v>
       </c>
       <c r="D489">
-        <v>207251.949792317</v>
+        <v>185867.4558853358</v>
       </c>
     </row>
     <row r="490">
@@ -6730,7 +6730,7 @@
         <v>2027</v>
       </c>
       <c r="D490">
-        <v>231261.2307858785</v>
+        <v>207266.9811141192</v>
       </c>
     </row>
     <row r="491">
@@ -6743,7 +6743,7 @@
         <v>2028</v>
       </c>
       <c r="D491">
-        <v>258060.1340902369</v>
+        <v>231263.6941920996</v>
       </c>
     </row>
     <row r="492">
@@ -6782,7 +6782,7 @@
         <v>2026</v>
       </c>
       <c r="D494">
-        <v>207251.949792317</v>
+        <v>185867.4558853358</v>
       </c>
     </row>
     <row r="495">
@@ -6795,7 +6795,7 @@
         <v>2027</v>
       </c>
       <c r="D495">
-        <v>231261.2307858785</v>
+        <v>207266.9811141192</v>
       </c>
     </row>
     <row r="496">
@@ -6808,7 +6808,7 @@
         <v>2028</v>
       </c>
       <c r="D496">
-        <v>258060.1340902369</v>
+        <v>231263.6941920996</v>
       </c>
     </row>
     <row r="497">
@@ -6847,7 +6847,7 @@
         <v>2026</v>
       </c>
       <c r="D499">
-        <v>206446.2222614812</v>
+        <v>185056.3350024821</v>
       </c>
     </row>
     <row r="500">
@@ -6860,7 +6860,7 @@
         <v>2027</v>
       </c>
       <c r="D500">
-        <v>230472.2133488198</v>
+        <v>206461.1459496455</v>
       </c>
     </row>
     <row r="501">
@@ -6873,7 +6873,7 @@
         <v>2028</v>
       </c>
       <c r="D501">
-        <v>257302.4910716562</v>
+        <v>230474.6519890972</v>
       </c>
     </row>
     <row r="502">
@@ -6912,7 +6912,7 @@
         <v>2026</v>
       </c>
       <c r="D504">
-        <v>334119.5702832622</v>
+        <v>307476.8806618343</v>
       </c>
     </row>
     <row r="505">
@@ -6925,7 +6925,7 @@
         <v>2027</v>
       </c>
       <c r="D505">
-        <v>363226.447924901</v>
+        <v>334133.3042245762</v>
       </c>
     </row>
     <row r="506">
@@ -6938,7 +6938,7 @@
         <v>2028</v>
       </c>
       <c r="D506">
-        <v>394875.5334686319</v>
+        <v>363228.4586757288</v>
       </c>
     </row>
     <row r="507">
@@ -6977,7 +6977,7 @@
         <v>2026</v>
       </c>
       <c r="D509">
-        <v>285401.3083668167</v>
+        <v>260588.6288992723</v>
       </c>
     </row>
     <row r="510">
@@ -6990,7 +6990,7 @@
         <v>2027</v>
       </c>
       <c r="D510">
-        <v>312583.7907247833</v>
+        <v>285401.5100063474</v>
       </c>
     </row>
     <row r="511">
@@ -7003,7 +7003,7 @@
         <v>2028</v>
       </c>
       <c r="D511">
-        <v>342355.2393139287</v>
+        <v>312583.7981921734</v>
       </c>
     </row>
     <row r="512">
@@ -7042,7 +7042,7 @@
         <v>2026</v>
       </c>
       <c r="D514">
-        <v>260786.6773118163</v>
+        <v>232943.6667820439</v>
       </c>
     </row>
     <row r="515">
@@ -7055,7 +7055,7 @@
         <v>2027</v>
       </c>
       <c r="D515">
-        <v>292057.0869140218</v>
+        <v>260794.8863651546</v>
       </c>
     </row>
     <row r="516">
@@ -7068,7 +7068,7 @@
         <v>2028</v>
       </c>
       <c r="D516">
-        <v>327081.0208504402</v>
+        <v>292058.2631891792</v>
       </c>
     </row>
     <row r="517">
@@ -7107,7 +7107,7 @@
         <v>2026</v>
       </c>
       <c r="D519">
-        <v>292934.5982973256</v>
+        <v>267853.9827021851</v>
       </c>
     </row>
     <row r="520">
@@ -7120,7 +7120,7 @@
         <v>2027</v>
       </c>
       <c r="D520">
-        <v>320379.1303443337</v>
+        <v>292935.1954108629</v>
       </c>
     </row>
     <row r="521">
@@ -7133,7 +7133,7 @@
         <v>2028</v>
       </c>
       <c r="D521">
-        <v>350394.9962420352</v>
+        <v>320379.1618792212</v>
       </c>
     </row>
     <row r="522">
@@ -7172,7 +7172,7 @@
         <v>2026</v>
       </c>
       <c r="D524">
-        <v>288965.8951294243</v>
+        <v>264027.5761911435</v>
       </c>
     </row>
     <row r="525">
@@ -7185,7 +7185,7 @@
         <v>2027</v>
       </c>
       <c r="D525">
-        <v>316269.4496385023</v>
+        <v>288966.2043795905</v>
       </c>
     </row>
     <row r="526">
@@ -7198,7 +7198,7 @@
         <v>2028</v>
       </c>
       <c r="D526">
-        <v>346152.881501302</v>
+        <v>316269.462791856</v>
       </c>
     </row>
     <row r="527">
@@ -7237,7 +7237,7 @@
         <v>2026</v>
       </c>
       <c r="D529">
-        <v>336908.3736201967</v>
+        <v>310130.5513515816</v>
       </c>
     </row>
     <row r="530">
@@ -7250,7 +7250,7 @@
         <v>2027</v>
       </c>
       <c r="D530">
-        <v>366121.8664034181</v>
+        <v>336918.4147576817</v>
       </c>
     </row>
     <row r="531">
@@ -7263,7 +7263,7 @@
         <v>2028</v>
       </c>
       <c r="D531">
-        <v>397872.7478299304</v>
+        <v>366123.176818919</v>
       </c>
     </row>
     <row r="532">
@@ -7302,7 +7302,7 @@
         <v>2026</v>
       </c>
       <c r="D534">
-        <v>338353.6329026203</v>
+        <v>311516.5561679903</v>
       </c>
     </row>
     <row r="535">
@@ -7315,7 +7315,7 @@
         <v>2027</v>
       </c>
       <c r="D535">
-        <v>367630.4580733303</v>
+        <v>338364.1158090527</v>
       </c>
     </row>
     <row r="536">
@@ -7328,7 +7328,7 @@
         <v>2028</v>
       </c>
       <c r="D536">
-        <v>399445.0458174883</v>
+        <v>367631.8441466709</v>
       </c>
     </row>
     <row r="537">
@@ -7367,7 +7367,7 @@
         <v>2026</v>
       </c>
       <c r="D539">
-        <v>284681.7767434124</v>
+        <v>259895.1274509263</v>
       </c>
     </row>
     <row r="540">
@@ -7380,7 +7380,7 @@
         <v>2027</v>
       </c>
       <c r="D540">
-        <v>311837.2451986275</v>
+        <v>284681.8916629478</v>
       </c>
     </row>
     <row r="541">
@@ -7393,7 +7393,7 @@
         <v>2028</v>
       </c>
       <c r="D541">
-        <v>341583.0542538528</v>
+        <v>311837.248723286</v>
       </c>
     </row>
     <row r="542">
@@ -7432,7 +7432,7 @@
         <v>2026</v>
       </c>
       <c r="D544">
-        <v>260786.6773118163</v>
+        <v>232943.6667820439</v>
       </c>
     </row>
     <row r="545">
@@ -7445,7 +7445,7 @@
         <v>2027</v>
       </c>
       <c r="D545">
-        <v>292057.0869140218</v>
+        <v>260794.8863651546</v>
       </c>
     </row>
     <row r="546">
@@ -7458,7 +7458,7 @@
         <v>2028</v>
       </c>
       <c r="D546">
-        <v>327081.0208504402</v>
+        <v>292058.2631891792</v>
       </c>
     </row>
     <row r="547">
@@ -7497,7 +7497,7 @@
         <v>2026</v>
       </c>
       <c r="D549">
-        <v>260786.6773118163</v>
+        <v>232943.6667820439</v>
       </c>
     </row>
     <row r="550">
@@ -7510,7 +7510,7 @@
         <v>2027</v>
       </c>
       <c r="D550">
-        <v>292057.0869140218</v>
+        <v>260794.8863651546</v>
       </c>
     </row>
     <row r="551">
@@ -7523,7 +7523,7 @@
         <v>2028</v>
       </c>
       <c r="D551">
-        <v>327081.0208504402</v>
+        <v>292058.2631891792</v>
       </c>
     </row>
     <row r="552">
@@ -7562,7 +7562,7 @@
         <v>2026</v>
       </c>
       <c r="D554">
-        <v>260786.6773118163</v>
+        <v>232943.6667820439</v>
       </c>
     </row>
     <row r="555">
@@ -7575,7 +7575,7 @@
         <v>2027</v>
       </c>
       <c r="D555">
-        <v>292057.0869140218</v>
+        <v>260794.8863651546</v>
       </c>
     </row>
     <row r="556">
@@ -7588,7 +7588,7 @@
         <v>2028</v>
       </c>
       <c r="D556">
-        <v>327081.0208504402</v>
+        <v>292058.2631891792</v>
       </c>
     </row>
     <row r="557">
@@ -7627,7 +7627,7 @@
         <v>2026</v>
       </c>
       <c r="D559">
-        <v>260786.6773118163</v>
+        <v>232943.6667820439</v>
       </c>
     </row>
     <row r="560">
@@ -7640,7 +7640,7 @@
         <v>2027</v>
       </c>
       <c r="D560">
-        <v>292057.0869140218</v>
+        <v>260794.8863651546</v>
       </c>
     </row>
     <row r="561">
@@ -7653,7 +7653,7 @@
         <v>2028</v>
       </c>
       <c r="D561">
-        <v>327081.0208504402</v>
+        <v>292058.2631891792</v>
       </c>
     </row>
     <row r="562">
@@ -7692,7 +7692,7 @@
         <v>2026</v>
       </c>
       <c r="D564">
-        <v>182229.5997253017</v>
+        <v>157832.4812135399</v>
       </c>
     </row>
     <row r="565">
@@ -7705,7 +7705,7 @@
         <v>2027</v>
       </c>
       <c r="D565">
-        <v>210517.3801599728</v>
+        <v>182238.4222230733</v>
       </c>
     </row>
     <row r="566">
@@ -7718,7 +7718,7 @@
         <v>2028</v>
       </c>
       <c r="D566">
-        <v>243200.3650912515</v>
+        <v>210518.5484405709</v>
       </c>
     </row>
     <row r="567">
@@ -7757,7 +7757,7 @@
         <v>2026</v>
       </c>
       <c r="D569">
-        <v>179609.2140971918</v>
+        <v>155239.5064070644</v>
       </c>
     </row>
     <row r="570">
@@ -7770,7 +7770,7 @@
         <v>2027</v>
       </c>
       <c r="D570">
-        <v>207923.4724925383</v>
+        <v>179617.9086694608</v>
       </c>
     </row>
     <row r="571">
@@ -7783,7 +7783,7 @@
         <v>2028</v>
       </c>
       <c r="D571">
-        <v>240705.2568939184</v>
+        <v>207924.6133009189</v>
       </c>
     </row>
     <row r="572">
@@ -7822,7 +7822,7 @@
         <v>2026</v>
       </c>
       <c r="D574">
-        <v>179609.2140971918</v>
+        <v>155239.5064070644</v>
       </c>
     </row>
     <row r="575">
@@ -7835,7 +7835,7 @@
         <v>2027</v>
       </c>
       <c r="D575">
-        <v>207923.4724925383</v>
+        <v>179617.9086694608</v>
       </c>
     </row>
     <row r="576">
@@ -7848,7 +7848,7 @@
         <v>2028</v>
       </c>
       <c r="D576">
-        <v>240705.2568939184</v>
+        <v>207924.6133009189</v>
       </c>
     </row>
     <row r="577">
@@ -7887,7 +7887,7 @@
         <v>2026</v>
       </c>
       <c r="D579">
-        <v>180091.8344391545</v>
+        <v>155718.1345292624</v>
       </c>
     </row>
     <row r="580">
@@ -7900,7 +7900,7 @@
         <v>2027</v>
       </c>
       <c r="D580">
-        <v>208399.6888883742</v>
+        <v>180100.5550038125</v>
       </c>
     </row>
     <row r="581">
@@ -7913,7 +7913,7 @@
         <v>2028</v>
       </c>
       <c r="D581">
-        <v>241161.1116339078</v>
+        <v>208400.8351741917</v>
       </c>
     </row>
     <row r="582">
@@ -7952,7 +7952,7 @@
         <v>2026</v>
       </c>
       <c r="D584">
-        <v>260786.6773118163</v>
+        <v>232943.6667820439</v>
       </c>
     </row>
     <row r="585">
@@ -7965,7 +7965,7 @@
         <v>2027</v>
       </c>
       <c r="D585">
-        <v>292057.0869140218</v>
+        <v>260794.8863651546</v>
       </c>
     </row>
     <row r="586">
@@ -7978,7 +7978,7 @@
         <v>2028</v>
       </c>
       <c r="D586">
-        <v>327081.0208504402</v>
+        <v>292058.2631891792</v>
       </c>
     </row>
     <row r="587">
@@ -8017,7 +8017,7 @@
         <v>2026</v>
       </c>
       <c r="D589">
-        <v>284681.7767434124</v>
+        <v>259895.1274509263</v>
       </c>
     </row>
     <row r="590">
@@ -8030,7 +8030,7 @@
         <v>2027</v>
       </c>
       <c r="D590">
-        <v>311837.2451986275</v>
+        <v>284681.8916629478</v>
       </c>
     </row>
     <row r="591">
@@ -8043,7 +8043,7 @@
         <v>2028</v>
       </c>
       <c r="D591">
-        <v>341583.0542538528</v>
+        <v>311837.248723286</v>
       </c>
     </row>
     <row r="592">
@@ -8082,7 +8082,7 @@
         <v>2026</v>
       </c>
       <c r="D594">
-        <v>260786.6773118163</v>
+        <v>232943.6667820439</v>
       </c>
     </row>
     <row r="595">
@@ -8095,7 +8095,7 @@
         <v>2027</v>
       </c>
       <c r="D595">
-        <v>292057.0869140218</v>
+        <v>260794.8863651546</v>
       </c>
     </row>
     <row r="596">
@@ -8108,7 +8108,7 @@
         <v>2028</v>
       </c>
       <c r="D596">
-        <v>327081.0208504402</v>
+        <v>292058.2631891792</v>
       </c>
     </row>
     <row r="597">
@@ -8147,7 +8147,7 @@
         <v>2026</v>
       </c>
       <c r="D599">
-        <v>260786.6773118163</v>
+        <v>232943.6667820439</v>
       </c>
     </row>
     <row r="600">
@@ -8160,7 +8160,7 @@
         <v>2027</v>
       </c>
       <c r="D600">
-        <v>292057.0869140218</v>
+        <v>260794.8863651546</v>
       </c>
     </row>
     <row r="601">
@@ -8173,7 +8173,7 @@
         <v>2028</v>
       </c>
       <c r="D601">
-        <v>327081.0208504402</v>
+        <v>292058.2631891792</v>
       </c>
     </row>
     <row r="602">
@@ -8212,7 +8212,7 @@
         <v>2026</v>
       </c>
       <c r="D604">
-        <v>256914.4034884734</v>
+        <v>229292.4632137711</v>
       </c>
     </row>
     <row r="605">
@@ -8225,7 +8225,7 @@
         <v>2027</v>
       </c>
       <c r="D605">
-        <v>287964.3863175741</v>
+        <v>256922.6803605375</v>
       </c>
     </row>
     <row r="606">
@@ -8238,7 +8238,7 @@
         <v>2028</v>
       </c>
       <c r="D606">
-        <v>322770.9657685719</v>
+        <v>287965.5697305485</v>
       </c>
     </row>
     <row r="607">
@@ -8277,7 +8277,7 @@
         <v>2026</v>
       </c>
       <c r="D609">
-        <v>179609.2140971918</v>
+        <v>155239.5064070644</v>
       </c>
     </row>
     <row r="610">
@@ -8290,7 +8290,7 @@
         <v>2027</v>
       </c>
       <c r="D610">
-        <v>207923.4724925383</v>
+        <v>179617.9086694608</v>
       </c>
     </row>
     <row r="611">
@@ -8303,7 +8303,7 @@
         <v>2028</v>
       </c>
       <c r="D611">
-        <v>240705.2568939184</v>
+        <v>207924.6133009189</v>
       </c>
     </row>
     <row r="612">
@@ -8342,7 +8342,7 @@
         <v>2026</v>
       </c>
       <c r="D614">
-        <v>179609.2140971918</v>
+        <v>155239.5064070644</v>
       </c>
     </row>
     <row r="615">
@@ -8355,7 +8355,7 @@
         <v>2027</v>
       </c>
       <c r="D615">
-        <v>207923.4724925383</v>
+        <v>179617.9086694608</v>
       </c>
     </row>
     <row r="616">
@@ -8368,7 +8368,7 @@
         <v>2028</v>
       </c>
       <c r="D616">
-        <v>240705.2568939184</v>
+        <v>207924.6133009189</v>
       </c>
     </row>
     <row r="617">
@@ -8407,7 +8407,7 @@
         <v>2026</v>
       </c>
       <c r="D619">
-        <v>179609.2140971918</v>
+        <v>155239.5064070644</v>
       </c>
     </row>
     <row r="620">
@@ -8420,7 +8420,7 @@
         <v>2027</v>
       </c>
       <c r="D620">
-        <v>207923.4724925383</v>
+        <v>179617.9086694608</v>
       </c>
     </row>
     <row r="621">
@@ -8433,7 +8433,7 @@
         <v>2028</v>
       </c>
       <c r="D621">
-        <v>240705.2568939184</v>
+        <v>207924.6133009189</v>
       </c>
     </row>
     <row r="622">
@@ -8472,7 +8472,7 @@
         <v>2026</v>
       </c>
       <c r="D624">
-        <v>179609.2140971918</v>
+        <v>155239.5064070644</v>
       </c>
     </row>
     <row r="625">
@@ -8485,7 +8485,7 @@
         <v>2027</v>
       </c>
       <c r="D625">
-        <v>207923.4724925383</v>
+        <v>179617.9086694608</v>
       </c>
     </row>
     <row r="626">
@@ -8498,7 +8498,7 @@
         <v>2028</v>
       </c>
       <c r="D626">
-        <v>240705.2568939184</v>
+        <v>207924.6133009189</v>
       </c>
     </row>
     <row r="627">
@@ -8537,7 +8537,7 @@
         <v>2026</v>
       </c>
       <c r="D629">
-        <v>212379.200233795</v>
+        <v>187510.4335980942</v>
       </c>
     </row>
     <row r="630">
@@ -8550,7 +8550,7 @@
         <v>2027</v>
       </c>
       <c r="D630">
-        <v>240595.9471752125</v>
+        <v>212382.1558800192</v>
       </c>
     </row>
     <row r="631">
@@ -8563,7 +8563,7 @@
         <v>2028</v>
       </c>
       <c r="D631">
-        <v>272562.5371672182</v>
+        <v>240596.2296126256</v>
       </c>
     </row>
     <row r="632">
@@ -8602,7 +8602,7 @@
         <v>2026</v>
       </c>
       <c r="D634">
-        <v>265937.2030728207</v>
+        <v>241818.8031931348</v>
       </c>
     </row>
     <row r="635">
@@ -8615,7 +8615,7 @@
         <v>2027</v>
       </c>
       <c r="D635">
-        <v>292462.0854805097</v>
+        <v>265937.2140715529</v>
       </c>
     </row>
     <row r="636">
@@ -8628,7 +8628,7 @@
         <v>2028</v>
       </c>
       <c r="D636">
-        <v>321632.5906725196</v>
+        <v>292462.0856365482</v>
       </c>
     </row>
     <row r="637">
@@ -8667,7 +8667,7 @@
         <v>2026</v>
       </c>
       <c r="D639">
-        <v>258022.8074432346</v>
+        <v>230427.8932615744</v>
       </c>
     </row>
     <row r="640">
@@ -8680,7 +8680,7 @@
         <v>2027</v>
       </c>
       <c r="D640">
-        <v>289007.4112428436</v>
+        <v>258029.4569281852</v>
       </c>
     </row>
     <row r="641">
@@ -8693,7 +8693,7 @@
         <v>2028</v>
       </c>
       <c r="D641">
-        <v>323715.76495655</v>
+        <v>289008.2955709007</v>
       </c>
     </row>
     <row r="642">
@@ -8732,7 +8732,7 @@
         <v>2026</v>
       </c>
       <c r="D644">
-        <v>260786.6773118163</v>
+        <v>232943.6667820439</v>
       </c>
     </row>
     <row r="645">
@@ -8745,7 +8745,7 @@
         <v>2027</v>
       </c>
       <c r="D645">
-        <v>292057.0869140218</v>
+        <v>260794.8863651546</v>
       </c>
     </row>
     <row r="646">
@@ -8758,7 +8758,7 @@
         <v>2028</v>
       </c>
       <c r="D646">
-        <v>327081.0208504402</v>
+        <v>292058.2631891792</v>
       </c>
     </row>
     <row r="647">
@@ -8797,7 +8797,7 @@
         <v>2026</v>
       </c>
       <c r="D649">
-        <v>313232.7355075887</v>
+        <v>287523.0002731558</v>
       </c>
     </row>
     <row r="650">
@@ -8810,7 +8810,7 @@
         <v>2027</v>
       </c>
       <c r="D650">
-        <v>341531.4991818194</v>
+        <v>313264.8006110343</v>
       </c>
     </row>
     <row r="651">
@@ -8823,7 +8823,7 @@
         <v>2028</v>
       </c>
       <c r="D651">
-        <v>372408.4615176573</v>
+        <v>341538.0930719335</v>
       </c>
     </row>
     <row r="652">
@@ -8862,7 +8862,7 @@
         <v>2026</v>
       </c>
       <c r="D654">
-        <v>208821.2199137375</v>
+        <v>186058.6459123499</v>
       </c>
     </row>
     <row r="655">
@@ -8875,7 +8875,7 @@
         <v>2027</v>
       </c>
       <c r="D655">
-        <v>234390.2958941993</v>
+        <v>208819.5369586506</v>
       </c>
     </row>
     <row r="656">
@@ -8888,7 +8888,7 @@
         <v>2028</v>
       </c>
       <c r="D656">
-        <v>263090.6116036313</v>
+        <v>234390.4262373376</v>
       </c>
     </row>
     <row r="657">
@@ -8927,7 +8927,7 @@
         <v>2026</v>
       </c>
       <c r="D659">
-        <v>205907.1257719559</v>
+        <v>183182.8113035031</v>
       </c>
     </row>
     <row r="660">
@@ -8940,7 +8940,7 @@
         <v>2027</v>
       </c>
       <c r="D660">
-        <v>231479.9609448984</v>
+        <v>205904.2667096594</v>
       </c>
     </row>
     <row r="661">
@@ -8953,7 +8953,7 @@
         <v>2028</v>
       </c>
       <c r="D661">
-        <v>260229.729061073</v>
+        <v>231480.2248008847</v>
       </c>
     </row>
     <row r="662">
@@ -8992,7 +8992,7 @@
         <v>2026</v>
       </c>
       <c r="D664">
-        <v>205907.1257719559</v>
+        <v>183182.8113035031</v>
       </c>
     </row>
     <row r="665">
@@ -9005,7 +9005,7 @@
         <v>2027</v>
       </c>
       <c r="D665">
-        <v>231479.9609448984</v>
+        <v>205904.2667096594</v>
       </c>
     </row>
     <row r="666">
@@ -9018,7 +9018,7 @@
         <v>2028</v>
       </c>
       <c r="D666">
-        <v>260229.729061073</v>
+        <v>231480.2248008847</v>
       </c>
     </row>
     <row r="667">
@@ -9057,7 +9057,7 @@
         <v>2026</v>
       </c>
       <c r="D669">
-        <v>206652.1525802338</v>
+        <v>183884.2918757344</v>
       </c>
     </row>
     <row r="670">
@@ -9070,7 +9070,7 @@
         <v>2027</v>
       </c>
       <c r="D670">
-        <v>232267.6951671139</v>
+        <v>206649.4364342981</v>
       </c>
     </row>
     <row r="671">
@@ -9083,7 +9083,7 @@
         <v>2028</v>
       </c>
       <c r="D671">
-        <v>261059.2403468347</v>
+        <v>232267.9416502477</v>
       </c>
     </row>
     <row r="672">
@@ -9122,7 +9122,7 @@
         <v>2026</v>
       </c>
       <c r="D674">
-        <v>205907.1257719559</v>
+        <v>183182.8113035031</v>
       </c>
     </row>
     <row r="675">
@@ -9135,7 +9135,7 @@
         <v>2027</v>
       </c>
       <c r="D675">
-        <v>231479.9609448984</v>
+        <v>205904.2667096594</v>
       </c>
     </row>
     <row r="676">
@@ -9148,7 +9148,7 @@
         <v>2028</v>
       </c>
       <c r="D676">
-        <v>260229.729061073</v>
+        <v>231480.2248008847</v>
       </c>
     </row>
     <row r="677">
@@ -9187,7 +9187,7 @@
         <v>2026</v>
       </c>
       <c r="D679">
-        <v>238219.6120979452</v>
+        <v>213047.2612708629</v>
       </c>
     </row>
     <row r="680">
@@ -9200,7 +9200,7 @@
         <v>2027</v>
       </c>
       <c r="D680">
-        <v>266398.7744010065</v>
+        <v>238221.3175322081</v>
       </c>
     </row>
     <row r="681">
@@ -9213,7 +9213,7 @@
         <v>2028</v>
       </c>
       <c r="D681">
-        <v>297911.7231871804</v>
+        <v>266398.9097052668</v>
       </c>
     </row>
     <row r="682">
@@ -9252,7 +9252,7 @@
         <v>2026</v>
       </c>
       <c r="D684">
-        <v>231383.9294820002</v>
+        <v>209475.2644608464</v>
       </c>
     </row>
     <row r="685">
@@ -9265,7 +9265,7 @@
         <v>2027</v>
       </c>
       <c r="D685">
-        <v>257377.4116350598</v>
+        <v>231684.6372883838</v>
       </c>
     </row>
     <row r="686">
@@ -9278,7 +9278,7 @@
         <v>2028</v>
       </c>
       <c r="D686">
-        <v>286759.27118353</v>
+        <v>257517.6673209237</v>
       </c>
     </row>
     <row r="687">
@@ -9317,7 +9317,7 @@
         <v>2026</v>
       </c>
       <c r="D689">
-        <v>252453.4813323453</v>
+        <v>227720.9376320322</v>
       </c>
     </row>
     <row r="690">
@@ -9330,7 +9330,7 @@
         <v>2027</v>
       </c>
       <c r="D690">
-        <v>281164.9630901179</v>
+        <v>252646.6207272556</v>
       </c>
     </row>
     <row r="691">
@@ -9343,7 +9343,7 @@
         <v>2028</v>
       </c>
       <c r="D691">
-        <v>313379.3001120143</v>
+        <v>281236.0289255272</v>
       </c>
     </row>
     <row r="692">
@@ -9382,7 +9382,7 @@
         <v>2026</v>
       </c>
       <c r="D694">
-        <v>343007.5912093547</v>
+        <v>309862.565276546</v>
       </c>
     </row>
     <row r="695">
@@ -9395,7 +9395,7 @@
         <v>2027</v>
       </c>
       <c r="D695">
-        <v>379698.5059762803</v>
+        <v>343007.5937048209</v>
       </c>
     </row>
     <row r="696">
@@ -9408,7 +9408,7 @@
         <v>2028</v>
       </c>
       <c r="D696">
-        <v>420314.1829927404</v>
+        <v>379698.5059928267</v>
       </c>
     </row>
     <row r="697">
@@ -9447,7 +9447,7 @@
         <v>2026</v>
       </c>
       <c r="D699">
-        <v>168783.7910555859</v>
+        <v>142945.9426211637</v>
       </c>
     </row>
     <row r="700">
@@ -9460,7 +9460,7 @@
         <v>2027</v>
       </c>
       <c r="D700">
-        <v>199292.8311895965</v>
+        <v>168783.7986805491</v>
       </c>
     </row>
     <row r="701">
@@ -9473,7 +9473,7 @@
         <v>2028</v>
       </c>
       <c r="D701">
-        <v>235316.6282651318</v>
+        <v>199292.8312789829</v>
       </c>
     </row>
     <row r="702">
@@ -9512,7 +9512,7 @@
         <v>2026</v>
       </c>
       <c r="D704">
-        <v>168783.7910555859</v>
+        <v>142945.9426211637</v>
       </c>
     </row>
     <row r="705">
@@ -9525,7 +9525,7 @@
         <v>2027</v>
       </c>
       <c r="D705">
-        <v>199292.8311895965</v>
+        <v>168783.7986805491</v>
       </c>
     </row>
     <row r="706">
@@ -9538,7 +9538,7 @@
         <v>2028</v>
       </c>
       <c r="D706">
-        <v>235316.6282651318</v>
+        <v>199292.8312789829</v>
       </c>
     </row>
     <row r="707">
@@ -9577,7 +9577,7 @@
         <v>2026</v>
       </c>
       <c r="D709">
-        <v>168783.7910555859</v>
+        <v>142945.9426211637</v>
       </c>
     </row>
     <row r="710">
@@ -9590,7 +9590,7 @@
         <v>2027</v>
       </c>
       <c r="D710">
-        <v>199292.8311895965</v>
+        <v>168783.7986805491</v>
       </c>
     </row>
     <row r="711">
@@ -9603,7 +9603,7 @@
         <v>2028</v>
       </c>
       <c r="D711">
-        <v>235316.6282651318</v>
+        <v>199292.8312789829</v>
       </c>
     </row>
     <row r="712">
@@ -9642,7 +9642,7 @@
         <v>2026</v>
       </c>
       <c r="D714">
-        <v>205990.6279321154</v>
+        <v>179613.8613634334</v>
       </c>
     </row>
     <row r="715">
@@ -9655,7 +9655,7 @@
         <v>2027</v>
       </c>
       <c r="D715">
-        <v>236262.6066111528</v>
+        <v>205989.5046387402</v>
       </c>
     </row>
     <row r="716">
@@ -9668,7 +9668,7 @@
         <v>2028</v>
       </c>
       <c r="D716">
-        <v>270983.5191790374</v>
+        <v>236262.6714997333</v>
       </c>
     </row>
     <row r="717">
@@ -9707,7 +9707,7 @@
         <v>2026</v>
       </c>
       <c r="D719">
-        <v>343007.5912081982</v>
+        <v>309862.565275585</v>
       </c>
     </row>
     <row r="720">
@@ -9720,7 +9720,7 @@
         <v>2027</v>
       </c>
       <c r="D720">
-        <v>379698.505974901</v>
+        <v>343007.5937036644</v>
       </c>
     </row>
     <row r="721">
@@ -9733,7 +9733,7 @@
         <v>2028</v>
       </c>
       <c r="D721">
-        <v>420314.1829911045</v>
+        <v>379698.5059914481</v>
       </c>
     </row>
     <row r="722">
@@ -9772,7 +9772,7 @@
         <v>2026</v>
       </c>
       <c r="D724">
-        <v>262469.6055368262</v>
+        <v>236430.1104585481</v>
       </c>
     </row>
     <row r="725">
@@ -9785,7 +9785,7 @@
         <v>2027</v>
       </c>
       <c r="D725">
-        <v>292388.0873309211</v>
+        <v>262609.3019566659</v>
       </c>
     </row>
     <row r="726">
@@ -9798,7 +9798,7 @@
         <v>2028</v>
       </c>
       <c r="D726">
-        <v>325865.0837264584</v>
+        <v>292432.4125252917</v>
       </c>
     </row>
     <row r="727">
@@ -9837,7 +9837,7 @@
         <v>2026</v>
       </c>
       <c r="D729">
-        <v>231383.9294820002</v>
+        <v>209475.2644608464</v>
       </c>
     </row>
     <row r="730">
@@ -9850,7 +9850,7 @@
         <v>2027</v>
       </c>
       <c r="D730">
-        <v>257377.4116350598</v>
+        <v>231684.6372883838</v>
       </c>
     </row>
     <row r="731">
@@ -9863,7 +9863,7 @@
         <v>2028</v>
       </c>
       <c r="D731">
-        <v>286759.27118353</v>
+        <v>257517.6673209237</v>
       </c>
     </row>
     <row r="732">
@@ -9902,7 +9902,7 @@
         <v>2026</v>
       </c>
       <c r="D734">
-        <v>255904.9636129032</v>
+        <v>230716.6841534972</v>
       </c>
     </row>
     <row r="735">
@@ -9915,7 +9915,7 @@
         <v>2027</v>
       </c>
       <c r="D735">
-        <v>285040.0251563397</v>
+        <v>256079.3979248046</v>
       </c>
     </row>
     <row r="736">
@@ -9928,7 +9928,7 @@
         <v>2028</v>
       </c>
       <c r="D736">
-        <v>317696.6147323789</v>
+        <v>285101.2019019449</v>
       </c>
     </row>
     <row r="737">
@@ -9967,7 +9967,7 @@
         <v>2026</v>
       </c>
       <c r="D739">
-        <v>336756.7761455744</v>
+        <v>304983.8915083713</v>
       </c>
     </row>
     <row r="740">
@@ -9980,7 +9980,7 @@
         <v>2027</v>
       </c>
       <c r="D740">
-        <v>371846.5390186359</v>
+        <v>336756.9074103047</v>
       </c>
     </row>
     <row r="741">
@@ -9993,7 +9993,7 @@
         <v>2028</v>
       </c>
       <c r="D741">
-        <v>410592.6355404828</v>
+        <v>371846.542311742</v>
       </c>
     </row>
     <row r="742">
@@ -10032,7 +10032,7 @@
         <v>2026</v>
       </c>
       <c r="D744">
-        <v>341490.0619023379</v>
+        <v>309365.9628899692</v>
       </c>
     </row>
     <row r="745">
@@ -10045,7 +10045,7 @@
         <v>2027</v>
       </c>
       <c r="D745">
-        <v>376951.3463265015</v>
+        <v>341490.0754853163</v>
       </c>
     </row>
     <row r="746">
@@ -10058,7 +10058,7 @@
         <v>2028</v>
       </c>
       <c r="D746">
-        <v>416095.0303636446</v>
+        <v>376951.3464845894</v>
       </c>
     </row>
     <row r="747">
@@ -10097,7 +10097,7 @@
         <v>2026</v>
       </c>
       <c r="D749">
-        <v>168783.7910555859</v>
+        <v>142945.9426211637</v>
       </c>
     </row>
     <row r="750">
@@ -10110,7 +10110,7 @@
         <v>2027</v>
       </c>
       <c r="D750">
-        <v>199292.8311895965</v>
+        <v>168783.7986805491</v>
       </c>
     </row>
     <row r="751">
@@ -10123,7 +10123,7 @@
         <v>2028</v>
       </c>
       <c r="D751">
-        <v>235316.6282651318</v>
+        <v>199292.8312789829</v>
       </c>
     </row>
     <row r="752">
@@ -10162,7 +10162,7 @@
         <v>2026</v>
       </c>
       <c r="D754">
-        <v>168783.7910555859</v>
+        <v>142945.9426211637</v>
       </c>
     </row>
     <row r="755">
@@ -10175,7 +10175,7 @@
         <v>2027</v>
       </c>
       <c r="D755">
-        <v>199292.8311895965</v>
+        <v>168783.7986805491</v>
       </c>
     </row>
     <row r="756">
@@ -10188,7 +10188,7 @@
         <v>2028</v>
       </c>
       <c r="D756">
-        <v>235316.6282651318</v>
+        <v>199292.8312789829</v>
       </c>
     </row>
     <row r="757">
@@ -10227,7 +10227,7 @@
         <v>2026</v>
       </c>
       <c r="D759">
-        <v>168783.7910555859</v>
+        <v>142945.9426211637</v>
       </c>
     </row>
     <row r="760">
@@ -10240,7 +10240,7 @@
         <v>2027</v>
       </c>
       <c r="D760">
-        <v>199292.8311895965</v>
+        <v>168783.7986805491</v>
       </c>
     </row>
     <row r="761">
@@ -10253,7 +10253,7 @@
         <v>2028</v>
       </c>
       <c r="D761">
-        <v>235316.6282651318</v>
+        <v>199292.8312789829</v>
       </c>
     </row>
     <row r="762">
@@ -10292,7 +10292,7 @@
         <v>2026</v>
       </c>
       <c r="D764">
-        <v>170307.5204993238</v>
+        <v>144371.299445731</v>
       </c>
     </row>
     <row r="765">
@@ -10305,7 +10305,7 @@
         <v>2027</v>
       </c>
       <c r="D765">
-        <v>200909.7795162045</v>
+        <v>170307.655616793</v>
       </c>
     </row>
     <row r="766">
@@ -10318,7 +10318,7 @@
         <v>2028</v>
       </c>
       <c r="D766">
-        <v>237010.9193297708</v>
+        <v>200909.7836591398</v>
       </c>
     </row>
     <row r="767">
@@ -10357,7 +10357,7 @@
         <v>2026</v>
       </c>
       <c r="D769">
-        <v>205292.9183762159</v>
+        <v>182740.0365596495</v>
       </c>
     </row>
     <row r="770">
@@ -10370,7 +10370,7 @@
         <v>2027</v>
       </c>
       <c r="D770">
-        <v>233232.7567249403</v>
+        <v>205750.2328642244</v>
       </c>
     </row>
     <row r="771">
@@ -10383,7 +10383,7 @@
         <v>2028</v>
       </c>
       <c r="D771">
-        <v>265841.5002218289</v>
+        <v>233486.6734670292</v>
       </c>
     </row>
     <row r="772">
@@ -10422,7 +10422,7 @@
         <v>2026</v>
       </c>
       <c r="D774">
-        <v>192374.2044560037</v>
+        <v>168603.6401980227</v>
       </c>
     </row>
     <row r="775">
@@ -10435,7 +10435,7 @@
         <v>2027</v>
       </c>
       <c r="D775">
-        <v>221299.2517672461</v>
+        <v>192658.3357131263</v>
       </c>
     </row>
     <row r="776">
@@ -10448,7 +10448,7 @@
         <v>2028</v>
       </c>
       <c r="D776">
-        <v>255016.9535400195</v>
+        <v>221427.6980855008</v>
       </c>
     </row>
     <row r="777">
@@ -10487,7 +10487,7 @@
         <v>2026</v>
       </c>
       <c r="D779">
-        <v>202400.036695902</v>
+        <v>178174.6275353663</v>
       </c>
     </row>
     <row r="780">
@@ -10500,7 +10500,7 @@
         <v>2027</v>
       </c>
       <c r="D780">
-        <v>231769.4432677363</v>
+        <v>202692.6194268643</v>
       </c>
     </row>
     <row r="781">
@@ -10513,7 +10513,7 @@
         <v>2028</v>
       </c>
       <c r="D781">
-        <v>265852.1944232216</v>
+        <v>231900.8486579407</v>
       </c>
     </row>
     <row r="782">
@@ -10552,7 +10552,7 @@
         <v>2026</v>
       </c>
       <c r="D784">
-        <v>294490.3286115596</v>
+        <v>266917.5684611124</v>
       </c>
     </row>
     <row r="785">
@@ -10565,7 +10565,7 @@
         <v>2027</v>
       </c>
       <c r="D785">
-        <v>324916.3214326671</v>
+        <v>294490.4142516046</v>
       </c>
     </row>
     <row r="786">
@@ -10578,7 +10578,7 @@
         <v>2028</v>
       </c>
       <c r="D786">
-        <v>358485.8568923848</v>
+        <v>324916.3233464911</v>
       </c>
     </row>
     <row r="787">
@@ -10617,7 +10617,7 @@
         <v>2026</v>
       </c>
       <c r="D789">
-        <v>409734.3834982847</v>
+        <v>383219.5811209911</v>
       </c>
     </row>
     <row r="790">
@@ -10630,7 +10630,7 @@
         <v>2027</v>
       </c>
       <c r="D790">
-        <v>441437.4407215411</v>
+        <v>410317.475160171</v>
       </c>
     </row>
     <row r="791">
@@ -10643,7 +10643,7 @@
         <v>2028</v>
       </c>
       <c r="D791">
-        <v>476453.0434768921</v>
+        <v>441703.2148957663</v>
       </c>
     </row>
     <row r="792">
@@ -10682,7 +10682,7 @@
         <v>2026</v>
       </c>
       <c r="D794">
-        <v>409734.3834982847</v>
+        <v>383219.5811209911</v>
       </c>
     </row>
     <row r="795">
@@ -10695,7 +10695,7 @@
         <v>2027</v>
       </c>
       <c r="D795">
-        <v>441437.4407215411</v>
+        <v>410317.475160171</v>
       </c>
     </row>
     <row r="796">
@@ -10708,7 +10708,7 @@
         <v>2028</v>
       </c>
       <c r="D796">
-        <v>476453.0434768921</v>
+        <v>441703.2148957663</v>
       </c>
     </row>
     <row r="797">
@@ -10747,7 +10747,7 @@
         <v>2026</v>
       </c>
       <c r="D799">
-        <v>369208.9377357886</v>
+        <v>341354.7728353556</v>
       </c>
     </row>
     <row r="800">
@@ -10760,7 +10760,7 @@
         <v>2027</v>
       </c>
       <c r="D800">
-        <v>401053.6618924176</v>
+        <v>369464.8161158978</v>
       </c>
     </row>
     <row r="801">
@@ -10773,7 +10773,7 @@
         <v>2028</v>
       </c>
       <c r="D801">
-        <v>435928.4932680223</v>
+        <v>401140.6274120216</v>
       </c>
     </row>
     <row r="802">
@@ -10812,7 +10812,7 @@
         <v>2026</v>
       </c>
       <c r="D804">
-        <v>371284.1807334778</v>
+        <v>358949.7903808304</v>
       </c>
     </row>
     <row r="805">
@@ -10825,7 +10825,7 @@
         <v>2027</v>
       </c>
       <c r="D805">
-        <v>386101.3378687893</v>
+        <v>371640.1601711105</v>
       </c>
     </row>
     <row r="806">
@@ -10838,7 +10838,7 @@
         <v>2028</v>
       </c>
       <c r="D806">
-        <v>401957.5768311861</v>
+        <v>386244.8103394544</v>
       </c>
     </row>
     <row r="807">
@@ -10877,7 +10877,7 @@
         <v>2026</v>
       </c>
       <c r="D809">
-        <v>383847.9900097605</v>
+        <v>366953.5316390537</v>
       </c>
     </row>
     <row r="810">
@@ -10890,7 +10890,7 @@
         <v>2027</v>
       </c>
       <c r="D810">
-        <v>404158.8110603074</v>
+        <v>384314.3799111735</v>
       </c>
     </row>
     <row r="811">
@@ -10903,7 +10903,7 @@
         <v>2028</v>
       </c>
       <c r="D811">
-        <v>426192.3983618908</v>
+        <v>404363.8663832605</v>
       </c>
     </row>
     <row r="812">
@@ -10942,7 +10942,7 @@
         <v>2026</v>
       </c>
       <c r="D814">
-        <v>362853.4637536003</v>
+        <v>334622.4118230866</v>
       </c>
     </row>
     <row r="815">
@@ -10955,7 +10955,7 @@
         <v>2027</v>
       </c>
       <c r="D815">
-        <v>395300.2905761518</v>
+        <v>363129.976058715</v>
       </c>
     </row>
     <row r="816">
@@ -10968,7 +10968,7 @@
         <v>2028</v>
       </c>
       <c r="D816">
-        <v>430965.6567263707</v>
+        <v>395397.2913840449</v>
       </c>
     </row>
     <row r="817">
@@ -11007,7 +11007,7 @@
         <v>2026</v>
       </c>
       <c r="D819">
-        <v>204623.522708952</v>
+        <v>182065.8224638034</v>
       </c>
     </row>
     <row r="820">
@@ -11020,7 +11020,7 @@
         <v>2027</v>
       </c>
       <c r="D820">
-        <v>232635.6403766697</v>
+        <v>205091.67813807</v>
       </c>
     </row>
     <row r="821">
@@ -11033,7 +11033,7 @@
         <v>2028</v>
       </c>
       <c r="D821">
-        <v>265376.6215385993</v>
+        <v>232897.497910312</v>
       </c>
     </row>
     <row r="822">
@@ -11072,7 +11072,7 @@
         <v>2026</v>
       </c>
       <c r="D824">
-        <v>204623.522708952</v>
+        <v>182065.8224638034</v>
       </c>
     </row>
     <row r="825">
@@ -11085,7 +11085,7 @@
         <v>2027</v>
       </c>
       <c r="D825">
-        <v>232635.6403766697</v>
+        <v>205091.67813807</v>
       </c>
     </row>
     <row r="826">
@@ -11098,7 +11098,7 @@
         <v>2028</v>
       </c>
       <c r="D826">
-        <v>265376.6215385993</v>
+        <v>232897.497910312</v>
       </c>
     </row>
     <row r="827">
@@ -11137,7 +11137,7 @@
         <v>2026</v>
       </c>
       <c r="D829">
-        <v>204623.522708952</v>
+        <v>182065.8224638034</v>
       </c>
     </row>
     <row r="830">
@@ -11150,7 +11150,7 @@
         <v>2027</v>
       </c>
       <c r="D830">
-        <v>232635.6403766697</v>
+        <v>205091.67813807</v>
       </c>
     </row>
     <row r="831">
@@ -11163,7 +11163,7 @@
         <v>2028</v>
       </c>
       <c r="D831">
-        <v>265376.6215385993</v>
+        <v>232897.497910312</v>
       </c>
     </row>
     <row r="832">
@@ -11202,7 +11202,7 @@
         <v>2026</v>
       </c>
       <c r="D834">
-        <v>204623.522708952</v>
+        <v>182065.8224638034</v>
       </c>
     </row>
     <row r="835">
@@ -11215,7 +11215,7 @@
         <v>2027</v>
       </c>
       <c r="D835">
-        <v>232635.6403766697</v>
+        <v>205091.67813807</v>
       </c>
     </row>
     <row r="836">
@@ -11228,7 +11228,7 @@
         <v>2028</v>
       </c>
       <c r="D836">
-        <v>265376.6215385993</v>
+        <v>232897.497910312</v>
       </c>
     </row>
     <row r="837">
@@ -11267,7 +11267,7 @@
         <v>2026</v>
       </c>
       <c r="D839">
-        <v>204623.522708952</v>
+        <v>182065.8224638034</v>
       </c>
     </row>
     <row r="840">
@@ -11280,7 +11280,7 @@
         <v>2027</v>
       </c>
       <c r="D840">
-        <v>232635.6403766697</v>
+        <v>205091.67813807</v>
       </c>
     </row>
     <row r="841">
@@ -11293,7 +11293,7 @@
         <v>2028</v>
       </c>
       <c r="D841">
-        <v>265376.6215385993</v>
+        <v>232897.497910312</v>
       </c>
     </row>
     <row r="842">
@@ -11332,7 +11332,7 @@
         <v>2026</v>
       </c>
       <c r="D844">
-        <v>204623.522708952</v>
+        <v>182065.8224638034</v>
       </c>
     </row>
     <row r="845">
@@ -11345,7 +11345,7 @@
         <v>2027</v>
       </c>
       <c r="D845">
-        <v>232635.6403766697</v>
+        <v>205091.67813807</v>
       </c>
     </row>
     <row r="846">
@@ -11358,7 +11358,7 @@
         <v>2028</v>
       </c>
       <c r="D846">
-        <v>265376.6215385993</v>
+        <v>232897.497910312</v>
       </c>
     </row>
     <row r="847">
@@ -11397,7 +11397,7 @@
         <v>2026</v>
       </c>
       <c r="D849">
-        <v>205627.6691195907</v>
+        <v>183072.0221817615</v>
       </c>
     </row>
     <row r="850">
@@ -11410,7 +11410,7 @@
         <v>2027</v>
       </c>
       <c r="D850">
-        <v>233538.444757263</v>
+        <v>206079.6216156358</v>
       </c>
     </row>
     <row r="851">
@@ -11423,7 +11423,7 @@
         <v>2028</v>
       </c>
       <c r="D851">
-        <v>266090.3187755329</v>
+        <v>233788.4240270539</v>
       </c>
     </row>
     <row r="852">
@@ -11462,7 +11462,7 @@
         <v>2026</v>
       </c>
       <c r="D854">
-        <v>205096.9313906876</v>
+        <v>182544.1814366574</v>
       </c>
     </row>
     <row r="855">
@@ -11475,7 +11475,7 @@
         <v>2027</v>
       </c>
       <c r="D855">
-        <v>233055.8031278225</v>
+        <v>205557.3989360381</v>
       </c>
     </row>
     <row r="856">
@@ -11488,7 +11488,7 @@
         <v>2028</v>
       </c>
       <c r="D856">
-        <v>265700.4737266998</v>
+        <v>233312.0327851917</v>
       </c>
     </row>
     <row r="857">
@@ -11527,7 +11527,7 @@
         <v>2026</v>
       </c>
       <c r="D859">
-        <v>215107.4911354785</v>
+        <v>190952.102126012</v>
       </c>
     </row>
     <row r="860">
@@ -11540,7 +11540,7 @@
         <v>2027</v>
       </c>
       <c r="D860">
-        <v>244461.2638242252</v>
+        <v>215465.3203095079</v>
       </c>
     </row>
     <row r="861">
@@ -11553,7 +11553,7 @@
         <v>2028</v>
       </c>
       <c r="D861">
-        <v>278424.4947166929</v>
+        <v>244638.239421971</v>
       </c>
     </row>
     <row r="862">
@@ -11592,7 +11592,7 @@
         <v>2026</v>
       </c>
       <c r="D864">
-        <v>207333.152170966</v>
+        <v>184372.4908882896</v>
       </c>
     </row>
     <row r="865">
@@ -11605,7 +11605,7 @@
         <v>2027</v>
       </c>
       <c r="D865">
-        <v>235706.2041505044</v>
+        <v>207777.8921406976</v>
       </c>
     </row>
     <row r="866">
@@ -11618,7 +11618,7 @@
         <v>2028</v>
       </c>
       <c r="D866">
-        <v>268790.4920339425</v>
+        <v>235948.8630175234</v>
       </c>
     </row>
     <row r="867">
@@ -11657,7 +11657,7 @@
         <v>2026</v>
       </c>
       <c r="D869">
-        <v>259159.9977077669</v>
+        <v>230607.8776274819</v>
       </c>
     </row>
     <row r="870">
@@ -11670,7 +11670,7 @@
         <v>2027</v>
       </c>
       <c r="D870">
-        <v>292133.5939051784</v>
+        <v>259272.427309345</v>
       </c>
     </row>
     <row r="871">
@@ -11683,7 +11683,7 @@
         <v>2028</v>
       </c>
       <c r="D871">
-        <v>329409.4821814721</v>
+        <v>292165.224362526</v>
       </c>
     </row>
     <row r="872">
@@ -11722,7 +11722,7 @@
         <v>2026</v>
       </c>
       <c r="D874">
-        <v>229827.0746646975</v>
+        <v>203585.8725149863</v>
       </c>
     </row>
     <row r="875">
@@ -11735,7 +11735,7 @@
         <v>2027</v>
       </c>
       <c r="D875">
-        <v>260790.1753748745</v>
+        <v>230026.0635487457</v>
       </c>
     </row>
     <row r="876">
@@ -11748,7 +11748,7 @@
         <v>2028</v>
       </c>
       <c r="D876">
-        <v>296185.2641244577</v>
+        <v>260866.6860243719</v>
       </c>
     </row>
     <row r="877">
@@ -11787,7 +11787,7 @@
         <v>2026</v>
       </c>
       <c r="D879">
-        <v>330323.0022043082</v>
+        <v>314254.7719171714</v>
       </c>
     </row>
     <row r="880">
@@ -11800,7 +11800,7 @@
         <v>2027</v>
       </c>
       <c r="D880">
-        <v>349243.7347271001</v>
+        <v>330672.9303753027</v>
       </c>
     </row>
     <row r="881">
@@ -11813,7 +11813,7 @@
         <v>2028</v>
       </c>
       <c r="D881">
-        <v>369716.1265249142</v>
+        <v>349391.1860919286</v>
       </c>
     </row>
     <row r="882">
@@ -11852,7 +11852,7 @@
         <v>2026</v>
       </c>
       <c r="D884">
-        <v>210110.7071588186</v>
+        <v>185817.2945585882</v>
       </c>
     </row>
     <row r="885">
@@ -11865,7 +11865,7 @@
         <v>2027</v>
       </c>
       <c r="D885">
-        <v>237657.8927873163</v>
+        <v>210116.0581973307</v>
       </c>
     </row>
     <row r="886">
@@ -11878,7 +11878,7 @@
         <v>2028</v>
       </c>
       <c r="D886">
-        <v>268818.8210481876</v>
+        <v>237658.5079331556</v>
       </c>
     </row>
     <row r="887">
@@ -11917,7 +11917,7 @@
         <v>2026</v>
       </c>
       <c r="D889">
-        <v>213344.6726479939</v>
+        <v>194014.5753555011</v>
       </c>
     </row>
     <row r="890">
@@ -11930,7 +11930,7 @@
         <v>2027</v>
       </c>
       <c r="D890">
-        <v>238231.8939401805</v>
+        <v>214059.1230169427</v>
       </c>
     </row>
     <row r="891">
@@ -11943,7 +11943,7 @@
         <v>2028</v>
       </c>
       <c r="D891">
-        <v>267701.0713576115</v>
+        <v>238731.9828080261</v>
       </c>
     </row>
     <row r="892">
@@ -11982,7 +11982,7 @@
         <v>2026</v>
       </c>
       <c r="D894">
-        <v>219214.7701185542</v>
+        <v>196800.0454733213</v>
       </c>
     </row>
     <row r="895">
@@ -11995,7 +11995,7 @@
         <v>2027</v>
       </c>
       <c r="D895">
-        <v>246823.295954972</v>
+        <v>219690.359770176</v>
       </c>
     </row>
     <row r="896">
@@ -12008,7 +12008,7 @@
         <v>2028</v>
       </c>
       <c r="D896">
-        <v>278830.5818144723</v>
+        <v>247095.8519755877</v>
       </c>
     </row>
     <row r="897">
@@ -12047,7 +12047,7 @@
         <v>2026</v>
       </c>
       <c r="D899">
-        <v>228791.0728986891</v>
+        <v>202608.7664235221</v>
       </c>
     </row>
     <row r="900">
@@ -12060,7 +12060,7 @@
         <v>2027</v>
       </c>
       <c r="D900">
-        <v>259703.604680251</v>
+        <v>228991.8043790683</v>
       </c>
     </row>
     <row r="901">
@@ -12073,7 +12073,7 @@
         <v>2028</v>
       </c>
       <c r="D901">
-        <v>295057.7365314614</v>
+        <v>259781.3801060588</v>
       </c>
     </row>
     <row r="902">
@@ -12112,7 +12112,7 @@
         <v>2026</v>
       </c>
       <c r="D904">
-        <v>228791.0728986891</v>
+        <v>202608.7664235221</v>
       </c>
     </row>
     <row r="905">
@@ -12125,7 +12125,7 @@
         <v>2027</v>
       </c>
       <c r="D905">
-        <v>259703.604680251</v>
+        <v>228991.8043790683</v>
       </c>
     </row>
     <row r="906">
@@ -12138,7 +12138,7 @@
         <v>2028</v>
       </c>
       <c r="D906">
-        <v>295057.7365314614</v>
+        <v>259781.3801060588</v>
       </c>
     </row>
     <row r="907">
@@ -12177,7 +12177,7 @@
         <v>2026</v>
       </c>
       <c r="D909">
-        <v>228791.0728986891</v>
+        <v>202608.7664235221</v>
       </c>
     </row>
     <row r="910">
@@ -12190,7 +12190,7 @@
         <v>2027</v>
       </c>
       <c r="D910">
-        <v>259703.604680251</v>
+        <v>228991.8043790683</v>
       </c>
     </row>
     <row r="911">
@@ -12203,7 +12203,7 @@
         <v>2028</v>
       </c>
       <c r="D911">
-        <v>295057.7365314614</v>
+        <v>259781.3801060588</v>
       </c>
     </row>
     <row r="912">
@@ -12242,7 +12242,7 @@
         <v>2026</v>
       </c>
       <c r="D914">
-        <v>228791.0727591328</v>
+        <v>202608.7663330379</v>
       </c>
     </row>
     <row r="915">
@@ -12255,7 +12255,7 @@
         <v>2027</v>
       </c>
       <c r="D915">
-        <v>259703.6044954053</v>
+        <v>228991.804242394</v>
       </c>
     </row>
     <row r="916">
@@ -12268,7 +12268,7 @@
         <v>2028</v>
       </c>
       <c r="D916">
-        <v>295057.7362970568</v>
+        <v>259781.3799228121</v>
       </c>
     </row>
     <row r="917">
@@ -12307,7 +12307,7 @@
         <v>2026</v>
       </c>
       <c r="D919">
-        <v>228791.0728986891</v>
+        <v>202608.7664235221</v>
       </c>
     </row>
     <row r="920">
@@ -12320,7 +12320,7 @@
         <v>2027</v>
       </c>
       <c r="D920">
-        <v>259703.604680251</v>
+        <v>228991.8043790683</v>
       </c>
     </row>
     <row r="921">
@@ -12333,7 +12333,7 @@
         <v>2028</v>
       </c>
       <c r="D921">
-        <v>295057.7365314614</v>
+        <v>259781.3801060588</v>
       </c>
     </row>
     <row r="922">
@@ -12372,7 +12372,7 @@
         <v>2026</v>
       </c>
       <c r="D924">
-        <v>228791.0728986891</v>
+        <v>202608.7664235221</v>
       </c>
     </row>
     <row r="925">
@@ -12385,7 +12385,7 @@
         <v>2027</v>
       </c>
       <c r="D925">
-        <v>259703.604680251</v>
+        <v>228991.8043790683</v>
       </c>
     </row>
     <row r="926">
@@ -12398,7 +12398,7 @@
         <v>2028</v>
       </c>
       <c r="D926">
-        <v>295057.7365314614</v>
+        <v>259781.3801060588</v>
       </c>
     </row>
     <row r="927">
@@ -12437,7 +12437,7 @@
         <v>2026</v>
       </c>
       <c r="D929">
-        <v>228791.0728986891</v>
+        <v>202608.7664235221</v>
       </c>
     </row>
     <row r="930">
@@ -12450,7 +12450,7 @@
         <v>2027</v>
       </c>
       <c r="D930">
-        <v>259703.604680251</v>
+        <v>228991.8043790683</v>
       </c>
     </row>
     <row r="931">
@@ -12463,7 +12463,7 @@
         <v>2028</v>
       </c>
       <c r="D931">
-        <v>295057.7365314614</v>
+        <v>259781.3801060588</v>
       </c>
     </row>
     <row r="932">
@@ -12502,7 +12502,7 @@
         <v>2026</v>
       </c>
       <c r="D934">
-        <v>213045.8053338358</v>
+        <v>193511.521336636</v>
       </c>
     </row>
     <row r="935">
@@ -12515,7 +12515,7 @@
         <v>2027</v>
       </c>
       <c r="D935">
-        <v>237878.6051564449</v>
+        <v>213693.0531427103</v>
       </c>
     </row>
     <row r="936">
@@ -12528,7 +12528,7 @@
         <v>2028</v>
       </c>
       <c r="D936">
-        <v>267081.5416259561</v>
+        <v>238318.3125567015</v>
       </c>
     </row>
     <row r="937">
@@ -12567,7 +12567,7 @@
         <v>2026</v>
       </c>
       <c r="D939">
-        <v>212705.0179295561</v>
+        <v>193475.9549046597</v>
       </c>
     </row>
     <row r="940">
@@ -12580,7 +12580,7 @@
         <v>2027</v>
       </c>
       <c r="D940">
-        <v>237326.165024745</v>
+        <v>213388.485097455</v>
       </c>
     </row>
     <row r="941">
@@ -12593,7 +12593,7 @@
         <v>2028</v>
       </c>
       <c r="D941">
-        <v>266388.9709115258</v>
+        <v>237800.7385134164</v>
       </c>
     </row>
     <row r="942">
@@ -12632,7 +12632,7 @@
         <v>2026</v>
       </c>
       <c r="D944">
-        <v>213344.6726479939</v>
+        <v>194014.5753555011</v>
       </c>
     </row>
     <row r="945">
@@ -12645,7 +12645,7 @@
         <v>2027</v>
       </c>
       <c r="D945">
-        <v>238231.8939401805</v>
+        <v>214059.1230169427</v>
       </c>
     </row>
     <row r="946">
@@ -12658,7 +12658,7 @@
         <v>2028</v>
       </c>
       <c r="D946">
-        <v>267701.0713576115</v>
+        <v>238731.9828080261</v>
       </c>
     </row>
     <row r="947">
@@ -12697,7 +12697,7 @@
         <v>2026</v>
       </c>
       <c r="D949">
-        <v>264050.8799413288</v>
+        <v>237808.256898012</v>
       </c>
     </row>
     <row r="950">
@@ -12710,7 +12710,7 @@
         <v>2027</v>
       </c>
       <c r="D950">
-        <v>293198.1872329448</v>
+        <v>264051.1564745435</v>
       </c>
     </row>
     <row r="951">
@@ -12723,7 +12723,7 @@
         <v>2028</v>
       </c>
       <c r="D951">
-        <v>325562.9657379615</v>
+        <v>293198.19926432</v>
       </c>
     </row>
     <row r="952">
@@ -12762,7 +12762,7 @@
         <v>2026</v>
       </c>
       <c r="D954">
-        <v>168783.7910555859</v>
+        <v>142945.9426211637</v>
       </c>
     </row>
     <row r="955">
@@ -12775,7 +12775,7 @@
         <v>2027</v>
       </c>
       <c r="D955">
-        <v>199292.8311895965</v>
+        <v>168783.7986805491</v>
       </c>
     </row>
     <row r="956">
@@ -12788,7 +12788,7 @@
         <v>2028</v>
       </c>
       <c r="D956">
-        <v>235316.6282651318</v>
+        <v>199292.8312789829</v>
       </c>
     </row>
     <row r="957">
@@ -12827,7 +12827,7 @@
         <v>2026</v>
       </c>
       <c r="D959">
-        <v>168783.791055919</v>
+        <v>142945.9426214006</v>
       </c>
     </row>
     <row r="960">
@@ -12840,7 +12840,7 @@
         <v>2027</v>
       </c>
       <c r="D960">
-        <v>199292.8311900514</v>
+        <v>168783.7986808819</v>
       </c>
     </row>
     <row r="961">
@@ -12853,7 +12853,7 @@
         <v>2028</v>
       </c>
       <c r="D961">
-        <v>235316.6282657413</v>
+        <v>199292.8312794374</v>
       </c>
     </row>
     <row r="962">
@@ -12892,7 +12892,7 @@
         <v>2026</v>
       </c>
       <c r="D964">
-        <v>207314.0314540845</v>
+        <v>185839.571885252</v>
       </c>
     </row>
     <row r="965">
@@ -12905,7 +12905,7 @@
         <v>2027</v>
       </c>
       <c r="D965">
-        <v>231425.5221604517</v>
+        <v>207327.9752692725</v>
       </c>
     </row>
     <row r="966">
@@ -12918,7 +12918,7 @@
         <v>2028</v>
       </c>
       <c r="D966">
-        <v>258348.7283870816</v>
+        <v>231427.7461745699</v>
       </c>
     </row>
     <row r="967">
@@ -12957,7 +12957,7 @@
         <v>2026</v>
       </c>
       <c r="D969">
-        <v>207251.949792317</v>
+        <v>185867.4558853358</v>
       </c>
     </row>
     <row r="970">
@@ -12970,7 +12970,7 @@
         <v>2027</v>
       </c>
       <c r="D970">
-        <v>231261.2307858785</v>
+        <v>207266.9811141192</v>
       </c>
     </row>
     <row r="971">
@@ -12983,7 +12983,7 @@
         <v>2028</v>
       </c>
       <c r="D971">
-        <v>258060.1340902369</v>
+        <v>231263.6941920996</v>
       </c>
     </row>
     <row r="972">
@@ -13022,7 +13022,7 @@
         <v>2026</v>
       </c>
       <c r="D974">
-        <v>243877.2064528882</v>
+        <v>218522.6479431362</v>
       </c>
     </row>
     <row r="975">
@@ -13035,7 +13035,7 @@
         <v>2027</v>
       </c>
       <c r="D975">
-        <v>272208.525925965</v>
+        <v>243873.793326335</v>
       </c>
     </row>
     <row r="976">
@@ -13048,7 +13048,7 @@
         <v>2028</v>
       </c>
       <c r="D976">
-        <v>303832.1548557578</v>
+        <v>272208.8388842047</v>
       </c>
     </row>
     <row r="977">
@@ -13087,7 +13087,7 @@
         <v>2026</v>
       </c>
       <c r="D979">
-        <v>239437.4365925901</v>
+        <v>214232.4366757724</v>
       </c>
     </row>
     <row r="980">
@@ -13100,7 +13100,7 @@
         <v>2027</v>
       </c>
       <c r="D980">
-        <v>267636.4240960814</v>
+        <v>239435.0531447549</v>
       </c>
     </row>
     <row r="981">
@@ -13113,7 +13113,7 @@
         <v>2028</v>
       </c>
       <c r="D981">
-        <v>299157.1094721097</v>
+        <v>267636.6182990943</v>
       </c>
     </row>
     <row r="982">
@@ -13152,7 +13152,7 @@
         <v>2026</v>
       </c>
       <c r="D984">
-        <v>271739.9989438782</v>
+        <v>247222.077796373</v>
       </c>
     </row>
     <row r="985">
@@ -13165,7 +13165,7 @@
         <v>2027</v>
       </c>
       <c r="D985">
-        <v>298689.484983733</v>
+        <v>271739.9988754472</v>
       </c>
     </row>
     <row r="986">
@@ -13178,7 +13178,7 @@
         <v>2028</v>
       </c>
       <c r="D986">
-        <v>328311.6537379075</v>
+        <v>298689.4849839049</v>
       </c>
     </row>
     <row r="987">
@@ -13217,7 +13217,7 @@
         <v>2026</v>
       </c>
       <c r="D989">
-        <v>273750.0517216091</v>
+        <v>247585.0779466876</v>
       </c>
     </row>
     <row r="990">
@@ -13230,7 +13230,7 @@
         <v>2027</v>
       </c>
       <c r="D990">
-        <v>302704.5669450988</v>
+        <v>273748.4038976505</v>
       </c>
     </row>
     <row r="991">
@@ -13243,7 +13243,7 @@
         <v>2028</v>
       </c>
       <c r="D991">
-        <v>334721.9669735088</v>
+        <v>302704.678078649</v>
       </c>
     </row>
     <row r="992">
@@ -13282,7 +13282,7 @@
         <v>2026</v>
       </c>
       <c r="D994">
-        <v>271818.1037353462</v>
+        <v>247301.3626374819</v>
       </c>
     </row>
     <row r="995">
@@ -13295,7 +13295,7 @@
         <v>2027</v>
       </c>
       <c r="D995">
-        <v>298765.3918417389</v>
+        <v>271818.1036801805</v>
       </c>
     </row>
     <row r="996">
@@ -13308,7 +13308,7 @@
         <v>2028</v>
       </c>
       <c r="D996">
-        <v>328384.1588762314</v>
+        <v>298765.3918418684</v>
       </c>
     </row>
     <row r="997">
@@ -13347,7 +13347,7 @@
         <v>2026</v>
       </c>
       <c r="D999">
-        <v>273750.0517216091</v>
+        <v>247585.0779466876</v>
       </c>
     </row>
     <row r="1000">
@@ -13360,7 +13360,7 @@
         <v>2027</v>
       </c>
       <c r="D1000">
-        <v>302704.5669450988</v>
+        <v>273748.4038976505</v>
       </c>
     </row>
     <row r="1001">
@@ -13373,7 +13373,7 @@
         <v>2028</v>
       </c>
       <c r="D1001">
-        <v>334721.9669735088</v>
+        <v>302704.678078649</v>
       </c>
     </row>
     <row r="1002">
@@ -13412,7 +13412,7 @@
         <v>2026</v>
       </c>
       <c r="D1004">
-        <v>273708.1177815152</v>
+        <v>247573.8145315762</v>
       </c>
     </row>
     <row r="1005">
@@ -13425,7 +13425,7 @@
         <v>2027</v>
       </c>
       <c r="D1005">
-        <v>302624.7053851104</v>
+        <v>273706.5668519655</v>
       </c>
     </row>
     <row r="1006">
@@ -13438,7 +13438,7 @@
         <v>2028</v>
       </c>
       <c r="D1006">
-        <v>334596.5995973356</v>
+        <v>302624.8080231567</v>
       </c>
     </row>
     <row r="1007">
@@ -13477,7 +13477,7 @@
         <v>2026</v>
       </c>
       <c r="D1009">
-        <v>271818.1037353462</v>
+        <v>247301.3626374819</v>
       </c>
     </row>
     <row r="1010">
@@ -13490,7 +13490,7 @@
         <v>2027</v>
       </c>
       <c r="D1010">
-        <v>298765.3918417389</v>
+        <v>271818.1036801805</v>
       </c>
     </row>
     <row r="1011">
@@ -13503,7 +13503,7 @@
         <v>2028</v>
       </c>
       <c r="D1011">
-        <v>328384.1588762314</v>
+        <v>298765.3918418684</v>
       </c>
     </row>
     <row r="1012">
@@ -13542,7 +13542,7 @@
         <v>2026</v>
       </c>
       <c r="D1014">
-        <v>271479.4577239094</v>
+        <v>246957.5612536028</v>
       </c>
     </row>
     <row r="1015">
@@ -13555,7 +13555,7 @@
         <v>2027</v>
       </c>
       <c r="D1015">
-        <v>298436.3297710774</v>
+        <v>271479.4575958123</v>
       </c>
     </row>
     <row r="1016">
@@ -13568,7 +13568,7 @@
         <v>2028</v>
       </c>
       <c r="D1016">
-        <v>328069.9161340005</v>
+        <v>298436.3297714745</v>
       </c>
     </row>
     <row r="1017">
@@ -13607,7 +13607,7 @@
         <v>2026</v>
       </c>
       <c r="D1019">
-        <v>243877.2064528882</v>
+        <v>218522.6479431362</v>
       </c>
     </row>
     <row r="1020">
@@ -13620,7 +13620,7 @@
         <v>2027</v>
       </c>
       <c r="D1020">
-        <v>272208.525925965</v>
+        <v>243873.793326335</v>
       </c>
     </row>
     <row r="1021">
@@ -13633,7 +13633,7 @@
         <v>2028</v>
       </c>
       <c r="D1021">
-        <v>303832.1548557578</v>
+        <v>272208.8388842047</v>
       </c>
     </row>
     <row r="1022">
@@ -13672,7 +13672,7 @@
         <v>2026</v>
       </c>
       <c r="D1024">
-        <v>243877.2064528882</v>
+        <v>218522.6479431362</v>
       </c>
     </row>
     <row r="1025">
@@ -13685,7 +13685,7 @@
         <v>2027</v>
       </c>
       <c r="D1025">
-        <v>272208.525925965</v>
+        <v>243873.793326335</v>
       </c>
     </row>
     <row r="1026">
@@ -13698,7 +13698,7 @@
         <v>2028</v>
       </c>
       <c r="D1026">
-        <v>303832.1548557578</v>
+        <v>272208.8388842047</v>
       </c>
     </row>
     <row r="1027">
@@ -13737,7 +13737,7 @@
         <v>2026</v>
       </c>
       <c r="D1029">
-        <v>243877.2064528882</v>
+        <v>218522.6479431362</v>
       </c>
     </row>
     <row r="1030">
@@ -13750,7 +13750,7 @@
         <v>2027</v>
       </c>
       <c r="D1030">
-        <v>272208.525925965</v>
+        <v>243873.793326335</v>
       </c>
     </row>
     <row r="1031">
@@ -13763,7 +13763,7 @@
         <v>2028</v>
       </c>
       <c r="D1031">
-        <v>303832.1548557578</v>
+        <v>272208.8388842047</v>
       </c>
     </row>
     <row r="1032">
@@ -13802,7 +13802,7 @@
         <v>2026</v>
       </c>
       <c r="D1034">
-        <v>243877.2064528882</v>
+        <v>218522.6479431362</v>
       </c>
     </row>
     <row r="1035">
@@ -13815,7 +13815,7 @@
         <v>2027</v>
       </c>
       <c r="D1035">
-        <v>272208.525925965</v>
+        <v>243873.793326335</v>
       </c>
     </row>
     <row r="1036">
@@ -13828,7 +13828,7 @@
         <v>2028</v>
       </c>
       <c r="D1036">
-        <v>303832.1548557578</v>
+        <v>272208.8388842047</v>
       </c>
     </row>
     <row r="1037">
@@ -13867,7 +13867,7 @@
         <v>2026</v>
       </c>
       <c r="D1039">
-        <v>204650.426543716</v>
+        <v>180311.2070181801</v>
       </c>
     </row>
     <row r="1040">
@@ -13880,7 +13880,7 @@
         <v>2027</v>
       </c>
       <c r="D1040">
-        <v>232275.6647489435</v>
+        <v>204650.4214785869</v>
       </c>
     </row>
     <row r="1041">
@@ -13893,7 +13893,7 @@
         <v>2028</v>
       </c>
       <c r="D1041">
-        <v>263629.9634600662</v>
+        <v>232275.6648023902</v>
       </c>
     </row>
     <row r="1042">
@@ -13932,7 +13932,7 @@
         <v>2026</v>
       </c>
       <c r="D1044">
-        <v>243877.2064528882</v>
+        <v>218522.6479431362</v>
       </c>
     </row>
     <row r="1045">
@@ -13945,7 +13945,7 @@
         <v>2027</v>
       </c>
       <c r="D1045">
-        <v>272208.525925965</v>
+        <v>243873.793326335</v>
       </c>
     </row>
     <row r="1046">
@@ -13958,7 +13958,7 @@
         <v>2028</v>
       </c>
       <c r="D1046">
-        <v>303832.1548557578</v>
+        <v>272208.8388842047</v>
       </c>
     </row>
     <row r="1047">
@@ -13997,7 +13997,7 @@
         <v>2026</v>
       </c>
       <c r="D1049">
-        <v>243846.923962321</v>
+        <v>218483.9432431642</v>
       </c>
     </row>
     <row r="1050">
@@ -14010,7 +14010,7 @@
         <v>2027</v>
       </c>
       <c r="D1050">
-        <v>272188.4828991726</v>
+        <v>243843.6257876051</v>
       </c>
     </row>
     <row r="1051">
@@ -14023,7 +14023,7 @@
         <v>2028</v>
       </c>
       <c r="D1051">
-        <v>303825.0930694542</v>
+        <v>272188.7818884716</v>
       </c>
     </row>
     <row r="1052">
@@ -14062,7 +14062,7 @@
         <v>2026</v>
       </c>
       <c r="D1054">
-        <v>244003.4530868894</v>
+        <v>218559.2439257923</v>
       </c>
     </row>
     <row r="1055">
@@ -14075,7 +14075,7 @@
         <v>2027</v>
       </c>
       <c r="D1055">
-        <v>272447.9163472741</v>
+        <v>243999.5040568123</v>
       </c>
     </row>
     <row r="1056">
@@ -14088,7 +14088,7 @@
         <v>2028</v>
       </c>
       <c r="D1056">
-        <v>304209.534002327</v>
+        <v>272448.2951794608</v>
       </c>
     </row>
     <row r="1057">
@@ -14127,7 +14127,7 @@
         <v>2026</v>
       </c>
       <c r="D1059">
-        <v>243877.2064528882</v>
+        <v>218522.6479431362</v>
       </c>
     </row>
     <row r="1060">
@@ -14140,7 +14140,7 @@
         <v>2027</v>
       </c>
       <c r="D1060">
-        <v>272208.525925965</v>
+        <v>243873.793326335</v>
       </c>
     </row>
     <row r="1061">
@@ -14153,7 +14153,7 @@
         <v>2028</v>
       </c>
       <c r="D1061">
-        <v>303832.1548557578</v>
+        <v>272208.8388842047</v>
       </c>
     </row>
     <row r="1062">
@@ -14192,7 +14192,7 @@
         <v>2026</v>
       </c>
       <c r="D1064">
-        <v>353224.3242060327</v>
+        <v>325552.4147549802</v>
       </c>
     </row>
     <row r="1065">
@@ -14205,7 +14205,7 @@
         <v>2027</v>
       </c>
       <c r="D1065">
-        <v>383272.1783052991</v>
+        <v>353225.2046238869</v>
       </c>
     </row>
     <row r="1066">
@@ -14218,7 +14218,7 @@
         <v>2028</v>
       </c>
       <c r="D1066">
-        <v>415876.2651210933</v>
+        <v>383272.2218233995</v>
       </c>
     </row>
     <row r="1067">
@@ -14257,7 +14257,7 @@
         <v>2026</v>
       </c>
       <c r="D1069">
-        <v>275750.5004290138</v>
+        <v>246639.2451944523</v>
       </c>
     </row>
     <row r="1070">
@@ -14270,7 +14270,7 @@
         <v>2027</v>
       </c>
       <c r="D1070">
-        <v>308371.9031743505</v>
+        <v>275741.0640917733</v>
       </c>
     </row>
     <row r="1071">
@@ -14283,7 +14283,7 @@
         <v>2028</v>
       </c>
       <c r="D1071">
-        <v>344855.9644172157</v>
+        <v>308372.9561164529</v>
       </c>
     </row>
     <row r="1072">
@@ -14322,7 +14322,7 @@
         <v>2026</v>
       </c>
       <c r="D1074">
-        <v>317893.8680764018</v>
+        <v>291683.2480251834</v>
       </c>
     </row>
     <row r="1075">
@@ -14335,7 +14335,7 @@
         <v>2027</v>
       </c>
       <c r="D1075">
-        <v>346469.8084777088</v>
+        <v>317894.1437442131</v>
       </c>
     </row>
     <row r="1076">
@@ -14348,7 +14348,7 @@
         <v>2028</v>
       </c>
       <c r="D1076">
-        <v>377614.5138715015</v>
+        <v>346469.818358148</v>
       </c>
     </row>
     <row r="1077">
@@ -14387,7 +14387,7 @@
         <v>2026</v>
       </c>
       <c r="D1079">
-        <v>353458.7754253999</v>
+        <v>325778.963420152</v>
       </c>
     </row>
     <row r="1080">
@@ -14400,7 +14400,7 @@
         <v>2027</v>
       </c>
       <c r="D1080">
-        <v>383514.3190203005</v>
+        <v>353459.6597509771</v>
       </c>
     </row>
     <row r="1081">
@@ -14413,7 +14413,7 @@
         <v>2028</v>
       </c>
       <c r="D1081">
-        <v>416125.7082008488</v>
+        <v>383514.3627823247</v>
       </c>
     </row>
     <row r="1082">
@@ -14452,7 +14452,7 @@
         <v>2026</v>
       </c>
       <c r="D1084">
-        <v>263858.8528950249</v>
+        <v>237628.3648309114</v>
       </c>
     </row>
     <row r="1085">
@@ -14465,7 +14465,7 @@
         <v>2027</v>
       </c>
       <c r="D1085">
-        <v>292993.3890568613</v>
+        <v>263859.1227134042</v>
       </c>
     </row>
     <row r="1086">
@@ -14478,7 +14478,7 @@
         <v>2028</v>
       </c>
       <c r="D1086">
-        <v>325344.9157489813</v>
+        <v>292993.4006995918</v>
       </c>
     </row>
     <row r="1087">
@@ -14517,7 +14517,7 @@
         <v>2026</v>
       </c>
       <c r="D1089">
-        <v>205997.702098545</v>
+        <v>183268.0950057741</v>
       </c>
     </row>
     <row r="1090">
@@ -14530,7 +14530,7 @@
         <v>2027</v>
       </c>
       <c r="D1090">
-        <v>231575.7268806805</v>
+        <v>205994.8605260157</v>
       </c>
     </row>
     <row r="1091">
@@ -14543,7 +14543,7 @@
         <v>2028</v>
       </c>
       <c r="D1091">
-        <v>260330.5694881345</v>
+        <v>231575.988594984</v>
       </c>
     </row>
     <row r="1092">
@@ -14582,7 +14582,7 @@
         <v>2026</v>
       </c>
       <c r="D1094">
-        <v>264050.8799413288</v>
+        <v>237808.256898012</v>
       </c>
     </row>
     <row r="1095">
@@ -14595,7 +14595,7 @@
         <v>2027</v>
       </c>
       <c r="D1095">
-        <v>293198.1872329448</v>
+        <v>264051.1564745435</v>
       </c>
     </row>
     <row r="1096">
@@ -14608,7 +14608,7 @@
         <v>2028</v>
       </c>
       <c r="D1096">
-        <v>325562.9657379615</v>
+        <v>293198.19926432</v>
       </c>
     </row>
     <row r="1097">
@@ -14647,7 +14647,7 @@
         <v>2026</v>
       </c>
       <c r="D1099">
-        <v>215240.9494353832</v>
+        <v>192091.5735409019</v>
       </c>
     </row>
     <row r="1100">
@@ -14660,7 +14660,7 @@
         <v>2027</v>
       </c>
       <c r="D1100">
-        <v>241194.9462677319</v>
+        <v>215240.0555165232</v>
       </c>
     </row>
     <row r="1101">
@@ -14673,7 +14673,7 @@
         <v>2028</v>
       </c>
       <c r="D1101">
-        <v>270278.6943927155</v>
+        <v>241195.0024990649</v>
       </c>
     </row>
     <row r="1102">
@@ -14712,7 +14712,7 @@
         <v>2026</v>
       </c>
       <c r="D1104">
-        <v>264050.8799413288</v>
+        <v>237808.256898012</v>
       </c>
     </row>
     <row r="1105">
@@ -14725,7 +14725,7 @@
         <v>2027</v>
       </c>
       <c r="D1105">
-        <v>293198.1872329448</v>
+        <v>264051.1564745435</v>
       </c>
     </row>
     <row r="1106">
@@ -14738,7 +14738,7 @@
         <v>2028</v>
       </c>
       <c r="D1106">
-        <v>325562.9657379615</v>
+        <v>293198.19926432</v>
       </c>
     </row>
     <row r="1107">
@@ -14777,7 +14777,7 @@
         <v>2026</v>
       </c>
       <c r="D1109">
-        <v>264050.8799413288</v>
+        <v>237808.256898012</v>
       </c>
     </row>
     <row r="1110">
@@ -14790,7 +14790,7 @@
         <v>2027</v>
       </c>
       <c r="D1110">
-        <v>293198.1872329448</v>
+        <v>264051.1564745435</v>
       </c>
     </row>
     <row r="1111">
@@ -14803,7 +14803,7 @@
         <v>2028</v>
       </c>
       <c r="D1111">
-        <v>325562.9657379615</v>
+        <v>293198.19926432</v>
       </c>
     </row>
     <row r="1112">
@@ -14842,7 +14842,7 @@
         <v>2026</v>
       </c>
       <c r="D1114">
-        <v>264050.8799413288</v>
+        <v>237808.256898012</v>
       </c>
     </row>
     <row r="1115">
@@ -14855,7 +14855,7 @@
         <v>2027</v>
       </c>
       <c r="D1115">
-        <v>293198.1872329448</v>
+        <v>264051.1564745435</v>
       </c>
     </row>
     <row r="1116">
@@ -14868,7 +14868,7 @@
         <v>2028</v>
       </c>
       <c r="D1116">
-        <v>325562.9657379615</v>
+        <v>293198.19926432</v>
       </c>
     </row>
     <row r="1117">
@@ -14907,7 +14907,7 @@
         <v>2026</v>
       </c>
       <c r="D1119">
-        <v>312675.861046824</v>
+        <v>288345.2500341216</v>
       </c>
     </row>
     <row r="1120">
@@ -14920,7 +14920,7 @@
         <v>2027</v>
       </c>
       <c r="D1120">
-        <v>339197.0551360661</v>
+        <v>312687.2926588604</v>
       </c>
     </row>
     <row r="1121">
@@ -14933,7 +14933,7 @@
         <v>2028</v>
       </c>
       <c r="D1121">
-        <v>367972.7648279381</v>
+        <v>339198.5870522122</v>
       </c>
     </row>
     <row r="1122">
@@ -14972,7 +14972,7 @@
         <v>2026</v>
       </c>
       <c r="D1124">
-        <v>312675.861046824</v>
+        <v>288345.2500341216</v>
       </c>
     </row>
     <row r="1125">
@@ -14985,7 +14985,7 @@
         <v>2027</v>
       </c>
       <c r="D1125">
-        <v>339197.0551360661</v>
+        <v>312687.2926588604</v>
       </c>
     </row>
     <row r="1126">
@@ -14998,7 +14998,7 @@
         <v>2028</v>
       </c>
       <c r="D1126">
-        <v>367972.7648279381</v>
+        <v>339198.5870522122</v>
       </c>
     </row>
     <row r="1127">
@@ -15037,7 +15037,7 @@
         <v>2026</v>
       </c>
       <c r="D1129">
-        <v>312409.9391281122</v>
+        <v>288057.6954992844</v>
       </c>
     </row>
     <row r="1130">
@@ -15050,7 +15050,7 @@
         <v>2027</v>
       </c>
       <c r="D1130">
-        <v>338958.3432859245</v>
+        <v>312421.3493938503</v>
       </c>
     </row>
     <row r="1131">
@@ -15063,7 +15063,7 @@
         <v>2028</v>
       </c>
       <c r="D1131">
-        <v>367767.786812234</v>
+        <v>338959.8709084004</v>
       </c>
     </row>
     <row r="1132">
@@ -15102,7 +15102,7 @@
         <v>2026</v>
       </c>
       <c r="D1134">
-        <v>274881.3315458015</v>
+        <v>248918.4225529008</v>
       </c>
     </row>
     <row r="1135">
@@ -15115,7 +15115,7 @@
         <v>2027</v>
       </c>
       <c r="D1135">
-        <v>303864.5154323435</v>
+        <v>274914.3611099199</v>
       </c>
     </row>
     <row r="1136">
@@ -15128,7 +15128,7 @@
         <v>2028</v>
       </c>
       <c r="D1136">
-        <v>335925.4419621531</v>
+        <v>303871.0851566192</v>
       </c>
     </row>
     <row r="1137">
@@ -15167,7 +15167,7 @@
         <v>2026</v>
       </c>
       <c r="D1139">
-        <v>313272.6326561285</v>
+        <v>287333.4012015837</v>
       </c>
     </row>
     <row r="1140">
@@ -15180,7 +15180,7 @@
         <v>2027</v>
       </c>
       <c r="D1140">
-        <v>341689.3422609052</v>
+        <v>313283.7852843853</v>
       </c>
     </row>
     <row r="1141">
@@ -15193,7 +15193,7 @@
         <v>2028</v>
       </c>
       <c r="D1141">
-        <v>372688.5831040686</v>
+        <v>341690.8318874545</v>
       </c>
     </row>
     <row r="1142">
@@ -15232,7 +15232,7 @@
         <v>2026</v>
       </c>
       <c r="D1144">
-        <v>281117.17082443</v>
+        <v>256833.3489790663</v>
       </c>
     </row>
     <row r="1145">
@@ -15245,7 +15245,7 @@
         <v>2027</v>
       </c>
       <c r="D1145">
-        <v>307772.5213490571</v>
+        <v>281122.7134152005</v>
       </c>
     </row>
     <row r="1146">
@@ -15258,7 +15258,7 @@
         <v>2028</v>
       </c>
       <c r="D1146">
-        <v>336957.4266689753</v>
+        <v>307773.1642206867</v>
       </c>
     </row>
     <row r="1147">
@@ -15297,7 +15297,7 @@
         <v>2026</v>
       </c>
       <c r="D1149">
-        <v>317279.7399204466</v>
+        <v>291515.3106277023</v>
       </c>
     </row>
     <row r="1150">
@@ -15310,7 +15310,7 @@
         <v>2027</v>
       </c>
       <c r="D1150">
-        <v>345487.1829816456</v>
+        <v>317294.3985747451</v>
       </c>
     </row>
     <row r="1151">
@@ -15323,7 +15323,7 @@
         <v>2028</v>
       </c>
       <c r="D1151">
-        <v>376209.4292277241</v>
+        <v>345489.340555591</v>
       </c>
     </row>
     <row r="1152">
@@ -15362,7 +15362,7 @@
         <v>2026</v>
       </c>
       <c r="D1154">
-        <v>228791.0728986891</v>
+        <v>202608.7664235221</v>
       </c>
     </row>
     <row r="1155">
@@ -15375,7 +15375,7 @@
         <v>2027</v>
       </c>
       <c r="D1155">
-        <v>259703.604680251</v>
+        <v>228991.8043790683</v>
       </c>
     </row>
     <row r="1156">
@@ -15388,7 +15388,7 @@
         <v>2028</v>
       </c>
       <c r="D1156">
-        <v>295057.7365314614</v>
+        <v>259781.3801060588</v>
       </c>
     </row>
     <row r="1157">
@@ -15427,7 +15427,7 @@
         <v>2026</v>
       </c>
       <c r="D1159">
-        <v>311209.8769980611</v>
+        <v>285715.8709318609</v>
       </c>
     </row>
     <row r="1160">
@@ -15440,7 +15440,7 @@
         <v>2027</v>
       </c>
       <c r="D1160">
-        <v>339132.5104451982</v>
+        <v>311223.2977595943</v>
       </c>
     </row>
     <row r="1161">
@@ -15453,7 +15453,7 @@
         <v>2028</v>
       </c>
       <c r="D1161">
-        <v>369566.7985229966</v>
+        <v>339134.4548756128</v>
       </c>
     </row>
     <row r="1162">
@@ -15492,7 +15492,7 @@
         <v>2026</v>
       </c>
       <c r="D1164">
-        <v>281173.1405805672</v>
+        <v>256904.902848399</v>
       </c>
     </row>
     <row r="1165">
@@ -15505,7 +15505,7 @@
         <v>2027</v>
       </c>
       <c r="D1165">
-        <v>307810.4333174827</v>
+        <v>281178.7981864843</v>
       </c>
     </row>
     <row r="1166">
@@ -15518,7 +15518,7 @@
         <v>2028</v>
       </c>
       <c r="D1166">
-        <v>336973.415300042</v>
+        <v>307811.0945595961</v>
       </c>
     </row>
     <row r="1167">
@@ -15557,7 +15557,7 @@
         <v>2026</v>
       </c>
       <c r="D1169">
-        <v>281173.1405805672</v>
+        <v>256904.902848399</v>
       </c>
     </row>
     <row r="1170">
@@ -15570,7 +15570,7 @@
         <v>2027</v>
       </c>
       <c r="D1170">
-        <v>307810.4333174827</v>
+        <v>281178.7981864843</v>
       </c>
     </row>
     <row r="1171">
@@ -15583,7 +15583,7 @@
         <v>2028</v>
       </c>
       <c r="D1171">
-        <v>336973.415300042</v>
+        <v>307811.0945595961</v>
       </c>
     </row>
     <row r="1172">
@@ -15622,7 +15622,7 @@
         <v>2026</v>
       </c>
       <c r="D1174">
-        <v>290743.3446444619</v>
+        <v>266525.2398855627</v>
       </c>
     </row>
     <row r="1175">
@@ -15635,7 +15635,7 @@
         <v>2027</v>
       </c>
       <c r="D1175">
-        <v>317263.7537160502</v>
+        <v>290751.4054633724</v>
       </c>
     </row>
     <row r="1176">
@@ -15648,7 +15648,7 @@
         <v>2028</v>
       </c>
       <c r="D1176">
-        <v>346206.6075027224</v>
+        <v>317264.7808091015</v>
       </c>
     </row>
     <row r="1177">
@@ -15687,7 +15687,7 @@
         <v>2026</v>
       </c>
       <c r="D1179">
-        <v>297252.4721850222</v>
+        <v>273027.1963060285</v>
       </c>
     </row>
     <row r="1180">
@@ -15700,7 +15700,7 @@
         <v>2027</v>
       </c>
       <c r="D1180">
-        <v>323741.9878375013</v>
+        <v>297261.7869996103</v>
       </c>
     </row>
     <row r="1181">
@@ -15713,7 +15713,7 @@
         <v>2028</v>
       </c>
       <c r="D1181">
-        <v>352596.0906247579</v>
+        <v>323743.2078703114</v>
       </c>
     </row>
     <row r="1182">
@@ -15752,7 +15752,7 @@
         <v>2026</v>
       </c>
       <c r="D1184">
-        <v>281173.1405805672</v>
+        <v>256904.902848399</v>
       </c>
     </row>
     <row r="1185">
@@ -15765,7 +15765,7 @@
         <v>2027</v>
       </c>
       <c r="D1185">
-        <v>307810.4333174827</v>
+        <v>281178.7981864843</v>
       </c>
     </row>
     <row r="1186">
@@ -15778,7 +15778,7 @@
         <v>2028</v>
       </c>
       <c r="D1186">
-        <v>336973.415300042</v>
+        <v>307811.0945595961</v>
       </c>
     </row>
     <row r="1187">
@@ -15817,7 +15817,7 @@
         <v>2026</v>
       </c>
       <c r="D1189">
-        <v>295865.8931833606</v>
+        <v>271026.5065839178</v>
       </c>
     </row>
     <row r="1190">
@@ -15830,7 +15830,7 @@
         <v>2027</v>
       </c>
       <c r="D1190">
-        <v>323100.2936944597</v>
+        <v>295875.6968992485</v>
       </c>
     </row>
     <row r="1191">
@@ -15843,7 +15843,7 @@
         <v>2028</v>
       </c>
       <c r="D1191">
-        <v>352845.9615796853</v>
+        <v>323101.6202053665</v>
       </c>
     </row>
     <row r="1192">
@@ -15882,7 +15882,7 @@
         <v>2026</v>
       </c>
       <c r="D1194">
-        <v>317279.7709730204</v>
+        <v>291515.3292407325</v>
       </c>
     </row>
     <row r="1195">
@@ -15895,7 +15895,7 @@
         <v>2027</v>
       </c>
       <c r="D1195">
-        <v>345487.2286217796</v>
+        <v>317294.4296347342</v>
       </c>
     </row>
     <row r="1196">
@@ -15908,7 +15908,7 @@
         <v>2028</v>
       </c>
       <c r="D1196">
-        <v>376209.4918075196</v>
+        <v>345489.3861968</v>
       </c>
     </row>
     <row r="1197">
@@ -15947,7 +15947,7 @@
         <v>2026</v>
       </c>
       <c r="D1199">
-        <v>293481.5421600609</v>
+        <v>269263.791394387</v>
       </c>
     </row>
     <row r="1200">
@@ -15960,7 +15960,7 @@
         <v>2027</v>
       </c>
       <c r="D1200">
-        <v>319984.976296037</v>
+        <v>293490.1633759764</v>
       </c>
     </row>
     <row r="1201">
@@ -15973,7 +15973,7 @@
         <v>2028</v>
       </c>
       <c r="D1201">
-        <v>348885.4981185233</v>
+        <v>319986.0898547861</v>
       </c>
     </row>
     <row r="1202">
@@ -16012,7 +16012,7 @@
         <v>2026</v>
       </c>
       <c r="D1204">
-        <v>281173.1405801427</v>
+        <v>256904.9028481375</v>
       </c>
     </row>
     <row r="1205">
@@ -16025,7 +16025,7 @@
         <v>2027</v>
       </c>
       <c r="D1205">
-        <v>307810.4333168676</v>
+        <v>281178.7981860597</v>
       </c>
     </row>
     <row r="1206">
@@ -16038,7 +16038,7 @@
         <v>2028</v>
       </c>
       <c r="D1206">
-        <v>336973.4152992057</v>
+        <v>307811.0945589821</v>
       </c>
     </row>
     <row r="1207">
@@ -16077,7 +16077,7 @@
         <v>2026</v>
       </c>
       <c r="D1209">
-        <v>281173.1405805672</v>
+        <v>256904.902848399</v>
       </c>
     </row>
     <row r="1210">
@@ -16090,7 +16090,7 @@
         <v>2027</v>
       </c>
       <c r="D1210">
-        <v>307810.4333174827</v>
+        <v>281178.7981864843</v>
       </c>
     </row>
     <row r="1211">
@@ -16103,7 +16103,7 @@
         <v>2028</v>
       </c>
       <c r="D1211">
-        <v>336973.415300042</v>
+        <v>307811.0945595961</v>
       </c>
     </row>
     <row r="1212">
@@ -16142,7 +16142,7 @@
         <v>2026</v>
       </c>
       <c r="D1214">
-        <v>299910.051417019</v>
+        <v>275674.5412180913</v>
       </c>
     </row>
     <row r="1215">
@@ -16155,7 +16155,7 @@
         <v>2027</v>
       </c>
       <c r="D1215">
-        <v>326395.5949997471</v>
+        <v>299919.8065175906</v>
       </c>
     </row>
     <row r="1216">
@@ -16168,7 +16168,7 @@
         <v>2028</v>
       </c>
       <c r="D1216">
-        <v>355224.3217751789</v>
+        <v>326396.8819533513</v>
       </c>
     </row>
     <row r="1217">
@@ -16207,7 +16207,7 @@
         <v>2026</v>
       </c>
       <c r="D1219">
-        <v>306756.1457551786</v>
+        <v>282478.1266758847</v>
       </c>
     </row>
     <row r="1220">
@@ -16220,7 +16220,7 @@
         <v>2027</v>
       </c>
       <c r="D1220">
-        <v>333250.6546136077</v>
+        <v>306766.8792840306</v>
       </c>
     </row>
     <row r="1221">
@@ -16233,7 +16233,7 @@
         <v>2028</v>
       </c>
       <c r="D1221">
-        <v>362038.1608336713</v>
+        <v>333252.086995967</v>
       </c>
     </row>
     <row r="1222">
@@ -16272,7 +16272,7 @@
         <v>2026</v>
       </c>
       <c r="D1224">
-        <v>281173.1405805672</v>
+        <v>256904.902848399</v>
       </c>
     </row>
     <row r="1225">
@@ -16285,7 +16285,7 @@
         <v>2027</v>
       </c>
       <c r="D1225">
-        <v>307810.4333174827</v>
+        <v>281178.7981864843</v>
       </c>
     </row>
     <row r="1226">
@@ -16298,7 +16298,7 @@
         <v>2028</v>
       </c>
       <c r="D1226">
-        <v>336973.415300042</v>
+        <v>307811.0945595961</v>
       </c>
     </row>
     <row r="1227">
@@ -16337,7 +16337,7 @@
         <v>2026</v>
       </c>
       <c r="D1229">
-        <v>281173.1405805672</v>
+        <v>256904.902848399</v>
       </c>
     </row>
     <row r="1230">
@@ -16350,7 +16350,7 @@
         <v>2027</v>
       </c>
       <c r="D1230">
-        <v>307810.4333174827</v>
+        <v>281178.7981864843</v>
       </c>
     </row>
     <row r="1231">
@@ -16363,7 +16363,7 @@
         <v>2028</v>
       </c>
       <c r="D1231">
-        <v>336973.415300042</v>
+        <v>307811.0945595961</v>
       </c>
     </row>
     <row r="1232">
@@ -16402,7 +16402,7 @@
         <v>2026</v>
       </c>
       <c r="D1234">
-        <v>295298.3397951444</v>
+        <v>270482.2107431616</v>
       </c>
     </row>
     <row r="1235">
@@ -16415,7 +16415,7 @@
         <v>2027</v>
       </c>
       <c r="D1235">
-        <v>322508.3339201001</v>
+        <v>295307.9952215215</v>
       </c>
     </row>
     <row r="1236">
@@ -16428,7 +16428,7 @@
         <v>2028</v>
       </c>
       <c r="D1236">
-        <v>352229.8326845847</v>
+        <v>322509.6355557944</v>
       </c>
     </row>
     <row r="1237">
@@ -16467,7 +16467,7 @@
         <v>2026</v>
       </c>
       <c r="D1239">
-        <v>281392.0853990689</v>
+        <v>257126.0259768872</v>
       </c>
     </row>
     <row r="1240">
@@ -16480,7 +16480,7 @@
         <v>2027</v>
       </c>
       <c r="D1240">
-        <v>308025.489832354</v>
+        <v>281397.8063949984</v>
       </c>
     </row>
     <row r="1241">
@@ -16493,7 +16493,7 @@
         <v>2028</v>
       </c>
       <c r="D1241">
-        <v>337181.9146269222</v>
+        <v>308026.160478053</v>
       </c>
     </row>
     <row r="1242">
@@ -16532,7 +16532,7 @@
         <v>2026</v>
       </c>
       <c r="D1244">
-        <v>312675.861046824</v>
+        <v>288345.2500341216</v>
       </c>
     </row>
     <row r="1245">
@@ -16545,7 +16545,7 @@
         <v>2027</v>
       </c>
       <c r="D1245">
-        <v>339197.0551360661</v>
+        <v>312687.2926588604</v>
       </c>
     </row>
     <row r="1246">
@@ -16558,7 +16558,7 @@
         <v>2028</v>
       </c>
       <c r="D1246">
-        <v>367972.7648279381</v>
+        <v>339198.5870522122</v>
       </c>
     </row>
     <row r="1247">
@@ -16597,7 +16597,7 @@
         <v>2026</v>
       </c>
       <c r="D1249">
-        <v>271042.4842053469</v>
+        <v>241968.6813651387</v>
       </c>
     </row>
     <row r="1250">
@@ -16610,7 +16610,7 @@
         <v>2027</v>
       </c>
       <c r="D1250">
-        <v>303637.0251038811</v>
+        <v>271040.7313315425</v>
       </c>
     </row>
     <row r="1251">
@@ -16623,7 +16623,7 @@
         <v>2028</v>
       </c>
       <c r="D1251">
-        <v>340151.6514603993</v>
+        <v>303637.1410366051</v>
       </c>
     </row>
     <row r="1252">
@@ -16662,7 +16662,7 @@
         <v>2026</v>
       </c>
       <c r="D1254">
-        <v>306844.0860692507</v>
+        <v>280023.373655737</v>
       </c>
     </row>
     <row r="1255">
@@ -16675,7 +16675,7 @@
         <v>2027</v>
       </c>
       <c r="D1255">
-        <v>336269.3310427562</v>
+        <v>306845.7907383136</v>
       </c>
     </row>
     <row r="1256">
@@ -16688,7 +16688,7 @@
         <v>2028</v>
       </c>
       <c r="D1256">
-        <v>368516.7332597596</v>
+        <v>336269.4472376459</v>
       </c>
     </row>
     <row r="1257">
@@ -16727,7 +16727,7 @@
         <v>2026</v>
       </c>
       <c r="D1259">
-        <v>352602.8891955841</v>
+        <v>324918.2137557142</v>
       </c>
     </row>
     <row r="1260">
@@ -16740,7 +16740,7 @@
         <v>2027</v>
       </c>
       <c r="D1260">
-        <v>382669.0678174248</v>
+        <v>352603.7066838162</v>
       </c>
     </row>
     <row r="1261">
@@ -16753,7 +16753,7 @@
         <v>2028</v>
       </c>
       <c r="D1261">
-        <v>415299.0948303965</v>
+        <v>382669.1072363832</v>
       </c>
     </row>
     <row r="1262">
@@ -16792,7 +16792,7 @@
         <v>2026</v>
       </c>
       <c r="D1264">
-        <v>353458.7754253999</v>
+        <v>325778.963420152</v>
       </c>
     </row>
     <row r="1265">
@@ -16805,7 +16805,7 @@
         <v>2027</v>
       </c>
       <c r="D1265">
-        <v>383514.3190203005</v>
+        <v>353459.6597509771</v>
       </c>
     </row>
     <row r="1266">
@@ -16818,7 +16818,7 @@
         <v>2028</v>
       </c>
       <c r="D1266">
-        <v>416125.7082008488</v>
+        <v>383514.3627823247</v>
       </c>
     </row>
     <row r="1267">
@@ -16857,7 +16857,7 @@
         <v>2026</v>
       </c>
       <c r="D1269">
-        <v>353458.7754253999</v>
+        <v>325778.963420152</v>
       </c>
     </row>
     <row r="1270">
@@ -16870,7 +16870,7 @@
         <v>2027</v>
       </c>
       <c r="D1270">
-        <v>383514.3190203005</v>
+        <v>353459.6597509771</v>
       </c>
     </row>
     <row r="1271">
@@ -16883,7 +16883,7 @@
         <v>2028</v>
       </c>
       <c r="D1271">
-        <v>416125.7082008488</v>
+        <v>383514.3627823247</v>
       </c>
     </row>
     <row r="1272">
@@ -16922,7 +16922,7 @@
         <v>2026</v>
       </c>
       <c r="D1274">
-        <v>317279.7709730204</v>
+        <v>291515.3292407325</v>
       </c>
     </row>
     <row r="1275">
@@ -16935,7 +16935,7 @@
         <v>2027</v>
       </c>
       <c r="D1275">
-        <v>345487.2286217796</v>
+        <v>317294.4296347342</v>
       </c>
     </row>
     <row r="1276">
@@ -16948,7 +16948,7 @@
         <v>2028</v>
       </c>
       <c r="D1276">
-        <v>376209.4918075196</v>
+        <v>345489.3861968</v>
       </c>
     </row>
     <row r="1277">
@@ -16987,7 +16987,7 @@
         <v>2026</v>
       </c>
       <c r="D1279">
-        <v>353458.7754253999</v>
+        <v>325778.963420152</v>
       </c>
     </row>
     <row r="1280">
@@ -17000,7 +17000,7 @@
         <v>2027</v>
       </c>
       <c r="D1280">
-        <v>383514.3190203005</v>
+        <v>353459.6597509771</v>
       </c>
     </row>
     <row r="1281">
@@ -17013,7 +17013,7 @@
         <v>2028</v>
       </c>
       <c r="D1281">
-        <v>416125.7082008488</v>
+        <v>383514.3627823247</v>
       </c>
     </row>
     <row r="1282">
@@ -17052,7 +17052,7 @@
         <v>2026</v>
       </c>
       <c r="D1284">
-        <v>317545.9926950312</v>
+        <v>291767.0019925156</v>
       </c>
     </row>
     <row r="1285">
@@ -17065,7 +17065,7 @@
         <v>2027</v>
       </c>
       <c r="D1285">
-        <v>345766.9425884486</v>
+        <v>317560.4410117819</v>
       </c>
     </row>
     <row r="1286">
@@ -17078,7 +17078,7 @@
         <v>2028</v>
       </c>
       <c r="D1286">
-        <v>376502.8487606173</v>
+        <v>345769.0560176249</v>
       </c>
     </row>
     <row r="1287">
@@ -17117,7 +17117,7 @@
         <v>2026</v>
       </c>
       <c r="D1289">
-        <v>317279.7709730204</v>
+        <v>291515.3292407325</v>
       </c>
     </row>
     <row r="1290">
@@ -17130,7 +17130,7 @@
         <v>2027</v>
       </c>
       <c r="D1290">
-        <v>345487.2286217796</v>
+        <v>317294.4296347342</v>
       </c>
     </row>
     <row r="1291">
@@ -17143,7 +17143,7 @@
         <v>2028</v>
       </c>
       <c r="D1291">
-        <v>376209.4918075196</v>
+        <v>345489.3861968</v>
       </c>
     </row>
     <row r="1292">
@@ -17182,7 +17182,7 @@
         <v>2026</v>
       </c>
       <c r="D1294">
-        <v>317279.7709730204</v>
+        <v>291515.3292407325</v>
       </c>
     </row>
     <row r="1295">
@@ -17195,7 +17195,7 @@
         <v>2027</v>
       </c>
       <c r="D1295">
-        <v>345487.2286217796</v>
+        <v>317294.4296347342</v>
       </c>
     </row>
     <row r="1296">
@@ -17208,7 +17208,7 @@
         <v>2028</v>
       </c>
       <c r="D1296">
-        <v>376209.4918075196</v>
+        <v>345489.3861968</v>
       </c>
     </row>
     <row r="1297">
@@ -17247,7 +17247,7 @@
         <v>2026</v>
       </c>
       <c r="D1299">
-        <v>317279.7399204466</v>
+        <v>291515.3106277023</v>
       </c>
     </row>
     <row r="1300">
@@ -17260,7 +17260,7 @@
         <v>2027</v>
       </c>
       <c r="D1300">
-        <v>345487.1829816456</v>
+        <v>317294.3985747451</v>
       </c>
     </row>
     <row r="1301">
@@ -17273,7 +17273,7 @@
         <v>2028</v>
       </c>
       <c r="D1301">
-        <v>376209.4292277241</v>
+        <v>345489.340555591</v>
       </c>
     </row>
     <row r="1302">
@@ -17312,7 +17312,7 @@
         <v>2026</v>
       </c>
       <c r="D1304">
-        <v>231383.9294820002</v>
+        <v>209475.2644608464</v>
       </c>
     </row>
     <row r="1305">
@@ -17325,7 +17325,7 @@
         <v>2027</v>
       </c>
       <c r="D1305">
-        <v>257377.4116350598</v>
+        <v>231684.6372883838</v>
       </c>
     </row>
     <row r="1306">
@@ -17338,7 +17338,7 @@
         <v>2028</v>
       </c>
       <c r="D1306">
-        <v>286759.27118353</v>
+        <v>257517.6673209237</v>
       </c>
     </row>
     <row r="1307">
@@ -17377,7 +17377,7 @@
         <v>2026</v>
       </c>
       <c r="D1309">
-        <v>207251.949792317</v>
+        <v>185867.4558853358</v>
       </c>
     </row>
     <row r="1310">
@@ -17390,7 +17390,7 @@
         <v>2027</v>
       </c>
       <c r="D1310">
-        <v>231261.2307858785</v>
+        <v>207266.9811141192</v>
       </c>
     </row>
     <row r="1311">
@@ -17403,7 +17403,7 @@
         <v>2028</v>
       </c>
       <c r="D1311">
-        <v>258060.1340902369</v>
+        <v>231263.6941920996</v>
       </c>
     </row>
     <row r="1312">
@@ -17442,7 +17442,7 @@
         <v>2026</v>
       </c>
       <c r="D1314">
-        <v>208033.1755336304</v>
+        <v>186635.5796111301</v>
       </c>
     </row>
     <row r="1315">
@@ -17455,7 +17455,7 @@
         <v>2027</v>
       </c>
       <c r="D1315">
-        <v>232045.220215083</v>
+        <v>208047.82165816</v>
       </c>
     </row>
     <row r="1316">
@@ -17468,7 +17468,7 @@
         <v>2028</v>
       </c>
       <c r="D1316">
-        <v>258836.7872376061</v>
+        <v>232047.5969822018</v>
       </c>
     </row>
     <row r="1317">
@@ -17507,7 +17507,7 @@
         <v>2026</v>
       </c>
       <c r="D1319">
-        <v>179609.2140971918</v>
+        <v>155239.5064070644</v>
       </c>
     </row>
     <row r="1320">
@@ -17520,7 +17520,7 @@
         <v>2027</v>
       </c>
       <c r="D1320">
-        <v>207923.4724925383</v>
+        <v>179617.9086694608</v>
       </c>
     </row>
     <row r="1321">
@@ -17533,7 +17533,7 @@
         <v>2028</v>
       </c>
       <c r="D1321">
-        <v>240705.2568939184</v>
+        <v>207924.6133009189</v>
       </c>
     </row>
     <row r="1322">
@@ -17572,7 +17572,7 @@
         <v>2026</v>
       </c>
       <c r="D1324">
-        <v>205907.1257719559</v>
+        <v>183182.8113035031</v>
       </c>
     </row>
     <row r="1325">
@@ -17585,7 +17585,7 @@
         <v>2027</v>
       </c>
       <c r="D1325">
-        <v>231479.9609448984</v>
+        <v>205904.2667096594</v>
       </c>
     </row>
     <row r="1326">
@@ -17598,7 +17598,7 @@
         <v>2028</v>
       </c>
       <c r="D1326">
-        <v>260229.729061073</v>
+        <v>231480.2248008847</v>
       </c>
     </row>
     <row r="1327">
@@ -17637,7 +17637,7 @@
         <v>2026</v>
       </c>
       <c r="D1329">
-        <v>227319.7810440725</v>
+        <v>203331.3474259457</v>
       </c>
     </row>
     <row r="1330">
@@ -17650,7 +17650,7 @@
         <v>2027</v>
       </c>
       <c r="D1330">
-        <v>254144.7958808823</v>
+        <v>227319.5438449454</v>
       </c>
     </row>
     <row r="1331">
@@ -17663,7 +17663,7 @@
         <v>2028</v>
       </c>
       <c r="D1331">
-        <v>284135.3459415777</v>
+        <v>254144.805524972</v>
       </c>
     </row>
     <row r="1332">
@@ -17702,7 +17702,7 @@
         <v>2026</v>
       </c>
       <c r="D1334">
-        <v>409734.3834982847</v>
+        <v>383219.5811209911</v>
       </c>
     </row>
     <row r="1335">
@@ -17715,7 +17715,7 @@
         <v>2027</v>
       </c>
       <c r="D1335">
-        <v>441437.4407215411</v>
+        <v>410317.475160171</v>
       </c>
     </row>
     <row r="1336">
@@ -17728,7 +17728,7 @@
         <v>2028</v>
       </c>
       <c r="D1336">
-        <v>476453.0434768921</v>
+        <v>441703.2148957663</v>
       </c>
     </row>
     <row r="1337">
@@ -17767,7 +17767,7 @@
         <v>2026</v>
       </c>
       <c r="D1339">
-        <v>336522.0510040715</v>
+        <v>314175.0652283816</v>
       </c>
     </row>
     <row r="1340">
@@ -17780,7 +17780,7 @@
         <v>2027</v>
       </c>
       <c r="D1340">
-        <v>362806.3156274122</v>
+        <v>336917.0965182788</v>
       </c>
     </row>
     <row r="1341">
@@ -17793,7 +17793,7 @@
         <v>2028</v>
       </c>
       <c r="D1341">
-        <v>391687.2773671714</v>
+        <v>362974.356203335</v>
       </c>
     </row>
     <row r="1342">
@@ -17832,7 +17832,7 @@
         <v>2026</v>
       </c>
       <c r="D1344">
-        <v>374272.6406680486</v>
+        <v>360858.4721327236</v>
       </c>
     </row>
     <row r="1345">
@@ -17845,7 +17845,7 @@
         <v>2027</v>
       </c>
       <c r="D1345">
-        <v>390397.8673260267</v>
+        <v>374658.3735145808</v>
       </c>
     </row>
     <row r="1346">
@@ -17858,7 +17858,7 @@
         <v>2028</v>
       </c>
       <c r="D1346">
-        <v>407718.0710945333</v>
+        <v>390557.659603275</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/forecast_zhvi_by_tract.xlsx
+++ b/outputs/forecast_zhvi_by_tract.xlsx
@@ -386,7 +386,7 @@
         <v>2024</v>
       </c>
       <c r="D2">
-        <v>255151.7405387399</v>
+        <v>255151.7405387403</v>
       </c>
     </row>
     <row r="3">
@@ -412,7 +412,7 @@
         <v>2026</v>
       </c>
       <c r="D4">
-        <v>278415.3311344833</v>
+        <v>303864.5921946415</v>
       </c>
     </row>
     <row r="5">
@@ -425,7 +425,7 @@
         <v>2027</v>
       </c>
       <c r="D5">
-        <v>303871.8456027544</v>
+        <v>331734.3832042146</v>
       </c>
     </row>
     <row r="6">
@@ -438,7 +438,7 @@
         <v>2028</v>
       </c>
       <c r="D6">
-        <v>331735.2722038388</v>
+        <v>362163.2416684655</v>
       </c>
     </row>
     <row r="7">
@@ -451,7 +451,7 @@
         <v>2024</v>
       </c>
       <c r="D7">
-        <v>341196.6491843323</v>
+        <v>341196.6491843318</v>
       </c>
     </row>
     <row r="8">
@@ -477,7 +477,7 @@
         <v>2026</v>
       </c>
       <c r="D9">
-        <v>366563.4106603409</v>
+        <v>393824.3812634929</v>
       </c>
     </row>
     <row r="10">
@@ -490,7 +490,7 @@
         <v>2027</v>
       </c>
       <c r="D10">
-        <v>393824.6579744138</v>
+        <v>423122.512403396</v>
       </c>
     </row>
     <row r="11">
@@ -503,7 +503,7 @@
         <v>2028</v>
       </c>
       <c r="D11">
-        <v>423122.5223383044</v>
+        <v>454600.2777665246</v>
       </c>
     </row>
     <row r="12">
@@ -516,7 +516,7 @@
         <v>2024</v>
       </c>
       <c r="D12">
-        <v>341196.6491843323</v>
+        <v>341196.6491843318</v>
       </c>
     </row>
     <row r="13">
@@ -542,7 +542,7 @@
         <v>2026</v>
       </c>
       <c r="D14">
-        <v>366563.4106603409</v>
+        <v>393824.3812634929</v>
       </c>
     </row>
     <row r="15">
@@ -555,7 +555,7 @@
         <v>2027</v>
       </c>
       <c r="D15">
-        <v>393824.6579744138</v>
+        <v>423122.512403396</v>
       </c>
     </row>
     <row r="16">
@@ -568,7 +568,7 @@
         <v>2028</v>
       </c>
       <c r="D16">
-        <v>423122.5223383044</v>
+        <v>454600.2777665246</v>
       </c>
     </row>
     <row r="17">
@@ -581,7 +581,7 @@
         <v>2024</v>
       </c>
       <c r="D17">
-        <v>341196.6491843323</v>
+        <v>341196.6491843318</v>
       </c>
     </row>
     <row r="18">
@@ -607,7 +607,7 @@
         <v>2026</v>
       </c>
       <c r="D19">
-        <v>366563.4106603409</v>
+        <v>393824.3812634929</v>
       </c>
     </row>
     <row r="20">
@@ -620,7 +620,7 @@
         <v>2027</v>
       </c>
       <c r="D20">
-        <v>393824.6579744138</v>
+        <v>423122.512403396</v>
       </c>
     </row>
     <row r="21">
@@ -633,7 +633,7 @@
         <v>2028</v>
       </c>
       <c r="D21">
-        <v>423122.5223383044</v>
+        <v>454600.2777665246</v>
       </c>
     </row>
     <row r="22">
@@ -646,7 +646,7 @@
         <v>2024</v>
       </c>
       <c r="D22">
-        <v>341196.6491843323</v>
+        <v>341196.6491843318</v>
       </c>
     </row>
     <row r="23">
@@ -672,7 +672,7 @@
         <v>2026</v>
       </c>
       <c r="D24">
-        <v>366563.4106603409</v>
+        <v>393824.3812634929</v>
       </c>
     </row>
     <row r="25">
@@ -685,7 +685,7 @@
         <v>2027</v>
       </c>
       <c r="D25">
-        <v>393824.6579744138</v>
+        <v>423122.512403396</v>
       </c>
     </row>
     <row r="26">
@@ -698,7 +698,7 @@
         <v>2028</v>
       </c>
       <c r="D26">
-        <v>423122.5223383044</v>
+        <v>454600.2777665246</v>
       </c>
     </row>
     <row r="27">
@@ -711,7 +711,7 @@
         <v>2024</v>
       </c>
       <c r="D27">
-        <v>341196.6491843323</v>
+        <v>341196.6491843318</v>
       </c>
     </row>
     <row r="28">
@@ -737,7 +737,7 @@
         <v>2026</v>
       </c>
       <c r="D29">
-        <v>366563.4106603409</v>
+        <v>393824.3812634929</v>
       </c>
     </row>
     <row r="30">
@@ -750,7 +750,7 @@
         <v>2027</v>
       </c>
       <c r="D30">
-        <v>393824.6579744138</v>
+        <v>423122.512403396</v>
       </c>
     </row>
     <row r="31">
@@ -763,7 +763,7 @@
         <v>2028</v>
       </c>
       <c r="D31">
-        <v>423122.5223383044</v>
+        <v>454600.2777665246</v>
       </c>
     </row>
     <row r="32">
@@ -776,7 +776,7 @@
         <v>2024</v>
       </c>
       <c r="D32">
-        <v>322737.0514028475</v>
+        <v>322737.0514028469</v>
       </c>
     </row>
     <row r="33">
@@ -802,7 +802,7 @@
         <v>2026</v>
       </c>
       <c r="D34">
-        <v>348851.8338514452</v>
+        <v>377215.8042992281</v>
       </c>
     </row>
     <row r="35">
@@ -815,7 +815,7 @@
         <v>2027</v>
       </c>
       <c r="D35">
-        <v>377251.1855309155</v>
+        <v>408147.9651275449</v>
       </c>
     </row>
     <row r="36">
@@ -828,7 +828,7 @@
         <v>2028</v>
       </c>
       <c r="D36">
-        <v>408157.9169207505</v>
+        <v>441648.9056093694</v>
       </c>
     </row>
     <row r="37">
@@ -841,7 +841,7 @@
         <v>2024</v>
       </c>
       <c r="D37">
-        <v>322737.0514028475</v>
+        <v>322737.0514028469</v>
       </c>
     </row>
     <row r="38">
@@ -867,7 +867,7 @@
         <v>2026</v>
       </c>
       <c r="D39">
-        <v>348851.8338514452</v>
+        <v>377215.8042992281</v>
       </c>
     </row>
     <row r="40">
@@ -880,7 +880,7 @@
         <v>2027</v>
       </c>
       <c r="D40">
-        <v>377251.1855309155</v>
+        <v>408147.9651275449</v>
       </c>
     </row>
     <row r="41">
@@ -893,7 +893,7 @@
         <v>2028</v>
       </c>
       <c r="D41">
-        <v>408157.9169207505</v>
+        <v>441648.9056093694</v>
       </c>
     </row>
     <row r="42">
@@ -906,7 +906,7 @@
         <v>2024</v>
       </c>
       <c r="D42">
-        <v>278296.453596845</v>
+        <v>278296.4535968445</v>
       </c>
     </row>
     <row r="43">
@@ -932,7 +932,7 @@
         <v>2026</v>
       </c>
       <c r="D44">
-        <v>300512.6650659974</v>
+        <v>324660.0782210762</v>
       </c>
     </row>
     <row r="45">
@@ -945,7 +945,7 @@
         <v>2027</v>
       </c>
       <c r="D45">
-        <v>324689.5169400455</v>
+        <v>351013.7532750868</v>
       </c>
     </row>
     <row r="46">
@@ -958,7 +958,7 @@
         <v>2028</v>
       </c>
       <c r="D46">
-        <v>351019.6930269767</v>
+        <v>379525.9046725643</v>
       </c>
     </row>
     <row r="47">
@@ -971,7 +971,7 @@
         <v>2024</v>
       </c>
       <c r="D47">
-        <v>322737.0514028475</v>
+        <v>322737.0514028469</v>
       </c>
     </row>
     <row r="48">
@@ -997,7 +997,7 @@
         <v>2026</v>
       </c>
       <c r="D49">
-        <v>348851.8338514452</v>
+        <v>377215.8042992281</v>
       </c>
     </row>
     <row r="50">
@@ -1010,7 +1010,7 @@
         <v>2027</v>
       </c>
       <c r="D50">
-        <v>377251.1855309155</v>
+        <v>408147.9651275449</v>
       </c>
     </row>
     <row r="51">
@@ -1023,7 +1023,7 @@
         <v>2028</v>
       </c>
       <c r="D51">
-        <v>408157.9169207505</v>
+        <v>441648.9056093694</v>
       </c>
     </row>
     <row r="52">
@@ -1036,7 +1036,7 @@
         <v>2024</v>
       </c>
       <c r="D52">
-        <v>225327.2137918228</v>
+        <v>225327.2137918224</v>
       </c>
     </row>
     <row r="53">
@@ -1062,7 +1062,7 @@
         <v>2026</v>
       </c>
       <c r="D54">
-        <v>247645.1172390108</v>
+        <v>272173.5507725673</v>
       </c>
     </row>
     <row r="55">
@@ -1075,7 +1075,7 @@
         <v>2027</v>
       </c>
       <c r="D55">
-        <v>272173.5507439406</v>
+        <v>299131.4631912823</v>
       </c>
     </row>
     <row r="56">
@@ -1088,7 +1088,7 @@
         <v>2028</v>
       </c>
       <c r="D56">
-        <v>299131.463191336</v>
+        <v>328759.4698934436</v>
       </c>
     </row>
     <row r="57">
@@ -1101,7 +1101,7 @@
         <v>2024</v>
       </c>
       <c r="D57">
-        <v>300283.2652560791</v>
+        <v>300283.2652560786</v>
       </c>
     </row>
     <row r="58">
@@ -1127,7 +1127,7 @@
         <v>2026</v>
       </c>
       <c r="D59">
-        <v>325778.963420152</v>
+        <v>353458.7754253999</v>
       </c>
     </row>
     <row r="60">
@@ -1140,7 +1140,7 @@
         <v>2027</v>
       </c>
       <c r="D60">
-        <v>353459.6597509771</v>
+        <v>383514.3190203005</v>
       </c>
     </row>
     <row r="61">
@@ -1153,7 +1153,7 @@
         <v>2028</v>
       </c>
       <c r="D61">
-        <v>383514.3627823247</v>
+        <v>416125.7082008481</v>
       </c>
     </row>
     <row r="62">
@@ -1166,7 +1166,7 @@
         <v>2024</v>
       </c>
       <c r="D62">
-        <v>224900.7774771928</v>
+        <v>224900.7774771924</v>
       </c>
     </row>
     <row r="63">
@@ -1192,7 +1192,7 @@
         <v>2026</v>
       </c>
       <c r="D64">
-        <v>247295.1784669193</v>
+        <v>271919.6816277375</v>
       </c>
     </row>
     <row r="65">
@@ -1205,7 +1205,7 @@
         <v>2027</v>
       </c>
       <c r="D65">
-        <v>271919.6805486455</v>
+        <v>298996.3825409782</v>
       </c>
     </row>
     <row r="66">
@@ -1218,7 +1218,7 @@
         <v>2028</v>
       </c>
       <c r="D66">
-        <v>298996.3825477516</v>
+        <v>328769.2757049297</v>
       </c>
     </row>
     <row r="67">
@@ -1231,7 +1231,7 @@
         <v>2024</v>
       </c>
       <c r="D67">
-        <v>224995.9401072134</v>
+        <v>224995.9401072138</v>
       </c>
     </row>
     <row r="68">
@@ -1257,7 +1257,7 @@
         <v>2026</v>
       </c>
       <c r="D69">
-        <v>247301.3626374819</v>
+        <v>271818.1037353462</v>
       </c>
     </row>
     <row r="70">
@@ -1270,7 +1270,7 @@
         <v>2027</v>
       </c>
       <c r="D70">
-        <v>271818.1036801805</v>
+        <v>298765.3918417389</v>
       </c>
     </row>
     <row r="71">
@@ -1283,7 +1283,7 @@
         <v>2028</v>
       </c>
       <c r="D71">
-        <v>298765.3918418684</v>
+        <v>328384.1588762326</v>
       </c>
     </row>
     <row r="72">
@@ -1296,7 +1296,7 @@
         <v>2024</v>
       </c>
       <c r="D72">
-        <v>414379.9782629547</v>
+        <v>414379.978262954</v>
       </c>
     </row>
     <row r="73">
@@ -1322,7 +1322,7 @@
         <v>2026</v>
       </c>
       <c r="D74">
-        <v>441289.8530637257</v>
+        <v>470254.5105612233</v>
       </c>
     </row>
     <row r="75">
@@ -1335,7 +1335,7 @@
         <v>2027</v>
       </c>
       <c r="D75">
-        <v>470331.9281969927</v>
+        <v>501695.6362554573</v>
       </c>
     </row>
     <row r="76">
@@ -1348,7 +1348,7 @@
         <v>2028</v>
       </c>
       <c r="D76">
-        <v>501716.4373780646</v>
+        <v>535305.4879425718</v>
       </c>
     </row>
     <row r="77">
@@ -1361,7 +1361,7 @@
         <v>2024</v>
       </c>
       <c r="D77">
-        <v>416137.227864706</v>
+        <v>416137.2278647053</v>
       </c>
     </row>
     <row r="78">
@@ -1387,7 +1387,7 @@
         <v>2026</v>
       </c>
       <c r="D79">
-        <v>443088.9510598898</v>
+        <v>472095.5726504429</v>
       </c>
     </row>
     <row r="80">
@@ -1400,7 +1400,7 @@
         <v>2027</v>
       </c>
       <c r="D80">
-        <v>472173.8158483912</v>
+        <v>503581.1991800835</v>
       </c>
     </row>
     <row r="81">
@@ -1413,7 +1413,7 @@
         <v>2028</v>
       </c>
       <c r="D81">
-        <v>503602.3002011494</v>
+        <v>537234.2348224048</v>
       </c>
     </row>
     <row r="82">
@@ -1426,7 +1426,7 @@
         <v>2024</v>
       </c>
       <c r="D82">
-        <v>287176.0135016118</v>
+        <v>287176.0135016113</v>
       </c>
     </row>
     <row r="83">
@@ -1452,7 +1452,7 @@
         <v>2026</v>
       </c>
       <c r="D84">
-        <v>311824.0560333859</v>
+        <v>338674.3064026155</v>
       </c>
     </row>
     <row r="85">
@@ -1465,7 +1465,7 @@
         <v>2027</v>
       </c>
       <c r="D85">
-        <v>338684.8879635837</v>
+        <v>367965.2193650494</v>
       </c>
     </row>
     <row r="86">
@@ -1478,7 +1478,7 @@
         <v>2028</v>
       </c>
       <c r="D86">
-        <v>367966.6224599352</v>
+        <v>399793.9878487976</v>
       </c>
     </row>
     <row r="87">
@@ -1491,7 +1491,7 @@
         <v>2024</v>
       </c>
       <c r="D87">
-        <v>287176.0135016118</v>
+        <v>287176.0135016113</v>
       </c>
     </row>
     <row r="88">
@@ -1517,7 +1517,7 @@
         <v>2026</v>
       </c>
       <c r="D89">
-        <v>311824.0560333859</v>
+        <v>338674.3064026155</v>
       </c>
     </row>
     <row r="90">
@@ -1530,7 +1530,7 @@
         <v>2027</v>
       </c>
       <c r="D90">
-        <v>338684.8879635837</v>
+        <v>367965.2193650494</v>
       </c>
     </row>
     <row r="91">
@@ -1543,7 +1543,7 @@
         <v>2028</v>
       </c>
       <c r="D91">
-        <v>367966.6224599352</v>
+        <v>399793.9878487976</v>
       </c>
     </row>
     <row r="92">
@@ -1556,7 +1556,7 @@
         <v>2024</v>
       </c>
       <c r="D92">
-        <v>264066.7633851426</v>
+        <v>264066.763385144</v>
       </c>
     </row>
     <row r="93">
@@ -1582,7 +1582,7 @@
         <v>2026</v>
       </c>
       <c r="D94">
-        <v>287523.0002731558</v>
+        <v>313232.7355075887</v>
       </c>
     </row>
     <row r="95">
@@ -1595,7 +1595,7 @@
         <v>2027</v>
       </c>
       <c r="D95">
-        <v>313264.8006110343</v>
+        <v>341531.4991818194</v>
       </c>
     </row>
     <row r="96">
@@ -1608,7 +1608,7 @@
         <v>2028</v>
       </c>
       <c r="D96">
-        <v>341538.0930719335</v>
+        <v>372408.4615176566</v>
       </c>
     </row>
     <row r="97">
@@ -1621,7 +1621,7 @@
         <v>2024</v>
       </c>
       <c r="D97">
-        <v>264066.7633851426</v>
+        <v>264066.763385144</v>
       </c>
     </row>
     <row r="98">
@@ -1647,7 +1647,7 @@
         <v>2026</v>
       </c>
       <c r="D99">
-        <v>287523.0002731558</v>
+        <v>313232.7355075887</v>
       </c>
     </row>
     <row r="100">
@@ -1660,7 +1660,7 @@
         <v>2027</v>
       </c>
       <c r="D100">
-        <v>313264.8006110343</v>
+        <v>341531.4991818194</v>
       </c>
     </row>
     <row r="101">
@@ -1673,7 +1673,7 @@
         <v>2028</v>
       </c>
       <c r="D101">
-        <v>341538.0930719335</v>
+        <v>372408.4615176566</v>
       </c>
     </row>
     <row r="102">
@@ -1686,7 +1686,7 @@
         <v>2024</v>
       </c>
       <c r="D102">
-        <v>287176.0135016118</v>
+        <v>287176.0135016113</v>
       </c>
     </row>
     <row r="103">
@@ -1712,7 +1712,7 @@
         <v>2026</v>
       </c>
       <c r="D104">
-        <v>311824.0560333859</v>
+        <v>338674.3064026155</v>
       </c>
     </row>
     <row r="105">
@@ -1725,7 +1725,7 @@
         <v>2027</v>
       </c>
       <c r="D105">
-        <v>338684.8879635837</v>
+        <v>367965.2193650494</v>
       </c>
     </row>
     <row r="106">
@@ -1738,7 +1738,7 @@
         <v>2028</v>
       </c>
       <c r="D106">
-        <v>367966.6224599352</v>
+        <v>399793.9878487976</v>
       </c>
     </row>
     <row r="107">
@@ -1751,7 +1751,7 @@
         <v>2024</v>
       </c>
       <c r="D107">
-        <v>264066.7633500627</v>
+        <v>264066.7633500636</v>
       </c>
     </row>
     <row r="108">
@@ -1777,7 +1777,7 @@
         <v>2026</v>
       </c>
       <c r="D109">
-        <v>287523.0002169756</v>
+        <v>313232.7354296903</v>
       </c>
     </row>
     <row r="110">
@@ -1790,7 +1790,7 @@
         <v>2027</v>
       </c>
       <c r="D110">
-        <v>313264.8005339944</v>
+        <v>341531.4990846733</v>
       </c>
     </row>
     <row r="111">
@@ -1803,7 +1803,7 @@
         <v>2028</v>
       </c>
       <c r="D111">
-        <v>341538.0929750294</v>
+        <v>372408.4613992136</v>
       </c>
     </row>
     <row r="112">
@@ -1816,7 +1816,7 @@
         <v>2024</v>
       </c>
       <c r="D112">
-        <v>287176.0135016118</v>
+        <v>287176.0135016113</v>
       </c>
     </row>
     <row r="113">
@@ -1842,7 +1842,7 @@
         <v>2026</v>
       </c>
       <c r="D114">
-        <v>311824.0560333859</v>
+        <v>338674.3064026155</v>
       </c>
     </row>
     <row r="115">
@@ -1855,7 +1855,7 @@
         <v>2027</v>
       </c>
       <c r="D115">
-        <v>338684.8879635837</v>
+        <v>367965.2193650494</v>
       </c>
     </row>
     <row r="116">
@@ -1868,7 +1868,7 @@
         <v>2028</v>
       </c>
       <c r="D116">
-        <v>367966.6224599352</v>
+        <v>399793.9878487976</v>
       </c>
     </row>
     <row r="117">
@@ -1881,7 +1881,7 @@
         <v>2024</v>
       </c>
       <c r="D117">
-        <v>287176.0135016118</v>
+        <v>287176.0135016113</v>
       </c>
     </row>
     <row r="118">
@@ -1907,7 +1907,7 @@
         <v>2026</v>
       </c>
       <c r="D119">
-        <v>311824.0560333859</v>
+        <v>338674.3064026155</v>
       </c>
     </row>
     <row r="120">
@@ -1920,7 +1920,7 @@
         <v>2027</v>
       </c>
       <c r="D120">
-        <v>338684.8879635837</v>
+        <v>367965.2193650494</v>
       </c>
     </row>
     <row r="121">
@@ -1933,7 +1933,7 @@
         <v>2028</v>
       </c>
       <c r="D121">
-        <v>367966.6224599352</v>
+        <v>399793.9878487976</v>
       </c>
     </row>
     <row r="122">
@@ -1946,7 +1946,7 @@
         <v>2024</v>
       </c>
       <c r="D122">
-        <v>255151.7405387399</v>
+        <v>255151.7405387403</v>
       </c>
     </row>
     <row r="123">
@@ -1972,7 +1972,7 @@
         <v>2026</v>
       </c>
       <c r="D124">
-        <v>278415.3311344833</v>
+        <v>303864.5921946415</v>
       </c>
     </row>
     <row r="125">
@@ -1985,7 +1985,7 @@
         <v>2027</v>
       </c>
       <c r="D125">
-        <v>303871.8456027544</v>
+        <v>331734.3832042146</v>
       </c>
     </row>
     <row r="126">
@@ -1998,7 +1998,7 @@
         <v>2028</v>
       </c>
       <c r="D126">
-        <v>331735.2722038388</v>
+        <v>362163.2416684655</v>
       </c>
     </row>
     <row r="127">
@@ -2011,7 +2011,7 @@
         <v>2024</v>
       </c>
       <c r="D127">
-        <v>311660.0661203283</v>
+        <v>311660.0661203266</v>
       </c>
     </row>
     <row r="128">
@@ -2037,7 +2037,7 @@
         <v>2026</v>
       </c>
       <c r="D129">
-        <v>335874.3882508578</v>
+        <v>362142.5349108929</v>
       </c>
     </row>
     <row r="130">
@@ -2050,7 +2050,7 @@
         <v>2027</v>
       </c>
       <c r="D130">
-        <v>362175.3469870159</v>
+        <v>390757.342895754</v>
       </c>
     </row>
     <row r="131">
@@ -2063,7 +2063,7 @@
         <v>2028</v>
       </c>
       <c r="D131">
-        <v>390764.0752071551</v>
+        <v>421654.9522437037</v>
       </c>
     </row>
     <row r="132">
@@ -2076,7 +2076,7 @@
         <v>2024</v>
       </c>
       <c r="D132">
-        <v>260670.2007843759</v>
+        <v>260670.2007843746</v>
       </c>
     </row>
     <row r="133">
@@ -2102,7 +2102,7 @@
         <v>2026</v>
       </c>
       <c r="D134">
-        <v>283650.8450274403</v>
+        <v>308744.3864057814</v>
       </c>
     </row>
     <row r="135">
@@ -2115,7 +2115,7 @@
         <v>2027</v>
       </c>
       <c r="D135">
-        <v>308755.9034308086</v>
+        <v>336190.1241662781</v>
       </c>
     </row>
     <row r="136">
@@ -2128,7 +2128,7 @@
         <v>2028</v>
       </c>
       <c r="D136">
-        <v>336191.7854160077</v>
+        <v>366081.0691920608</v>
       </c>
     </row>
     <row r="137">
@@ -2167,7 +2167,7 @@
         <v>2026</v>
       </c>
       <c r="D139">
-        <v>284694.0353213935</v>
+        <v>310349.9174415245</v>
       </c>
     </row>
     <row r="140">
@@ -2180,7 +2180,7 @@
         <v>2027</v>
       </c>
       <c r="D140">
-        <v>310359.1548938031</v>
+        <v>338431.4025530138</v>
       </c>
     </row>
     <row r="141">
@@ -2193,7 +2193,7 @@
         <v>2028</v>
       </c>
       <c r="D141">
-        <v>338432.6197592693</v>
+        <v>369057.7751885096</v>
       </c>
     </row>
     <row r="142">
@@ -2206,7 +2206,7 @@
         <v>2024</v>
       </c>
       <c r="D142">
-        <v>224709.8637424866</v>
+        <v>224709.863742487</v>
       </c>
     </row>
     <row r="143">
@@ -2232,7 +2232,7 @@
         <v>2026</v>
       </c>
       <c r="D144">
-        <v>246709.7220193894</v>
+        <v>270914.2664060779</v>
       </c>
     </row>
     <row r="145">
@@ -2245,7 +2245,7 @@
         <v>2027</v>
       </c>
       <c r="D145">
-        <v>270919.6639445653</v>
+        <v>297567.1114660384</v>
       </c>
     </row>
     <row r="146">
@@ -2258,7 +2258,7 @@
         <v>2028</v>
       </c>
       <c r="D146">
-        <v>297567.7409946572</v>
+        <v>326844.1672825909</v>
       </c>
     </row>
     <row r="147">
@@ -2271,7 +2271,7 @@
         <v>2024</v>
       </c>
       <c r="D147">
-        <v>224709.8637424866</v>
+        <v>224709.863742487</v>
       </c>
     </row>
     <row r="148">
@@ -2297,7 +2297,7 @@
         <v>2026</v>
       </c>
       <c r="D149">
-        <v>246709.7220193894</v>
+        <v>270914.2664060779</v>
       </c>
     </row>
     <row r="150">
@@ -2310,7 +2310,7 @@
         <v>2027</v>
       </c>
       <c r="D150">
-        <v>270919.6639445653</v>
+        <v>297567.1114660384</v>
       </c>
     </row>
     <row r="151">
@@ -2323,7 +2323,7 @@
         <v>2028</v>
       </c>
       <c r="D151">
-        <v>297567.7409946572</v>
+        <v>326844.1672825909</v>
       </c>
     </row>
     <row r="152">
@@ -2336,7 +2336,7 @@
         <v>2024</v>
       </c>
       <c r="D152">
-        <v>416137.227864706</v>
+        <v>416137.2278647053</v>
       </c>
     </row>
     <row r="153">
@@ -2362,7 +2362,7 @@
         <v>2026</v>
       </c>
       <c r="D154">
-        <v>443088.9510598898</v>
+        <v>472095.5726504429</v>
       </c>
     </row>
     <row r="155">
@@ -2375,7 +2375,7 @@
         <v>2027</v>
       </c>
       <c r="D155">
-        <v>472173.8158483912</v>
+        <v>503581.1991800835</v>
       </c>
     </row>
     <row r="156">
@@ -2388,7 +2388,7 @@
         <v>2028</v>
       </c>
       <c r="D156">
-        <v>503602.3002011494</v>
+        <v>537234.2348224048</v>
       </c>
     </row>
     <row r="157">
@@ -2401,7 +2401,7 @@
         <v>2024</v>
       </c>
       <c r="D157">
-        <v>416056.1420630708</v>
+        <v>416056.1420630679</v>
       </c>
     </row>
     <row r="158">
@@ -2427,7 +2427,7 @@
         <v>2026</v>
       </c>
       <c r="D159">
-        <v>443005.9267907981</v>
+        <v>472010.6034654264</v>
       </c>
     </row>
     <row r="160">
@@ -2440,7 +2440,7 @@
         <v>2027</v>
       </c>
       <c r="D160">
-        <v>472088.8086770794</v>
+        <v>503494.167148654</v>
       </c>
     </row>
     <row r="161">
@@ -2453,7 +2453,7 @@
         <v>2028</v>
       </c>
       <c r="D161">
-        <v>503515.254349565</v>
+        <v>537145.1990130919</v>
       </c>
     </row>
     <row r="162">
@@ -2466,7 +2466,7 @@
         <v>2024</v>
       </c>
       <c r="D162">
-        <v>255151.7405387399</v>
+        <v>255151.7405387403</v>
       </c>
     </row>
     <row r="163">
@@ -2492,7 +2492,7 @@
         <v>2026</v>
       </c>
       <c r="D164">
-        <v>278415.3311344833</v>
+        <v>303864.5921946415</v>
       </c>
     </row>
     <row r="165">
@@ -2505,7 +2505,7 @@
         <v>2027</v>
       </c>
       <c r="D165">
-        <v>303871.8456027544</v>
+        <v>331734.3832042146</v>
       </c>
     </row>
     <row r="166">
@@ -2518,7 +2518,7 @@
         <v>2028</v>
       </c>
       <c r="D166">
-        <v>331735.2722038388</v>
+        <v>362163.2416684655</v>
       </c>
     </row>
     <row r="167">
@@ -2531,7 +2531,7 @@
         <v>2024</v>
       </c>
       <c r="D167">
-        <v>304932.8155269603</v>
+        <v>304932.8155269597</v>
       </c>
     </row>
     <row r="168">
@@ -2557,7 +2557,7 @@
         <v>2026</v>
       </c>
       <c r="D169">
-        <v>329005.8925436896</v>
+        <v>355140.5944977046</v>
       </c>
     </row>
     <row r="170">
@@ -2570,7 +2570,7 @@
         <v>2027</v>
       </c>
       <c r="D170">
-        <v>355170.1661664348</v>
+        <v>383621.1741467959</v>
       </c>
     </row>
     <row r="171">
@@ -2583,7 +2583,7 @@
         <v>2028</v>
       </c>
       <c r="D171">
-        <v>383627.0335805306</v>
+        <v>414404.7485573036</v>
       </c>
     </row>
     <row r="172">
@@ -2596,7 +2596,7 @@
         <v>2024</v>
       </c>
       <c r="D172">
-        <v>256370.5941469218</v>
+        <v>256370.5941469205</v>
       </c>
     </row>
     <row r="173">
@@ -2622,7 +2622,7 @@
         <v>2026</v>
       </c>
       <c r="D174">
-        <v>279569.8940553228</v>
+        <v>304937.9751242995</v>
       </c>
     </row>
     <row r="175">
@@ -2635,7 +2635,7 @@
         <v>2027</v>
       </c>
       <c r="D175">
-        <v>304946.0914226463</v>
+        <v>332710.2786442924</v>
       </c>
     </row>
     <row r="176">
@@ -2648,7 +2648,7 @@
         <v>2028</v>
       </c>
       <c r="D176">
-        <v>332711.3134436555</v>
+        <v>363015.338902299</v>
       </c>
     </row>
     <row r="177">
@@ -2661,7 +2661,7 @@
         <v>2024</v>
       </c>
       <c r="D177">
-        <v>224709.8637424866</v>
+        <v>224709.863742487</v>
       </c>
     </row>
     <row r="178">
@@ -2687,7 +2687,7 @@
         <v>2026</v>
       </c>
       <c r="D179">
-        <v>246709.7220193894</v>
+        <v>270914.2664060779</v>
       </c>
     </row>
     <row r="180">
@@ -2700,7 +2700,7 @@
         <v>2027</v>
       </c>
       <c r="D180">
-        <v>270919.6639445653</v>
+        <v>297567.1114660384</v>
       </c>
     </row>
     <row r="181">
@@ -2713,7 +2713,7 @@
         <v>2028</v>
       </c>
       <c r="D181">
-        <v>297567.7409946572</v>
+        <v>326844.1672825909</v>
       </c>
     </row>
     <row r="182">
@@ -2726,7 +2726,7 @@
         <v>2024</v>
       </c>
       <c r="D182">
-        <v>224709.8637424866</v>
+        <v>224709.863742487</v>
       </c>
     </row>
     <row r="183">
@@ -2752,7 +2752,7 @@
         <v>2026</v>
       </c>
       <c r="D184">
-        <v>246709.7220193894</v>
+        <v>270914.2664060779</v>
       </c>
     </row>
     <row r="185">
@@ -2765,7 +2765,7 @@
         <v>2027</v>
       </c>
       <c r="D185">
-        <v>270919.6639445653</v>
+        <v>297567.1114660384</v>
       </c>
     </row>
     <row r="186">
@@ -2778,7 +2778,7 @@
         <v>2028</v>
       </c>
       <c r="D186">
-        <v>297567.7409946572</v>
+        <v>326844.1672825909</v>
       </c>
     </row>
     <row r="187">
@@ -2817,7 +2817,7 @@
         <v>2026</v>
       </c>
       <c r="D189">
-        <v>284025.0312810856</v>
+        <v>309827.7317955933</v>
       </c>
     </row>
     <row r="190">
@@ -2830,7 +2830,7 @@
         <v>2027</v>
       </c>
       <c r="D190">
-        <v>309832.3625674977</v>
+        <v>338042.8908072146</v>
       </c>
     </row>
     <row r="191">
@@ -2843,7 +2843,7 @@
         <v>2028</v>
       </c>
       <c r="D191">
-        <v>338043.3704513524</v>
+        <v>368829.0966873575</v>
       </c>
     </row>
     <row r="192">
@@ -2856,7 +2856,7 @@
         <v>2024</v>
       </c>
       <c r="D192">
-        <v>224709.86374257</v>
+        <v>224709.8637425696</v>
       </c>
     </row>
     <row r="193">
@@ -2882,7 +2882,7 @@
         <v>2026</v>
       </c>
       <c r="D194">
-        <v>246709.7220194933</v>
+        <v>270914.2664062006</v>
       </c>
     </row>
     <row r="195">
@@ -2895,7 +2895,7 @@
         <v>2027</v>
       </c>
       <c r="D195">
-        <v>270919.6639446866</v>
+        <v>297567.1114661727</v>
       </c>
     </row>
     <row r="196">
@@ -2908,7 +2908,7 @@
         <v>2028</v>
       </c>
       <c r="D196">
-        <v>297567.7409947909</v>
+        <v>326844.1672827366</v>
       </c>
     </row>
     <row r="197">
@@ -2921,7 +2921,7 @@
         <v>2024</v>
       </c>
       <c r="D197">
-        <v>224709.8637424866</v>
+        <v>224709.863742487</v>
       </c>
     </row>
     <row r="198">
@@ -2947,7 +2947,7 @@
         <v>2026</v>
       </c>
       <c r="D199">
-        <v>246709.7220193894</v>
+        <v>270914.2664060779</v>
       </c>
     </row>
     <row r="200">
@@ -2960,7 +2960,7 @@
         <v>2027</v>
       </c>
       <c r="D200">
-        <v>270919.6639445653</v>
+        <v>297567.1114660384</v>
       </c>
     </row>
     <row r="201">
@@ -2973,7 +2973,7 @@
         <v>2028</v>
       </c>
       <c r="D201">
-        <v>297567.7409946572</v>
+        <v>326844.1672825909</v>
       </c>
     </row>
     <row r="202">
@@ -2986,7 +2986,7 @@
         <v>2024</v>
       </c>
       <c r="D202">
-        <v>268025.017911129</v>
+        <v>268025.0179111281</v>
       </c>
     </row>
     <row r="203">
@@ -3012,7 +3012,7 @@
         <v>2026</v>
       </c>
       <c r="D204">
-        <v>291996.3805548427</v>
+        <v>318160.109935311</v>
       </c>
     </row>
     <row r="205">
@@ -3025,7 +3025,7 @@
         <v>2027</v>
       </c>
       <c r="D205">
-        <v>318164.6123266579</v>
+        <v>346735.6933542024</v>
       </c>
     </row>
     <row r="206">
@@ -3038,7 +3038,7 @@
         <v>2028</v>
       </c>
       <c r="D206">
-        <v>346736.1493950812</v>
+        <v>377879.2867774632</v>
       </c>
     </row>
     <row r="207">
@@ -3051,7 +3051,7 @@
         <v>2024</v>
       </c>
       <c r="D207">
-        <v>224709.8637424866</v>
+        <v>224709.863742487</v>
       </c>
     </row>
     <row r="208">
@@ -3077,7 +3077,7 @@
         <v>2026</v>
       </c>
       <c r="D209">
-        <v>246709.7220193894</v>
+        <v>270914.2664060779</v>
       </c>
     </row>
     <row r="210">
@@ -3090,7 +3090,7 @@
         <v>2027</v>
       </c>
       <c r="D210">
-        <v>270919.6639445653</v>
+        <v>297567.1114660384</v>
       </c>
     </row>
     <row r="211">
@@ -3103,7 +3103,7 @@
         <v>2028</v>
       </c>
       <c r="D211">
-        <v>297567.7409946572</v>
+        <v>326844.1672825909</v>
       </c>
     </row>
     <row r="212">
@@ -3116,7 +3116,7 @@
         <v>2024</v>
       </c>
       <c r="D212">
-        <v>305659.5079597998</v>
+        <v>305659.5079597987</v>
       </c>
     </row>
     <row r="213">
@@ -3142,7 +3142,7 @@
         <v>2026</v>
       </c>
       <c r="D214">
-        <v>327132.7170364123</v>
+        <v>350351.4762329028</v>
       </c>
     </row>
     <row r="215">
@@ -3155,7 +3155,7 @@
         <v>2027</v>
       </c>
       <c r="D215">
-        <v>350407.8967404912</v>
+        <v>375653.6576701892</v>
       </c>
     </row>
     <row r="216">
@@ -3168,7 +3168,7 @@
         <v>2028</v>
       </c>
       <c r="D216">
-        <v>375668.0515174768</v>
+        <v>402829.4499118198</v>
       </c>
     </row>
     <row r="217">
@@ -3181,7 +3181,7 @@
         <v>2024</v>
       </c>
       <c r="D217">
-        <v>305659.5079597998</v>
+        <v>305659.5079597987</v>
       </c>
     </row>
     <row r="218">
@@ -3207,7 +3207,7 @@
         <v>2026</v>
       </c>
       <c r="D219">
-        <v>327132.7170364123</v>
+        <v>350351.4762329028</v>
       </c>
     </row>
     <row r="220">
@@ -3220,7 +3220,7 @@
         <v>2027</v>
       </c>
       <c r="D220">
-        <v>350407.8967404912</v>
+        <v>375653.6576701892</v>
       </c>
     </row>
     <row r="221">
@@ -3233,7 +3233,7 @@
         <v>2028</v>
       </c>
       <c r="D221">
-        <v>375668.0515174768</v>
+        <v>402829.4499118198</v>
       </c>
     </row>
     <row r="222">
@@ -3246,7 +3246,7 @@
         <v>2024</v>
       </c>
       <c r="D222">
-        <v>305659.5079597998</v>
+        <v>305659.5079597987</v>
       </c>
     </row>
     <row r="223">
@@ -3272,7 +3272,7 @@
         <v>2026</v>
       </c>
       <c r="D224">
-        <v>327132.7170364123</v>
+        <v>350351.4762329028</v>
       </c>
     </row>
     <row r="225">
@@ -3285,7 +3285,7 @@
         <v>2027</v>
       </c>
       <c r="D225">
-        <v>350407.8967404912</v>
+        <v>375653.6576701892</v>
       </c>
     </row>
     <row r="226">
@@ -3298,7 +3298,7 @@
         <v>2028</v>
       </c>
       <c r="D226">
-        <v>375668.0515174768</v>
+        <v>402829.4499118198</v>
       </c>
     </row>
     <row r="227">
@@ -3311,7 +3311,7 @@
         <v>2024</v>
       </c>
       <c r="D227">
-        <v>305659.5079597998</v>
+        <v>305659.5079597987</v>
       </c>
     </row>
     <row r="228">
@@ -3337,7 +3337,7 @@
         <v>2026</v>
       </c>
       <c r="D229">
-        <v>327132.7170364123</v>
+        <v>350351.4762329028</v>
       </c>
     </row>
     <row r="230">
@@ -3350,7 +3350,7 @@
         <v>2027</v>
       </c>
       <c r="D230">
-        <v>350407.8967404912</v>
+        <v>375653.6576701892</v>
       </c>
     </row>
     <row r="231">
@@ -3363,7 +3363,7 @@
         <v>2028</v>
       </c>
       <c r="D231">
-        <v>375668.0515174768</v>
+        <v>402829.4499118198</v>
       </c>
     </row>
     <row r="232">
@@ -3376,7 +3376,7 @@
         <v>2024</v>
       </c>
       <c r="D232">
-        <v>305659.5079597998</v>
+        <v>305659.5079597987</v>
       </c>
     </row>
     <row r="233">
@@ -3402,7 +3402,7 @@
         <v>2026</v>
       </c>
       <c r="D234">
-        <v>327132.7170364123</v>
+        <v>350351.4762329028</v>
       </c>
     </row>
     <row r="235">
@@ -3415,7 +3415,7 @@
         <v>2027</v>
       </c>
       <c r="D235">
-        <v>350407.8967404912</v>
+        <v>375653.6576701892</v>
       </c>
     </row>
     <row r="236">
@@ -3428,7 +3428,7 @@
         <v>2028</v>
       </c>
       <c r="D236">
-        <v>375668.0515174768</v>
+        <v>402829.4499118198</v>
       </c>
     </row>
     <row r="237">
@@ -3467,7 +3467,7 @@
         <v>2026</v>
       </c>
       <c r="D239">
-        <v>369718.944202198</v>
+        <v>395392.0065353211</v>
       </c>
     </row>
     <row r="240">
@@ -3480,7 +3480,7 @@
         <v>2027</v>
       </c>
       <c r="D240">
-        <v>395397.6225311106</v>
+        <v>422929.9474505896</v>
       </c>
     </row>
     <row r="241">
@@ -3493,7 +3493,7 @@
         <v>2028</v>
       </c>
       <c r="D241">
-        <v>422930.5100226681</v>
+        <v>452387.6337425844</v>
       </c>
     </row>
     <row r="242">
@@ -3506,7 +3506,7 @@
         <v>2024</v>
       </c>
       <c r="D242">
-        <v>322737.0514028475</v>
+        <v>322737.0514028469</v>
       </c>
     </row>
     <row r="243">
@@ -3532,7 +3532,7 @@
         <v>2026</v>
       </c>
       <c r="D244">
-        <v>348851.8338514452</v>
+        <v>377215.8042992281</v>
       </c>
     </row>
     <row r="245">
@@ -3545,7 +3545,7 @@
         <v>2027</v>
       </c>
       <c r="D245">
-        <v>377251.1855309155</v>
+        <v>408147.9651275449</v>
       </c>
     </row>
     <row r="246">
@@ -3558,7 +3558,7 @@
         <v>2028</v>
       </c>
       <c r="D246">
-        <v>408157.9169207505</v>
+        <v>441648.9056093694</v>
       </c>
     </row>
     <row r="247">
@@ -3597,7 +3597,7 @@
         <v>2026</v>
       </c>
       <c r="D249">
-        <v>369718.944202198</v>
+        <v>395392.0065353211</v>
       </c>
     </row>
     <row r="250">
@@ -3610,7 +3610,7 @@
         <v>2027</v>
       </c>
       <c r="D250">
-        <v>395397.6225311106</v>
+        <v>422929.9474505896</v>
       </c>
     </row>
     <row r="251">
@@ -3623,7 +3623,7 @@
         <v>2028</v>
       </c>
       <c r="D251">
-        <v>422930.5100226681</v>
+        <v>452387.6337425844</v>
       </c>
     </row>
     <row r="252">
@@ -3662,7 +3662,7 @@
         <v>2026</v>
       </c>
       <c r="D254">
-        <v>369718.944202198</v>
+        <v>395392.0065353211</v>
       </c>
     </row>
     <row r="255">
@@ -3675,7 +3675,7 @@
         <v>2027</v>
       </c>
       <c r="D255">
-        <v>395397.6225311106</v>
+        <v>422929.9474505896</v>
       </c>
     </row>
     <row r="256">
@@ -3688,7 +3688,7 @@
         <v>2028</v>
       </c>
       <c r="D256">
-        <v>422930.5100226681</v>
+        <v>452387.6337425844</v>
       </c>
     </row>
     <row r="257">
@@ -3727,7 +3727,7 @@
         <v>2026</v>
       </c>
       <c r="D259">
-        <v>369718.944202198</v>
+        <v>395392.0065353211</v>
       </c>
     </row>
     <row r="260">
@@ -3740,7 +3740,7 @@
         <v>2027</v>
       </c>
       <c r="D260">
-        <v>395397.6225311106</v>
+        <v>422929.9474505896</v>
       </c>
     </row>
     <row r="261">
@@ -3753,7 +3753,7 @@
         <v>2028</v>
       </c>
       <c r="D261">
-        <v>422930.5100226681</v>
+        <v>452387.6337425844</v>
       </c>
     </row>
     <row r="262">
@@ -3792,7 +3792,7 @@
         <v>2026</v>
       </c>
       <c r="D264">
-        <v>369718.944202198</v>
+        <v>395392.0065353211</v>
       </c>
     </row>
     <row r="265">
@@ -3805,7 +3805,7 @@
         <v>2027</v>
       </c>
       <c r="D265">
-        <v>395397.6225311106</v>
+        <v>422929.9474505896</v>
       </c>
     </row>
     <row r="266">
@@ -3818,7 +3818,7 @@
         <v>2028</v>
       </c>
       <c r="D266">
-        <v>422930.5100226681</v>
+        <v>452387.6337425844</v>
       </c>
     </row>
     <row r="267">
@@ -3857,7 +3857,7 @@
         <v>2026</v>
       </c>
       <c r="D269">
-        <v>369718.944202198</v>
+        <v>395392.0065353211</v>
       </c>
     </row>
     <row r="270">
@@ -3870,7 +3870,7 @@
         <v>2027</v>
       </c>
       <c r="D270">
-        <v>395397.6225311106</v>
+        <v>422929.9474505896</v>
       </c>
     </row>
     <row r="271">
@@ -3883,7 +3883,7 @@
         <v>2028</v>
       </c>
       <c r="D271">
-        <v>422930.5100226681</v>
+        <v>452387.6337425844</v>
       </c>
     </row>
     <row r="272">
@@ -3922,7 +3922,7 @@
         <v>2026</v>
       </c>
       <c r="D274">
-        <v>369718.944202198</v>
+        <v>395392.0065353211</v>
       </c>
     </row>
     <row r="275">
@@ -3935,7 +3935,7 @@
         <v>2027</v>
       </c>
       <c r="D275">
-        <v>395397.6225311106</v>
+        <v>422929.9474505896</v>
       </c>
     </row>
     <row r="276">
@@ -3948,7 +3948,7 @@
         <v>2028</v>
       </c>
       <c r="D276">
-        <v>422930.5100226681</v>
+        <v>452387.6337425844</v>
       </c>
     </row>
     <row r="277">
@@ -3961,7 +3961,7 @@
         <v>2024</v>
       </c>
       <c r="D277">
-        <v>345734.7262446327</v>
+        <v>345734.7262446321</v>
       </c>
     </row>
     <row r="278">
@@ -3987,7 +3987,7 @@
         <v>2026</v>
       </c>
       <c r="D279">
-        <v>369686.5061424968</v>
+        <v>395357.6997577403</v>
       </c>
     </row>
     <row r="280">
@@ -4000,7 +4000,7 @@
         <v>2027</v>
       </c>
       <c r="D280">
-        <v>395363.3338714255</v>
+        <v>422893.8578786106</v>
       </c>
     </row>
     <row r="281">
@@ -4013,7 +4013,7 @@
         <v>2028</v>
       </c>
       <c r="D281">
-        <v>422894.422934767</v>
+        <v>452349.6874307289</v>
       </c>
     </row>
     <row r="282">
@@ -4026,7 +4026,7 @@
         <v>2024</v>
       </c>
       <c r="D282">
-        <v>309092.6760637733</v>
+        <v>309092.6760637739</v>
       </c>
     </row>
     <row r="283">
@@ -4052,7 +4052,7 @@
         <v>2026</v>
       </c>
       <c r="D284">
-        <v>330762.1690683965</v>
+        <v>354175.7036716905</v>
       </c>
     </row>
     <row r="285">
@@ -4065,7 +4065,7 @@
         <v>2027</v>
       </c>
       <c r="D285">
-        <v>354226.6553395889</v>
+        <v>379651.3392268324</v>
       </c>
     </row>
     <row r="286">
@@ -4078,7 +4078,7 @@
         <v>2028</v>
       </c>
       <c r="D286">
-        <v>379663.7092741048</v>
+        <v>406999.2019679836</v>
       </c>
     </row>
     <row r="287">
@@ -4091,7 +4091,7 @@
         <v>2024</v>
       </c>
       <c r="D287">
-        <v>305659.5079597998</v>
+        <v>305659.5079597987</v>
       </c>
     </row>
     <row r="288">
@@ -4117,7 +4117,7 @@
         <v>2026</v>
       </c>
       <c r="D289">
-        <v>327132.7170364123</v>
+        <v>350351.4762329028</v>
       </c>
     </row>
     <row r="290">
@@ -4130,7 +4130,7 @@
         <v>2027</v>
       </c>
       <c r="D290">
-        <v>350407.8967404912</v>
+        <v>375653.6576701892</v>
       </c>
     </row>
     <row r="291">
@@ -4143,7 +4143,7 @@
         <v>2028</v>
       </c>
       <c r="D291">
-        <v>375668.0515174768</v>
+        <v>402829.4499118198</v>
       </c>
     </row>
     <row r="292">
@@ -4156,7 +4156,7 @@
         <v>2024</v>
       </c>
       <c r="D292">
-        <v>305659.5079597998</v>
+        <v>305659.5079597987</v>
       </c>
     </row>
     <row r="293">
@@ -4182,7 +4182,7 @@
         <v>2026</v>
       </c>
       <c r="D294">
-        <v>327132.7170364123</v>
+        <v>350351.4762329028</v>
       </c>
     </row>
     <row r="295">
@@ -4195,7 +4195,7 @@
         <v>2027</v>
       </c>
       <c r="D295">
-        <v>350407.8967404912</v>
+        <v>375653.6576701892</v>
       </c>
     </row>
     <row r="296">
@@ -4208,7 +4208,7 @@
         <v>2028</v>
       </c>
       <c r="D296">
-        <v>375668.0515174768</v>
+        <v>402829.4499118198</v>
       </c>
     </row>
     <row r="297">
@@ -4221,7 +4221,7 @@
         <v>2024</v>
       </c>
       <c r="D297">
-        <v>305529.3734568059</v>
+        <v>305529.3734568054</v>
       </c>
     </row>
     <row r="298">
@@ -4247,7 +4247,7 @@
         <v>2026</v>
       </c>
       <c r="D299">
-        <v>327004.8447748426</v>
+        <v>350226.5664179342</v>
       </c>
     </row>
     <row r="300">
@@ -4260,7 +4260,7 @@
         <v>2027</v>
       </c>
       <c r="D300">
-        <v>350282.8883136607</v>
+        <v>375532.1940414257</v>
       </c>
     </row>
     <row r="301">
@@ -4273,7 +4273,7 @@
         <v>2028</v>
       </c>
       <c r="D301">
-        <v>375546.5538727458</v>
+        <v>402712.4742694903</v>
       </c>
     </row>
     <row r="302">
@@ -4286,7 +4286,7 @@
         <v>2024</v>
       </c>
       <c r="D302">
-        <v>274312.0118264747</v>
+        <v>274312.0118264743</v>
       </c>
     </row>
     <row r="303">
@@ -4312,7 +4312,7 @@
         <v>2026</v>
       </c>
       <c r="D304">
-        <v>298513.7471730451</v>
+        <v>324901.6406089331</v>
       </c>
     </row>
     <row r="305">
@@ -4325,7 +4325,7 @@
         <v>2027</v>
       </c>
       <c r="D305">
-        <v>324906.4416619404</v>
+        <v>353693.2588895752</v>
       </c>
     </row>
     <row r="306">
@@ -4338,7 +4338,7 @@
         <v>2028</v>
       </c>
       <c r="D306">
-        <v>353693.7517208442</v>
+        <v>385037.8966492338</v>
       </c>
     </row>
     <row r="307">
@@ -4377,7 +4377,7 @@
         <v>2026</v>
       </c>
       <c r="D309">
-        <v>298242.6301645385</v>
+        <v>324693.716265775</v>
       </c>
     </row>
     <row r="310">
@@ -4390,7 +4390,7 @@
         <v>2027</v>
       </c>
       <c r="D310">
-        <v>324698.1276041339</v>
+        <v>353557.6568893177</v>
       </c>
     </row>
     <row r="311">
@@ -4403,7 +4403,7 @@
         <v>2028</v>
       </c>
       <c r="D311">
-        <v>353558.0963090294</v>
+        <v>384988.9189846065</v>
       </c>
     </row>
     <row r="312">
@@ -4416,7 +4416,7 @@
         <v>2024</v>
       </c>
       <c r="D312">
-        <v>266737.0804598138</v>
+        <v>266737.0804598124</v>
       </c>
     </row>
     <row r="313">
@@ -4442,7 +4442,7 @@
         <v>2026</v>
       </c>
       <c r="D314">
-        <v>290685.0903413373</v>
+        <v>316854.7391454254</v>
       </c>
     </row>
     <row r="315">
@@ -4455,7 +4455,7 @@
         <v>2027</v>
       </c>
       <c r="D315">
-        <v>316862.7496772689</v>
+        <v>345484.591653891</v>
       </c>
     </row>
     <row r="316">
@@ -4468,7 +4468,7 @@
         <v>2028</v>
       </c>
       <c r="D316">
-        <v>345485.5693262916</v>
+        <v>376704.5325163717</v>
       </c>
     </row>
     <row r="317">
@@ -4481,7 +4481,7 @@
         <v>2024</v>
       </c>
       <c r="D317">
-        <v>322395.5665317627</v>
+        <v>322395.5665317633</v>
       </c>
     </row>
     <row r="318">
@@ -4507,7 +4507,7 @@
         <v>2026</v>
       </c>
       <c r="D319">
-        <v>345879.8487804518</v>
+        <v>371166.9275757635</v>
       </c>
     </row>
     <row r="320">
@@ -4520,7 +4520,7 @@
         <v>2027</v>
       </c>
       <c r="D320">
-        <v>371177.87183998</v>
+        <v>398436.8627135377</v>
       </c>
     </row>
     <row r="321">
@@ -4533,7 +4533,7 @@
         <v>2028</v>
       </c>
       <c r="D321">
-        <v>398438.2581154539</v>
+        <v>427714.8358837243</v>
       </c>
     </row>
     <row r="322">
@@ -4572,7 +4572,7 @@
         <v>2026</v>
       </c>
       <c r="D324">
-        <v>369718.944202198</v>
+        <v>395392.0065353211</v>
       </c>
     </row>
     <row r="325">
@@ -4585,7 +4585,7 @@
         <v>2027</v>
       </c>
       <c r="D325">
-        <v>395397.6225311106</v>
+        <v>422929.9474505896</v>
       </c>
     </row>
     <row r="326">
@@ -4598,7 +4598,7 @@
         <v>2028</v>
       </c>
       <c r="D326">
-        <v>422930.5100226681</v>
+        <v>452387.6337425844</v>
       </c>
     </row>
     <row r="327">
@@ -4637,7 +4637,7 @@
         <v>2026</v>
       </c>
       <c r="D329">
-        <v>369718.944202198</v>
+        <v>395392.0065353211</v>
       </c>
     </row>
     <row r="330">
@@ -4650,7 +4650,7 @@
         <v>2027</v>
       </c>
       <c r="D330">
-        <v>395397.6225311106</v>
+        <v>422929.9474505896</v>
       </c>
     </row>
     <row r="331">
@@ -4663,7 +4663,7 @@
         <v>2028</v>
       </c>
       <c r="D331">
-        <v>422930.5100226681</v>
+        <v>452387.6337425844</v>
       </c>
     </row>
     <row r="332">
@@ -4676,7 +4676,7 @@
         <v>2024</v>
       </c>
       <c r="D332">
-        <v>288411.1414377519</v>
+        <v>288411.1414377524</v>
       </c>
     </row>
     <row r="333">
@@ -4702,7 +4702,7 @@
         <v>2026</v>
       </c>
       <c r="D334">
-        <v>314182.3661402086</v>
+        <v>342274.8895230365</v>
       </c>
     </row>
     <row r="335">
@@ -4715,7 +4715,7 @@
         <v>2027</v>
       </c>
       <c r="D335">
-        <v>342274.0646266888</v>
+        <v>372896.7445487161</v>
       </c>
     </row>
     <row r="336">
@@ -4728,7 +4728,7 @@
         <v>2028</v>
       </c>
       <c r="D336">
-        <v>372896.78464394</v>
+        <v>406258.3356405188</v>
       </c>
     </row>
     <row r="337">
@@ -4767,7 +4767,7 @@
         <v>2026</v>
       </c>
       <c r="D339">
-        <v>356434.2727005602</v>
+        <v>383849.8401997011</v>
       </c>
     </row>
     <row r="340">
@@ -4780,7 +4780,7 @@
         <v>2027</v>
       </c>
       <c r="D340">
-        <v>383849.9073768063</v>
+        <v>413377.9275966179</v>
       </c>
     </row>
     <row r="341">
@@ -4793,7 +4793,7 @@
         <v>2028</v>
       </c>
       <c r="D341">
-        <v>413377.9290497213</v>
+        <v>445177.5015386613</v>
       </c>
     </row>
     <row r="342">
@@ -4806,7 +4806,7 @@
         <v>2024</v>
       </c>
       <c r="D342">
-        <v>287741.1701923698</v>
+        <v>287741.1701923703</v>
       </c>
     </row>
     <row r="343">
@@ -4832,7 +4832,7 @@
         <v>2026</v>
       </c>
       <c r="D344">
-        <v>310639.3549958317</v>
+        <v>335522.0135228338</v>
       </c>
     </row>
     <row r="345">
@@ -4845,7 +4845,7 @@
         <v>2027</v>
       </c>
       <c r="D345">
-        <v>335548.3313939571</v>
+        <v>362658.4730572659</v>
       </c>
     </row>
     <row r="346">
@@ -4858,7 +4858,7 @@
         <v>2028</v>
       </c>
       <c r="D346">
-        <v>362663.0855896368</v>
+        <v>392004.6410216913</v>
       </c>
     </row>
     <row r="347">
@@ -4871,7 +4871,7 @@
         <v>2024</v>
       </c>
       <c r="D347">
-        <v>195287.4145333217</v>
+        <v>195287.4145333213</v>
       </c>
     </row>
     <row r="348">
@@ -4897,7 +4897,7 @@
         <v>2026</v>
       </c>
       <c r="D349">
-        <v>215358.36881839</v>
+        <v>238176.0223991052</v>
       </c>
     </row>
     <row r="350">
@@ -4910,7 +4910,7 @@
         <v>2027</v>
       </c>
       <c r="D350">
-        <v>238444.6433551398</v>
+        <v>265064.5861475251</v>
       </c>
     </row>
     <row r="351">
@@ -4923,7 +4923,7 @@
         <v>2028</v>
       </c>
       <c r="D351">
-        <v>265181.7348536342</v>
+        <v>295379.9934113534</v>
       </c>
     </row>
     <row r="352">
@@ -4936,7 +4936,7 @@
         <v>2024</v>
       </c>
       <c r="D352">
-        <v>194919.6175545366</v>
+        <v>194919.6175545356</v>
       </c>
     </row>
     <row r="353">
@@ -4962,7 +4962,7 @@
         <v>2026</v>
       </c>
       <c r="D354">
-        <v>214929.9535655357</v>
+        <v>237681.0746062641</v>
       </c>
     </row>
     <row r="355">
@@ -4975,7 +4975,7 @@
         <v>2027</v>
       </c>
       <c r="D355">
-        <v>237952.1502398725</v>
+        <v>264504.836089653</v>
       </c>
     </row>
     <row r="356">
@@ -4988,7 +4988,7 @@
         <v>2028</v>
       </c>
       <c r="D356">
-        <v>264623.6675692835</v>
+        <v>294752.7282224756</v>
       </c>
     </row>
     <row r="357">
@@ -5001,7 +5001,7 @@
         <v>2024</v>
       </c>
       <c r="D357">
-        <v>279920.7027369796</v>
+        <v>279920.7027369791</v>
       </c>
     </row>
     <row r="358">
@@ -5027,7 +5027,7 @@
         <v>2026</v>
       </c>
       <c r="D359">
-        <v>309862.565275585</v>
+        <v>343007.5912081982</v>
       </c>
     </row>
     <row r="360">
@@ -5040,7 +5040,7 @@
         <v>2027</v>
       </c>
       <c r="D360">
-        <v>343007.5937036644</v>
+        <v>379698.505974901</v>
       </c>
     </row>
     <row r="361">
@@ -5053,7 +5053,7 @@
         <v>2028</v>
       </c>
       <c r="D361">
-        <v>379698.5059914481</v>
+        <v>420314.1829911052</v>
       </c>
     </row>
     <row r="362">
@@ -5066,7 +5066,7 @@
         <v>2024</v>
       </c>
       <c r="D362">
-        <v>279920.7027369796</v>
+        <v>279920.7027369791</v>
       </c>
     </row>
     <row r="363">
@@ -5092,7 +5092,7 @@
         <v>2026</v>
       </c>
       <c r="D364">
-        <v>309862.565275585</v>
+        <v>343007.5912081982</v>
       </c>
     </row>
     <row r="365">
@@ -5105,7 +5105,7 @@
         <v>2027</v>
       </c>
       <c r="D365">
-        <v>343007.5937036644</v>
+        <v>379698.505974901</v>
       </c>
     </row>
     <row r="366">
@@ -5118,7 +5118,7 @@
         <v>2028</v>
       </c>
       <c r="D366">
-        <v>379698.5059914481</v>
+        <v>420314.1829911052</v>
       </c>
     </row>
     <row r="367">
@@ -5131,7 +5131,7 @@
         <v>2024</v>
       </c>
       <c r="D367">
-        <v>279920.7027369796</v>
+        <v>279920.7027369791</v>
       </c>
     </row>
     <row r="368">
@@ -5157,7 +5157,7 @@
         <v>2026</v>
       </c>
       <c r="D369">
-        <v>309862.565275585</v>
+        <v>343007.5912081982</v>
       </c>
     </row>
     <row r="370">
@@ -5170,7 +5170,7 @@
         <v>2027</v>
       </c>
       <c r="D370">
-        <v>343007.5937036644</v>
+        <v>379698.505974901</v>
       </c>
     </row>
     <row r="371">
@@ -5183,7 +5183,7 @@
         <v>2028</v>
       </c>
       <c r="D371">
-        <v>379698.5059914481</v>
+        <v>420314.1829911052</v>
       </c>
     </row>
     <row r="372">
@@ -5196,7 +5196,7 @@
         <v>2024</v>
       </c>
       <c r="D372">
-        <v>279920.7027369796</v>
+        <v>279920.7027369791</v>
       </c>
     </row>
     <row r="373">
@@ -5222,7 +5222,7 @@
         <v>2026</v>
       </c>
       <c r="D374">
-        <v>309862.565275585</v>
+        <v>343007.5912081982</v>
       </c>
     </row>
     <row r="375">
@@ -5235,7 +5235,7 @@
         <v>2027</v>
       </c>
       <c r="D375">
-        <v>343007.5937036644</v>
+        <v>379698.505974901</v>
       </c>
     </row>
     <row r="376">
@@ -5248,7 +5248,7 @@
         <v>2028</v>
       </c>
       <c r="D376">
-        <v>379698.5059914481</v>
+        <v>420314.1829911052</v>
       </c>
     </row>
     <row r="377">
@@ -5261,7 +5261,7 @@
         <v>2024</v>
       </c>
       <c r="D377">
-        <v>279920.7027369796</v>
+        <v>279920.7027369791</v>
       </c>
     </row>
     <row r="378">
@@ -5287,7 +5287,7 @@
         <v>2026</v>
       </c>
       <c r="D379">
-        <v>309862.565275585</v>
+        <v>343007.5912081982</v>
       </c>
     </row>
     <row r="380">
@@ -5300,7 +5300,7 @@
         <v>2027</v>
       </c>
       <c r="D380">
-        <v>343007.5937036644</v>
+        <v>379698.505974901</v>
       </c>
     </row>
     <row r="381">
@@ -5313,7 +5313,7 @@
         <v>2028</v>
       </c>
       <c r="D381">
-        <v>379698.5059914481</v>
+        <v>420314.1829911052</v>
       </c>
     </row>
     <row r="382">
@@ -5326,7 +5326,7 @@
         <v>2024</v>
       </c>
       <c r="D382">
-        <v>269459.0687036096</v>
+        <v>269459.0687036086</v>
       </c>
     </row>
     <row r="383">
@@ -5352,7 +5352,7 @@
         <v>2026</v>
       </c>
       <c r="D384">
-        <v>298800.626722076</v>
+        <v>331339.7204341433</v>
       </c>
     </row>
     <row r="385">
@@ -5365,7 +5365,7 @@
         <v>2027</v>
       </c>
       <c r="D385">
-        <v>331339.6832978525</v>
+        <v>367424.9558627411</v>
       </c>
     </row>
     <row r="386">
@@ -5378,7 +5378,7 @@
         <v>2028</v>
       </c>
       <c r="D386">
-        <v>367424.956470565</v>
+        <v>407440.1302802992</v>
       </c>
     </row>
     <row r="387">
@@ -5391,7 +5391,7 @@
         <v>2024</v>
       </c>
       <c r="D387">
-        <v>278971.3020838107</v>
+        <v>278971.3020838102</v>
       </c>
     </row>
     <row r="388">
@@ -5417,7 +5417,7 @@
         <v>2026</v>
       </c>
       <c r="D389">
-        <v>308843.6622148303</v>
+        <v>341914.8988819366</v>
       </c>
     </row>
     <row r="390">
@@ -5430,7 +5430,7 @@
         <v>2027</v>
       </c>
       <c r="D390">
-        <v>341914.8993277834</v>
+        <v>378527.5788535576</v>
       </c>
     </row>
     <row r="391">
@@ -5443,7 +5443,7 @@
         <v>2028</v>
       </c>
       <c r="D391">
-        <v>378527.5788552238</v>
+        <v>419060.7909253595</v>
       </c>
     </row>
     <row r="392">
@@ -5456,7 +5456,7 @@
         <v>2024</v>
       </c>
       <c r="D392">
-        <v>165926.5141536148</v>
+        <v>165926.5141536142</v>
       </c>
     </row>
     <row r="393">
@@ -5482,7 +5482,7 @@
         <v>2026</v>
       </c>
       <c r="D394">
-        <v>185018.0899168191</v>
+        <v>206408.2563636045</v>
       </c>
     </row>
     <row r="395">
@@ -5495,7 +5495,7 @@
         <v>2027</v>
       </c>
       <c r="D395">
-        <v>206423.1748052656</v>
+        <v>230435.0672019241</v>
       </c>
     </row>
     <row r="396">
@@ -5508,7 +5508,7 @@
         <v>2028</v>
       </c>
       <c r="D396">
-        <v>230437.5046377698</v>
+        <v>257266.8659761062</v>
       </c>
     </row>
     <row r="397">
@@ -5521,7 +5521,7 @@
         <v>2024</v>
       </c>
       <c r="D397">
-        <v>341196.6491843323</v>
+        <v>341196.6491843318</v>
       </c>
     </row>
     <row r="398">
@@ -5547,7 +5547,7 @@
         <v>2026</v>
       </c>
       <c r="D399">
-        <v>366563.4106603409</v>
+        <v>393824.3812634929</v>
       </c>
     </row>
     <row r="400">
@@ -5560,7 +5560,7 @@
         <v>2027</v>
       </c>
       <c r="D400">
-        <v>393824.6579744138</v>
+        <v>423122.512403396</v>
       </c>
     </row>
     <row r="401">
@@ -5573,7 +5573,7 @@
         <v>2028</v>
       </c>
       <c r="D401">
-        <v>423122.5223383044</v>
+        <v>454600.2777665246</v>
       </c>
     </row>
     <row r="402">
@@ -5586,7 +5586,7 @@
         <v>2024</v>
       </c>
       <c r="D402">
-        <v>341196.6491843323</v>
+        <v>341196.6491843318</v>
       </c>
     </row>
     <row r="403">
@@ -5612,7 +5612,7 @@
         <v>2026</v>
       </c>
       <c r="D404">
-        <v>366563.4106603409</v>
+        <v>393824.3812634929</v>
       </c>
     </row>
     <row r="405">
@@ -5625,7 +5625,7 @@
         <v>2027</v>
       </c>
       <c r="D405">
-        <v>393824.6579744138</v>
+        <v>423122.512403396</v>
       </c>
     </row>
     <row r="406">
@@ -5638,7 +5638,7 @@
         <v>2028</v>
       </c>
       <c r="D406">
-        <v>423122.5223383044</v>
+        <v>454600.2777665246</v>
       </c>
     </row>
     <row r="407">
@@ -5651,7 +5651,7 @@
         <v>2024</v>
       </c>
       <c r="D407">
-        <v>341196.6491843323</v>
+        <v>341196.6491843318</v>
       </c>
     </row>
     <row r="408">
@@ -5677,7 +5677,7 @@
         <v>2026</v>
       </c>
       <c r="D409">
-        <v>366563.4106603409</v>
+        <v>393824.3812634929</v>
       </c>
     </row>
     <row r="410">
@@ -5690,7 +5690,7 @@
         <v>2027</v>
       </c>
       <c r="D410">
-        <v>393824.6579744138</v>
+        <v>423122.512403396</v>
       </c>
     </row>
     <row r="411">
@@ -5703,7 +5703,7 @@
         <v>2028</v>
       </c>
       <c r="D411">
-        <v>423122.5223383044</v>
+        <v>454600.2777665246</v>
       </c>
     </row>
     <row r="412">
@@ -5716,7 +5716,7 @@
         <v>2024</v>
       </c>
       <c r="D412">
-        <v>341196.6491843323</v>
+        <v>341196.6491843318</v>
       </c>
     </row>
     <row r="413">
@@ -5742,7 +5742,7 @@
         <v>2026</v>
       </c>
       <c r="D414">
-        <v>366563.4106603409</v>
+        <v>393824.3812634929</v>
       </c>
     </row>
     <row r="415">
@@ -5755,7 +5755,7 @@
         <v>2027</v>
       </c>
       <c r="D415">
-        <v>393824.6579744138</v>
+        <v>423122.512403396</v>
       </c>
     </row>
     <row r="416">
@@ -5768,7 +5768,7 @@
         <v>2028</v>
       </c>
       <c r="D416">
-        <v>423122.5223383044</v>
+        <v>454600.2777665246</v>
       </c>
     </row>
     <row r="417">
@@ -5781,7 +5781,7 @@
         <v>2024</v>
       </c>
       <c r="D417">
-        <v>341196.6491843323</v>
+        <v>341196.6491843318</v>
       </c>
     </row>
     <row r="418">
@@ -5807,7 +5807,7 @@
         <v>2026</v>
       </c>
       <c r="D419">
-        <v>366563.4106603409</v>
+        <v>393824.3812634929</v>
       </c>
     </row>
     <row r="420">
@@ -5820,7 +5820,7 @@
         <v>2027</v>
       </c>
       <c r="D420">
-        <v>393824.6579744138</v>
+        <v>423122.512403396</v>
       </c>
     </row>
     <row r="421">
@@ -5833,7 +5833,7 @@
         <v>2028</v>
       </c>
       <c r="D421">
-        <v>423122.5223383044</v>
+        <v>454600.2777665246</v>
       </c>
     </row>
     <row r="422">
@@ -5846,7 +5846,7 @@
         <v>2024</v>
       </c>
       <c r="D422">
-        <v>341196.6491843323</v>
+        <v>341196.6491843318</v>
       </c>
     </row>
     <row r="423">
@@ -5872,7 +5872,7 @@
         <v>2026</v>
       </c>
       <c r="D424">
-        <v>366563.4106603409</v>
+        <v>393824.3812634929</v>
       </c>
     </row>
     <row r="425">
@@ -5885,7 +5885,7 @@
         <v>2027</v>
       </c>
       <c r="D425">
-        <v>393824.6579744138</v>
+        <v>423122.512403396</v>
       </c>
     </row>
     <row r="426">
@@ -5898,7 +5898,7 @@
         <v>2028</v>
       </c>
       <c r="D426">
-        <v>423122.5223383044</v>
+        <v>454600.2777665246</v>
       </c>
     </row>
     <row r="427">
@@ -5911,7 +5911,7 @@
         <v>2024</v>
       </c>
       <c r="D427">
-        <v>223943.0476868082</v>
+        <v>223943.0476868078</v>
       </c>
     </row>
     <row r="428">
@@ -5937,7 +5937,7 @@
         <v>2026</v>
       </c>
       <c r="D429">
-        <v>247585.0779466876</v>
+        <v>273750.0517216091</v>
       </c>
     </row>
     <row r="430">
@@ -5950,7 +5950,7 @@
         <v>2027</v>
       </c>
       <c r="D430">
-        <v>273748.4038976505</v>
+        <v>302704.5669450988</v>
       </c>
     </row>
     <row r="431">
@@ -5963,7 +5963,7 @@
         <v>2028</v>
       </c>
       <c r="D431">
-        <v>302704.678078649</v>
+        <v>334721.9669735093</v>
       </c>
     </row>
     <row r="432">
@@ -5976,7 +5976,7 @@
         <v>2024</v>
       </c>
       <c r="D432">
-        <v>223943.0476868082</v>
+        <v>223943.0476868078</v>
       </c>
     </row>
     <row r="433">
@@ -6002,7 +6002,7 @@
         <v>2026</v>
       </c>
       <c r="D434">
-        <v>247585.0779466876</v>
+        <v>273750.0517216091</v>
       </c>
     </row>
     <row r="435">
@@ -6015,7 +6015,7 @@
         <v>2027</v>
       </c>
       <c r="D435">
-        <v>273748.4038976505</v>
+        <v>302704.5669450988</v>
       </c>
     </row>
     <row r="436">
@@ -6028,7 +6028,7 @@
         <v>2028</v>
       </c>
       <c r="D436">
-        <v>302704.678078649</v>
+        <v>334721.9669735093</v>
       </c>
     </row>
     <row r="437">
@@ -6041,7 +6041,7 @@
         <v>2024</v>
       </c>
       <c r="D437">
-        <v>223943.0476868082</v>
+        <v>223943.0476868078</v>
       </c>
     </row>
     <row r="438">
@@ -6067,7 +6067,7 @@
         <v>2026</v>
       </c>
       <c r="D439">
-        <v>247585.0779466876</v>
+        <v>273750.0517216091</v>
       </c>
     </row>
     <row r="440">
@@ -6080,7 +6080,7 @@
         <v>2027</v>
       </c>
       <c r="D440">
-        <v>273748.4038976505</v>
+        <v>302704.5669450988</v>
       </c>
     </row>
     <row r="441">
@@ -6093,7 +6093,7 @@
         <v>2028</v>
       </c>
       <c r="D441">
-        <v>302704.678078649</v>
+        <v>334721.9669735093</v>
       </c>
     </row>
     <row r="442">
@@ -6106,7 +6106,7 @@
         <v>2024</v>
       </c>
       <c r="D442">
-        <v>223943.0476868082</v>
+        <v>223943.0476868078</v>
       </c>
     </row>
     <row r="443">
@@ -6132,7 +6132,7 @@
         <v>2026</v>
       </c>
       <c r="D444">
-        <v>247585.0779466876</v>
+        <v>273750.0517216091</v>
       </c>
     </row>
     <row r="445">
@@ -6145,7 +6145,7 @@
         <v>2027</v>
       </c>
       <c r="D445">
-        <v>273748.4038976505</v>
+        <v>302704.5669450988</v>
       </c>
     </row>
     <row r="446">
@@ -6158,7 +6158,7 @@
         <v>2028</v>
       </c>
       <c r="D446">
-        <v>302704.678078649</v>
+        <v>334721.9669735093</v>
       </c>
     </row>
     <row r="447">
@@ -6171,7 +6171,7 @@
         <v>2024</v>
       </c>
       <c r="D447">
-        <v>339972.7015386743</v>
+        <v>339972.7015386731</v>
       </c>
     </row>
     <row r="448">
@@ -6197,7 +6197,7 @@
         <v>2026</v>
       </c>
       <c r="D449">
-        <v>364532.3706096096</v>
+        <v>390894.3923337234</v>
       </c>
     </row>
     <row r="450">
@@ -6210,7 +6210,7 @@
         <v>2027</v>
       </c>
       <c r="D450">
-        <v>390896.1680930458</v>
+        <v>419198.7568271771</v>
       </c>
     </row>
     <row r="451">
@@ -6223,7 +6223,7 @@
         <v>2028</v>
       </c>
       <c r="D451">
-        <v>419198.876912808</v>
+        <v>449553.0050856059</v>
       </c>
     </row>
     <row r="452">
@@ -6236,7 +6236,7 @@
         <v>2024</v>
       </c>
       <c r="D452">
-        <v>166771.7670543181</v>
+        <v>166771.7670543178</v>
       </c>
     </row>
     <row r="453">
@@ -6262,7 +6262,7 @@
         <v>2026</v>
       </c>
       <c r="D454">
-        <v>185867.4558853358</v>
+        <v>207251.949792317</v>
       </c>
     </row>
     <row r="455">
@@ -6275,7 +6275,7 @@
         <v>2027</v>
       </c>
       <c r="D455">
-        <v>207266.9811141192</v>
+        <v>231261.2307858785</v>
       </c>
     </row>
     <row r="456">
@@ -6288,7 +6288,7 @@
         <v>2028</v>
       </c>
       <c r="D456">
-        <v>231263.6941920996</v>
+        <v>258060.1340902383</v>
       </c>
     </row>
     <row r="457">
@@ -6301,7 +6301,7 @@
         <v>2024</v>
       </c>
       <c r="D457">
-        <v>166771.7670543181</v>
+        <v>166771.7670543178</v>
       </c>
     </row>
     <row r="458">
@@ -6327,7 +6327,7 @@
         <v>2026</v>
       </c>
       <c r="D459">
-        <v>185867.4558853358</v>
+        <v>207251.949792317</v>
       </c>
     </row>
     <row r="460">
@@ -6340,7 +6340,7 @@
         <v>2027</v>
       </c>
       <c r="D460">
-        <v>207266.9811141192</v>
+        <v>231261.2307858785</v>
       </c>
     </row>
     <row r="461">
@@ -6353,7 +6353,7 @@
         <v>2028</v>
       </c>
       <c r="D461">
-        <v>231263.6941920996</v>
+        <v>258060.1340902383</v>
       </c>
     </row>
     <row r="462">
@@ -6366,7 +6366,7 @@
         <v>2024</v>
       </c>
       <c r="D462">
-        <v>166771.7670543181</v>
+        <v>166771.7670543178</v>
       </c>
     </row>
     <row r="463">
@@ -6392,7 +6392,7 @@
         <v>2026</v>
       </c>
       <c r="D464">
-        <v>185867.4558853358</v>
+        <v>207251.949792317</v>
       </c>
     </row>
     <row r="465">
@@ -6405,7 +6405,7 @@
         <v>2027</v>
       </c>
       <c r="D465">
-        <v>207266.9811141192</v>
+        <v>231261.2307858785</v>
       </c>
     </row>
     <row r="466">
@@ -6418,7 +6418,7 @@
         <v>2028</v>
       </c>
       <c r="D466">
-        <v>231263.6941920996</v>
+        <v>258060.1340902383</v>
       </c>
     </row>
     <row r="467">
@@ -6431,7 +6431,7 @@
         <v>2024</v>
       </c>
       <c r="D467">
-        <v>215333.0622573817</v>
+        <v>215333.0622573809</v>
       </c>
     </row>
     <row r="468">
@@ -6457,7 +6457,7 @@
         <v>2026</v>
       </c>
       <c r="D469">
-        <v>238406.7957066435</v>
+        <v>263966.0428220129</v>
       </c>
     </row>
     <row r="470">
@@ -6470,7 +6470,7 @@
         <v>2027</v>
       </c>
       <c r="D470">
-        <v>263965.4763094994</v>
+        <v>292278.0585794365</v>
       </c>
     </row>
     <row r="471">
@@ -6483,7 +6483,7 @@
         <v>2028</v>
       </c>
       <c r="D471">
-        <v>292278.0857513974</v>
+        <v>323626.8060807805</v>
       </c>
     </row>
     <row r="472">
@@ -6496,7 +6496,7 @@
         <v>2024</v>
       </c>
       <c r="D472">
-        <v>223943.0476868082</v>
+        <v>223943.0476868078</v>
       </c>
     </row>
     <row r="473">
@@ -6522,7 +6522,7 @@
         <v>2026</v>
       </c>
       <c r="D474">
-        <v>247585.0779466876</v>
+        <v>273750.0517216091</v>
       </c>
     </row>
     <row r="475">
@@ -6535,7 +6535,7 @@
         <v>2027</v>
       </c>
       <c r="D475">
-        <v>273748.4038976505</v>
+        <v>302704.5669450988</v>
       </c>
     </row>
     <row r="476">
@@ -6548,7 +6548,7 @@
         <v>2028</v>
       </c>
       <c r="D476">
-        <v>302704.678078649</v>
+        <v>334721.9669735093</v>
       </c>
     </row>
     <row r="477">
@@ -6561,7 +6561,7 @@
         <v>2024</v>
       </c>
       <c r="D477">
-        <v>223512.4728760135</v>
+        <v>223512.4728760131</v>
       </c>
     </row>
     <row r="478">
@@ -6587,7 +6587,7 @@
         <v>2026</v>
       </c>
       <c r="D479">
-        <v>247126.4464581462</v>
+        <v>273261.4887401669</v>
       </c>
     </row>
     <row r="480">
@@ -6600,7 +6600,7 @@
         <v>2027</v>
       </c>
       <c r="D480">
-        <v>273259.9076267802</v>
+        <v>302184.2619738968</v>
       </c>
     </row>
     <row r="481">
@@ -6613,7 +6613,7 @@
         <v>2028</v>
       </c>
       <c r="D481">
-        <v>302184.367224369</v>
+        <v>334168.6529662397</v>
       </c>
     </row>
     <row r="482">
@@ -6626,7 +6626,7 @@
         <v>2024</v>
       </c>
       <c r="D482">
-        <v>166771.7670543181</v>
+        <v>166771.7670543178</v>
       </c>
     </row>
     <row r="483">
@@ -6652,7 +6652,7 @@
         <v>2026</v>
       </c>
       <c r="D484">
-        <v>185867.4558853358</v>
+        <v>207251.949792317</v>
       </c>
     </row>
     <row r="485">
@@ -6665,7 +6665,7 @@
         <v>2027</v>
       </c>
       <c r="D485">
-        <v>207266.9811141192</v>
+        <v>231261.2307858785</v>
       </c>
     </row>
     <row r="486">
@@ -6678,7 +6678,7 @@
         <v>2028</v>
       </c>
       <c r="D486">
-        <v>231263.6941920996</v>
+        <v>258060.1340902383</v>
       </c>
     </row>
     <row r="487">
@@ -6691,7 +6691,7 @@
         <v>2024</v>
       </c>
       <c r="D487">
-        <v>166771.7670543181</v>
+        <v>166771.7670543178</v>
       </c>
     </row>
     <row r="488">
@@ -6717,7 +6717,7 @@
         <v>2026</v>
       </c>
       <c r="D489">
-        <v>185867.4558853358</v>
+        <v>207251.949792317</v>
       </c>
     </row>
     <row r="490">
@@ -6730,7 +6730,7 @@
         <v>2027</v>
       </c>
       <c r="D490">
-        <v>207266.9811141192</v>
+        <v>231261.2307858785</v>
       </c>
     </row>
     <row r="491">
@@ -6743,7 +6743,7 @@
         <v>2028</v>
       </c>
       <c r="D491">
-        <v>231263.6941920996</v>
+        <v>258060.1340902383</v>
       </c>
     </row>
     <row r="492">
@@ -6756,7 +6756,7 @@
         <v>2024</v>
       </c>
       <c r="D492">
-        <v>166771.7670543181</v>
+        <v>166771.7670543178</v>
       </c>
     </row>
     <row r="493">
@@ -6782,7 +6782,7 @@
         <v>2026</v>
       </c>
       <c r="D494">
-        <v>185867.4558853358</v>
+        <v>207251.949792317</v>
       </c>
     </row>
     <row r="495">
@@ -6795,7 +6795,7 @@
         <v>2027</v>
       </c>
       <c r="D495">
-        <v>207266.9811141192</v>
+        <v>231261.2307858785</v>
       </c>
     </row>
     <row r="496">
@@ -6808,7 +6808,7 @@
         <v>2028</v>
       </c>
       <c r="D496">
-        <v>231263.6941920996</v>
+        <v>258060.1340902383</v>
       </c>
     </row>
     <row r="497">
@@ -6821,7 +6821,7 @@
         <v>2024</v>
       </c>
       <c r="D497">
-        <v>165964.5919316634</v>
+        <v>165964.5919316631</v>
       </c>
     </row>
     <row r="498">
@@ -6847,7 +6847,7 @@
         <v>2026</v>
       </c>
       <c r="D499">
-        <v>185056.3350024821</v>
+        <v>206446.2222614812</v>
       </c>
     </row>
     <row r="500">
@@ -6860,7 +6860,7 @@
         <v>2027</v>
       </c>
       <c r="D500">
-        <v>206461.1459496455</v>
+        <v>230472.2133488198</v>
       </c>
     </row>
     <row r="501">
@@ -6873,7 +6873,7 @@
         <v>2028</v>
       </c>
       <c r="D501">
-        <v>230474.6519890972</v>
+        <v>257302.4910716571</v>
       </c>
     </row>
     <row r="502">
@@ -6886,7 +6886,7 @@
         <v>2024</v>
       </c>
       <c r="D502">
-        <v>283045.0517975623</v>
+        <v>283045.0517975618</v>
       </c>
     </row>
     <row r="503">
@@ -6912,7 +6912,7 @@
         <v>2026</v>
       </c>
       <c r="D504">
-        <v>307476.8806618343</v>
+        <v>334119.5702832622</v>
       </c>
     </row>
     <row r="505">
@@ -6925,7 +6925,7 @@
         <v>2027</v>
       </c>
       <c r="D505">
-        <v>334133.3042245762</v>
+        <v>363226.447924901</v>
       </c>
     </row>
     <row r="506">
@@ -6938,7 +6938,7 @@
         <v>2028</v>
       </c>
       <c r="D506">
-        <v>363228.4586757288</v>
+        <v>394875.5334686326</v>
       </c>
     </row>
     <row r="507">
@@ -6951,7 +6951,7 @@
         <v>2024</v>
       </c>
       <c r="D507">
-        <v>237938.1257981927</v>
+        <v>237938.1257981932</v>
       </c>
     </row>
     <row r="508">
@@ -6977,7 +6977,7 @@
         <v>2026</v>
       </c>
       <c r="D509">
-        <v>260588.6288992723</v>
+        <v>285401.3083668167</v>
       </c>
     </row>
     <row r="510">
@@ -6990,7 +6990,7 @@
         <v>2027</v>
       </c>
       <c r="D510">
-        <v>285401.5100063474</v>
+        <v>312583.7907247833</v>
       </c>
     </row>
     <row r="511">
@@ -7003,7 +7003,7 @@
         <v>2028</v>
       </c>
       <c r="D511">
-        <v>312583.7981921734</v>
+        <v>342355.2393139287</v>
       </c>
     </row>
     <row r="512">
@@ -7042,7 +7042,7 @@
         <v>2026</v>
       </c>
       <c r="D514">
-        <v>232943.6667820439</v>
+        <v>260786.6773118163</v>
       </c>
     </row>
     <row r="515">
@@ -7055,7 +7055,7 @@
         <v>2027</v>
       </c>
       <c r="D515">
-        <v>260794.8863651546</v>
+        <v>292057.0869140218</v>
       </c>
     </row>
     <row r="516">
@@ -7068,7 +7068,7 @@
         <v>2028</v>
       </c>
       <c r="D516">
-        <v>292058.2631891792</v>
+        <v>327081.0208504408</v>
       </c>
     </row>
     <row r="517">
@@ -7081,7 +7081,7 @@
         <v>2024</v>
       </c>
       <c r="D517">
-        <v>244931.0703566761</v>
+        <v>244931.0703566756</v>
       </c>
     </row>
     <row r="518">
@@ -7107,7 +7107,7 @@
         <v>2026</v>
       </c>
       <c r="D519">
-        <v>267853.9827021851</v>
+        <v>292934.5982973256</v>
       </c>
     </row>
     <row r="520">
@@ -7120,7 +7120,7 @@
         <v>2027</v>
       </c>
       <c r="D520">
-        <v>292935.1954108629</v>
+        <v>320379.1303443337</v>
       </c>
     </row>
     <row r="521">
@@ -7133,7 +7133,7 @@
         <v>2028</v>
       </c>
       <c r="D521">
-        <v>320379.1618792212</v>
+        <v>350394.9962420365</v>
       </c>
     </row>
     <row r="522">
@@ -7172,7 +7172,7 @@
         <v>2026</v>
       </c>
       <c r="D524">
-        <v>264027.5761911435</v>
+        <v>288965.8951294243</v>
       </c>
     </row>
     <row r="525">
@@ -7185,7 +7185,7 @@
         <v>2027</v>
       </c>
       <c r="D525">
-        <v>288966.2043795905</v>
+        <v>316269.4496385023</v>
       </c>
     </row>
     <row r="526">
@@ -7198,7 +7198,7 @@
         <v>2028</v>
       </c>
       <c r="D526">
-        <v>316269.462791856</v>
+        <v>346152.881501302</v>
       </c>
     </row>
     <row r="527">
@@ -7237,7 +7237,7 @@
         <v>2026</v>
       </c>
       <c r="D529">
-        <v>310130.5513515816</v>
+        <v>336908.3736201967</v>
       </c>
     </row>
     <row r="530">
@@ -7250,7 +7250,7 @@
         <v>2027</v>
       </c>
       <c r="D530">
-        <v>336918.4147576817</v>
+        <v>366121.8664034181</v>
       </c>
     </row>
     <row r="531">
@@ -7263,7 +7263,7 @@
         <v>2028</v>
       </c>
       <c r="D531">
-        <v>366123.176818919</v>
+        <v>397872.747829929</v>
       </c>
     </row>
     <row r="532">
@@ -7276,7 +7276,7 @@
         <v>2024</v>
       </c>
       <c r="D532">
-        <v>286881.1330594054</v>
+        <v>286881.1330594059</v>
       </c>
     </row>
     <row r="533">
@@ -7302,7 +7302,7 @@
         <v>2026</v>
       </c>
       <c r="D534">
-        <v>311516.5561679903</v>
+        <v>338353.6329026203</v>
       </c>
     </row>
     <row r="535">
@@ -7315,7 +7315,7 @@
         <v>2027</v>
       </c>
       <c r="D535">
-        <v>338364.1158090527</v>
+        <v>367630.4580733303</v>
       </c>
     </row>
     <row r="536">
@@ -7328,7 +7328,7 @@
         <v>2028</v>
       </c>
       <c r="D536">
-        <v>367631.8441466709</v>
+        <v>399445.0458174876</v>
       </c>
     </row>
     <row r="537">
@@ -7341,7 +7341,7 @@
         <v>2024</v>
       </c>
       <c r="D537">
-        <v>237270.020811105</v>
+        <v>237270.0208111046</v>
       </c>
     </row>
     <row r="538">
@@ -7367,7 +7367,7 @@
         <v>2026</v>
       </c>
       <c r="D539">
-        <v>259895.1274509263</v>
+        <v>284681.7767434124</v>
       </c>
     </row>
     <row r="540">
@@ -7380,7 +7380,7 @@
         <v>2027</v>
       </c>
       <c r="D540">
-        <v>284681.8916629478</v>
+        <v>311837.2451986275</v>
       </c>
     </row>
     <row r="541">
@@ -7393,7 +7393,7 @@
         <v>2028</v>
       </c>
       <c r="D541">
-        <v>311837.248723286</v>
+        <v>341583.0542538528</v>
       </c>
     </row>
     <row r="542">
@@ -7432,7 +7432,7 @@
         <v>2026</v>
       </c>
       <c r="D544">
-        <v>232943.6667820439</v>
+        <v>260786.6773118163</v>
       </c>
     </row>
     <row r="545">
@@ -7445,7 +7445,7 @@
         <v>2027</v>
       </c>
       <c r="D545">
-        <v>260794.8863651546</v>
+        <v>292057.0869140218</v>
       </c>
     </row>
     <row r="546">
@@ -7458,7 +7458,7 @@
         <v>2028</v>
       </c>
       <c r="D546">
-        <v>292058.2631891792</v>
+        <v>327081.0208504408</v>
       </c>
     </row>
     <row r="547">
@@ -7497,7 +7497,7 @@
         <v>2026</v>
       </c>
       <c r="D549">
-        <v>232943.6667820439</v>
+        <v>260786.6773118163</v>
       </c>
     </row>
     <row r="550">
@@ -7510,7 +7510,7 @@
         <v>2027</v>
       </c>
       <c r="D550">
-        <v>260794.8863651546</v>
+        <v>292057.0869140218</v>
       </c>
     </row>
     <row r="551">
@@ -7523,7 +7523,7 @@
         <v>2028</v>
       </c>
       <c r="D551">
-        <v>292058.2631891792</v>
+        <v>327081.0208504408</v>
       </c>
     </row>
     <row r="552">
@@ -7562,7 +7562,7 @@
         <v>2026</v>
       </c>
       <c r="D554">
-        <v>232943.6667820439</v>
+        <v>260786.6773118163</v>
       </c>
     </row>
     <row r="555">
@@ -7575,7 +7575,7 @@
         <v>2027</v>
       </c>
       <c r="D555">
-        <v>260794.8863651546</v>
+        <v>292057.0869140218</v>
       </c>
     </row>
     <row r="556">
@@ -7588,7 +7588,7 @@
         <v>2028</v>
       </c>
       <c r="D556">
-        <v>292058.2631891792</v>
+        <v>327081.0208504408</v>
       </c>
     </row>
     <row r="557">
@@ -7627,7 +7627,7 @@
         <v>2026</v>
       </c>
       <c r="D559">
-        <v>232943.6667820439</v>
+        <v>260786.6773118163</v>
       </c>
     </row>
     <row r="560">
@@ -7640,7 +7640,7 @@
         <v>2027</v>
       </c>
       <c r="D560">
-        <v>260794.8863651546</v>
+        <v>292057.0869140218</v>
       </c>
     </row>
     <row r="561">
@@ -7653,7 +7653,7 @@
         <v>2028</v>
       </c>
       <c r="D561">
-        <v>292058.2631891792</v>
+        <v>327081.0208504408</v>
       </c>
     </row>
     <row r="562">
@@ -7692,7 +7692,7 @@
         <v>2026</v>
       </c>
       <c r="D564">
-        <v>157832.4812135399</v>
+        <v>182229.5997253017</v>
       </c>
     </row>
     <row r="565">
@@ -7705,7 +7705,7 @@
         <v>2027</v>
       </c>
       <c r="D565">
-        <v>182238.4222230733</v>
+        <v>210517.3801599728</v>
       </c>
     </row>
     <row r="566">
@@ -7718,7 +7718,7 @@
         <v>2028</v>
       </c>
       <c r="D566">
-        <v>210518.5484405709</v>
+        <v>243200.3650912523</v>
       </c>
     </row>
     <row r="567">
@@ -7731,7 +7731,7 @@
         <v>2024</v>
       </c>
       <c r="D567">
-        <v>134233.6417578442</v>
+        <v>134233.6417578439</v>
       </c>
     </row>
     <row r="568">
@@ -7757,7 +7757,7 @@
         <v>2026</v>
       </c>
       <c r="D569">
-        <v>155239.5064070644</v>
+        <v>179609.2140971918</v>
       </c>
     </row>
     <row r="570">
@@ -7770,7 +7770,7 @@
         <v>2027</v>
       </c>
       <c r="D570">
-        <v>179617.9086694608</v>
+        <v>207923.4724925383</v>
       </c>
     </row>
     <row r="571">
@@ -7783,7 +7783,7 @@
         <v>2028</v>
       </c>
       <c r="D571">
-        <v>207924.6133009189</v>
+        <v>240705.2568939188</v>
       </c>
     </row>
     <row r="572">
@@ -7796,7 +7796,7 @@
         <v>2024</v>
       </c>
       <c r="D572">
-        <v>134233.6417578442</v>
+        <v>134233.6417578439</v>
       </c>
     </row>
     <row r="573">
@@ -7822,7 +7822,7 @@
         <v>2026</v>
       </c>
       <c r="D574">
-        <v>155239.5064070644</v>
+        <v>179609.2140971918</v>
       </c>
     </row>
     <row r="575">
@@ -7835,7 +7835,7 @@
         <v>2027</v>
       </c>
       <c r="D575">
-        <v>179617.9086694608</v>
+        <v>207923.4724925383</v>
       </c>
     </row>
     <row r="576">
@@ -7848,7 +7848,7 @@
         <v>2028</v>
       </c>
       <c r="D576">
-        <v>207924.6133009189</v>
+        <v>240705.2568939188</v>
       </c>
     </row>
     <row r="577">
@@ -7887,7 +7887,7 @@
         <v>2026</v>
       </c>
       <c r="D579">
-        <v>155718.1345292624</v>
+        <v>180091.8344391545</v>
       </c>
     </row>
     <row r="580">
@@ -7900,7 +7900,7 @@
         <v>2027</v>
       </c>
       <c r="D580">
-        <v>180100.5550038125</v>
+        <v>208399.6888883742</v>
       </c>
     </row>
     <row r="581">
@@ -7913,7 +7913,7 @@
         <v>2028</v>
       </c>
       <c r="D581">
-        <v>208400.8351741917</v>
+        <v>241161.1116339082</v>
       </c>
     </row>
     <row r="582">
@@ -7952,7 +7952,7 @@
         <v>2026</v>
       </c>
       <c r="D584">
-        <v>232943.6667820439</v>
+        <v>260786.6773118163</v>
       </c>
     </row>
     <row r="585">
@@ -7965,7 +7965,7 @@
         <v>2027</v>
       </c>
       <c r="D585">
-        <v>260794.8863651546</v>
+        <v>292057.0869140218</v>
       </c>
     </row>
     <row r="586">
@@ -7978,7 +7978,7 @@
         <v>2028</v>
       </c>
       <c r="D586">
-        <v>292058.2631891792</v>
+        <v>327081.0208504408</v>
       </c>
     </row>
     <row r="587">
@@ -7991,7 +7991,7 @@
         <v>2024</v>
       </c>
       <c r="D587">
-        <v>237270.020811105</v>
+        <v>237270.0208111046</v>
       </c>
     </row>
     <row r="588">
@@ -8017,7 +8017,7 @@
         <v>2026</v>
       </c>
       <c r="D589">
-        <v>259895.1274509263</v>
+        <v>284681.7767434124</v>
       </c>
     </row>
     <row r="590">
@@ -8030,7 +8030,7 @@
         <v>2027</v>
       </c>
       <c r="D590">
-        <v>284681.8916629478</v>
+        <v>311837.2451986275</v>
       </c>
     </row>
     <row r="591">
@@ -8043,7 +8043,7 @@
         <v>2028</v>
       </c>
       <c r="D591">
-        <v>311837.248723286</v>
+        <v>341583.0542538528</v>
       </c>
     </row>
     <row r="592">
@@ -8082,7 +8082,7 @@
         <v>2026</v>
       </c>
       <c r="D594">
-        <v>232943.6667820439</v>
+        <v>260786.6773118163</v>
       </c>
     </row>
     <row r="595">
@@ -8095,7 +8095,7 @@
         <v>2027</v>
       </c>
       <c r="D595">
-        <v>260794.8863651546</v>
+        <v>292057.0869140218</v>
       </c>
     </row>
     <row r="596">
@@ -8108,7 +8108,7 @@
         <v>2028</v>
       </c>
       <c r="D596">
-        <v>292058.2631891792</v>
+        <v>327081.0208504408</v>
       </c>
     </row>
     <row r="597">
@@ -8147,7 +8147,7 @@
         <v>2026</v>
       </c>
       <c r="D599">
-        <v>232943.6667820439</v>
+        <v>260786.6773118163</v>
       </c>
     </row>
     <row r="600">
@@ -8160,7 +8160,7 @@
         <v>2027</v>
       </c>
       <c r="D600">
-        <v>260794.8863651546</v>
+        <v>292057.0869140218</v>
       </c>
     </row>
     <row r="601">
@@ -8173,7 +8173,7 @@
         <v>2028</v>
       </c>
       <c r="D601">
-        <v>292058.2631891792</v>
+        <v>327081.0208504408</v>
       </c>
     </row>
     <row r="602">
@@ -8186,7 +8186,7 @@
         <v>2024</v>
       </c>
       <c r="D602">
-        <v>204691.961211762</v>
+        <v>204691.9612117613</v>
       </c>
     </row>
     <row r="603">
@@ -8212,7 +8212,7 @@
         <v>2026</v>
       </c>
       <c r="D604">
-        <v>229292.4632137711</v>
+        <v>256914.4034884734</v>
       </c>
     </row>
     <row r="605">
@@ -8225,7 +8225,7 @@
         <v>2027</v>
       </c>
       <c r="D605">
-        <v>256922.6803605375</v>
+        <v>287964.3863175741</v>
       </c>
     </row>
     <row r="606">
@@ -8238,7 +8238,7 @@
         <v>2028</v>
       </c>
       <c r="D606">
-        <v>287965.5697305485</v>
+        <v>322770.965768573</v>
       </c>
     </row>
     <row r="607">
@@ -8251,7 +8251,7 @@
         <v>2024</v>
       </c>
       <c r="D607">
-        <v>134233.6417578442</v>
+        <v>134233.6417578439</v>
       </c>
     </row>
     <row r="608">
@@ -8277,7 +8277,7 @@
         <v>2026</v>
       </c>
       <c r="D609">
-        <v>155239.5064070644</v>
+        <v>179609.2140971918</v>
       </c>
     </row>
     <row r="610">
@@ -8290,7 +8290,7 @@
         <v>2027</v>
       </c>
       <c r="D610">
-        <v>179617.9086694608</v>
+        <v>207923.4724925383</v>
       </c>
     </row>
     <row r="611">
@@ -8303,7 +8303,7 @@
         <v>2028</v>
       </c>
       <c r="D611">
-        <v>207924.6133009189</v>
+        <v>240705.2568939188</v>
       </c>
     </row>
     <row r="612">
@@ -8316,7 +8316,7 @@
         <v>2024</v>
       </c>
       <c r="D612">
-        <v>134233.6417578442</v>
+        <v>134233.6417578439</v>
       </c>
     </row>
     <row r="613">
@@ -8342,7 +8342,7 @@
         <v>2026</v>
       </c>
       <c r="D614">
-        <v>155239.5064070644</v>
+        <v>179609.2140971918</v>
       </c>
     </row>
     <row r="615">
@@ -8355,7 +8355,7 @@
         <v>2027</v>
       </c>
       <c r="D615">
-        <v>179617.9086694608</v>
+        <v>207923.4724925383</v>
       </c>
     </row>
     <row r="616">
@@ -8368,7 +8368,7 @@
         <v>2028</v>
       </c>
       <c r="D616">
-        <v>207924.6133009189</v>
+        <v>240705.2568939188</v>
       </c>
     </row>
     <row r="617">
@@ -8381,7 +8381,7 @@
         <v>2024</v>
       </c>
       <c r="D617">
-        <v>134233.6417578442</v>
+        <v>134233.6417578439</v>
       </c>
     </row>
     <row r="618">
@@ -8407,7 +8407,7 @@
         <v>2026</v>
       </c>
       <c r="D619">
-        <v>155239.5064070644</v>
+        <v>179609.2140971918</v>
       </c>
     </row>
     <row r="620">
@@ -8420,7 +8420,7 @@
         <v>2027</v>
       </c>
       <c r="D620">
-        <v>179617.9086694608</v>
+        <v>207923.4724925383</v>
       </c>
     </row>
     <row r="621">
@@ -8433,7 +8433,7 @@
         <v>2028</v>
       </c>
       <c r="D621">
-        <v>207924.6133009189</v>
+        <v>240705.2568939188</v>
       </c>
     </row>
     <row r="622">
@@ -8446,7 +8446,7 @@
         <v>2024</v>
       </c>
       <c r="D622">
-        <v>134233.6417578442</v>
+        <v>134233.6417578439</v>
       </c>
     </row>
     <row r="623">
@@ -8472,7 +8472,7 @@
         <v>2026</v>
       </c>
       <c r="D624">
-        <v>155239.5064070644</v>
+        <v>179609.2140971918</v>
       </c>
     </row>
     <row r="625">
@@ -8485,7 +8485,7 @@
         <v>2027</v>
       </c>
       <c r="D625">
-        <v>179617.9086694608</v>
+        <v>207923.4724925383</v>
       </c>
     </row>
     <row r="626">
@@ -8498,7 +8498,7 @@
         <v>2028</v>
       </c>
       <c r="D626">
-        <v>207924.6133009189</v>
+        <v>240705.2568939188</v>
       </c>
     </row>
     <row r="627">
@@ -8511,7 +8511,7 @@
         <v>2024</v>
       </c>
       <c r="D627">
-        <v>165581.0173702447</v>
+        <v>165581.0173702443</v>
       </c>
     </row>
     <row r="628">
@@ -8537,7 +8537,7 @@
         <v>2026</v>
       </c>
       <c r="D629">
-        <v>187510.4335980942</v>
+        <v>212379.200233795</v>
       </c>
     </row>
     <row r="630">
@@ -8550,7 +8550,7 @@
         <v>2027</v>
       </c>
       <c r="D630">
-        <v>212382.1558800192</v>
+        <v>240595.9471752125</v>
       </c>
     </row>
     <row r="631">
@@ -8563,7 +8563,7 @@
         <v>2028</v>
       </c>
       <c r="D631">
-        <v>240596.2296126256</v>
+        <v>272562.5371672192</v>
       </c>
     </row>
     <row r="632">
@@ -8576,7 +8576,7 @@
         <v>2024</v>
       </c>
       <c r="D632">
-        <v>219888.456288204</v>
+        <v>219888.4562882032</v>
       </c>
     </row>
     <row r="633">
@@ -8602,7 +8602,7 @@
         <v>2026</v>
       </c>
       <c r="D634">
-        <v>241818.8031931348</v>
+        <v>265937.2030728207</v>
       </c>
     </row>
     <row r="635">
@@ -8615,7 +8615,7 @@
         <v>2027</v>
       </c>
       <c r="D635">
-        <v>265937.2140715529</v>
+        <v>292462.0854805097</v>
       </c>
     </row>
     <row r="636">
@@ -8628,7 +8628,7 @@
         <v>2028</v>
       </c>
       <c r="D636">
-        <v>292462.0856365482</v>
+        <v>321632.5906725202</v>
       </c>
     </row>
     <row r="637">
@@ -8641,7 +8641,7 @@
         <v>2024</v>
       </c>
       <c r="D637">
-        <v>205828.8570724619</v>
+        <v>205828.8570724615</v>
       </c>
     </row>
     <row r="638">
@@ -8667,7 +8667,7 @@
         <v>2026</v>
       </c>
       <c r="D639">
-        <v>230427.8932615744</v>
+        <v>258022.8074432346</v>
       </c>
     </row>
     <row r="640">
@@ -8680,7 +8680,7 @@
         <v>2027</v>
       </c>
       <c r="D640">
-        <v>258029.4569281852</v>
+        <v>289007.4112428436</v>
       </c>
     </row>
     <row r="641">
@@ -8693,7 +8693,7 @@
         <v>2028</v>
       </c>
       <c r="D641">
-        <v>289008.2955709007</v>
+        <v>323715.7649565506</v>
       </c>
     </row>
     <row r="642">
@@ -8732,7 +8732,7 @@
         <v>2026</v>
       </c>
       <c r="D644">
-        <v>232943.6667820439</v>
+        <v>260786.6773118163</v>
       </c>
     </row>
     <row r="645">
@@ -8745,7 +8745,7 @@
         <v>2027</v>
       </c>
       <c r="D645">
-        <v>260794.8863651546</v>
+        <v>292057.0869140218</v>
       </c>
     </row>
     <row r="646">
@@ -8758,7 +8758,7 @@
         <v>2028</v>
       </c>
       <c r="D646">
-        <v>292058.2631891792</v>
+        <v>327081.0208504408</v>
       </c>
     </row>
     <row r="647">
@@ -8771,7 +8771,7 @@
         <v>2024</v>
       </c>
       <c r="D647">
-        <v>264066.7633851426</v>
+        <v>264066.763385144</v>
       </c>
     </row>
     <row r="648">
@@ -8797,7 +8797,7 @@
         <v>2026</v>
       </c>
       <c r="D649">
-        <v>287523.0002731558</v>
+        <v>313232.7355075887</v>
       </c>
     </row>
     <row r="650">
@@ -8810,7 +8810,7 @@
         <v>2027</v>
       </c>
       <c r="D650">
-        <v>313264.8006110343</v>
+        <v>341531.4991818194</v>
       </c>
     </row>
     <row r="651">
@@ -8823,7 +8823,7 @@
         <v>2028</v>
       </c>
       <c r="D651">
-        <v>341538.0930719335</v>
+        <v>372408.4615176566</v>
       </c>
     </row>
     <row r="652">
@@ -8836,7 +8836,7 @@
         <v>2024</v>
       </c>
       <c r="D652">
-        <v>165796.6724132109</v>
+        <v>165796.6724132106</v>
       </c>
     </row>
     <row r="653">
@@ -8862,7 +8862,7 @@
         <v>2026</v>
       </c>
       <c r="D654">
-        <v>186058.6459123499</v>
+        <v>208821.2199137375</v>
       </c>
     </row>
     <row r="655">
@@ -8875,7 +8875,7 @@
         <v>2027</v>
       </c>
       <c r="D655">
-        <v>208819.5369586506</v>
+        <v>234390.2958941993</v>
       </c>
     </row>
     <row r="656">
@@ -8888,7 +8888,7 @@
         <v>2028</v>
       </c>
       <c r="D656">
-        <v>234390.4262373376</v>
+        <v>263090.6116036318</v>
       </c>
     </row>
     <row r="657">
@@ -8901,7 +8901,7 @@
         <v>2024</v>
       </c>
       <c r="D657">
-        <v>162993.9639321426</v>
+        <v>162993.9639321429</v>
       </c>
     </row>
     <row r="658">
@@ -8927,7 +8927,7 @@
         <v>2026</v>
       </c>
       <c r="D659">
-        <v>183182.8113035031</v>
+        <v>205907.1257719559</v>
       </c>
     </row>
     <row r="660">
@@ -8940,7 +8940,7 @@
         <v>2027</v>
       </c>
       <c r="D660">
-        <v>205904.2667096594</v>
+        <v>231479.9609448984</v>
       </c>
     </row>
     <row r="661">
@@ -8953,7 +8953,7 @@
         <v>2028</v>
       </c>
       <c r="D661">
-        <v>231480.2248008847</v>
+        <v>260229.729061073</v>
       </c>
     </row>
     <row r="662">
@@ -8966,7 +8966,7 @@
         <v>2024</v>
       </c>
       <c r="D662">
-        <v>162993.9639321426</v>
+        <v>162993.9639321429</v>
       </c>
     </row>
     <row r="663">
@@ -8992,7 +8992,7 @@
         <v>2026</v>
       </c>
       <c r="D664">
-        <v>183182.8113035031</v>
+        <v>205907.1257719559</v>
       </c>
     </row>
     <row r="665">
@@ -9005,7 +9005,7 @@
         <v>2027</v>
       </c>
       <c r="D665">
-        <v>205904.2667096594</v>
+        <v>231479.9609448984</v>
       </c>
     </row>
     <row r="666">
@@ -9018,7 +9018,7 @@
         <v>2028</v>
       </c>
       <c r="D666">
-        <v>231480.2248008847</v>
+        <v>260229.729061073</v>
       </c>
     </row>
     <row r="667">
@@ -9057,7 +9057,7 @@
         <v>2026</v>
       </c>
       <c r="D669">
-        <v>183884.2918757344</v>
+        <v>206652.1525802338</v>
       </c>
     </row>
     <row r="670">
@@ -9070,7 +9070,7 @@
         <v>2027</v>
       </c>
       <c r="D670">
-        <v>206649.4364342981</v>
+        <v>232267.6951671139</v>
       </c>
     </row>
     <row r="671">
@@ -9083,7 +9083,7 @@
         <v>2028</v>
       </c>
       <c r="D671">
-        <v>232267.9416502477</v>
+        <v>261059.2403468351</v>
       </c>
     </row>
     <row r="672">
@@ -9096,7 +9096,7 @@
         <v>2024</v>
       </c>
       <c r="D672">
-        <v>162993.9639321426</v>
+        <v>162993.9639321429</v>
       </c>
     </row>
     <row r="673">
@@ -9122,7 +9122,7 @@
         <v>2026</v>
       </c>
       <c r="D674">
-        <v>183182.8113035031</v>
+        <v>205907.1257719559</v>
       </c>
     </row>
     <row r="675">
@@ -9135,7 +9135,7 @@
         <v>2027</v>
       </c>
       <c r="D675">
-        <v>205904.2667096594</v>
+        <v>231479.9609448984</v>
       </c>
     </row>
     <row r="676">
@@ -9148,7 +9148,7 @@
         <v>2028</v>
       </c>
       <c r="D676">
-        <v>231480.2248008847</v>
+        <v>260229.729061073</v>
       </c>
     </row>
     <row r="677">
@@ -9161,7 +9161,7 @@
         <v>2024</v>
       </c>
       <c r="D677">
-        <v>190554.0671822158</v>
+        <v>190554.0671822151</v>
       </c>
     </row>
     <row r="678">
@@ -9187,7 +9187,7 @@
         <v>2026</v>
       </c>
       <c r="D679">
-        <v>213047.2612708629</v>
+        <v>238219.6120979452</v>
       </c>
     </row>
     <row r="680">
@@ -9200,7 +9200,7 @@
         <v>2027</v>
       </c>
       <c r="D680">
-        <v>238221.3175322081</v>
+        <v>266398.7744010065</v>
       </c>
     </row>
     <row r="681">
@@ -9213,7 +9213,7 @@
         <v>2028</v>
       </c>
       <c r="D681">
-        <v>266398.9097052668</v>
+        <v>297911.723187181</v>
       </c>
     </row>
     <row r="682">
@@ -9226,7 +9226,7 @@
         <v>2024</v>
       </c>
       <c r="D682">
-        <v>190229.1027386646</v>
+        <v>190229.102738665</v>
       </c>
     </row>
     <row r="683">
@@ -9252,7 +9252,7 @@
         <v>2026</v>
       </c>
       <c r="D684">
-        <v>209475.2644608464</v>
+        <v>231383.9294820002</v>
       </c>
     </row>
     <row r="685">
@@ -9265,7 +9265,7 @@
         <v>2027</v>
       </c>
       <c r="D685">
-        <v>231684.6372883838</v>
+        <v>257377.4116350598</v>
       </c>
     </row>
     <row r="686">
@@ -9278,7 +9278,7 @@
         <v>2028</v>
       </c>
       <c r="D686">
-        <v>257517.6673209237</v>
+        <v>286759.27118353</v>
       </c>
     </row>
     <row r="687">
@@ -9317,7 +9317,7 @@
         <v>2026</v>
       </c>
       <c r="D689">
-        <v>227720.9376320322</v>
+        <v>252453.4813323453</v>
       </c>
     </row>
     <row r="690">
@@ -9330,7 +9330,7 @@
         <v>2027</v>
       </c>
       <c r="D690">
-        <v>252646.6207272556</v>
+        <v>281164.9630901179</v>
       </c>
     </row>
     <row r="691">
@@ -9343,7 +9343,7 @@
         <v>2028</v>
       </c>
       <c r="D691">
-        <v>281236.0289255272</v>
+        <v>313379.3001120149</v>
       </c>
     </row>
     <row r="692">
@@ -9382,7 +9382,7 @@
         <v>2026</v>
       </c>
       <c r="D694">
-        <v>309862.565276546</v>
+        <v>343007.5912093547</v>
       </c>
     </row>
     <row r="695">
@@ -9395,7 +9395,7 @@
         <v>2027</v>
       </c>
       <c r="D695">
-        <v>343007.5937048209</v>
+        <v>379698.5059762803</v>
       </c>
     </row>
     <row r="696">
@@ -9408,7 +9408,7 @@
         <v>2028</v>
       </c>
       <c r="D696">
-        <v>379698.5059928267</v>
+        <v>420314.1829927426</v>
       </c>
     </row>
     <row r="697">
@@ -9421,7 +9421,7 @@
         <v>2024</v>
       </c>
       <c r="D697">
-        <v>121063.9680637751</v>
+        <v>121063.9680637748</v>
       </c>
     </row>
     <row r="698">
@@ -9447,7 +9447,7 @@
         <v>2026</v>
       </c>
       <c r="D699">
-        <v>142945.9426211637</v>
+        <v>168783.7910555859</v>
       </c>
     </row>
     <row r="700">
@@ -9460,7 +9460,7 @@
         <v>2027</v>
       </c>
       <c r="D700">
-        <v>168783.7986805491</v>
+        <v>199292.8311895965</v>
       </c>
     </row>
     <row r="701">
@@ -9473,7 +9473,7 @@
         <v>2028</v>
       </c>
       <c r="D701">
-        <v>199292.8312789829</v>
+        <v>235316.6282651322</v>
       </c>
     </row>
     <row r="702">
@@ -9486,7 +9486,7 @@
         <v>2024</v>
       </c>
       <c r="D702">
-        <v>121063.9680637751</v>
+        <v>121063.9680637748</v>
       </c>
     </row>
     <row r="703">
@@ -9512,7 +9512,7 @@
         <v>2026</v>
       </c>
       <c r="D704">
-        <v>142945.9426211637</v>
+        <v>168783.7910555859</v>
       </c>
     </row>
     <row r="705">
@@ -9525,7 +9525,7 @@
         <v>2027</v>
       </c>
       <c r="D705">
-        <v>168783.7986805491</v>
+        <v>199292.8311895965</v>
       </c>
     </row>
     <row r="706">
@@ -9538,7 +9538,7 @@
         <v>2028</v>
       </c>
       <c r="D706">
-        <v>199292.8312789829</v>
+        <v>235316.6282651322</v>
       </c>
     </row>
     <row r="707">
@@ -9551,7 +9551,7 @@
         <v>2024</v>
       </c>
       <c r="D707">
-        <v>121063.9680637751</v>
+        <v>121063.9680637748</v>
       </c>
     </row>
     <row r="708">
@@ -9577,7 +9577,7 @@
         <v>2026</v>
       </c>
       <c r="D709">
-        <v>142945.9426211637</v>
+        <v>168783.7910555859</v>
       </c>
     </row>
     <row r="710">
@@ -9590,7 +9590,7 @@
         <v>2027</v>
       </c>
       <c r="D710">
-        <v>168783.7986805491</v>
+        <v>199292.8311895965</v>
       </c>
     </row>
     <row r="711">
@@ -9603,7 +9603,7 @@
         <v>2028</v>
       </c>
       <c r="D711">
-        <v>199292.8312789829</v>
+        <v>235316.6282651322</v>
       </c>
     </row>
     <row r="712">
@@ -9616,7 +9616,7 @@
         <v>2024</v>
       </c>
       <c r="D712">
-        <v>156631.555138357</v>
+        <v>156631.5551383564</v>
       </c>
     </row>
     <row r="713">
@@ -9642,7 +9642,7 @@
         <v>2026</v>
       </c>
       <c r="D714">
-        <v>179613.8613634334</v>
+        <v>205990.6279321154</v>
       </c>
     </row>
     <row r="715">
@@ -9655,7 +9655,7 @@
         <v>2027</v>
       </c>
       <c r="D715">
-        <v>205989.5046387402</v>
+        <v>236262.6066111528</v>
       </c>
     </row>
     <row r="716">
@@ -9668,7 +9668,7 @@
         <v>2028</v>
       </c>
       <c r="D716">
-        <v>236262.6714997333</v>
+        <v>270983.5191790378</v>
       </c>
     </row>
     <row r="717">
@@ -9681,7 +9681,7 @@
         <v>2024</v>
       </c>
       <c r="D717">
-        <v>279920.7027369796</v>
+        <v>279920.7027369791</v>
       </c>
     </row>
     <row r="718">
@@ -9707,7 +9707,7 @@
         <v>2026</v>
       </c>
       <c r="D719">
-        <v>309862.565275585</v>
+        <v>343007.5912081982</v>
       </c>
     </row>
     <row r="720">
@@ -9720,7 +9720,7 @@
         <v>2027</v>
       </c>
       <c r="D720">
-        <v>343007.5937036644</v>
+        <v>379698.505974901</v>
       </c>
     </row>
     <row r="721">
@@ -9733,7 +9733,7 @@
         <v>2028</v>
       </c>
       <c r="D721">
-        <v>379698.5059914481</v>
+        <v>420314.1829911052</v>
       </c>
     </row>
     <row r="722">
@@ -9772,7 +9772,7 @@
         <v>2026</v>
       </c>
       <c r="D724">
-        <v>236430.1104585481</v>
+        <v>262469.6055368262</v>
       </c>
     </row>
     <row r="725">
@@ -9785,7 +9785,7 @@
         <v>2027</v>
       </c>
       <c r="D725">
-        <v>262609.3019566659</v>
+        <v>292388.0873309211</v>
       </c>
     </row>
     <row r="726">
@@ -9798,7 +9798,7 @@
         <v>2028</v>
       </c>
       <c r="D726">
-        <v>292432.4125252917</v>
+        <v>325865.0837264584</v>
       </c>
     </row>
     <row r="727">
@@ -9811,7 +9811,7 @@
         <v>2024</v>
       </c>
       <c r="D727">
-        <v>190229.1027386646</v>
+        <v>190229.102738665</v>
       </c>
     </row>
     <row r="728">
@@ -9837,7 +9837,7 @@
         <v>2026</v>
       </c>
       <c r="D729">
-        <v>209475.2644608464</v>
+        <v>231383.9294820002</v>
       </c>
     </row>
     <row r="730">
@@ -9850,7 +9850,7 @@
         <v>2027</v>
       </c>
       <c r="D730">
-        <v>231684.6372883838</v>
+        <v>257377.4116350598</v>
       </c>
     </row>
     <row r="731">
@@ -9863,7 +9863,7 @@
         <v>2028</v>
       </c>
       <c r="D731">
-        <v>257517.6673209237</v>
+        <v>286759.27118353</v>
       </c>
     </row>
     <row r="732">
@@ -9902,7 +9902,7 @@
         <v>2026</v>
       </c>
       <c r="D734">
-        <v>230716.6841534972</v>
+        <v>255904.9636129032</v>
       </c>
     </row>
     <row r="735">
@@ -9915,7 +9915,7 @@
         <v>2027</v>
       </c>
       <c r="D735">
-        <v>256079.3979248046</v>
+        <v>285040.0251563397</v>
       </c>
     </row>
     <row r="736">
@@ -9928,7 +9928,7 @@
         <v>2028</v>
       </c>
       <c r="D736">
-        <v>285101.2019019449</v>
+        <v>317696.61473238</v>
       </c>
     </row>
     <row r="737">
@@ -9941,7 +9941,7 @@
         <v>2024</v>
       </c>
       <c r="D737">
-        <v>276213.5062154866</v>
+        <v>276213.506215485</v>
       </c>
     </row>
     <row r="738">
@@ -9967,7 +9967,7 @@
         <v>2026</v>
       </c>
       <c r="D739">
-        <v>304983.8915083713</v>
+        <v>336756.7761455744</v>
       </c>
     </row>
     <row r="740">
@@ -9980,7 +9980,7 @@
         <v>2027</v>
       </c>
       <c r="D740">
-        <v>336756.9074103047</v>
+        <v>371846.5390186359</v>
       </c>
     </row>
     <row r="741">
@@ -9993,7 +9993,7 @@
         <v>2028</v>
       </c>
       <c r="D741">
-        <v>371846.542311742</v>
+        <v>410592.6355404835</v>
       </c>
     </row>
     <row r="742">
@@ -10006,7 +10006,7 @@
         <v>2024</v>
       </c>
       <c r="D742">
-        <v>280264.847276273</v>
+        <v>280264.8472762739</v>
       </c>
     </row>
     <row r="743">
@@ -10032,7 +10032,7 @@
         <v>2026</v>
       </c>
       <c r="D744">
-        <v>309365.9628899692</v>
+        <v>341490.0619023379</v>
       </c>
     </row>
     <row r="745">
@@ -10045,7 +10045,7 @@
         <v>2027</v>
       </c>
       <c r="D745">
-        <v>341490.0754853163</v>
+        <v>376951.3463265015</v>
       </c>
     </row>
     <row r="746">
@@ -10058,7 +10058,7 @@
         <v>2028</v>
       </c>
       <c r="D746">
-        <v>376951.3464845894</v>
+        <v>416095.0303636446</v>
       </c>
     </row>
     <row r="747">
@@ -10071,7 +10071,7 @@
         <v>2024</v>
       </c>
       <c r="D747">
-        <v>121063.9680637751</v>
+        <v>121063.9680637748</v>
       </c>
     </row>
     <row r="748">
@@ -10097,7 +10097,7 @@
         <v>2026</v>
       </c>
       <c r="D749">
-        <v>142945.9426211637</v>
+        <v>168783.7910555859</v>
       </c>
     </row>
     <row r="750">
@@ -10110,7 +10110,7 @@
         <v>2027</v>
       </c>
       <c r="D750">
-        <v>168783.7986805491</v>
+        <v>199292.8311895965</v>
       </c>
     </row>
     <row r="751">
@@ -10123,7 +10123,7 @@
         <v>2028</v>
       </c>
       <c r="D751">
-        <v>199292.8312789829</v>
+        <v>235316.6282651322</v>
       </c>
     </row>
     <row r="752">
@@ -10136,7 +10136,7 @@
         <v>2024</v>
       </c>
       <c r="D752">
-        <v>121063.9680637751</v>
+        <v>121063.9680637748</v>
       </c>
     </row>
     <row r="753">
@@ -10162,7 +10162,7 @@
         <v>2026</v>
       </c>
       <c r="D754">
-        <v>142945.9426211637</v>
+        <v>168783.7910555859</v>
       </c>
     </row>
     <row r="755">
@@ -10175,7 +10175,7 @@
         <v>2027</v>
       </c>
       <c r="D755">
-        <v>168783.7986805491</v>
+        <v>199292.8311895965</v>
       </c>
     </row>
     <row r="756">
@@ -10188,7 +10188,7 @@
         <v>2028</v>
       </c>
       <c r="D756">
-        <v>199292.8312789829</v>
+        <v>235316.6282651322</v>
       </c>
     </row>
     <row r="757">
@@ -10201,7 +10201,7 @@
         <v>2024</v>
       </c>
       <c r="D757">
-        <v>121063.9680637751</v>
+        <v>121063.9680637748</v>
       </c>
     </row>
     <row r="758">
@@ -10227,7 +10227,7 @@
         <v>2026</v>
       </c>
       <c r="D759">
-        <v>142945.9426211637</v>
+        <v>168783.7910555859</v>
       </c>
     </row>
     <row r="760">
@@ -10240,7 +10240,7 @@
         <v>2027</v>
       </c>
       <c r="D760">
-        <v>168783.7986805491</v>
+        <v>199292.8311895965</v>
       </c>
     </row>
     <row r="761">
@@ -10253,7 +10253,7 @@
         <v>2028</v>
       </c>
       <c r="D761">
-        <v>199292.8312789829</v>
+        <v>235316.6282651322</v>
       </c>
     </row>
     <row r="762">
@@ -10292,7 +10292,7 @@
         <v>2026</v>
       </c>
       <c r="D764">
-        <v>144371.299445731</v>
+        <v>170307.5204993238</v>
       </c>
     </row>
     <row r="765">
@@ -10305,7 +10305,7 @@
         <v>2027</v>
       </c>
       <c r="D765">
-        <v>170307.655616793</v>
+        <v>200909.7795162045</v>
       </c>
     </row>
     <row r="766">
@@ -10318,7 +10318,7 @@
         <v>2028</v>
       </c>
       <c r="D766">
-        <v>200909.7836591398</v>
+        <v>237010.9193297708</v>
       </c>
     </row>
     <row r="767">
@@ -10331,7 +10331,7 @@
         <v>2024</v>
       </c>
       <c r="D767">
-        <v>163406.6255635169</v>
+        <v>163406.6255635157</v>
       </c>
     </row>
     <row r="768">
@@ -10357,7 +10357,7 @@
         <v>2026</v>
       </c>
       <c r="D769">
-        <v>182740.0365596495</v>
+        <v>205292.9183762159</v>
       </c>
     </row>
     <row r="770">
@@ -10370,7 +10370,7 @@
         <v>2027</v>
       </c>
       <c r="D770">
-        <v>205750.2328642244</v>
+        <v>233232.7567249403</v>
       </c>
     </row>
     <row r="771">
@@ -10383,7 +10383,7 @@
         <v>2028</v>
       </c>
       <c r="D771">
-        <v>233486.6734670292</v>
+        <v>265841.5002218285</v>
       </c>
     </row>
     <row r="772">
@@ -10396,7 +10396,7 @@
         <v>2024</v>
       </c>
       <c r="D772">
-        <v>148326.0302038058</v>
+        <v>148326.0302038053</v>
       </c>
     </row>
     <row r="773">
@@ -10422,7 +10422,7 @@
         <v>2026</v>
       </c>
       <c r="D774">
-        <v>168603.6401980227</v>
+        <v>192374.2044560037</v>
       </c>
     </row>
     <row r="775">
@@ -10435,7 +10435,7 @@
         <v>2027</v>
       </c>
       <c r="D775">
-        <v>192658.3357131263</v>
+        <v>221299.2517672461</v>
       </c>
     </row>
     <row r="776">
@@ -10448,7 +10448,7 @@
         <v>2028</v>
       </c>
       <c r="D776">
-        <v>221427.6980855008</v>
+        <v>255016.95354002</v>
       </c>
     </row>
     <row r="777">
@@ -10461,7 +10461,7 @@
         <v>2024</v>
       </c>
       <c r="D777">
-        <v>157427.2651306523</v>
+        <v>157427.265130652</v>
       </c>
     </row>
     <row r="778">
@@ -10487,7 +10487,7 @@
         <v>2026</v>
       </c>
       <c r="D779">
-        <v>178174.6275353663</v>
+        <v>202400.036695902</v>
       </c>
     </row>
     <row r="780">
@@ -10500,7 +10500,7 @@
         <v>2027</v>
       </c>
       <c r="D780">
-        <v>202692.6194268643</v>
+        <v>231769.4432677363</v>
       </c>
     </row>
     <row r="781">
@@ -10513,7 +10513,7 @@
         <v>2028</v>
       </c>
       <c r="D781">
-        <v>231900.8486579407</v>
+        <v>265852.1944232221</v>
       </c>
     </row>
     <row r="782">
@@ -10526,7 +10526,7 @@
         <v>2024</v>
       </c>
       <c r="D782">
-        <v>241929.8847651431</v>
+        <v>241929.8847651436</v>
       </c>
     </row>
     <row r="783">
@@ -10552,7 +10552,7 @@
         <v>2026</v>
       </c>
       <c r="D784">
-        <v>266917.5684611124</v>
+        <v>294490.3286115596</v>
       </c>
     </row>
     <row r="785">
@@ -10565,7 +10565,7 @@
         <v>2027</v>
       </c>
       <c r="D785">
-        <v>294490.4142516046</v>
+        <v>324916.3214326671</v>
       </c>
     </row>
     <row r="786">
@@ -10578,7 +10578,7 @@
         <v>2028</v>
       </c>
       <c r="D786">
-        <v>324916.3233464911</v>
+        <v>358485.8568923861</v>
       </c>
     </row>
     <row r="787">
@@ -10617,7 +10617,7 @@
         <v>2026</v>
       </c>
       <c r="D789">
-        <v>383219.5811209911</v>
+        <v>409734.3834982847</v>
       </c>
     </row>
     <row r="790">
@@ -10630,7 +10630,7 @@
         <v>2027</v>
       </c>
       <c r="D790">
-        <v>410317.475160171</v>
+        <v>441437.4407215411</v>
       </c>
     </row>
     <row r="791">
@@ -10643,7 +10643,7 @@
         <v>2028</v>
       </c>
       <c r="D791">
-        <v>441703.2148957663</v>
+        <v>476453.0434768921</v>
       </c>
     </row>
     <row r="792">
@@ -10682,7 +10682,7 @@
         <v>2026</v>
       </c>
       <c r="D794">
-        <v>383219.5811209911</v>
+        <v>409734.3834982847</v>
       </c>
     </row>
     <row r="795">
@@ -10695,7 +10695,7 @@
         <v>2027</v>
       </c>
       <c r="D795">
-        <v>410317.475160171</v>
+        <v>441437.4407215411</v>
       </c>
     </row>
     <row r="796">
@@ -10708,7 +10708,7 @@
         <v>2028</v>
       </c>
       <c r="D796">
-        <v>441703.2148957663</v>
+        <v>476453.0434768921</v>
       </c>
     </row>
     <row r="797">
@@ -10721,7 +10721,7 @@
         <v>2024</v>
       </c>
       <c r="D797">
-        <v>316301.4358226198</v>
+        <v>316301.4358226192</v>
       </c>
     </row>
     <row r="798">
@@ -10747,7 +10747,7 @@
         <v>2026</v>
       </c>
       <c r="D799">
-        <v>341354.7728353556</v>
+        <v>369208.9377357886</v>
       </c>
     </row>
     <row r="800">
@@ -10760,7 +10760,7 @@
         <v>2027</v>
       </c>
       <c r="D800">
-        <v>369464.8161158978</v>
+        <v>401053.6618924176</v>
       </c>
     </row>
     <row r="801">
@@ -10773,7 +10773,7 @@
         <v>2028</v>
       </c>
       <c r="D801">
-        <v>401140.6274120216</v>
+        <v>435928.4932680214</v>
       </c>
     </row>
     <row r="802">
@@ -10786,7 +10786,7 @@
         <v>2024</v>
       </c>
       <c r="D802">
-        <v>347884.0383829161</v>
+        <v>347884.0383829155</v>
       </c>
     </row>
     <row r="803">
@@ -10812,7 +10812,7 @@
         <v>2026</v>
       </c>
       <c r="D804">
-        <v>358949.7903808304</v>
+        <v>371284.1807334778</v>
       </c>
     </row>
     <row r="805">
@@ -10825,7 +10825,7 @@
         <v>2027</v>
       </c>
       <c r="D805">
-        <v>371640.1601711105</v>
+        <v>386101.3378687893</v>
       </c>
     </row>
     <row r="806">
@@ -10838,7 +10838,7 @@
         <v>2028</v>
       </c>
       <c r="D806">
-        <v>386244.8103394544</v>
+        <v>401957.5768311868</v>
       </c>
     </row>
     <row r="807">
@@ -10851,7 +10851,7 @@
         <v>2024</v>
       </c>
       <c r="D807">
-        <v>351823.9193020058</v>
+        <v>351823.9193020052</v>
       </c>
     </row>
     <row r="808">
@@ -10877,7 +10877,7 @@
         <v>2026</v>
       </c>
       <c r="D809">
-        <v>366953.5316390537</v>
+        <v>383847.9900097605</v>
       </c>
     </row>
     <row r="810">
@@ -10890,7 +10890,7 @@
         <v>2027</v>
       </c>
       <c r="D810">
-        <v>384314.3799111735</v>
+        <v>404158.8110603074</v>
       </c>
     </row>
     <row r="811">
@@ -10903,7 +10903,7 @@
         <v>2028</v>
       </c>
       <c r="D811">
-        <v>404363.8663832605</v>
+        <v>426192.3983618915</v>
       </c>
     </row>
     <row r="812">
@@ -10916,7 +10916,7 @@
         <v>2024</v>
       </c>
       <c r="D812">
-        <v>309318.5073985964</v>
+        <v>309318.5073985948</v>
       </c>
     </row>
     <row r="813">
@@ -10942,7 +10942,7 @@
         <v>2026</v>
       </c>
       <c r="D814">
-        <v>334622.4118230866</v>
+        <v>362853.4637536003</v>
       </c>
     </row>
     <row r="815">
@@ -10955,7 +10955,7 @@
         <v>2027</v>
       </c>
       <c r="D815">
-        <v>363129.976058715</v>
+        <v>395300.2905761518</v>
       </c>
     </row>
     <row r="816">
@@ -10968,7 +10968,7 @@
         <v>2028</v>
       </c>
       <c r="D816">
-        <v>395397.2913840449</v>
+        <v>430965.6567263715</v>
       </c>
     </row>
     <row r="817">
@@ -10981,7 +10981,7 @@
         <v>2024</v>
       </c>
       <c r="D817">
-        <v>162748.6581716617</v>
+        <v>162748.6581716614</v>
       </c>
     </row>
     <row r="818">
@@ -11007,7 +11007,7 @@
         <v>2026</v>
       </c>
       <c r="D819">
-        <v>182065.8224638034</v>
+        <v>204623.522708952</v>
       </c>
     </row>
     <row r="820">
@@ -11020,7 +11020,7 @@
         <v>2027</v>
       </c>
       <c r="D820">
-        <v>205091.67813807</v>
+        <v>232635.6403766697</v>
       </c>
     </row>
     <row r="821">
@@ -11033,7 +11033,7 @@
         <v>2028</v>
       </c>
       <c r="D821">
-        <v>232897.497910312</v>
+        <v>265376.6215386007</v>
       </c>
     </row>
     <row r="822">
@@ -11046,7 +11046,7 @@
         <v>2024</v>
       </c>
       <c r="D822">
-        <v>162748.6581716617</v>
+        <v>162748.6581716614</v>
       </c>
     </row>
     <row r="823">
@@ -11072,7 +11072,7 @@
         <v>2026</v>
       </c>
       <c r="D824">
-        <v>182065.8224638034</v>
+        <v>204623.522708952</v>
       </c>
     </row>
     <row r="825">
@@ -11085,7 +11085,7 @@
         <v>2027</v>
       </c>
       <c r="D825">
-        <v>205091.67813807</v>
+        <v>232635.6403766697</v>
       </c>
     </row>
     <row r="826">
@@ -11098,7 +11098,7 @@
         <v>2028</v>
       </c>
       <c r="D826">
-        <v>232897.497910312</v>
+        <v>265376.6215386007</v>
       </c>
     </row>
     <row r="827">
@@ -11111,7 +11111,7 @@
         <v>2024</v>
       </c>
       <c r="D827">
-        <v>162748.6581716617</v>
+        <v>162748.6581716614</v>
       </c>
     </row>
     <row r="828">
@@ -11137,7 +11137,7 @@
         <v>2026</v>
       </c>
       <c r="D829">
-        <v>182065.8224638034</v>
+        <v>204623.522708952</v>
       </c>
     </row>
     <row r="830">
@@ -11150,7 +11150,7 @@
         <v>2027</v>
       </c>
       <c r="D830">
-        <v>205091.67813807</v>
+        <v>232635.6403766697</v>
       </c>
     </row>
     <row r="831">
@@ -11163,7 +11163,7 @@
         <v>2028</v>
       </c>
       <c r="D831">
-        <v>232897.497910312</v>
+        <v>265376.6215386007</v>
       </c>
     </row>
     <row r="832">
@@ -11176,7 +11176,7 @@
         <v>2024</v>
       </c>
       <c r="D832">
-        <v>162748.6581716617</v>
+        <v>162748.6581716614</v>
       </c>
     </row>
     <row r="833">
@@ -11202,7 +11202,7 @@
         <v>2026</v>
       </c>
       <c r="D834">
-        <v>182065.8224638034</v>
+        <v>204623.522708952</v>
       </c>
     </row>
     <row r="835">
@@ -11215,7 +11215,7 @@
         <v>2027</v>
       </c>
       <c r="D835">
-        <v>205091.67813807</v>
+        <v>232635.6403766697</v>
       </c>
     </row>
     <row r="836">
@@ -11228,7 +11228,7 @@
         <v>2028</v>
       </c>
       <c r="D836">
-        <v>232897.497910312</v>
+        <v>265376.6215386007</v>
       </c>
     </row>
     <row r="837">
@@ -11241,7 +11241,7 @@
         <v>2024</v>
       </c>
       <c r="D837">
-        <v>162748.6581716617</v>
+        <v>162748.6581716614</v>
       </c>
     </row>
     <row r="838">
@@ -11267,7 +11267,7 @@
         <v>2026</v>
       </c>
       <c r="D839">
-        <v>182065.8224638034</v>
+        <v>204623.522708952</v>
       </c>
     </row>
     <row r="840">
@@ -11280,7 +11280,7 @@
         <v>2027</v>
       </c>
       <c r="D840">
-        <v>205091.67813807</v>
+        <v>232635.6403766697</v>
       </c>
     </row>
     <row r="841">
@@ -11293,7 +11293,7 @@
         <v>2028</v>
       </c>
       <c r="D841">
-        <v>232897.497910312</v>
+        <v>265376.6215386007</v>
       </c>
     </row>
     <row r="842">
@@ -11306,7 +11306,7 @@
         <v>2024</v>
       </c>
       <c r="D842">
-        <v>162748.6581716617</v>
+        <v>162748.6581716614</v>
       </c>
     </row>
     <row r="843">
@@ -11332,7 +11332,7 @@
         <v>2026</v>
       </c>
       <c r="D844">
-        <v>182065.8224638034</v>
+        <v>204623.522708952</v>
       </c>
     </row>
     <row r="845">
@@ -11345,7 +11345,7 @@
         <v>2027</v>
       </c>
       <c r="D845">
-        <v>205091.67813807</v>
+        <v>232635.6403766697</v>
       </c>
     </row>
     <row r="846">
@@ -11358,7 +11358,7 @@
         <v>2028</v>
       </c>
       <c r="D846">
-        <v>232897.497910312</v>
+        <v>265376.6215386007</v>
       </c>
     </row>
     <row r="847">
@@ -11371,7 +11371,7 @@
         <v>2024</v>
       </c>
       <c r="D847">
-        <v>163726.5742912607</v>
+        <v>163726.5742912601</v>
       </c>
     </row>
     <row r="848">
@@ -11397,7 +11397,7 @@
         <v>2026</v>
       </c>
       <c r="D849">
-        <v>183072.0221817615</v>
+        <v>205627.6691195907</v>
       </c>
     </row>
     <row r="850">
@@ -11410,7 +11410,7 @@
         <v>2027</v>
       </c>
       <c r="D850">
-        <v>206079.6216156358</v>
+        <v>233538.444757263</v>
       </c>
     </row>
     <row r="851">
@@ -11423,7 +11423,7 @@
         <v>2028</v>
       </c>
       <c r="D851">
-        <v>233788.4240270539</v>
+        <v>266090.3187755334</v>
       </c>
     </row>
     <row r="852">
@@ -11436,7 +11436,7 @@
         <v>2024</v>
       </c>
       <c r="D852">
-        <v>163216.6891379997</v>
+        <v>163216.6891379989</v>
       </c>
     </row>
     <row r="853">
@@ -11462,7 +11462,7 @@
         <v>2026</v>
       </c>
       <c r="D854">
-        <v>182544.1814366574</v>
+        <v>205096.9313906876</v>
       </c>
     </row>
     <row r="855">
@@ -11475,7 +11475,7 @@
         <v>2027</v>
       </c>
       <c r="D855">
-        <v>205557.3989360381</v>
+        <v>233055.8031278225</v>
       </c>
     </row>
     <row r="856">
@@ -11488,7 +11488,7 @@
         <v>2028</v>
       </c>
       <c r="D856">
-        <v>233312.0327851917</v>
+        <v>265700.4737267003</v>
       </c>
     </row>
     <row r="857">
@@ -11501,7 +11501,7 @@
         <v>2024</v>
       </c>
       <c r="D857">
-        <v>170157.5586642948</v>
+        <v>170157.5586642945</v>
       </c>
     </row>
     <row r="858">
@@ -11527,7 +11527,7 @@
         <v>2026</v>
       </c>
       <c r="D859">
-        <v>190952.102126012</v>
+        <v>215107.4911354785</v>
       </c>
     </row>
     <row r="860">
@@ -11540,7 +11540,7 @@
         <v>2027</v>
       </c>
       <c r="D860">
-        <v>215465.3203095079</v>
+        <v>244461.2638242252</v>
       </c>
     </row>
     <row r="861">
@@ -11553,7 +11553,7 @@
         <v>2028</v>
       </c>
       <c r="D861">
-        <v>244638.239421971</v>
+        <v>278424.4947166925</v>
       </c>
     </row>
     <row r="862">
@@ -11566,7 +11566,7 @@
         <v>2024</v>
       </c>
       <c r="D862">
-        <v>164687.7798220335</v>
+        <v>164687.7798220329</v>
       </c>
     </row>
     <row r="863">
@@ -11592,7 +11592,7 @@
         <v>2026</v>
       </c>
       <c r="D864">
-        <v>184372.4908882896</v>
+        <v>207333.152170966</v>
       </c>
     </row>
     <row r="865">
@@ -11605,7 +11605,7 @@
         <v>2027</v>
       </c>
       <c r="D865">
-        <v>207777.8921406976</v>
+        <v>235706.2041505044</v>
       </c>
     </row>
     <row r="866">
@@ -11618,7 +11618,7 @@
         <v>2028</v>
       </c>
       <c r="D866">
-        <v>235948.8630175234</v>
+        <v>268790.492033943</v>
       </c>
     </row>
     <row r="867">
@@ -11631,7 +11631,7 @@
         <v>2024</v>
       </c>
       <c r="D867">
-        <v>205558.2526604264</v>
+        <v>205558.252660426</v>
       </c>
     </row>
     <row r="868">
@@ -11657,7 +11657,7 @@
         <v>2026</v>
       </c>
       <c r="D869">
-        <v>230607.8776274819</v>
+        <v>259159.9977077669</v>
       </c>
     </row>
     <row r="870">
@@ -11670,7 +11670,7 @@
         <v>2027</v>
       </c>
       <c r="D870">
-        <v>259272.427309345</v>
+        <v>292133.5939051784</v>
       </c>
     </row>
     <row r="871">
@@ -11683,7 +11683,7 @@
         <v>2028</v>
       </c>
       <c r="D871">
-        <v>292165.224362526</v>
+        <v>329409.4821814728</v>
       </c>
     </row>
     <row r="872">
@@ -11722,7 +11722,7 @@
         <v>2026</v>
       </c>
       <c r="D874">
-        <v>203585.8725149863</v>
+        <v>229827.0746646975</v>
       </c>
     </row>
     <row r="875">
@@ -11735,7 +11735,7 @@
         <v>2027</v>
       </c>
       <c r="D875">
-        <v>230026.0635487457</v>
+        <v>260790.1753748745</v>
       </c>
     </row>
     <row r="876">
@@ -11748,7 +11748,7 @@
         <v>2028</v>
       </c>
       <c r="D876">
-        <v>260866.6860243719</v>
+        <v>296185.2641244572</v>
       </c>
     </row>
     <row r="877">
@@ -11761,7 +11761,7 @@
         <v>2024</v>
       </c>
       <c r="D877">
-        <v>299763.2129397466</v>
+        <v>299763.2129397471</v>
       </c>
     </row>
     <row r="878">
@@ -11787,7 +11787,7 @@
         <v>2026</v>
       </c>
       <c r="D879">
-        <v>314254.7719171714</v>
+        <v>330323.0022043082</v>
       </c>
     </row>
     <row r="880">
@@ -11800,7 +11800,7 @@
         <v>2027</v>
       </c>
       <c r="D880">
-        <v>330672.9303753027</v>
+        <v>349243.7347271001</v>
       </c>
     </row>
     <row r="881">
@@ -11813,7 +11813,7 @@
         <v>2028</v>
       </c>
       <c r="D881">
-        <v>349391.1860919286</v>
+        <v>369716.1265249149</v>
       </c>
     </row>
     <row r="882">
@@ -11852,7 +11852,7 @@
         <v>2026</v>
       </c>
       <c r="D884">
-        <v>185817.2945585882</v>
+        <v>210110.7071588186</v>
       </c>
     </row>
     <row r="885">
@@ -11865,7 +11865,7 @@
         <v>2027</v>
       </c>
       <c r="D885">
-        <v>210116.0581973307</v>
+        <v>237657.8927873163</v>
       </c>
     </row>
     <row r="886">
@@ -11878,7 +11878,7 @@
         <v>2028</v>
       </c>
       <c r="D886">
-        <v>237658.5079331556</v>
+        <v>268818.8210481885</v>
       </c>
     </row>
     <row r="887">
@@ -11891,7 +11891,7 @@
         <v>2024</v>
       </c>
       <c r="D887">
-        <v>177378.8155540972</v>
+        <v>177378.8155540969</v>
       </c>
     </row>
     <row r="888">
@@ -11917,7 +11917,7 @@
         <v>2026</v>
       </c>
       <c r="D889">
-        <v>194014.5753555011</v>
+        <v>213344.6726479939</v>
       </c>
     </row>
     <row r="890">
@@ -11930,7 +11930,7 @@
         <v>2027</v>
       </c>
       <c r="D890">
-        <v>214059.1230169427</v>
+        <v>238231.8939401805</v>
       </c>
     </row>
     <row r="891">
@@ -11943,7 +11943,7 @@
         <v>2028</v>
       </c>
       <c r="D891">
-        <v>238731.9828080261</v>
+        <v>267701.0713576115</v>
       </c>
     </row>
     <row r="892">
@@ -11956,7 +11956,7 @@
         <v>2024</v>
       </c>
       <c r="D892">
-        <v>177430.6855243867</v>
+        <v>177430.6855243864</v>
       </c>
     </row>
     <row r="893">
@@ -11982,7 +11982,7 @@
         <v>2026</v>
       </c>
       <c r="D894">
-        <v>196800.0454733213</v>
+        <v>219214.7701185542</v>
       </c>
     </row>
     <row r="895">
@@ -11995,7 +11995,7 @@
         <v>2027</v>
       </c>
       <c r="D895">
-        <v>219690.359770176</v>
+        <v>246823.295954972</v>
       </c>
     </row>
     <row r="896">
@@ -12008,7 +12008,7 @@
         <v>2028</v>
       </c>
       <c r="D896">
-        <v>247095.8519755877</v>
+        <v>278830.5818144728</v>
       </c>
     </row>
     <row r="897">
@@ -12021,7 +12021,7 @@
         <v>2024</v>
       </c>
       <c r="D897">
-        <v>179884.1329317374</v>
+        <v>179884.1329317368</v>
       </c>
     </row>
     <row r="898">
@@ -12047,7 +12047,7 @@
         <v>2026</v>
       </c>
       <c r="D899">
-        <v>202608.7664235221</v>
+        <v>228791.0728986891</v>
       </c>
     </row>
     <row r="900">
@@ -12060,7 +12060,7 @@
         <v>2027</v>
       </c>
       <c r="D900">
-        <v>228991.8043790683</v>
+        <v>259703.604680251</v>
       </c>
     </row>
     <row r="901">
@@ -12073,7 +12073,7 @@
         <v>2028</v>
       </c>
       <c r="D901">
-        <v>259781.3801060588</v>
+        <v>295057.7365314625</v>
       </c>
     </row>
     <row r="902">
@@ -12086,7 +12086,7 @@
         <v>2024</v>
       </c>
       <c r="D902">
-        <v>179884.1329317374</v>
+        <v>179884.1329317368</v>
       </c>
     </row>
     <row r="903">
@@ -12112,7 +12112,7 @@
         <v>2026</v>
       </c>
       <c r="D904">
-        <v>202608.7664235221</v>
+        <v>228791.0728986891</v>
       </c>
     </row>
     <row r="905">
@@ -12125,7 +12125,7 @@
         <v>2027</v>
       </c>
       <c r="D905">
-        <v>228991.8043790683</v>
+        <v>259703.604680251</v>
       </c>
     </row>
     <row r="906">
@@ -12138,7 +12138,7 @@
         <v>2028</v>
       </c>
       <c r="D906">
-        <v>259781.3801060588</v>
+        <v>295057.7365314625</v>
       </c>
     </row>
     <row r="907">
@@ -12151,7 +12151,7 @@
         <v>2024</v>
       </c>
       <c r="D907">
-        <v>179884.1329317374</v>
+        <v>179884.1329317368</v>
       </c>
     </row>
     <row r="908">
@@ -12177,7 +12177,7 @@
         <v>2026</v>
       </c>
       <c r="D909">
-        <v>202608.7664235221</v>
+        <v>228791.0728986891</v>
       </c>
     </row>
     <row r="910">
@@ -12190,7 +12190,7 @@
         <v>2027</v>
       </c>
       <c r="D910">
-        <v>228991.8043790683</v>
+        <v>259703.604680251</v>
       </c>
     </row>
     <row r="911">
@@ -12203,7 +12203,7 @@
         <v>2028</v>
       </c>
       <c r="D911">
-        <v>259781.3801060588</v>
+        <v>295057.7365314625</v>
       </c>
     </row>
     <row r="912">
@@ -12216,7 +12216,7 @@
         <v>2024</v>
       </c>
       <c r="D912">
-        <v>179884.1328847909</v>
+        <v>179884.1328847905</v>
       </c>
     </row>
     <row r="913">
@@ -12242,7 +12242,7 @@
         <v>2026</v>
       </c>
       <c r="D914">
-        <v>202608.7663330379</v>
+        <v>228791.0727591328</v>
       </c>
     </row>
     <row r="915">
@@ -12255,7 +12255,7 @@
         <v>2027</v>
       </c>
       <c r="D915">
-        <v>228991.804242394</v>
+        <v>259703.6044954053</v>
       </c>
     </row>
     <row r="916">
@@ -12268,7 +12268,7 @@
         <v>2028</v>
       </c>
       <c r="D916">
-        <v>259781.3799228121</v>
+        <v>295057.7362970573</v>
       </c>
     </row>
     <row r="917">
@@ -12281,7 +12281,7 @@
         <v>2024</v>
       </c>
       <c r="D917">
-        <v>179884.1329317374</v>
+        <v>179884.1329317368</v>
       </c>
     </row>
     <row r="918">
@@ -12307,7 +12307,7 @@
         <v>2026</v>
       </c>
       <c r="D919">
-        <v>202608.7664235221</v>
+        <v>228791.0728986891</v>
       </c>
     </row>
     <row r="920">
@@ -12320,7 +12320,7 @@
         <v>2027</v>
       </c>
       <c r="D920">
-        <v>228991.8043790683</v>
+        <v>259703.604680251</v>
       </c>
     </row>
     <row r="921">
@@ -12333,7 +12333,7 @@
         <v>2028</v>
       </c>
       <c r="D921">
-        <v>259781.3801060588</v>
+        <v>295057.7365314625</v>
       </c>
     </row>
     <row r="922">
@@ -12346,7 +12346,7 @@
         <v>2024</v>
       </c>
       <c r="D922">
-        <v>179884.1329317374</v>
+        <v>179884.1329317368</v>
       </c>
     </row>
     <row r="923">
@@ -12372,7 +12372,7 @@
         <v>2026</v>
       </c>
       <c r="D924">
-        <v>202608.7664235221</v>
+        <v>228791.0728986891</v>
       </c>
     </row>
     <row r="925">
@@ -12385,7 +12385,7 @@
         <v>2027</v>
       </c>
       <c r="D925">
-        <v>228991.8043790683</v>
+        <v>259703.604680251</v>
       </c>
     </row>
     <row r="926">
@@ -12398,7 +12398,7 @@
         <v>2028</v>
       </c>
       <c r="D926">
-        <v>259781.3801060588</v>
+        <v>295057.7365314625</v>
       </c>
     </row>
     <row r="927">
@@ -12411,7 +12411,7 @@
         <v>2024</v>
       </c>
       <c r="D927">
-        <v>179884.1329317374</v>
+        <v>179884.1329317368</v>
       </c>
     </row>
     <row r="928">
@@ -12437,7 +12437,7 @@
         <v>2026</v>
       </c>
       <c r="D929">
-        <v>202608.7664235221</v>
+        <v>228791.0728986891</v>
       </c>
     </row>
     <row r="930">
@@ -12450,7 +12450,7 @@
         <v>2027</v>
       </c>
       <c r="D930">
-        <v>228991.8043790683</v>
+        <v>259703.604680251</v>
       </c>
     </row>
     <row r="931">
@@ -12463,7 +12463,7 @@
         <v>2028</v>
       </c>
       <c r="D931">
-        <v>259781.3801060588</v>
+        <v>295057.7365314625</v>
       </c>
     </row>
     <row r="932">
@@ -12476,7 +12476,7 @@
         <v>2024</v>
       </c>
       <c r="D932">
-        <v>176646.3437382649</v>
+        <v>176646.3437382646</v>
       </c>
     </row>
     <row r="933">
@@ -12502,7 +12502,7 @@
         <v>2026</v>
       </c>
       <c r="D934">
-        <v>193511.521336636</v>
+        <v>213045.8053338358</v>
       </c>
     </row>
     <row r="935">
@@ -12515,7 +12515,7 @@
         <v>2027</v>
       </c>
       <c r="D935">
-        <v>213693.0531427103</v>
+        <v>237878.6051564449</v>
       </c>
     </row>
     <row r="936">
@@ -12528,7 +12528,7 @@
         <v>2028</v>
       </c>
       <c r="D936">
-        <v>238318.3125567015</v>
+        <v>267081.5416259571</v>
       </c>
     </row>
     <row r="937">
@@ -12541,7 +12541,7 @@
         <v>2024</v>
       </c>
       <c r="D937">
-        <v>176894.2340630331</v>
+        <v>176894.2340630322</v>
       </c>
     </row>
     <row r="938">
@@ -12567,7 +12567,7 @@
         <v>2026</v>
       </c>
       <c r="D939">
-        <v>193475.9549046597</v>
+        <v>212705.0179295561</v>
       </c>
     </row>
     <row r="940">
@@ -12580,7 +12580,7 @@
         <v>2027</v>
       </c>
       <c r="D940">
-        <v>213388.485097455</v>
+        <v>237326.165024745</v>
       </c>
     </row>
     <row r="941">
@@ -12593,7 +12593,7 @@
         <v>2028</v>
       </c>
       <c r="D941">
-        <v>237800.7385134164</v>
+        <v>266388.9709115268</v>
       </c>
     </row>
     <row r="942">
@@ -12606,7 +12606,7 @@
         <v>2024</v>
       </c>
       <c r="D942">
-        <v>177378.8155540972</v>
+        <v>177378.8155540969</v>
       </c>
     </row>
     <row r="943">
@@ -12632,7 +12632,7 @@
         <v>2026</v>
       </c>
       <c r="D944">
-        <v>194014.5753555011</v>
+        <v>213344.6726479939</v>
       </c>
     </row>
     <row r="945">
@@ -12645,7 +12645,7 @@
         <v>2027</v>
       </c>
       <c r="D945">
-        <v>214059.1230169427</v>
+        <v>238231.8939401805</v>
       </c>
     </row>
     <row r="946">
@@ -12658,7 +12658,7 @@
         <v>2028</v>
       </c>
       <c r="D946">
-        <v>238731.9828080261</v>
+        <v>267701.0713576115</v>
       </c>
     </row>
     <row r="947">
@@ -12671,7 +12671,7 @@
         <v>2024</v>
       </c>
       <c r="D947">
-        <v>214179.4741175236</v>
+        <v>214179.4741175228</v>
       </c>
     </row>
     <row r="948">
@@ -12697,7 +12697,7 @@
         <v>2026</v>
       </c>
       <c r="D949">
-        <v>237808.256898012</v>
+        <v>264050.8799413288</v>
       </c>
     </row>
     <row r="950">
@@ -12710,7 +12710,7 @@
         <v>2027</v>
       </c>
       <c r="D950">
-        <v>264051.1564745435</v>
+        <v>293198.1872329448</v>
       </c>
     </row>
     <row r="951">
@@ -12723,7 +12723,7 @@
         <v>2028</v>
       </c>
       <c r="D951">
-        <v>293198.19926432</v>
+        <v>325562.9657379621</v>
       </c>
     </row>
     <row r="952">
@@ -12736,7 +12736,7 @@
         <v>2024</v>
       </c>
       <c r="D952">
-        <v>121063.9680637751</v>
+        <v>121063.9680637748</v>
       </c>
     </row>
     <row r="953">
@@ -12762,7 +12762,7 @@
         <v>2026</v>
       </c>
       <c r="D954">
-        <v>142945.9426211637</v>
+        <v>168783.7910555859</v>
       </c>
     </row>
     <row r="955">
@@ -12775,7 +12775,7 @@
         <v>2027</v>
       </c>
       <c r="D955">
-        <v>168783.7986805491</v>
+        <v>199292.8311895965</v>
       </c>
     </row>
     <row r="956">
@@ -12788,7 +12788,7 @@
         <v>2028</v>
       </c>
       <c r="D956">
-        <v>199292.8312789829</v>
+        <v>235316.6282651322</v>
       </c>
     </row>
     <row r="957">
@@ -12801,7 +12801,7 @@
         <v>2024</v>
       </c>
       <c r="D957">
-        <v>121063.968063937</v>
+        <v>121063.9680639366</v>
       </c>
     </row>
     <row r="958">
@@ -12827,7 +12827,7 @@
         <v>2026</v>
       </c>
       <c r="D959">
-        <v>142945.9426214006</v>
+        <v>168783.791055919</v>
       </c>
     </row>
     <row r="960">
@@ -12840,7 +12840,7 @@
         <v>2027</v>
       </c>
       <c r="D960">
-        <v>168783.7986808819</v>
+        <v>199292.8311900514</v>
       </c>
     </row>
     <row r="961">
@@ -12853,7 +12853,7 @@
         <v>2028</v>
       </c>
       <c r="D961">
-        <v>199292.8312794374</v>
+        <v>235316.6282657408</v>
       </c>
     </row>
     <row r="962">
@@ -12866,7 +12866,7 @@
         <v>2024</v>
       </c>
       <c r="D962">
-        <v>166667.9608190212</v>
+        <v>166667.9608190215</v>
       </c>
     </row>
     <row r="963">
@@ -12892,7 +12892,7 @@
         <v>2026</v>
       </c>
       <c r="D964">
-        <v>185839.571885252</v>
+        <v>207314.0314540845</v>
       </c>
     </row>
     <row r="965">
@@ -12905,7 +12905,7 @@
         <v>2027</v>
       </c>
       <c r="D965">
-        <v>207327.9752692725</v>
+        <v>231425.5221604517</v>
       </c>
     </row>
     <row r="966">
@@ -12918,7 +12918,7 @@
         <v>2028</v>
       </c>
       <c r="D966">
-        <v>231427.7461745699</v>
+        <v>258348.7283870816</v>
       </c>
     </row>
     <row r="967">
@@ -12931,7 +12931,7 @@
         <v>2024</v>
       </c>
       <c r="D967">
-        <v>166771.7670543181</v>
+        <v>166771.7670543178</v>
       </c>
     </row>
     <row r="968">
@@ -12957,7 +12957,7 @@
         <v>2026</v>
       </c>
       <c r="D969">
-        <v>185867.4558853358</v>
+        <v>207251.949792317</v>
       </c>
     </row>
     <row r="970">
@@ -12970,7 +12970,7 @@
         <v>2027</v>
       </c>
       <c r="D970">
-        <v>207266.9811141192</v>
+        <v>231261.2307858785</v>
       </c>
     </row>
     <row r="971">
@@ -12983,7 +12983,7 @@
         <v>2028</v>
       </c>
       <c r="D971">
-        <v>231263.6941920996</v>
+        <v>258060.1340902383</v>
       </c>
     </row>
     <row r="972">
@@ -12996,7 +12996,7 @@
         <v>2024</v>
       </c>
       <c r="D972">
-        <v>195837.4233273928</v>
+        <v>195837.4233273921</v>
       </c>
     </row>
     <row r="973">
@@ -13022,7 +13022,7 @@
         <v>2026</v>
       </c>
       <c r="D974">
-        <v>218522.6479431362</v>
+        <v>243877.2064528882</v>
       </c>
     </row>
     <row r="975">
@@ -13035,7 +13035,7 @@
         <v>2027</v>
       </c>
       <c r="D975">
-        <v>243873.793326335</v>
+        <v>272208.525925965</v>
       </c>
     </row>
     <row r="976">
@@ -13048,7 +13048,7 @@
         <v>2028</v>
       </c>
       <c r="D976">
-        <v>272208.8388842047</v>
+        <v>303832.1548557584</v>
       </c>
     </row>
     <row r="977">
@@ -13061,7 +13061,7 @@
         <v>2024</v>
       </c>
       <c r="D977">
-        <v>191706.8836958984</v>
+        <v>191706.8836958977</v>
       </c>
     </row>
     <row r="978">
@@ -13087,7 +13087,7 @@
         <v>2026</v>
       </c>
       <c r="D979">
-        <v>214232.4366757724</v>
+        <v>239437.4365925901</v>
       </c>
     </row>
     <row r="980">
@@ -13100,7 +13100,7 @@
         <v>2027</v>
       </c>
       <c r="D980">
-        <v>239435.0531447549</v>
+        <v>267636.4240960814</v>
       </c>
     </row>
     <row r="981">
@@ -13113,7 +13113,7 @@
         <v>2028</v>
       </c>
       <c r="D981">
-        <v>267636.6182990943</v>
+        <v>299157.1094721108</v>
       </c>
     </row>
     <row r="982">
@@ -13126,7 +13126,7 @@
         <v>2024</v>
       </c>
       <c r="D982">
-        <v>224916.3270446953</v>
+        <v>224916.3270446949</v>
       </c>
     </row>
     <row r="983">
@@ -13152,7 +13152,7 @@
         <v>2026</v>
       </c>
       <c r="D984">
-        <v>247222.077796373</v>
+        <v>271739.9989438782</v>
       </c>
     </row>
     <row r="985">
@@ -13165,7 +13165,7 @@
         <v>2027</v>
       </c>
       <c r="D985">
-        <v>271739.9988754472</v>
+        <v>298689.484983733</v>
       </c>
     </row>
     <row r="986">
@@ -13178,7 +13178,7 @@
         <v>2028</v>
       </c>
       <c r="D986">
-        <v>298689.4849839049</v>
+        <v>328311.6537379081</v>
       </c>
     </row>
     <row r="987">
@@ -13191,7 +13191,7 @@
         <v>2024</v>
       </c>
       <c r="D987">
-        <v>223943.0476868082</v>
+        <v>223943.0476868078</v>
       </c>
     </row>
     <row r="988">
@@ -13217,7 +13217,7 @@
         <v>2026</v>
       </c>
       <c r="D989">
-        <v>247585.0779466876</v>
+        <v>273750.0517216091</v>
       </c>
     </row>
     <row r="990">
@@ -13230,7 +13230,7 @@
         <v>2027</v>
       </c>
       <c r="D990">
-        <v>273748.4038976505</v>
+        <v>302704.5669450988</v>
       </c>
     </row>
     <row r="991">
@@ -13243,7 +13243,7 @@
         <v>2028</v>
       </c>
       <c r="D991">
-        <v>302704.678078649</v>
+        <v>334721.9669735093</v>
       </c>
     </row>
     <row r="992">
@@ -13256,7 +13256,7 @@
         <v>2024</v>
       </c>
       <c r="D992">
-        <v>224995.9401072134</v>
+        <v>224995.9401072138</v>
       </c>
     </row>
     <row r="993">
@@ -13282,7 +13282,7 @@
         <v>2026</v>
       </c>
       <c r="D994">
-        <v>247301.3626374819</v>
+        <v>271818.1037353462</v>
       </c>
     </row>
     <row r="995">
@@ -13295,7 +13295,7 @@
         <v>2027</v>
       </c>
       <c r="D995">
-        <v>271818.1036801805</v>
+        <v>298765.3918417389</v>
       </c>
     </row>
     <row r="996">
@@ -13308,7 +13308,7 @@
         <v>2028</v>
       </c>
       <c r="D996">
-        <v>298765.3918418684</v>
+        <v>328384.1588762326</v>
       </c>
     </row>
     <row r="997">
@@ -13321,7 +13321,7 @@
         <v>2024</v>
       </c>
       <c r="D997">
-        <v>223943.0476868082</v>
+        <v>223943.0476868078</v>
       </c>
     </row>
     <row r="998">
@@ -13347,7 +13347,7 @@
         <v>2026</v>
       </c>
       <c r="D999">
-        <v>247585.0779466876</v>
+        <v>273750.0517216091</v>
       </c>
     </row>
     <row r="1000">
@@ -13360,7 +13360,7 @@
         <v>2027</v>
       </c>
       <c r="D1000">
-        <v>273748.4038976505</v>
+        <v>302704.5669450988</v>
       </c>
     </row>
     <row r="1001">
@@ -13373,7 +13373,7 @@
         <v>2028</v>
       </c>
       <c r="D1001">
-        <v>302704.678078649</v>
+        <v>334721.9669735093</v>
       </c>
     </row>
     <row r="1002">
@@ -13386,7 +13386,7 @@
         <v>2024</v>
       </c>
       <c r="D1002">
-        <v>223956.0774977064</v>
+        <v>223956.077497706</v>
       </c>
     </row>
     <row r="1003">
@@ -13412,7 +13412,7 @@
         <v>2026</v>
       </c>
       <c r="D1004">
-        <v>247573.8145315762</v>
+        <v>273708.1177815152</v>
       </c>
     </row>
     <row r="1005">
@@ -13425,7 +13425,7 @@
         <v>2027</v>
       </c>
       <c r="D1005">
-        <v>273706.5668519655</v>
+        <v>302624.7053851104</v>
       </c>
     </row>
     <row r="1006">
@@ -13438,7 +13438,7 @@
         <v>2028</v>
       </c>
       <c r="D1006">
-        <v>302624.8080231567</v>
+        <v>334596.5995973361</v>
       </c>
     </row>
     <row r="1007">
@@ -13451,7 +13451,7 @@
         <v>2024</v>
       </c>
       <c r="D1007">
-        <v>224995.9401072134</v>
+        <v>224995.9401072138</v>
       </c>
     </row>
     <row r="1008">
@@ -13477,7 +13477,7 @@
         <v>2026</v>
       </c>
       <c r="D1009">
-        <v>247301.3626374819</v>
+        <v>271818.1037353462</v>
       </c>
     </row>
     <row r="1010">
@@ -13490,7 +13490,7 @@
         <v>2027</v>
       </c>
       <c r="D1010">
-        <v>271818.1036801805</v>
+        <v>298765.3918417389</v>
       </c>
     </row>
     <row r="1011">
@@ -13503,7 +13503,7 @@
         <v>2028</v>
       </c>
       <c r="D1011">
-        <v>298765.3918418684</v>
+        <v>328384.1588762326</v>
       </c>
     </row>
     <row r="1012">
@@ -13516,7 +13516,7 @@
         <v>2024</v>
       </c>
       <c r="D1012">
-        <v>224650.6891281444</v>
+        <v>224650.6891281436</v>
       </c>
     </row>
     <row r="1013">
@@ -13542,7 +13542,7 @@
         <v>2026</v>
       </c>
       <c r="D1014">
-        <v>246957.5612536028</v>
+        <v>271479.4577239094</v>
       </c>
     </row>
     <row r="1015">
@@ -13555,7 +13555,7 @@
         <v>2027</v>
       </c>
       <c r="D1015">
-        <v>271479.4575958123</v>
+        <v>298436.3297710774</v>
       </c>
     </row>
     <row r="1016">
@@ -13568,7 +13568,7 @@
         <v>2028</v>
       </c>
       <c r="D1016">
-        <v>298436.3297714745</v>
+        <v>328069.9161340017</v>
       </c>
     </row>
     <row r="1017">
@@ -13581,7 +13581,7 @@
         <v>2024</v>
       </c>
       <c r="D1017">
-        <v>195837.4233273928</v>
+        <v>195837.4233273921</v>
       </c>
     </row>
     <row r="1018">
@@ -13607,7 +13607,7 @@
         <v>2026</v>
       </c>
       <c r="D1019">
-        <v>218522.6479431362</v>
+        <v>243877.2064528882</v>
       </c>
     </row>
     <row r="1020">
@@ -13620,7 +13620,7 @@
         <v>2027</v>
       </c>
       <c r="D1020">
-        <v>243873.793326335</v>
+        <v>272208.525925965</v>
       </c>
     </row>
     <row r="1021">
@@ -13633,7 +13633,7 @@
         <v>2028</v>
       </c>
       <c r="D1021">
-        <v>272208.8388842047</v>
+        <v>303832.1548557584</v>
       </c>
     </row>
     <row r="1022">
@@ -13646,7 +13646,7 @@
         <v>2024</v>
       </c>
       <c r="D1022">
-        <v>195837.4233273928</v>
+        <v>195837.4233273921</v>
       </c>
     </row>
     <row r="1023">
@@ -13672,7 +13672,7 @@
         <v>2026</v>
       </c>
       <c r="D1024">
-        <v>218522.6479431362</v>
+        <v>243877.2064528882</v>
       </c>
     </row>
     <row r="1025">
@@ -13685,7 +13685,7 @@
         <v>2027</v>
       </c>
       <c r="D1025">
-        <v>243873.793326335</v>
+        <v>272208.525925965</v>
       </c>
     </row>
     <row r="1026">
@@ -13698,7 +13698,7 @@
         <v>2028</v>
       </c>
       <c r="D1026">
-        <v>272208.8388842047</v>
+        <v>303832.1548557584</v>
       </c>
     </row>
     <row r="1027">
@@ -13711,7 +13711,7 @@
         <v>2024</v>
       </c>
       <c r="D1027">
-        <v>195837.4233273928</v>
+        <v>195837.4233273921</v>
       </c>
     </row>
     <row r="1028">
@@ -13737,7 +13737,7 @@
         <v>2026</v>
       </c>
       <c r="D1029">
-        <v>218522.6479431362</v>
+        <v>243877.2064528882</v>
       </c>
     </row>
     <row r="1030">
@@ -13750,7 +13750,7 @@
         <v>2027</v>
       </c>
       <c r="D1030">
-        <v>243873.793326335</v>
+        <v>272208.525925965</v>
       </c>
     </row>
     <row r="1031">
@@ -13763,7 +13763,7 @@
         <v>2028</v>
       </c>
       <c r="D1031">
-        <v>272208.8388842047</v>
+        <v>303832.1548557584</v>
       </c>
     </row>
     <row r="1032">
@@ -13776,7 +13776,7 @@
         <v>2024</v>
       </c>
       <c r="D1032">
-        <v>195837.4233273928</v>
+        <v>195837.4233273921</v>
       </c>
     </row>
     <row r="1033">
@@ -13802,7 +13802,7 @@
         <v>2026</v>
       </c>
       <c r="D1034">
-        <v>218522.6479431362</v>
+        <v>243877.2064528882</v>
       </c>
     </row>
     <row r="1035">
@@ -13815,7 +13815,7 @@
         <v>2027</v>
       </c>
       <c r="D1035">
-        <v>243873.793326335</v>
+        <v>272208.525925965</v>
       </c>
     </row>
     <row r="1036">
@@ -13828,7 +13828,7 @@
         <v>2028</v>
       </c>
       <c r="D1036">
-        <v>272208.8388842047</v>
+        <v>303832.1548557584</v>
       </c>
     </row>
     <row r="1037">
@@ -13841,7 +13841,7 @@
         <v>2024</v>
       </c>
       <c r="D1037">
-        <v>158867.0909644556</v>
+        <v>158867.0909644558</v>
       </c>
     </row>
     <row r="1038">
@@ -13867,7 +13867,7 @@
         <v>2026</v>
       </c>
       <c r="D1039">
-        <v>180311.2070181801</v>
+        <v>204650.426543716</v>
       </c>
     </row>
     <row r="1040">
@@ -13880,7 +13880,7 @@
         <v>2027</v>
       </c>
       <c r="D1040">
-        <v>204650.4214785869</v>
+        <v>232275.6647489435</v>
       </c>
     </row>
     <row r="1041">
@@ -13893,7 +13893,7 @@
         <v>2028</v>
       </c>
       <c r="D1041">
-        <v>232275.6648023902</v>
+        <v>263629.9634600662</v>
       </c>
     </row>
     <row r="1042">
@@ -13906,7 +13906,7 @@
         <v>2024</v>
       </c>
       <c r="D1042">
-        <v>195837.4233273928</v>
+        <v>195837.4233273921</v>
       </c>
     </row>
     <row r="1043">
@@ -13932,7 +13932,7 @@
         <v>2026</v>
       </c>
       <c r="D1044">
-        <v>218522.6479431362</v>
+        <v>243877.2064528882</v>
       </c>
     </row>
     <row r="1045">
@@ -13945,7 +13945,7 @@
         <v>2027</v>
       </c>
       <c r="D1045">
-        <v>243873.793326335</v>
+        <v>272208.525925965</v>
       </c>
     </row>
     <row r="1046">
@@ -13958,7 +13958,7 @@
         <v>2028</v>
       </c>
       <c r="D1046">
-        <v>272208.8388842047</v>
+        <v>303832.1548557584</v>
       </c>
     </row>
     <row r="1047">
@@ -13971,7 +13971,7 @@
         <v>2024</v>
       </c>
       <c r="D1047">
-        <v>195791.6197212693</v>
+        <v>195791.6197212689</v>
       </c>
     </row>
     <row r="1048">
@@ -13997,7 +13997,7 @@
         <v>2026</v>
       </c>
       <c r="D1049">
-        <v>218483.9432431642</v>
+        <v>243846.923962321</v>
       </c>
     </row>
     <row r="1050">
@@ -14010,7 +14010,7 @@
         <v>2027</v>
       </c>
       <c r="D1050">
-        <v>243843.6257876051</v>
+        <v>272188.4828991726</v>
       </c>
     </row>
     <row r="1051">
@@ -14023,7 +14023,7 @@
         <v>2028</v>
       </c>
       <c r="D1051">
-        <v>272188.7818884716</v>
+        <v>303825.0930694542</v>
       </c>
     </row>
     <row r="1052">
@@ -14036,7 +14036,7 @@
         <v>2024</v>
       </c>
       <c r="D1052">
-        <v>195805.1899346632</v>
+        <v>195805.1899346635</v>
       </c>
     </row>
     <row r="1053">
@@ -14062,7 +14062,7 @@
         <v>2026</v>
       </c>
       <c r="D1054">
-        <v>218559.2439257923</v>
+        <v>244003.4530868894</v>
       </c>
     </row>
     <row r="1055">
@@ -14075,7 +14075,7 @@
         <v>2027</v>
       </c>
       <c r="D1055">
-        <v>243999.5040568123</v>
+        <v>272447.9163472741</v>
       </c>
     </row>
     <row r="1056">
@@ -14088,7 +14088,7 @@
         <v>2028</v>
       </c>
       <c r="D1056">
-        <v>272448.2951794608</v>
+        <v>304209.5340023275</v>
       </c>
     </row>
     <row r="1057">
@@ -14101,7 +14101,7 @@
         <v>2024</v>
       </c>
       <c r="D1057">
-        <v>195837.4233273928</v>
+        <v>195837.4233273921</v>
       </c>
     </row>
     <row r="1058">
@@ -14127,7 +14127,7 @@
         <v>2026</v>
       </c>
       <c r="D1059">
-        <v>218522.6479431362</v>
+        <v>243877.2064528882</v>
       </c>
     </row>
     <row r="1060">
@@ -14140,7 +14140,7 @@
         <v>2027</v>
       </c>
       <c r="D1060">
-        <v>243873.793326335</v>
+        <v>272208.525925965</v>
       </c>
     </row>
     <row r="1061">
@@ -14153,7 +14153,7 @@
         <v>2028</v>
       </c>
       <c r="D1061">
-        <v>272208.8388842047</v>
+        <v>303832.1548557584</v>
       </c>
     </row>
     <row r="1062">
@@ -14192,7 +14192,7 @@
         <v>2026</v>
       </c>
       <c r="D1064">
-        <v>325552.4147549802</v>
+        <v>353224.3242060327</v>
       </c>
     </row>
     <row r="1065">
@@ -14205,7 +14205,7 @@
         <v>2027</v>
       </c>
       <c r="D1065">
-        <v>353225.2046238869</v>
+        <v>383272.1783052991</v>
       </c>
     </row>
     <row r="1066">
@@ -14218,7 +14218,7 @@
         <v>2028</v>
       </c>
       <c r="D1066">
-        <v>383272.2218233995</v>
+        <v>415876.2651210948</v>
       </c>
     </row>
     <row r="1067">
@@ -14257,7 +14257,7 @@
         <v>2026</v>
       </c>
       <c r="D1069">
-        <v>246639.2451944523</v>
+        <v>275750.5004290138</v>
       </c>
     </row>
     <row r="1070">
@@ -14270,7 +14270,7 @@
         <v>2027</v>
       </c>
       <c r="D1070">
-        <v>275741.0640917733</v>
+        <v>308371.9031743505</v>
       </c>
     </row>
     <row r="1071">
@@ -14283,7 +14283,7 @@
         <v>2028</v>
       </c>
       <c r="D1071">
-        <v>308372.9561164529</v>
+        <v>344855.9644172175</v>
       </c>
     </row>
     <row r="1072">
@@ -14296,7 +14296,7 @@
         <v>2024</v>
       </c>
       <c r="D1072">
-        <v>267640.7732851647</v>
+        <v>267640.7732851643</v>
       </c>
     </row>
     <row r="1073">
@@ -14322,7 +14322,7 @@
         <v>2026</v>
       </c>
       <c r="D1074">
-        <v>291683.2480251834</v>
+        <v>317893.8680764018</v>
       </c>
     </row>
     <row r="1075">
@@ -14335,7 +14335,7 @@
         <v>2027</v>
       </c>
       <c r="D1075">
-        <v>317894.1437442131</v>
+        <v>346469.8084777088</v>
       </c>
     </row>
     <row r="1076">
@@ -14348,7 +14348,7 @@
         <v>2028</v>
       </c>
       <c r="D1076">
-        <v>346469.818358148</v>
+        <v>377614.5138715022</v>
       </c>
     </row>
     <row r="1077">
@@ -14361,7 +14361,7 @@
         <v>2024</v>
       </c>
       <c r="D1077">
-        <v>300283.2652560791</v>
+        <v>300283.2652560786</v>
       </c>
     </row>
     <row r="1078">
@@ -14387,7 +14387,7 @@
         <v>2026</v>
       </c>
       <c r="D1079">
-        <v>325778.963420152</v>
+        <v>353458.7754253999</v>
       </c>
     </row>
     <row r="1080">
@@ -14400,7 +14400,7 @@
         <v>2027</v>
       </c>
       <c r="D1080">
-        <v>353459.6597509771</v>
+        <v>383514.3190203005</v>
       </c>
     </row>
     <row r="1081">
@@ -14413,7 +14413,7 @@
         <v>2028</v>
       </c>
       <c r="D1081">
-        <v>383514.3627823247</v>
+        <v>416125.7082008481</v>
       </c>
     </row>
     <row r="1082">
@@ -14452,7 +14452,7 @@
         <v>2026</v>
       </c>
       <c r="D1084">
-        <v>237628.3648309114</v>
+        <v>263858.8528950249</v>
       </c>
     </row>
     <row r="1085">
@@ -14465,7 +14465,7 @@
         <v>2027</v>
       </c>
       <c r="D1085">
-        <v>263859.1227134042</v>
+        <v>292993.3890568613</v>
       </c>
     </row>
     <row r="1086">
@@ -14478,7 +14478,7 @@
         <v>2028</v>
       </c>
       <c r="D1086">
-        <v>292993.4006995918</v>
+        <v>325344.9157489807</v>
       </c>
     </row>
     <row r="1087">
@@ -14491,7 +14491,7 @@
         <v>2024</v>
       </c>
       <c r="D1087">
-        <v>163073.9074019679</v>
+        <v>163073.9074019676</v>
       </c>
     </row>
     <row r="1088">
@@ -14517,7 +14517,7 @@
         <v>2026</v>
       </c>
       <c r="D1089">
-        <v>183268.0950057741</v>
+        <v>205997.702098545</v>
       </c>
     </row>
     <row r="1090">
@@ -14530,7 +14530,7 @@
         <v>2027</v>
       </c>
       <c r="D1090">
-        <v>205994.8605260157</v>
+        <v>231575.7268806805</v>
       </c>
     </row>
     <row r="1091">
@@ -14543,7 +14543,7 @@
         <v>2028</v>
       </c>
       <c r="D1091">
-        <v>231575.988594984</v>
+        <v>260330.5694881354</v>
       </c>
     </row>
     <row r="1092">
@@ -14556,7 +14556,7 @@
         <v>2024</v>
       </c>
       <c r="D1092">
-        <v>214179.4741175236</v>
+        <v>214179.4741175228</v>
       </c>
     </row>
     <row r="1093">
@@ -14582,7 +14582,7 @@
         <v>2026</v>
       </c>
       <c r="D1094">
-        <v>237808.256898012</v>
+        <v>264050.8799413288</v>
       </c>
     </row>
     <row r="1095">
@@ -14595,7 +14595,7 @@
         <v>2027</v>
       </c>
       <c r="D1095">
-        <v>264051.1564745435</v>
+        <v>293198.1872329448</v>
       </c>
     </row>
     <row r="1096">
@@ -14608,7 +14608,7 @@
         <v>2028</v>
       </c>
       <c r="D1096">
-        <v>293198.19926432</v>
+        <v>325562.9657379621</v>
       </c>
     </row>
     <row r="1097">
@@ -14621,7 +14621,7 @@
         <v>2024</v>
       </c>
       <c r="D1097">
-        <v>171444.6194987344</v>
+        <v>171444.6194987338</v>
       </c>
     </row>
     <row r="1098">
@@ -14647,7 +14647,7 @@
         <v>2026</v>
       </c>
       <c r="D1099">
-        <v>192091.5735409019</v>
+        <v>215240.9494353832</v>
       </c>
     </row>
     <row r="1100">
@@ -14660,7 +14660,7 @@
         <v>2027</v>
       </c>
       <c r="D1100">
-        <v>215240.0555165232</v>
+        <v>241194.9462677319</v>
       </c>
     </row>
     <row r="1101">
@@ -14673,7 +14673,7 @@
         <v>2028</v>
       </c>
       <c r="D1101">
-        <v>241195.0024990649</v>
+        <v>270278.694392716</v>
       </c>
     </row>
     <row r="1102">
@@ -14686,7 +14686,7 @@
         <v>2024</v>
       </c>
       <c r="D1102">
-        <v>214179.4741175236</v>
+        <v>214179.4741175228</v>
       </c>
     </row>
     <row r="1103">
@@ -14712,7 +14712,7 @@
         <v>2026</v>
       </c>
       <c r="D1104">
-        <v>237808.256898012</v>
+        <v>264050.8799413288</v>
       </c>
     </row>
     <row r="1105">
@@ -14725,7 +14725,7 @@
         <v>2027</v>
       </c>
       <c r="D1105">
-        <v>264051.1564745435</v>
+        <v>293198.1872329448</v>
       </c>
     </row>
     <row r="1106">
@@ -14738,7 +14738,7 @@
         <v>2028</v>
       </c>
       <c r="D1106">
-        <v>293198.19926432</v>
+        <v>325562.9657379621</v>
       </c>
     </row>
     <row r="1107">
@@ -14751,7 +14751,7 @@
         <v>2024</v>
       </c>
       <c r="D1107">
-        <v>214179.4741175236</v>
+        <v>214179.4741175228</v>
       </c>
     </row>
     <row r="1108">
@@ -14777,7 +14777,7 @@
         <v>2026</v>
       </c>
       <c r="D1109">
-        <v>237808.256898012</v>
+        <v>264050.8799413288</v>
       </c>
     </row>
     <row r="1110">
@@ -14790,7 +14790,7 @@
         <v>2027</v>
       </c>
       <c r="D1110">
-        <v>264051.1564745435</v>
+        <v>293198.1872329448</v>
       </c>
     </row>
     <row r="1111">
@@ -14803,7 +14803,7 @@
         <v>2028</v>
       </c>
       <c r="D1111">
-        <v>293198.19926432</v>
+        <v>325562.9657379621</v>
       </c>
     </row>
     <row r="1112">
@@ -14816,7 +14816,7 @@
         <v>2024</v>
       </c>
       <c r="D1112">
-        <v>214179.4741175236</v>
+        <v>214179.4741175228</v>
       </c>
     </row>
     <row r="1113">
@@ -14842,7 +14842,7 @@
         <v>2026</v>
       </c>
       <c r="D1114">
-        <v>237808.256898012</v>
+        <v>264050.8799413288</v>
       </c>
     </row>
     <row r="1115">
@@ -14855,7 +14855,7 @@
         <v>2027</v>
       </c>
       <c r="D1115">
-        <v>264051.1564745435</v>
+        <v>293198.1872329448</v>
       </c>
     </row>
     <row r="1116">
@@ -14868,7 +14868,7 @@
         <v>2028</v>
       </c>
       <c r="D1116">
-        <v>293198.19926432</v>
+        <v>325562.9657379621</v>
       </c>
     </row>
     <row r="1117">
@@ -14881,7 +14881,7 @@
         <v>2024</v>
       </c>
       <c r="D1117">
-        <v>265986.6141172732</v>
+        <v>265986.6141172727</v>
       </c>
     </row>
     <row r="1118">
@@ -14907,7 +14907,7 @@
         <v>2026</v>
       </c>
       <c r="D1119">
-        <v>288345.2500341216</v>
+        <v>312675.861046824</v>
       </c>
     </row>
     <row r="1120">
@@ -14920,7 +14920,7 @@
         <v>2027</v>
       </c>
       <c r="D1120">
-        <v>312687.2926588604</v>
+        <v>339197.0551360661</v>
       </c>
     </row>
     <row r="1121">
@@ -14933,7 +14933,7 @@
         <v>2028</v>
       </c>
       <c r="D1121">
-        <v>339198.5870522122</v>
+        <v>367972.7648279381</v>
       </c>
     </row>
     <row r="1122">
@@ -14946,7 +14946,7 @@
         <v>2024</v>
       </c>
       <c r="D1122">
-        <v>265986.6141172732</v>
+        <v>265986.6141172727</v>
       </c>
     </row>
     <row r="1123">
@@ -14972,7 +14972,7 @@
         <v>2026</v>
       </c>
       <c r="D1124">
-        <v>288345.2500341216</v>
+        <v>312675.861046824</v>
       </c>
     </row>
     <row r="1125">
@@ -14985,7 +14985,7 @@
         <v>2027</v>
       </c>
       <c r="D1125">
-        <v>312687.2926588604</v>
+        <v>339197.0551360661</v>
       </c>
     </row>
     <row r="1126">
@@ -14998,7 +14998,7 @@
         <v>2028</v>
       </c>
       <c r="D1126">
-        <v>339198.5870522122</v>
+        <v>367972.7648279381</v>
       </c>
     </row>
     <row r="1127">
@@ -15037,7 +15037,7 @@
         <v>2026</v>
       </c>
       <c r="D1129">
-        <v>288057.6954992844</v>
+        <v>312409.9391281122</v>
       </c>
     </row>
     <row r="1130">
@@ -15050,7 +15050,7 @@
         <v>2027</v>
       </c>
       <c r="D1130">
-        <v>312421.3493938503</v>
+        <v>338958.3432859245</v>
       </c>
     </row>
     <row r="1131">
@@ -15063,7 +15063,7 @@
         <v>2028</v>
       </c>
       <c r="D1131">
-        <v>338959.8709084004</v>
+        <v>367767.7868122346</v>
       </c>
     </row>
     <row r="1132">
@@ -15076,7 +15076,7 @@
         <v>2024</v>
       </c>
       <c r="D1132">
-        <v>225558.3066573949</v>
+        <v>225558.3066573945</v>
       </c>
     </row>
     <row r="1133">
@@ -15102,7 +15102,7 @@
         <v>2026</v>
       </c>
       <c r="D1134">
-        <v>248918.4225529008</v>
+        <v>274881.3315458015</v>
       </c>
     </row>
     <row r="1135">
@@ -15115,7 +15115,7 @@
         <v>2027</v>
       </c>
       <c r="D1135">
-        <v>274914.3611099199</v>
+        <v>303864.5154323435</v>
       </c>
     </row>
     <row r="1136">
@@ -15128,7 +15128,7 @@
         <v>2028</v>
       </c>
       <c r="D1136">
-        <v>303871.0851566192</v>
+        <v>335925.4419621549</v>
       </c>
     </row>
     <row r="1137">
@@ -15167,7 +15167,7 @@
         <v>2026</v>
       </c>
       <c r="D1139">
-        <v>287333.4012015837</v>
+        <v>313272.6326561285</v>
       </c>
     </row>
     <row r="1140">
@@ -15180,7 +15180,7 @@
         <v>2027</v>
       </c>
       <c r="D1140">
-        <v>313283.7852843853</v>
+        <v>341689.3422609052</v>
       </c>
     </row>
     <row r="1141">
@@ -15193,7 +15193,7 @@
         <v>2028</v>
       </c>
       <c r="D1141">
-        <v>341690.8318874545</v>
+        <v>372688.5831040693</v>
       </c>
     </row>
     <row r="1142">
@@ -15206,7 +15206,7 @@
         <v>2024</v>
       </c>
       <c r="D1142">
-        <v>234690.9153064542</v>
+        <v>234690.9153064546</v>
       </c>
     </row>
     <row r="1143">
@@ -15232,7 +15232,7 @@
         <v>2026</v>
       </c>
       <c r="D1144">
-        <v>256833.3489790663</v>
+        <v>281117.17082443</v>
       </c>
     </row>
     <row r="1145">
@@ -15245,7 +15245,7 @@
         <v>2027</v>
       </c>
       <c r="D1145">
-        <v>281122.7134152005</v>
+        <v>307772.5213490571</v>
       </c>
     </row>
     <row r="1146">
@@ -15258,7 +15258,7 @@
         <v>2028</v>
       </c>
       <c r="D1146">
-        <v>307773.1642206867</v>
+        <v>336957.4266689753</v>
       </c>
     </row>
     <row r="1147">
@@ -15271,7 +15271,7 @@
         <v>2024</v>
       </c>
       <c r="D1147">
-        <v>267934.6197080353</v>
+        <v>267934.6197080343</v>
       </c>
     </row>
     <row r="1148">
@@ -15297,7 +15297,7 @@
         <v>2026</v>
       </c>
       <c r="D1149">
-        <v>291515.3106277023</v>
+        <v>317279.7399204466</v>
       </c>
     </row>
     <row r="1150">
@@ -15310,7 +15310,7 @@
         <v>2027</v>
       </c>
       <c r="D1150">
-        <v>317294.3985747451</v>
+        <v>345487.1829816456</v>
       </c>
     </row>
     <row r="1151">
@@ -15323,7 +15323,7 @@
         <v>2028</v>
       </c>
       <c r="D1151">
-        <v>345489.340555591</v>
+        <v>376209.4292277247</v>
       </c>
     </row>
     <row r="1152">
@@ -15336,7 +15336,7 @@
         <v>2024</v>
       </c>
       <c r="D1152">
-        <v>179884.1329317374</v>
+        <v>179884.1329317368</v>
       </c>
     </row>
     <row r="1153">
@@ -15362,7 +15362,7 @@
         <v>2026</v>
       </c>
       <c r="D1154">
-        <v>202608.7664235221</v>
+        <v>228791.0728986891</v>
       </c>
     </row>
     <row r="1155">
@@ -15375,7 +15375,7 @@
         <v>2027</v>
       </c>
       <c r="D1155">
-        <v>228991.8043790683</v>
+        <v>259703.604680251</v>
       </c>
     </row>
     <row r="1156">
@@ -15388,7 +15388,7 @@
         <v>2028</v>
       </c>
       <c r="D1156">
-        <v>259781.3801060588</v>
+        <v>295057.7365314625</v>
       </c>
     </row>
     <row r="1157">
@@ -15401,7 +15401,7 @@
         <v>2024</v>
       </c>
       <c r="D1157">
-        <v>262395.4015059543</v>
+        <v>262395.4015059524</v>
       </c>
     </row>
     <row r="1158">
@@ -15427,7 +15427,7 @@
         <v>2026</v>
       </c>
       <c r="D1159">
-        <v>285715.8709318609</v>
+        <v>311209.8769980611</v>
       </c>
     </row>
     <row r="1160">
@@ -15440,7 +15440,7 @@
         <v>2027</v>
       </c>
       <c r="D1160">
-        <v>311223.2977595943</v>
+        <v>339132.5104451982</v>
       </c>
     </row>
     <row r="1161">
@@ -15453,7 +15453,7 @@
         <v>2028</v>
       </c>
       <c r="D1161">
-        <v>339134.4548756128</v>
+        <v>369566.7985229966</v>
       </c>
     </row>
     <row r="1162">
@@ -15466,7 +15466,7 @@
         <v>2024</v>
       </c>
       <c r="D1162">
-        <v>234775.5155518502</v>
+        <v>234775.5155518494</v>
       </c>
     </row>
     <row r="1163">
@@ -15492,7 +15492,7 @@
         <v>2026</v>
       </c>
       <c r="D1164">
-        <v>256904.902848399</v>
+        <v>281173.1405805672</v>
       </c>
     </row>
     <row r="1165">
@@ -15505,7 +15505,7 @@
         <v>2027</v>
       </c>
       <c r="D1165">
-        <v>281178.7981864843</v>
+        <v>307810.4333174827</v>
       </c>
     </row>
     <row r="1166">
@@ -15518,7 +15518,7 @@
         <v>2028</v>
       </c>
       <c r="D1166">
-        <v>307811.0945595961</v>
+        <v>336973.415300042</v>
       </c>
     </row>
     <row r="1167">
@@ -15531,7 +15531,7 @@
         <v>2024</v>
       </c>
       <c r="D1167">
-        <v>234775.5155518502</v>
+        <v>234775.5155518494</v>
       </c>
     </row>
     <row r="1168">
@@ -15557,7 +15557,7 @@
         <v>2026</v>
       </c>
       <c r="D1169">
-        <v>256904.902848399</v>
+        <v>281173.1405805672</v>
       </c>
     </row>
     <row r="1170">
@@ -15570,7 +15570,7 @@
         <v>2027</v>
       </c>
       <c r="D1170">
-        <v>281178.7981864843</v>
+        <v>307810.4333174827</v>
       </c>
     </row>
     <row r="1171">
@@ -15583,7 +15583,7 @@
         <v>2028</v>
       </c>
       <c r="D1171">
-        <v>307811.0945595961</v>
+        <v>336973.415300042</v>
       </c>
     </row>
     <row r="1172">
@@ -15622,7 +15622,7 @@
         <v>2026</v>
       </c>
       <c r="D1174">
-        <v>266525.2398855627</v>
+        <v>290743.3446444619</v>
       </c>
     </row>
     <row r="1175">
@@ -15635,7 +15635,7 @@
         <v>2027</v>
       </c>
       <c r="D1175">
-        <v>290751.4054633724</v>
+        <v>317263.7537160502</v>
       </c>
     </row>
     <row r="1176">
@@ -15648,7 +15648,7 @@
         <v>2028</v>
       </c>
       <c r="D1176">
-        <v>317264.7808091015</v>
+        <v>346206.6075027224</v>
       </c>
     </row>
     <row r="1177">
@@ -15661,7 +15661,7 @@
         <v>2024</v>
       </c>
       <c r="D1177">
-        <v>250841.5665996838</v>
+        <v>250841.5665996842</v>
       </c>
     </row>
     <row r="1178">
@@ -15687,7 +15687,7 @@
         <v>2026</v>
       </c>
       <c r="D1179">
-        <v>273027.1963060285</v>
+        <v>297252.4721850222</v>
       </c>
     </row>
     <row r="1180">
@@ -15700,7 +15700,7 @@
         <v>2027</v>
       </c>
       <c r="D1180">
-        <v>297261.7869996103</v>
+        <v>323741.9878375013</v>
       </c>
     </row>
     <row r="1181">
@@ -15713,7 +15713,7 @@
         <v>2028</v>
       </c>
       <c r="D1181">
-        <v>323743.2078703114</v>
+        <v>352596.0906247598</v>
       </c>
     </row>
     <row r="1182">
@@ -15726,7 +15726,7 @@
         <v>2024</v>
       </c>
       <c r="D1182">
-        <v>234775.5155518502</v>
+        <v>234775.5155518494</v>
       </c>
     </row>
     <row r="1183">
@@ -15752,7 +15752,7 @@
         <v>2026</v>
       </c>
       <c r="D1184">
-        <v>256904.902848399</v>
+        <v>281173.1405805672</v>
       </c>
     </row>
     <row r="1185">
@@ -15765,7 +15765,7 @@
         <v>2027</v>
       </c>
       <c r="D1185">
-        <v>281178.7981864843</v>
+        <v>307810.4333174827</v>
       </c>
     </row>
     <row r="1186">
@@ -15778,7 +15778,7 @@
         <v>2028</v>
       </c>
       <c r="D1186">
-        <v>307811.0945595961</v>
+        <v>336973.415300042</v>
       </c>
     </row>
     <row r="1187">
@@ -15791,7 +15791,7 @@
         <v>2024</v>
       </c>
       <c r="D1187">
-        <v>248338.9113524757</v>
+        <v>248338.911352477</v>
       </c>
     </row>
     <row r="1188">
@@ -15817,7 +15817,7 @@
         <v>2026</v>
       </c>
       <c r="D1189">
-        <v>271026.5065839178</v>
+        <v>295865.8931833606</v>
       </c>
     </row>
     <row r="1190">
@@ -15830,7 +15830,7 @@
         <v>2027</v>
       </c>
       <c r="D1190">
-        <v>295875.6968992485</v>
+        <v>323100.2936944597</v>
       </c>
     </row>
     <row r="1191">
@@ -15843,7 +15843,7 @@
         <v>2028</v>
       </c>
       <c r="D1191">
-        <v>323101.6202053665</v>
+        <v>352845.9615796866</v>
       </c>
     </row>
     <row r="1192">
@@ -15856,7 +15856,7 @@
         <v>2024</v>
       </c>
       <c r="D1192">
-        <v>267934.6277409901</v>
+        <v>267934.6277409887</v>
       </c>
     </row>
     <row r="1193">
@@ -15882,7 +15882,7 @@
         <v>2026</v>
       </c>
       <c r="D1194">
-        <v>291515.3292407325</v>
+        <v>317279.7709730204</v>
       </c>
     </row>
     <row r="1195">
@@ -15895,7 +15895,7 @@
         <v>2027</v>
       </c>
       <c r="D1195">
-        <v>317294.4296347342</v>
+        <v>345487.2286217796</v>
       </c>
     </row>
     <row r="1196">
@@ -15908,7 +15908,7 @@
         <v>2028</v>
       </c>
       <c r="D1196">
-        <v>345489.3861968</v>
+        <v>376209.4918075189</v>
       </c>
     </row>
     <row r="1197">
@@ -15921,7 +15921,7 @@
         <v>2024</v>
       </c>
       <c r="D1197">
-        <v>247105.7253602679</v>
+        <v>247105.7253602688</v>
       </c>
     </row>
     <row r="1198">
@@ -15947,7 +15947,7 @@
         <v>2026</v>
       </c>
       <c r="D1199">
-        <v>269263.791394387</v>
+        <v>293481.5421600609</v>
       </c>
     </row>
     <row r="1200">
@@ -15960,7 +15960,7 @@
         <v>2027</v>
       </c>
       <c r="D1200">
-        <v>293490.1633759764</v>
+        <v>319984.976296037</v>
       </c>
     </row>
     <row r="1201">
@@ -15973,7 +15973,7 @@
         <v>2028</v>
       </c>
       <c r="D1201">
-        <v>319986.0898547861</v>
+        <v>348885.4981185227</v>
       </c>
     </row>
     <row r="1202">
@@ -15986,7 +15986,7 @@
         <v>2024</v>
       </c>
       <c r="D1202">
-        <v>234775.5155517272</v>
+        <v>234775.5155517263</v>
       </c>
     </row>
     <row r="1203">
@@ -16012,7 +16012,7 @@
         <v>2026</v>
       </c>
       <c r="D1204">
-        <v>256904.9028481375</v>
+        <v>281173.1405801427</v>
       </c>
     </row>
     <row r="1205">
@@ -16025,7 +16025,7 @@
         <v>2027</v>
       </c>
       <c r="D1205">
-        <v>281178.7981860597</v>
+        <v>307810.4333168676</v>
       </c>
     </row>
     <row r="1206">
@@ -16038,7 +16038,7 @@
         <v>2028</v>
       </c>
       <c r="D1206">
-        <v>307811.0945589821</v>
+        <v>336973.4152992063</v>
       </c>
     </row>
     <row r="1207">
@@ -16051,7 +16051,7 @@
         <v>2024</v>
       </c>
       <c r="D1207">
-        <v>234775.5155518502</v>
+        <v>234775.5155518494</v>
       </c>
     </row>
     <row r="1208">
@@ -16077,7 +16077,7 @@
         <v>2026</v>
       </c>
       <c r="D1209">
-        <v>256904.902848399</v>
+        <v>281173.1405805672</v>
       </c>
     </row>
     <row r="1210">
@@ -16090,7 +16090,7 @@
         <v>2027</v>
       </c>
       <c r="D1210">
-        <v>281178.7981864843</v>
+        <v>307810.4333174827</v>
       </c>
     </row>
     <row r="1211">
@@ -16103,7 +16103,7 @@
         <v>2028</v>
       </c>
       <c r="D1211">
-        <v>307811.0945595961</v>
+        <v>336973.415300042</v>
       </c>
     </row>
     <row r="1212">
@@ -16142,7 +16142,7 @@
         <v>2026</v>
       </c>
       <c r="D1214">
-        <v>275674.5412180913</v>
+        <v>299910.051417019</v>
       </c>
     </row>
     <row r="1215">
@@ -16155,7 +16155,7 @@
         <v>2027</v>
       </c>
       <c r="D1215">
-        <v>299919.8065175906</v>
+        <v>326395.5949997471</v>
       </c>
     </row>
     <row r="1216">
@@ -16168,7 +16168,7 @@
         <v>2028</v>
       </c>
       <c r="D1216">
-        <v>326396.8819533513</v>
+        <v>355224.3217751789</v>
       </c>
     </row>
     <row r="1217">
@@ -16181,7 +16181,7 @@
         <v>2024</v>
       </c>
       <c r="D1217">
-        <v>260195.6786824349</v>
+        <v>260195.6786824344</v>
       </c>
     </row>
     <row r="1218">
@@ -16207,7 +16207,7 @@
         <v>2026</v>
       </c>
       <c r="D1219">
-        <v>282478.1266758847</v>
+        <v>306756.1457551786</v>
       </c>
     </row>
     <row r="1220">
@@ -16220,7 +16220,7 @@
         <v>2027</v>
       </c>
       <c r="D1220">
-        <v>306766.8792840306</v>
+        <v>333250.6546136077</v>
       </c>
     </row>
     <row r="1221">
@@ -16233,7 +16233,7 @@
         <v>2028</v>
       </c>
       <c r="D1221">
-        <v>333252.086995967</v>
+        <v>362038.1608336719</v>
       </c>
     </row>
     <row r="1222">
@@ -16246,7 +16246,7 @@
         <v>2024</v>
       </c>
       <c r="D1222">
-        <v>234775.5155518502</v>
+        <v>234775.5155518494</v>
       </c>
     </row>
     <row r="1223">
@@ -16272,7 +16272,7 @@
         <v>2026</v>
       </c>
       <c r="D1224">
-        <v>256904.902848399</v>
+        <v>281173.1405805672</v>
       </c>
     </row>
     <row r="1225">
@@ -16285,7 +16285,7 @@
         <v>2027</v>
       </c>
       <c r="D1225">
-        <v>281178.7981864843</v>
+        <v>307810.4333174827</v>
       </c>
     </row>
     <row r="1226">
@@ -16298,7 +16298,7 @@
         <v>2028</v>
       </c>
       <c r="D1226">
-        <v>307811.0945595961</v>
+        <v>336973.415300042</v>
       </c>
     </row>
     <row r="1227">
@@ -16311,7 +16311,7 @@
         <v>2024</v>
       </c>
       <c r="D1227">
-        <v>234775.5155518502</v>
+        <v>234775.5155518494</v>
       </c>
     </row>
     <row r="1228">
@@ -16337,7 +16337,7 @@
         <v>2026</v>
       </c>
       <c r="D1229">
-        <v>256904.902848399</v>
+        <v>281173.1405805672</v>
       </c>
     </row>
     <row r="1230">
@@ -16350,7 +16350,7 @@
         <v>2027</v>
       </c>
       <c r="D1230">
-        <v>281178.7981864843</v>
+        <v>307810.4333174827</v>
       </c>
     </row>
     <row r="1231">
@@ -16363,7 +16363,7 @@
         <v>2028</v>
       </c>
       <c r="D1231">
-        <v>307811.0945595961</v>
+        <v>336973.415300042</v>
       </c>
     </row>
     <row r="1232">
@@ -16402,7 +16402,7 @@
         <v>2026</v>
       </c>
       <c r="D1234">
-        <v>270482.2107431616</v>
+        <v>295298.3397951444</v>
       </c>
     </row>
     <row r="1235">
@@ -16415,7 +16415,7 @@
         <v>2027</v>
       </c>
       <c r="D1235">
-        <v>295307.9952215215</v>
+        <v>322508.3339201001</v>
       </c>
     </row>
     <row r="1236">
@@ -16428,7 +16428,7 @@
         <v>2028</v>
       </c>
       <c r="D1236">
-        <v>322509.6355557944</v>
+        <v>352229.8326845865</v>
       </c>
     </row>
     <row r="1237">
@@ -16441,7 +16441,7 @@
         <v>2024</v>
       </c>
       <c r="D1237">
-        <v>234997.1779229189</v>
+        <v>234997.1779229172</v>
       </c>
     </row>
     <row r="1238">
@@ -16467,7 +16467,7 @@
         <v>2026</v>
       </c>
       <c r="D1239">
-        <v>257126.0259768872</v>
+        <v>281392.0853990689</v>
       </c>
     </row>
     <row r="1240">
@@ -16480,7 +16480,7 @@
         <v>2027</v>
       </c>
       <c r="D1240">
-        <v>281397.8063949984</v>
+        <v>308025.489832354</v>
       </c>
     </row>
     <row r="1241">
@@ -16493,7 +16493,7 @@
         <v>2028</v>
       </c>
       <c r="D1241">
-        <v>308026.160478053</v>
+        <v>337181.9146269229</v>
       </c>
     </row>
     <row r="1242">
@@ -16506,7 +16506,7 @@
         <v>2024</v>
       </c>
       <c r="D1242">
-        <v>265986.6141172732</v>
+        <v>265986.6141172727</v>
       </c>
     </row>
     <row r="1243">
@@ -16532,7 +16532,7 @@
         <v>2026</v>
       </c>
       <c r="D1244">
-        <v>288345.2500341216</v>
+        <v>312675.861046824</v>
       </c>
     </row>
     <row r="1245">
@@ -16545,7 +16545,7 @@
         <v>2027</v>
       </c>
       <c r="D1245">
-        <v>312687.2926588604</v>
+        <v>339197.0551360661</v>
       </c>
     </row>
     <row r="1246">
@@ -16558,7 +16558,7 @@
         <v>2028</v>
       </c>
       <c r="D1246">
-        <v>339198.5870522122</v>
+        <v>367972.7648279381</v>
       </c>
     </row>
     <row r="1247">
@@ -16571,7 +16571,7 @@
         <v>2024</v>
       </c>
       <c r="D1247">
-        <v>216037.1899061168</v>
+        <v>216037.1899061164</v>
       </c>
     </row>
     <row r="1248">
@@ -16597,7 +16597,7 @@
         <v>2026</v>
       </c>
       <c r="D1249">
-        <v>241968.6813651387</v>
+        <v>271042.4842053469</v>
       </c>
     </row>
     <row r="1250">
@@ -16610,7 +16610,7 @@
         <v>2027</v>
       </c>
       <c r="D1250">
-        <v>271040.7313315425</v>
+        <v>303637.0251038811</v>
       </c>
     </row>
     <row r="1251">
@@ -16623,7 +16623,7 @@
         <v>2028</v>
       </c>
       <c r="D1251">
-        <v>303637.1410366051</v>
+        <v>340151.6514603993</v>
       </c>
     </row>
     <row r="1252">
@@ -16636,7 +16636,7 @@
         <v>2024</v>
       </c>
       <c r="D1252">
-        <v>255569.8396162472</v>
+        <v>255569.8396162463</v>
       </c>
     </row>
     <row r="1253">
@@ -16662,7 +16662,7 @@
         <v>2026</v>
       </c>
       <c r="D1254">
-        <v>280023.373655737</v>
+        <v>306844.0860692507</v>
       </c>
     </row>
     <row r="1255">
@@ -16675,7 +16675,7 @@
         <v>2027</v>
       </c>
       <c r="D1255">
-        <v>306845.7907383136</v>
+        <v>336269.3310427562</v>
       </c>
     </row>
     <row r="1256">
@@ -16688,7 +16688,7 @@
         <v>2028</v>
       </c>
       <c r="D1256">
-        <v>336269.4472376459</v>
+        <v>368516.7332597608</v>
       </c>
     </row>
     <row r="1257">
@@ -16701,7 +16701,7 @@
         <v>2024</v>
       </c>
       <c r="D1257">
-        <v>299422.8289229385</v>
+        <v>299422.828922938</v>
       </c>
     </row>
     <row r="1258">
@@ -16727,7 +16727,7 @@
         <v>2026</v>
       </c>
       <c r="D1259">
-        <v>324918.2137557142</v>
+        <v>352602.8891955841</v>
       </c>
     </row>
     <row r="1260">
@@ -16740,7 +16740,7 @@
         <v>2027</v>
       </c>
       <c r="D1260">
-        <v>352603.7066838162</v>
+        <v>382669.0678174248</v>
       </c>
     </row>
     <row r="1261">
@@ -16753,7 +16753,7 @@
         <v>2028</v>
       </c>
       <c r="D1261">
-        <v>382669.1072363832</v>
+        <v>415299.094830398</v>
       </c>
     </row>
     <row r="1262">
@@ -16766,7 +16766,7 @@
         <v>2024</v>
       </c>
       <c r="D1262">
-        <v>300283.2652560791</v>
+        <v>300283.2652560786</v>
       </c>
     </row>
     <row r="1263">
@@ -16792,7 +16792,7 @@
         <v>2026</v>
       </c>
       <c r="D1264">
-        <v>325778.963420152</v>
+        <v>353458.7754253999</v>
       </c>
     </row>
     <row r="1265">
@@ -16805,7 +16805,7 @@
         <v>2027</v>
       </c>
       <c r="D1265">
-        <v>353459.6597509771</v>
+        <v>383514.3190203005</v>
       </c>
     </row>
     <row r="1266">
@@ -16818,7 +16818,7 @@
         <v>2028</v>
       </c>
       <c r="D1266">
-        <v>383514.3627823247</v>
+        <v>416125.7082008481</v>
       </c>
     </row>
     <row r="1267">
@@ -16831,7 +16831,7 @@
         <v>2024</v>
       </c>
       <c r="D1267">
-        <v>300283.2652560791</v>
+        <v>300283.2652560786</v>
       </c>
     </row>
     <row r="1268">
@@ -16857,7 +16857,7 @@
         <v>2026</v>
       </c>
       <c r="D1269">
-        <v>325778.963420152</v>
+        <v>353458.7754253999</v>
       </c>
     </row>
     <row r="1270">
@@ -16870,7 +16870,7 @@
         <v>2027</v>
       </c>
       <c r="D1270">
-        <v>353459.6597509771</v>
+        <v>383514.3190203005</v>
       </c>
     </row>
     <row r="1271">
@@ -16883,7 +16883,7 @@
         <v>2028</v>
       </c>
       <c r="D1271">
-        <v>383514.3627823247</v>
+        <v>416125.7082008481</v>
       </c>
     </row>
     <row r="1272">
@@ -16896,7 +16896,7 @@
         <v>2024</v>
       </c>
       <c r="D1272">
-        <v>267934.6277409901</v>
+        <v>267934.6277409887</v>
       </c>
     </row>
     <row r="1273">
@@ -16922,7 +16922,7 @@
         <v>2026</v>
       </c>
       <c r="D1274">
-        <v>291515.3292407325</v>
+        <v>317279.7709730204</v>
       </c>
     </row>
     <row r="1275">
@@ -16935,7 +16935,7 @@
         <v>2027</v>
       </c>
       <c r="D1275">
-        <v>317294.4296347342</v>
+        <v>345487.2286217796</v>
       </c>
     </row>
     <row r="1276">
@@ -16948,7 +16948,7 @@
         <v>2028</v>
       </c>
       <c r="D1276">
-        <v>345489.3861968</v>
+        <v>376209.4918075189</v>
       </c>
     </row>
     <row r="1277">
@@ -16961,7 +16961,7 @@
         <v>2024</v>
       </c>
       <c r="D1277">
-        <v>300283.2652560791</v>
+        <v>300283.2652560786</v>
       </c>
     </row>
     <row r="1278">
@@ -16987,7 +16987,7 @@
         <v>2026</v>
       </c>
       <c r="D1279">
-        <v>325778.963420152</v>
+        <v>353458.7754253999</v>
       </c>
     </row>
     <row r="1280">
@@ -17000,7 +17000,7 @@
         <v>2027</v>
       </c>
       <c r="D1280">
-        <v>353459.6597509771</v>
+        <v>383514.3190203005</v>
       </c>
     </row>
     <row r="1281">
@@ -17013,7 +17013,7 @@
         <v>2028</v>
       </c>
       <c r="D1281">
-        <v>383514.3627823247</v>
+        <v>416125.7082008481</v>
       </c>
     </row>
     <row r="1282">
@@ -17026,7 +17026,7 @@
         <v>2024</v>
       </c>
       <c r="D1282">
-        <v>268171.609902569</v>
+        <v>268171.6099025681</v>
       </c>
     </row>
     <row r="1283">
@@ -17052,7 +17052,7 @@
         <v>2026</v>
       </c>
       <c r="D1284">
-        <v>291767.0019925156</v>
+        <v>317545.9926950312</v>
       </c>
     </row>
     <row r="1285">
@@ -17065,7 +17065,7 @@
         <v>2027</v>
       </c>
       <c r="D1285">
-        <v>317560.4410117819</v>
+        <v>345766.9425884486</v>
       </c>
     </row>
     <row r="1286">
@@ -17078,7 +17078,7 @@
         <v>2028</v>
       </c>
       <c r="D1286">
-        <v>345769.0560176249</v>
+        <v>376502.8487606173</v>
       </c>
     </row>
     <row r="1287">
@@ -17091,7 +17091,7 @@
         <v>2024</v>
       </c>
       <c r="D1287">
-        <v>267934.6277409901</v>
+        <v>267934.6277409887</v>
       </c>
     </row>
     <row r="1288">
@@ -17117,7 +17117,7 @@
         <v>2026</v>
       </c>
       <c r="D1289">
-        <v>291515.3292407325</v>
+        <v>317279.7709730204</v>
       </c>
     </row>
     <row r="1290">
@@ -17130,7 +17130,7 @@
         <v>2027</v>
       </c>
       <c r="D1290">
-        <v>317294.4296347342</v>
+        <v>345487.2286217796</v>
       </c>
     </row>
     <row r="1291">
@@ -17143,7 +17143,7 @@
         <v>2028</v>
       </c>
       <c r="D1291">
-        <v>345489.3861968</v>
+        <v>376209.4918075189</v>
       </c>
     </row>
     <row r="1292">
@@ -17156,7 +17156,7 @@
         <v>2024</v>
       </c>
       <c r="D1292">
-        <v>267934.6277409901</v>
+        <v>267934.6277409887</v>
       </c>
     </row>
     <row r="1293">
@@ -17182,7 +17182,7 @@
         <v>2026</v>
       </c>
       <c r="D1294">
-        <v>291515.3292407325</v>
+        <v>317279.7709730204</v>
       </c>
     </row>
     <row r="1295">
@@ -17195,7 +17195,7 @@
         <v>2027</v>
       </c>
       <c r="D1295">
-        <v>317294.4296347342</v>
+        <v>345487.2286217796</v>
       </c>
     </row>
     <row r="1296">
@@ -17208,7 +17208,7 @@
         <v>2028</v>
       </c>
       <c r="D1296">
-        <v>345489.3861968</v>
+        <v>376209.4918075189</v>
       </c>
     </row>
     <row r="1297">
@@ -17221,7 +17221,7 @@
         <v>2024</v>
       </c>
       <c r="D1297">
-        <v>267934.6197080353</v>
+        <v>267934.6197080343</v>
       </c>
     </row>
     <row r="1298">
@@ -17247,7 +17247,7 @@
         <v>2026</v>
       </c>
       <c r="D1299">
-        <v>291515.3106277023</v>
+        <v>317279.7399204466</v>
       </c>
     </row>
     <row r="1300">
@@ -17260,7 +17260,7 @@
         <v>2027</v>
       </c>
       <c r="D1300">
-        <v>317294.3985747451</v>
+        <v>345487.1829816456</v>
       </c>
     </row>
     <row r="1301">
@@ -17273,7 +17273,7 @@
         <v>2028</v>
       </c>
       <c r="D1301">
-        <v>345489.340555591</v>
+        <v>376209.4292277247</v>
       </c>
     </row>
     <row r="1302">
@@ -17286,7 +17286,7 @@
         <v>2024</v>
       </c>
       <c r="D1302">
-        <v>190229.1027386646</v>
+        <v>190229.102738665</v>
       </c>
     </row>
     <row r="1303">
@@ -17312,7 +17312,7 @@
         <v>2026</v>
       </c>
       <c r="D1304">
-        <v>209475.2644608464</v>
+        <v>231383.9294820002</v>
       </c>
     </row>
     <row r="1305">
@@ -17325,7 +17325,7 @@
         <v>2027</v>
       </c>
       <c r="D1305">
-        <v>231684.6372883838</v>
+        <v>257377.4116350598</v>
       </c>
     </row>
     <row r="1306">
@@ -17338,7 +17338,7 @@
         <v>2028</v>
       </c>
       <c r="D1306">
-        <v>257517.6673209237</v>
+        <v>286759.27118353</v>
       </c>
     </row>
     <row r="1307">
@@ -17351,7 +17351,7 @@
         <v>2024</v>
       </c>
       <c r="D1307">
-        <v>166771.7670543181</v>
+        <v>166771.7670543178</v>
       </c>
     </row>
     <row r="1308">
@@ -17377,7 +17377,7 @@
         <v>2026</v>
       </c>
       <c r="D1309">
-        <v>185867.4558853358</v>
+        <v>207251.949792317</v>
       </c>
     </row>
     <row r="1310">
@@ -17390,7 +17390,7 @@
         <v>2027</v>
       </c>
       <c r="D1310">
-        <v>207266.9811141192</v>
+        <v>231261.2307858785</v>
       </c>
     </row>
     <row r="1311">
@@ -17403,7 +17403,7 @@
         <v>2028</v>
       </c>
       <c r="D1311">
-        <v>231263.6941920996</v>
+        <v>258060.1340902383</v>
       </c>
     </row>
     <row r="1312">
@@ -17442,7 +17442,7 @@
         <v>2026</v>
       </c>
       <c r="D1314">
-        <v>186635.5796111301</v>
+        <v>208033.1755336304</v>
       </c>
     </row>
     <row r="1315">
@@ -17455,7 +17455,7 @@
         <v>2027</v>
       </c>
       <c r="D1315">
-        <v>208047.82165816</v>
+        <v>232045.220215083</v>
       </c>
     </row>
     <row r="1316">
@@ -17468,7 +17468,7 @@
         <v>2028</v>
       </c>
       <c r="D1316">
-        <v>232047.5969822018</v>
+        <v>258836.787237607</v>
       </c>
     </row>
     <row r="1317">
@@ -17481,7 +17481,7 @@
         <v>2024</v>
       </c>
       <c r="D1317">
-        <v>134233.6417578442</v>
+        <v>134233.6417578439</v>
       </c>
     </row>
     <row r="1318">
@@ -17507,7 +17507,7 @@
         <v>2026</v>
       </c>
       <c r="D1319">
-        <v>155239.5064070644</v>
+        <v>179609.2140971918</v>
       </c>
     </row>
     <row r="1320">
@@ -17520,7 +17520,7 @@
         <v>2027</v>
       </c>
       <c r="D1320">
-        <v>179617.9086694608</v>
+        <v>207923.4724925383</v>
       </c>
     </row>
     <row r="1321">
@@ -17533,7 +17533,7 @@
         <v>2028</v>
       </c>
       <c r="D1321">
-        <v>207924.6133009189</v>
+        <v>240705.2568939188</v>
       </c>
     </row>
     <row r="1322">
@@ -17546,7 +17546,7 @@
         <v>2024</v>
       </c>
       <c r="D1322">
-        <v>162993.9639321426</v>
+        <v>162993.9639321429</v>
       </c>
     </row>
     <row r="1323">
@@ -17572,7 +17572,7 @@
         <v>2026</v>
       </c>
       <c r="D1324">
-        <v>183182.8113035031</v>
+        <v>205907.1257719559</v>
       </c>
     </row>
     <row r="1325">
@@ -17585,7 +17585,7 @@
         <v>2027</v>
       </c>
       <c r="D1325">
-        <v>205904.2667096594</v>
+        <v>231479.9609448984</v>
       </c>
     </row>
     <row r="1326">
@@ -17598,7 +17598,7 @@
         <v>2028</v>
       </c>
       <c r="D1326">
-        <v>231480.2248008847</v>
+        <v>260229.729061073</v>
       </c>
     </row>
     <row r="1327">
@@ -17611,7 +17611,7 @@
         <v>2024</v>
       </c>
       <c r="D1327">
-        <v>181879.5660269322</v>
+        <v>181879.5660269316</v>
       </c>
     </row>
     <row r="1328">
@@ -17637,7 +17637,7 @@
         <v>2026</v>
       </c>
       <c r="D1329">
-        <v>203331.3474259457</v>
+        <v>227319.7810440725</v>
       </c>
     </row>
     <row r="1330">
@@ -17650,7 +17650,7 @@
         <v>2027</v>
       </c>
       <c r="D1330">
-        <v>227319.5438449454</v>
+        <v>254144.7958808823</v>
       </c>
     </row>
     <row r="1331">
@@ -17663,7 +17663,7 @@
         <v>2028</v>
       </c>
       <c r="D1331">
-        <v>254144.805524972</v>
+        <v>284135.3459415782</v>
       </c>
     </row>
     <row r="1332">
@@ -17702,7 +17702,7 @@
         <v>2026</v>
       </c>
       <c r="D1334">
-        <v>383219.5811209911</v>
+        <v>409734.3834982847</v>
       </c>
     </row>
     <row r="1335">
@@ -17715,7 +17715,7 @@
         <v>2027</v>
       </c>
       <c r="D1335">
-        <v>410317.475160171</v>
+        <v>441437.4407215411</v>
       </c>
     </row>
     <row r="1336">
@@ -17728,7 +17728,7 @@
         <v>2028</v>
       </c>
       <c r="D1336">
-        <v>441703.2148957663</v>
+        <v>476453.0434768921</v>
       </c>
     </row>
     <row r="1337">
@@ -17741,7 +17741,7 @@
         <v>2024</v>
       </c>
       <c r="D1337">
-        <v>294185.2080602758</v>
+        <v>294185.2080602753</v>
       </c>
     </row>
     <row r="1338">
@@ -17767,7 +17767,7 @@
         <v>2026</v>
       </c>
       <c r="D1339">
-        <v>314175.0652283816</v>
+        <v>336522.0510040715</v>
       </c>
     </row>
     <row r="1340">
@@ -17780,7 +17780,7 @@
         <v>2027</v>
       </c>
       <c r="D1340">
-        <v>336917.0965182788</v>
+        <v>362806.3156274122</v>
       </c>
     </row>
     <row r="1341">
@@ -17793,7 +17793,7 @@
         <v>2028</v>
       </c>
       <c r="D1341">
-        <v>362974.356203335</v>
+        <v>391687.2773671728</v>
       </c>
     </row>
     <row r="1342">
@@ -17806,7 +17806,7 @@
         <v>2024</v>
       </c>
       <c r="D1342">
-        <v>348828.3906319274</v>
+        <v>348828.3906319286</v>
       </c>
     </row>
     <row r="1343">
@@ -17832,7 +17832,7 @@
         <v>2026</v>
       </c>
       <c r="D1344">
-        <v>360858.4721327236</v>
+        <v>374272.6406680486</v>
       </c>
     </row>
     <row r="1345">
@@ -17845,7 +17845,7 @@
         <v>2027</v>
       </c>
       <c r="D1345">
-        <v>374658.3735145808</v>
+        <v>390397.8673260267</v>
       </c>
     </row>
     <row r="1346">
@@ -17858,7 +17858,7 @@
         <v>2028</v>
       </c>
       <c r="D1346">
-        <v>390557.659603275</v>
+        <v>407718.0710945341</v>
       </c>
     </row>
   </sheetData>
